--- a/report/项目执行计划.xlsx
+++ b/report/项目执行计划.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,7 +36,7 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="0064748B"/>
+      <color rgb="00B45309"/>
       <sz val="9"/>
     </font>
     <font>
@@ -69,8 +69,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="00475569"/>
+      <sz val="8.199999999999999"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <color rgb="00B45309"/>
-      <sz val="8.5"/>
+      <sz val="8.199999999999999"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -109,18 +114,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00475569"/>
-      <sz val="8.800000000000001"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
       <color rgb="00B45309"/>
-      <sz val="8.800000000000001"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="00DC2626"/>
-      <sz val="8.800000000000001"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -162,12 +162,12 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="002563eb"/>
-      <sz val="9"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="000F172A"/>
-      <sz val="8.800000000000001"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -177,29 +177,34 @@
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="00B45309"/>
-      <sz val="8.199999999999999"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="0064748B"/>
-      <sz val="8.199999999999999"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00047857"/>
-      <sz val="9"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="007c3aed"/>
-      <sz val="9"/>
+      <sz val="8.5"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00b45309"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="0064748B"/>
       <sz val="9"/>
     </font>
     <font>
@@ -302,7 +307,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -330,21 +335,21 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -367,7 +372,7 @@
     <xf numFmtId="0" fontId="22" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -395,16 +400,17 @@
     <xf numFmtId="0" fontId="31" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -777,32 +783,32 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>B2 湖仓归档平台 · 项目执行计划（4 人 × 12 周 Agile）</t>
+          <t>B2 湖仓归档平台 · 项目执行计划 V2（4 人 × 12 周 Agile）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>目标：3 个月完成平台开发 → 部署 Azure → 首个系统接入上线 → 文档/审批交付 · Agile 双周 Sprint · 每人职责如下</t>
+          <t>修订：① C 角色 = 前后端 + DevOps  ② D 角色 = QA + SLC 全生命周期文档  ③ A 角色 = 架构师 + 需求分析  ④ Sprint 0 前两周加需求确认，不是直接搭环境</t>
         </is>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>角色编号</t>
+          <t>角色</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -841,7 +847,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1">
+    <row r="5" ht="58" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>A</t>
@@ -849,17 +855,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>数据平台架构师 / 技术负责人</t>
+          <t>架构师 / 需求分析师 / 技术负责人</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Azure 基础设施搭建（IaC）、Databricks 湖仓设计、UC 权限体系、网络与安全架构、技术决策、代码评审</t>
+          <t>① 需求分析：BRD、用户故事、验收标准、业务流程图 ② 技术架构：Azure 组件设计、Databricks 湖仓、UC 权限体系 ③ 代码评审与技术决策 ④ IaC（Terraform）⑤ 与业务方/源方/网络团队的沟通协调</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Databricks / Iceberg / Terraform / Azure 网络 / Spark SQL</t>
+          <t>需求分析 / Databricks / Terraform / Azure 网络 / 架构设计</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -867,24 +873,24 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Terraform 模块、UC Catalog 结构、权限矩阵、架构决策记录(ADR)、部署手册</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>需要 Azure 订阅 Owner 权限；NCC/PE 需网络团队配合</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>兼任 Scrum Master（前两周），之后逐步移交</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>BRD（业务需求文档）、用户故事地图、验收标准、Terraform 模块、UC 权限矩阵、架构决策记录（ADR）、部署手册</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>需要 Azure 订阅 Owner；源库账号与网络路径需多团队协调</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>前 2 周偏需求，之后偏架构；全程做代码评审</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -896,7 +902,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>SeaTunnel 抽取链路、Iceberg 四层建模（RAW→CURATED→LAKE→SERVE）、Databricks Jobs 开发、销毁回路、Compaction 策略</t>
+          <t>① SeaTunnel 抽取链路与配置生成器 ② Iceberg 四层建模（RAW→CURATED→LAKE→SERVE）③ Databricks Jobs 开发（ETL/Compaction/VACUUM/销毁）④ 数据对账脚本 ⑤ 性能调优</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -909,41 +915,41 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>SeaTunnel 配置生成器、四层转换 SQL、销毁作业、Compaction 调度、数据对账脚本</t>
-        </is>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>源库连接与账号依赖源方配合；Databricks Premium 需提前开通</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>核心开发角色，承担最多的代码量</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>SeaTunnel 配置生成器、四层转换 SQL、销毁作业、Compaction 调度、对账脚本、性能基准报告</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>源库连接依赖源方配合；Databricks Premium 需提前开通</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>核心开发角色，代码量最大</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>.NET 后端 + 前端开发</t>
+          <t>全栈开发 + DevOps</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>.NET 10 后端服务（元数据/查询代理/附件/权限/审计/调度）、React 配置化查询前端、SeaTunnel 集成、SSO 对接</t>
+          <t>① .NET 10 后端（元数据/查询代理/附件/权限/审计/调度）② React 前端（配置化查询平台）③ CI/CD 流水线（GitHub Actions）④ Docker 镜像构建 + Helm Chart + AKS 部署 ⑤ SSO（Entra ID OIDC）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>.NET 10 / EF Core / React / TypeScript / AKS / OIDC</t>
+          <t>.NET 10 / React / TypeScript / Docker / Helm / GitHub Actions / AKS / OIDC</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -951,41 +957,41 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>后端 API（15+ 接口）、前端查询平台（元数据驱动渲染）、SSO 集成、部署 Helm Chart</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>元数据库 35 张表需先建好；SSO 需 Entra ID 配置</t>
-        </is>
-      </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>前后端一个人做，压力最大，可考虑后期请求支援</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>后端 API（15+ 接口）、React 前端、CI/CD 流水线、Helm Chart、Docker Compose（本地开发）、SSO 集成</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>前后端 + DevOps 一人扛，压力最大；元数据库 35 张表需 A 先建</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>前 4 周偏 DevOps（搭 CI/CD），之后偏开发；建议 W5 后请求支援或简化 DevOps 任务</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>DevOps / QA / 文档与合规</t>
+          <t>QA 测试 + SLC 全生命周期文档</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>CI/CD 流水线（GitHub Actions）、AKS 部署（Helm）、测试用例编写与执行、验收测试、技术文档、审批材料准备</t>
+          <t>① 测试策略与计划 ② 功能测试 / 集成测试 / 性能测试 / 安全测试 / UAT 协调 ③ 缺陷管理与跟踪 ④ SLC 文档：架构图（C4/时序/部署图）、详细设计文档、接口文档、数据字典、用户手册、运维手册、审批材料包 ⑤ 培训材料与培训交付</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>GitHub Actions / Helm / Azure CLI / 测试 / 技术写作</t>
+          <t>测试设计 / 自动化测试 / 技术写作 / Visio/Draw.io / 文档管理</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -993,19 +999,19 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>CI/CD 流水线、自动化测试套件、用户手册、运维手册、审批文档包、验收报告</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>测试数据依赖 B 的 SeaTunnel 链路就绪；审批流程依赖业务方</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>前 3 周偏 DevOps，后 6 周偏 QA + 文档</t>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>测试计划、测试用例（80+）、自动化测试套件、测试报告（Sprint 每轮）、架构图（4 张）、详细设计（3 模块）、接口文档、用户手册、运维手册、审批文档包、培训材料</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>文档量极大（≈40% 工作量）；测试数据依赖 B 的链路就绪；审批流程依赖业务方</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>前 3 周偏测试框架搭建，W4 起文档与测试并重，W9~10 文档冲刺</t>
         </is>
       </c>
     </row>
@@ -1024,22 +1030,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
     <col width="32" customWidth="1" min="6" max="6"/>
     <col width="42" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>12 周 Sprint 计划（双周 Sprint × 6）</t>
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>12 周 Sprint 计划（双周 × 6）· V2 修订版</t>
         </is>
       </c>
     </row>
@@ -1080,11 +1086,11 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="72" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
+    <row r="4" ht="76" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Sprint 0
-筹备</t>
+需求+筹备</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
@@ -1094,31 +1100,31 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>环境搭建 + 需求确认 + 技术选型落地</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>① Azure 订阅开通 ② Terraform 基线（VNet/AKS/ADLS/SQL DB/Key Vault）③ Databricks Premium 工作区 + UC 初始化 ④ 源库 PoC 连通（1 套 SQL Server + 1 套 MySQL）⑤ 元数据库 35 张表建表 ⑥ CI/CD 流水线骨架</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>PoC：SeaTunnel 从源库抽数 → 写入 Iceberg RAW → SQL Warehouse 可查</t>
+          <t>需求确认 + 技术选型落地 + 环境搭建（并行推进）</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>① A：BRD 初稿 + 用户故事地图 + 验收标准 + 首系统确认 ② A：Terraform 基线（VNet/AKS/ADLS/SQL DB/Key Vault/Databricks）③ B：Databricks 工作区 + UC 初始化 + 源库 PoC ④ C：项目骨架 + CI/CD 流水线 + Docker 本地开发环境 ⑤ D：测试计划 + 架构图初稿（系统上下文图 + 容器图）</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>PoC：SeaTunnel 从源库抽数 → Iceberg RAW → SQL Warehouse 可查 + BRD 评审通过</t>
         </is>
       </c>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t>Azure 订阅权限；源库账号开通延迟；Databricks Premium 开通周期</t>
+          <t>需求不明确导致后续返工；源库账号/网络延迟</t>
         </is>
       </c>
       <c r="G4" s="18" t="inlineStr">
         <is>
-          <t>① 确认首个接入系统（建议 Dspot，最小）② 确认源库网络路径（ExpressRoute/VPN）③ 团队对技术栈是否有明显短板</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="72" customHeight="1">
+          <t>① 首个接入系统选谁 ② 源库网络路径 ③ PII 字段标记规则 ④ 性能验收标准 ⑤ UAT 签字人</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="76" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Sprint 1
@@ -1135,28 +1141,28 @@
           <t>端到端最小闭环：1 张表从源库到查询页可查</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>① SeaTunnel 配置生成器（读元数据→生成任务）② RAW→LAKE 两层转换（跳过 CURATED/SERVE）③ 查询代理 API + React 基础查询页 ④ SSO（Entra ID OIDC）⑤ 核心表 CRD API（系统建档/表清单/查询配置）</t>
-        </is>
-      </c>
-      <c r="E5" s="16" t="inlineStr">
-        <is>
-          <t>演示：用户登录 → 看到系统列表 → 点进查询页 → 输入条件 → 看到 1 张表数据</t>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>① B：SeaTunnel 配置生成器 + RAW→LAKE 直达 ② C：查询代理 API + React 基础查询页 + SSO + Helm 部署到 AKS Dev ③ A：代码评审 + UC 权限落地 ④ D：集成测试 + 架构图完善（组件图 + 部署图）+ 接口文档初稿</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>演示：登录 → 系统列表 → 查询页 → 输入条件 → 看到 1 张表数据</t>
         </is>
       </c>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>前后端联调时间可能超预期；UC 权限模型首次落地</t>
+          <t>前后端联调超预期；UC 权限首次落地</t>
         </is>
       </c>
       <c r="G5" s="18" t="inlineStr">
         <is>
-          <t>① UC 用 catalog-per-system 还是 schema-per-system ② 查询页 UI 框架组件库确认 ③ 是否需要附件预览功能（影响 Sprint 2 排期）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="72" customHeight="1">
+          <t>① UC catalog vs schema 命名 ② 查询页 UI 组件库 ③ 附件预览范围</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="76" customHeight="1">
       <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Sprint 2
@@ -1173,32 +1179,32 @@
           <t>完整四层转换 + 附件链路 + 权限体系</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>① CURATED/SERVE 两层转换 + Z-Order + Compaction ② UC 行/列级权限 + 掩码函数 ③ 附件代理 + SAS 签发 + SHA-256 台账 ④ Storage Mover 接入 ⑤ 前端：配置化查询表单（元数据驱动渲染）+ 附件预览</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>演示：① 带掩码的查询（有权限见明文/无权限见掩码）② 附件在线预览 ③ 多表 JOIN 查询</t>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>① B：四层转换 + Z-Order + Compaction + 附件链路 ② C：配置化查询表单（元数据驱动）+ 附件预览 + 多表 JOIN + 下钻 ③ A：掩码函数 + 密钥体系 ④ D：功能测试全量 + 性能测试 + 详细设计文档（数据层+应用层+安全层 3 模块）</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>演示：① 掩码查询（有权限明文/无权限掩码）② 附件在线预览 ③ 多表 JOIN</t>
         </is>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>掩码函数与前端联动复杂度；Storage Mover 网络打通</t>
+          <t>掩码函数复杂度；Storage Mover 网络打通；D 的文档量大</t>
         </is>
       </c>
       <c r="G6" s="18" t="inlineStr">
         <is>
-          <t>① 附件是否需要在线预览（图片/音频/视频各确认）② PII 字段标记规则（哪些列要掩码）③ 首个系统之外第二个接入系统确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="72" customHeight="1">
+          <t>① 附件预览格式范围 ② 第二系统选谁</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="76" customHeight="1">
       <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Sprint 3
-销毁与运维</t>
+销毁+第二系统</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -1208,31 +1214,31 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>保留策略 + 销毁回路 + 监控告警 + 第二个系统接入</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>① Retention 策略配置界面 + 到期扫描 Job + DROP PARTITION + VACUUM ② 销毁审批流程 ③ Azure Monitor 告警规则 + Dashboard ④ 第二系统接入（走零代码配置流程）⑤ 集成测试 + 性能测试（20GB 压力）</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>演示：① 设定保留期→到期自动销毁→审计留痕 ② 第二系统纯配置接入（不写代码）③ 监控大盘</t>
+          <t>保留策略 + 销毁回路 + 第二系统接入 + 全量测试</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>① B：到期扫描 + DROP PARTITION + VACUUM + 销毁作业 ② C：Retention 策略界面 + 审批界面 + 通知 + Dashboard ③ A：第二系统零代码接入验证 ④ D：全量回归测试 + 用户手册初稿 + 数据字典 + 运维手册初稿</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>演示：① 保留期→到期自动销毁→审计留痕 ② 第二系统纯配置接入 ③ 监控大盘</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
         <is>
-          <t>销毁是不可逆操作，需严格测试；性能瓶颈可能在 Iceberg 小文件</t>
+          <t>销毁不可逆需严格测试；UAT 场景可能不完整</t>
         </is>
       </c>
       <c r="G7" s="18" t="inlineStr">
         <is>
-          <t>① 销毁审批是否需要二级审批人 ② 保留期的合规底线（法务确认）③ 性能指标验收标准（首屏几秒？）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="72" customHeight="1">
+          <t>① 销毁是否需二级审批 ② 保留期合规底线 ③ 全量迁移窗口</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="76" customHeight="1">
       <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Sprint 4
@@ -1249,28 +1255,28 @@
           <t>生产部署 + 全量文档 + UAT + 审批材料</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>① 生产环境 Terraform apply（全组件）② Helm 部署到 AKS 生产 ③ 用户手册 + 运维手册 + 架构文档 ④ 安全评审材料（等保/个保法对照）⑤ UAT（业务方验证 5 个核心场景）⑥ 首系统正式全量数据迁移</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>演示：① 生产环境端到端演示 ② UAT 报告 ③ 文档包预览 ④ 审批材料提交状态</t>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>① A：生产 Terraform apply + 安全评审材料 ② B：首系统全量迁移 + 生产 Jobs 部署 ③ C：生产 AKS 部署 + SSO + 监控接入 ④ D：文档冲刺（用户手册终版 + 运维手册终版 + 架构图终版 + 详细设计终版 + 接口文档终版 + 审批材料包）+ UAT 执行</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>演示：① 生产环境端到端 ② UAT 报告 ③ 文档包 ④ 审批材料提交状态</t>
         </is>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>UAT 业务方配合度；安全评审可能提出整改项；全量迁移时长不可控</t>
+          <t>UAT 业务方配合度；安全评审整改；D 的文档冲刺压力最大</t>
         </is>
       </c>
       <c r="G8" s="18" t="inlineStr">
         <is>
-          <t>① UAT 验收标准（谁签字？几个场景？）② 安全评审流程和材料清单 ③ 全量迁移是否需要在周末执行 ④ 生产环境域名/证书</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="72" customHeight="1">
+          <t>① UAT 验收标准 ② 生产域名/证书 ③ 审批流程和材料清单</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="76" customHeight="1">
       <c r="A9" s="23" t="inlineStr">
         <is>
           <t>Sprint 5
@@ -1284,33 +1290,33 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>正式上线 + 首月运维 + 知识转移 + 项目关闭</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>① 生产上线（Go-Live）② 首月运维值守（含监控/告警/故障处理）③ 知识转移培训（运维团队 + 业务方）④ 项目关闭报告 ⑤ 后续接入手册（第 3~N 个系统的标准流程）⑥ Retro 总结</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>演示：① 生产环境运行报告 ② 运维团队独立操作演示 ③ 后续系统接入 SOP 演示</t>
+          <t>正式上线 + 培训 + 知识转移 + 项目关闭</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>① 全员：上线值守 ② A：运维培训 + 项目关闭报告 ③ B：运维知识转移（ETL/销毁）④ C：运维知识转移（部署/前端配置）⑤ D：培训交付（业务用户+运维）+ 培训视频 + 接入手册 + 文档归档 + Retro</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>演示：① 生产运行报告 ② 运维团队独立操作 ③ 后续接入 SOP</t>
         </is>
       </c>
       <c r="F9" s="17" t="inlineStr">
         <is>
-          <t>上线后首次真实数据可能出现意外；运维团队接手意愿/能力</t>
+          <t>上线后首周异常；运维团队接手意愿</t>
         </is>
       </c>
       <c r="G9" s="18" t="inlineStr">
         <is>
-          <t>① 上线窗口（哪天？是否需要停机？）② 运维移交范围（哪些留开发管/哪些移交？）③ 后续接入排期（第 3~N 系统节奏）</t>
+          <t>① 上线窗口 ② 运维移交范围 ③ 后续接入排期</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1326,25 +1332,25 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>周计划明细 · 4 人 × 12 周（每周每人具体任务）</t>
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>周计划明细 · 4 人 × 12 周（V2 修订版）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="24" t="inlineStr">
         <is>
-          <t>颜色：A=蓝(架构) B=绿(数据工程) C=紫(前后端) D=橙(DevOps/QA/文档) · 优先级：🔴 must 🟡 should ⚪ nice-to-have · 里程碑用 ★ 标记</t>
+          <t>A=蓝(架构+需求) B=绿(数据工程) C=紫(前后端+DevOps) D=橙(QA+SLC文档) · 🔴 must 🟡 should ⚪ nice</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1391,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1">
+    <row r="5" ht="44" customHeight="1">
       <c r="A5" s="25" t="inlineStr">
         <is>
           <t>W1
@@ -1394,12 +1400,12 @@
       </c>
       <c r="B5" s="26" t="inlineStr">
         <is>
-          <t>A · 架构师</t>
+          <t>A·架构+需求</t>
         </is>
       </c>
       <c r="C5" s="27" t="inlineStr">
         <is>
-          <t>① Azure 订阅与权限确认 ② Terraform 项目初始化 ③ VNet/子网/NAT/AppGateway 基线代码 ④ 与网络团队确认 ExpressRoute/VPN 路径</t>
+          <t>① 需求访谈（业务方：查询场景/附件/保留期/权限/审计）② BRD 初稿（业务流程图 + 功能清单 + 非功能需求）③ 首个接入系统选定（建议 Dspot）④ Azure 订阅与权限确认 ⑤ 与网络/源方/安全团队的协调会</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
@@ -1407,23 +1413,23 @@
           <t>🔴</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Terraform plan 可跑通；网络拓扑图确认</t>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>BRD 初稿（可评审）；首系统确认；订阅就绪</t>
         </is>
       </c>
       <c r="F5" s="29" t="inlineStr">
         <is>
-          <t>Azure 订阅 Owner 权限</t>
+          <t>业务方安排访谈时间</t>
         </is>
       </c>
       <c r="G5" s="30" t="inlineStr">
         <is>
-          <t>Kick-off；技术选型评审</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1">
+          <t>Kick-off；需求访谈 × 3 场</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
       <c r="A6" s="25" t="inlineStr">
         <is>
           <t>W1
@@ -1432,12 +1438,12 @@
       </c>
       <c r="B6" s="31" t="inlineStr">
         <is>
-          <t>B · 数据工程</t>
+          <t>B·数据工程</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
         <is>
-          <t>① Databricks Premium 工作区创建（或确认已有）② UC Catalog 结构设计（catalog/schema 命名）③ Iceberg 表分区策略设计 ④ 源库连接 PoC 准备（SeaTunnel 本地跑通）</t>
+          <t>① Databricks Premium 工作区创建（或确认已有）② UC Catalog 结构设计 ③ Iceberg 分区策略设计 ④ SeaTunnel 本地 PoC 准备</t>
         </is>
       </c>
       <c r="D6" s="28" t="inlineStr">
@@ -1445,19 +1451,19 @@
           <t>🔴</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>UC 结构设计文档；SeaTunnel 本地→HDFS/Iceberg PoC 通过</t>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>UC 结构设计文档；SeaTunnel 本地→Iceberg PoC 通过</t>
         </is>
       </c>
       <c r="F6" s="29" t="inlineStr">
         <is>
-          <t>Databricks 开通周期（可能 1~3 天）</t>
+          <t>Databricks 开通周期</t>
         </is>
       </c>
       <c r="G6" s="30" t="inlineStr"/>
     </row>
-    <row r="7" ht="42" customHeight="1">
+    <row r="7" ht="44" customHeight="1">
       <c r="A7" s="25" t="inlineStr">
         <is>
           <t>W1
@@ -1466,12 +1472,12 @@
       </c>
       <c r="B7" s="32" t="inlineStr">
         <is>
-          <t>C · 前后端</t>
+          <t>C·全栈+DevOps</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
         <is>
-          <t>① 元数据库 35 张表 DDL（SQL Database S2）② .NET 10 项目骨架（Clean Architecture）③ React 前端项目骨架 + 路由/布局 ④ CI/CD 骨架（GitHub Actions → ACR → AKS Dev）</t>
+          <t>① .NET 10 项目骨架 + Clean Architecture ② React 前端骨架 + 路由/布局 ③ Docker Compose 本地开发环境（SQL Server + Azurite 模拟 ADLS）④ GitHub Actions CI 骨架（build + test + push ACR）</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
@@ -1479,19 +1485,19 @@
           <t>🔴</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>EF Core migration 可执行；前端首页可访问；CI/CD 推镜像成功</t>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>本地可开发（docker compose up）；CI 推镜像成功</t>
         </is>
       </c>
       <c r="F7" s="29" t="inlineStr">
         <is>
-          <t>元数据库建表 SQL（A 提供）</t>
+          <t>ACR 先建好（A 的 Terraform）</t>
         </is>
       </c>
       <c r="G7" s="30" t="inlineStr"/>
     </row>
-    <row r="8" ht="42" customHeight="1">
+    <row r="8" ht="44" customHeight="1">
       <c r="A8" s="25" t="inlineStr">
         <is>
           <t>W1
@@ -1500,12 +1506,12 @@
       </c>
       <c r="B8" s="33" t="inlineStr">
         <is>
-          <t>D · DevOps/QA</t>
+          <t>D·QA+SLC文档</t>
         </is>
       </c>
       <c r="C8" s="27" t="inlineStr">
         <is>
-          <t>① Azure CLI 脚本：一键创建全部 PaaS 资源 ② Helm Chart 骨架（backend/frontend）③ 测试计划初稿（功能测试 + UAT 场景清单）④ 项目 Wiki 搭建</t>
+          <t>① 测试计划初稿（功能/集成/性能/安全/UAT）② 架构图初稿：系统上下文图（C4-L1）+ 容器图（C4-L2）③ 项目文档模板定稿（详细设计/接口/用户手册/运维手册 4 套模板）④ UAT 场景清单初稿</t>
         </is>
       </c>
       <c r="D8" s="28" t="inlineStr">
@@ -1513,14 +1519,14 @@
           <t>🟡</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>CLI 脚本可在 Dev 环境跑通；测试计划初稿评审通过</t>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>测试计划初稿；架构图 2 张初稿；文档模板 4 套</t>
         </is>
       </c>
       <c r="F8" s="29" t="inlineStr">
         <is>
-          <t>Terraform 基线（A 提供）</t>
+          <t>A 的 BRD 初稿（了解需求范围）</t>
         </is>
       </c>
       <c r="G8" s="30" t="inlineStr">
@@ -1529,7 +1535,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1">
+    <row r="9" ht="44" customHeight="1">
       <c r="A9" s="25" t="inlineStr">
         <is>
           <t>W2
@@ -1538,12 +1544,12 @@
       </c>
       <c r="B9" s="26" t="inlineStr">
         <is>
-          <t>A · 架构师</t>
+          <t>A·架构+需求</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>① Terraform 完整基线：AKS/ADLS(Blob+dfs)/SQL DB/Key Vault/AppGateway+WAF/PE×5/Private DNS ② NCC 配置 ③ UC 权限矩阵（SP-query/SP-audit/组）④ IaC 部署到 Dev 环境</t>
+          <t>① BRD 评审会（业务方确认）→ 定稿 ② 用户故事地图 + Sprint 1~6 验收标准 ③ Terraform 完整基线：VNet/AKS/ADLS/SQL DB/Key Vault/AppGateway+WAF/PE/NCC ④ IaC 部署到 Dev 环境 ⑤ UC 权限矩阵</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
@@ -1551,23 +1557,23 @@
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>Dev 环境全套组件部署成功；ADLS 可经 PE 写入</t>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>BRD 签字；Dev 环境全套组件部署成功；UC 权限矩阵</t>
         </is>
       </c>
       <c r="F9" s="29" t="inlineStr">
         <is>
-          <t>网络团队配合 NCC 路由</t>
+          <t>网络团队 NCC 路由；BRD 评审会业务方到场</t>
         </is>
       </c>
       <c r="G9" s="30" t="inlineStr">
         <is>
-          <t>Sprint 0 Review；Sprint 1 Planning</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
+          <t>BRD 评审会；Sprint 0 Review；Sprint 1 Planning</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
       <c r="A10" s="25" t="inlineStr">
         <is>
           <t>W2
@@ -1576,12 +1582,12 @@
       </c>
       <c r="B10" s="31" t="inlineStr">
         <is>
-          <t>B · 数据工程</t>
+          <t>B·数据工程</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
         <is>
-          <t>① SeaTunnel→Iceberg PoC（连真实源库 SQL Server）② RAW 层表创建 + 分区写入验证 ③ SQL Warehouse 查询验证（SELECT * FROM raw.table LIMIT 10）④ 技术验证结论记录</t>
+          <t>① SeaTunnel→Iceberg PoC（连真实源库 SQL Server，Dspot）② RAW 层表创建 + 写入验证 ③ SQL Warehouse 查询验证 ④ PoC 结论记录</t>
         </is>
       </c>
       <c r="D10" s="28" t="inlineStr">
@@ -1589,9 +1595,9 @@
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>PoC 端到端成功：源库→SeaTunnel→Iceberg RAW→SQL Warehouse 可查</t>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>PoC 端到端：源库→SeaTunnel→Iceberg→SQL Warehouse 可查</t>
         </is>
       </c>
       <c r="F10" s="29" t="inlineStr">
@@ -1605,7 +1611,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="42" customHeight="1">
+    <row r="11" ht="44" customHeight="1">
       <c r="A11" s="25" t="inlineStr">
         <is>
           <t>W2
@@ -1614,12 +1620,12 @@
       </c>
       <c r="B11" s="32" t="inlineStr">
         <is>
-          <t>C · 前后端</t>
+          <t>C·全栈+DevOps</t>
         </is>
       </c>
       <c r="C11" s="27" t="inlineStr">
         <is>
-          <t>① Entra ID 应用注册 + OIDC 配置（前端登录流）② 后端核心框架：认证中间件 + UC 权限校验 ③ 前端登录页 + 系统列表页 ④ 后端部署到 AKS Dev（Helm）</t>
+          <t>① CI/CD 完整流水线（自动测试→构建→推镜像→Helm 部署 AKS Dev）② Entra ID 应用注册 + OIDC ③ 后端认证中间件 ④ 前端登录页 + 系统列表页 ⑤ Helm Chart 初版</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
@@ -1627,14 +1633,14 @@
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>浏览器 → 登录 → 看到系统列表页（空数据也行）</t>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Pipeline 端到端自动部署成功；浏览器可登录看到列表页</t>
         </is>
       </c>
       <c r="F11" s="29" t="inlineStr">
         <is>
-          <t>Entra ID 管理员配合</t>
+          <t>Entra ID 管理员；AKS Dev 就绪</t>
         </is>
       </c>
       <c r="G11" s="30" t="inlineStr">
@@ -1643,7 +1649,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="42" customHeight="1">
+    <row r="12" ht="44" customHeight="1">
       <c r="A12" s="25" t="inlineStr">
         <is>
           <t>W2
@@ -1652,12 +1658,12 @@
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>D · DevOps/QA</t>
+          <t>D·QA+SLC文档</t>
         </is>
       </c>
       <c r="C12" s="27" t="inlineStr">
         <is>
-          <t>① CI/CD 流水线完善（自动测试→构建→推镜像→部署 AKS Dev）② 自动化冒烟测试脚本（登录/查询）③ 项目文档模板（ADR/周报/Retro）④ UAT 场景清单 V1</t>
+          <t>① 架构图完善：组件图（C4-L3）+ 部署图（Azure 拓扑）② 接口文档初稿（API 列表 + 请求/响应示例）③ 测试环境搭建（测试数据准备方案）④ 需求可追溯矩阵（BRD→测试用例映射）</t>
         </is>
       </c>
       <c r="D12" s="28" t="inlineStr">
@@ -1665,19 +1671,23 @@
           <t>🟡</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Pipeline 端到端自动运行成功；UAT 场景清单评审通过</t>
-        </is>
-      </c>
-      <c r="F12" s="29" t="inlineStr"/>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>架构图 4 张初稿（上下文/容器/组件/部署）；接口文档初稿</t>
+        </is>
+      </c>
+      <c r="F12" s="29" t="inlineStr">
+        <is>
+          <t>A 的 BRD 定稿；C 的 API 骨架</t>
+        </is>
+      </c>
       <c r="G12" s="30" t="inlineStr">
         <is>
           <t>Sprint 0 Review</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="42" customHeight="1">
+    <row r="13" ht="44" customHeight="1">
       <c r="A13" s="25" t="inlineStr">
         <is>
           <t>W3
@@ -1686,12 +1696,12 @@
       </c>
       <c r="B13" s="26" t="inlineStr">
         <is>
-          <t>A · 架构师</t>
+          <t>A·架构+需求</t>
         </is>
       </c>
       <c r="C13" s="27" t="inlineStr">
         <is>
-          <t>① 代码评审（B 的 SeaTunnel 生成器 + C 的后端 API）② Databricks Jobs API 对接方案确认（后端→REST 触发）③ 查询代理 SQL 拼装安全方案（表名白名单/参数化）④ 技术债清理</t>
+          <t>① 代码评审（B 的生成器 + C 的 API）② Databricks Jobs API 触发方案（后端 REST 调用）③ 查询 SQL 安全方案（表名白名单/参数化）④ 用户故事拆分到 Sprint 1 任务</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
@@ -1699,7 +1709,7 @@
           <t>🟡</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>ADR：Jobs 触发方式；SQL 安全评审意见</t>
         </is>
@@ -1707,11 +1717,11 @@
       <c r="F13" s="29" t="inlineStr"/>
       <c r="G13" s="30" t="inlineStr">
         <is>
-          <t>Daily Standup（15min/天）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="42" customHeight="1">
+          <t>Daily Standup</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
       <c r="A14" s="25" t="inlineStr">
         <is>
           <t>W3
@@ -1720,12 +1730,12 @@
       </c>
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>B · 数据工程</t>
+          <t>B·数据工程</t>
         </is>
       </c>
       <c r="C14" s="27" t="inlineStr">
         <is>
-          <t>① SeaTunnel 配置生成器（读元数据库 source_table→生成 .conf 文件→提交 K8s Job）② RAW→LAKE 直达转换（跳过 CURATED，简单表先通）③ ADF 触发方案（或后端直接调 K8s API）</t>
+          <t>① SeaTunnel 配置生成器（读 source_table→生成 .conf→提交 K8s Job）② RAW→LAKE 直达转换 ③ 触发方式（后端调 K8s API 或 ADF）</t>
         </is>
       </c>
       <c r="D14" s="28" t="inlineStr">
@@ -1733,19 +1743,19 @@
           <t>🔴</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>配置生成器跑通：选表→生成任务→SeaTunnel 执行→数据进 RAW</t>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>配置生成器跑通：选表→生成任务→数据进 RAW</t>
         </is>
       </c>
       <c r="F14" s="29" t="inlineStr">
         <is>
-          <t>元数据库 source_table 有数据</t>
+          <t>元数据库有测试数据</t>
         </is>
       </c>
       <c r="G14" s="30" t="inlineStr"/>
     </row>
-    <row r="15" ht="42" customHeight="1">
+    <row r="15" ht="44" customHeight="1">
       <c r="A15" s="25" t="inlineStr">
         <is>
           <t>W3
@@ -1754,12 +1764,12 @@
       </c>
       <c r="B15" s="32" t="inlineStr">
         <is>
-          <t>C · 前后端</t>
+          <t>C·全栈+DevOps</t>
         </is>
       </c>
       <c r="C15" s="27" t="inlineStr">
         <is>
-          <t>① 核心 CRUD API：系统建档/源库配置/表清单/查询配置 ② 查询代理 API（接收前端请求→拼 SQL→调 SQL Warehouse→返回结果）③ 前端：查询配置管理页（表单设计器）</t>
+          <t>① 核心 CRUD API：系统/源库/表清单/查询配置 ② 查询代理 API（→SQL Warehouse）③ Helm Chart 完善（后端+前端+Service+Ingress）④ 前端：查询配置管理页</t>
         </is>
       </c>
       <c r="D15" s="28" t="inlineStr">
@@ -1767,19 +1777,19 @@
           <t>🔴</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>Postman 全 API 联通；前端可配置查询字段</t>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Postman API 全通；前端可配置查询字段</t>
         </is>
       </c>
       <c r="F15" s="29" t="inlineStr">
         <is>
-          <t>SQL Warehouse 连接串（A 提供）</t>
+          <t>SQL Warehouse 连接串</t>
         </is>
       </c>
       <c r="G15" s="30" t="inlineStr"/>
     </row>
-    <row r="16" ht="42" customHeight="1">
+    <row r="16" ht="44" customHeight="1">
       <c r="A16" s="25" t="inlineStr">
         <is>
           <t>W3
@@ -1788,12 +1798,12 @@
       </c>
       <c r="B16" s="33" t="inlineStr">
         <is>
-          <t>D · DevOps/QA</t>
+          <t>D·QA+SLC文档</t>
         </is>
       </c>
       <c r="C16" s="27" t="inlineStr">
         <is>
-          <t>① 单元测试框架搭建（xUnit + Mock）② 后端 API 集成测试（10 个核心场景）③ 前端 E2E 测试骨架（Playwright）④ 部署文档 V1（Dev 环境操作手册）</t>
+          <t>① 单元测试框架搭建（xUnit + Mock）② API 集成测试（10 核心场景）③ E2E 测试骨架（Playwright）④ 详细设计文档初稿：应用层（API 设计 + 类图 + 时序图）</t>
         </is>
       </c>
       <c r="D16" s="28" t="inlineStr">
@@ -1801,9 +1811,9 @@
           <t>🟡</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>CI 里自动跑测试；测试通过率 &gt;80%</t>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>CI 里自动跑测试 &gt;80%；应用层详细设计初稿</t>
         </is>
       </c>
       <c r="F16" s="29" t="inlineStr">
@@ -1813,7 +1823,7 @@
       </c>
       <c r="G16" s="30" t="inlineStr"/>
     </row>
-    <row r="17" ht="42" customHeight="1">
+    <row r="17" ht="44" customHeight="1">
       <c r="A17" s="25" t="inlineStr">
         <is>
           <t>W4
@@ -1822,12 +1832,12 @@
       </c>
       <c r="B17" s="26" t="inlineStr">
         <is>
-          <t>A · 架构师</t>
+          <t>A·架构+需求</t>
         </is>
       </c>
       <c r="C17" s="27" t="inlineStr">
         <is>
-          <t>① 端到端联调支撑（前后端+数据链路）② UC 权限落地：SP-query 只读 LAKE/SERVE、SP-audit 全量 ③ 性能基线测试（10 万行 SELECT &lt;3s）④ Sprint 1 验收准备</t>
+          <t>① 端到端联调 ② UC 权限落地（SP-query/SP-audit）③ 性能基线测试（10 万行 &lt;3s）④ Sprint 1 验收准备 ⑤ 下一个 Sprint 的需求澄清（附件/掩码/多表 JOIN）</t>
         </is>
       </c>
       <c r="D17" s="28" t="inlineStr">
@@ -1835,23 +1845,23 @@
           <t>🔴</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>UC GRANT 执行成功；性能基线报告</t>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>UC GRANT 成功；性能基线报告；Sprint 2 需求就绪</t>
         </is>
       </c>
       <c r="F17" s="29" t="inlineStr">
         <is>
-          <t>B 的数据链路就绪</t>
+          <t>B 数据链路就绪</t>
         </is>
       </c>
       <c r="G17" s="30" t="inlineStr">
         <is>
-          <t>Sprint 1 Review（核心演示）；Sprint 2 Planning</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="42" customHeight="1">
+          <t>Sprint 1 Review ★ MVP 演示；Sprint 2 Planning</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
       <c r="A18" s="25" t="inlineStr">
         <is>
           <t>W4
@@ -1860,22 +1870,22 @@
       </c>
       <c r="B18" s="31" t="inlineStr">
         <is>
-          <t>B · 数据工程</t>
+          <t>B·数据工程</t>
         </is>
       </c>
       <c r="C18" s="27" t="inlineStr">
         <is>
-          <t>① 端到端联调：源库→SeaTunnel→RAW→LAKE→查询代理 ② 数据对账脚本（行数+校验和）③ Compaction 初版（OPTIMIZE 定时跑）④ 增量同步方案确认（watermark 列 vs CDC）</t>
+          <t>① 端到端联调：源→SeaTunnel→RAW→LAKE→查询代理 ② 对账脚本（行数+校验和）③ Compaction 初版 ④ 增量方案确认</t>
         </is>
       </c>
       <c r="D18" s="28" t="inlineStr">
         <is>
-          <t>🔴</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>1 张表端到端：源→查询页可查；对账通过</t>
+          <t>🔴 ★</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>1 张表端到端：源→查询页可查</t>
         </is>
       </c>
       <c r="F18" s="29" t="inlineStr"/>
@@ -1885,7 +1895,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="42" customHeight="1">
+    <row r="19" ht="44" customHeight="1">
       <c r="A19" s="25" t="inlineStr">
         <is>
           <t>W4
@@ -1894,12 +1904,12 @@
       </c>
       <c r="B19" s="32" t="inlineStr">
         <is>
-          <t>C · 前后端</t>
+          <t>C·全栈+DevOps</t>
         </is>
       </c>
       <c r="C19" s="27" t="inlineStr">
         <is>
-          <t>① 前端查询页（元数据驱动渲染：文本/日期/下拉筛选 + 表格 + 分页）② 查询结果导出 CSV ③ 附件预览框架（URL 生成 + Blob 直连）④ 前后端联调</t>
+          <t>① 前端查询页（元数据驱动渲染：筛选/表格/分页）② 查询结果导出 CSV ③ 附件 URL 生成框架 ④ 前后端联调</t>
         </is>
       </c>
       <c r="D19" s="28" t="inlineStr">
@@ -1907,23 +1917,23 @@
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>登录→选系统→查表→看到数据（端到端演示）</t>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>登录→选系统→查表→看到数据</t>
         </is>
       </c>
       <c r="F19" s="29" t="inlineStr">
         <is>
-          <t>查询代理 API 就绪</t>
+          <t>查询代理就绪</t>
         </is>
       </c>
       <c r="G19" s="30" t="inlineStr">
         <is>
-          <t>Sprint 1 Review（核心演示）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="42" customHeight="1">
+          <t>Sprint 1 Review ★ MVP 演示</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1">
       <c r="A20" s="25" t="inlineStr">
         <is>
           <t>W4
@@ -1932,12 +1942,12 @@
       </c>
       <c r="B20" s="33" t="inlineStr">
         <is>
-          <t>D · DevOps/QA</t>
+          <t>D·QA+SLC文档</t>
         </is>
       </c>
       <c r="C20" s="27" t="inlineStr">
         <is>
-          <t>① 集成测试执行 + Bug 跟踪 ② 性能测试协助 ③ Sprint 1 Review 演示脚本准备 ④ Sprint 1 测试报告 ⑤ 文档：部署手册 V2</t>
+          <t>① 集成测试执行 + Bug 跟踪 ② 详细设计初稿：数据层（Iceberg 表结构 + 四层转换逻辑 + ER 图）③ Sprint 1 测试报告 ④ 架构图更新（反映实际部署）</t>
         </is>
       </c>
       <c r="D20" s="28" t="inlineStr">
@@ -1945,9 +1955,9 @@
           <t>🟡</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>测试报告；演示脚本；部署手册更新</t>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>测试报告；数据层详细设计初稿</t>
         </is>
       </c>
       <c r="F20" s="29" t="inlineStr"/>
@@ -1957,7 +1967,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="42" customHeight="1">
+    <row r="21" ht="44" customHeight="1">
       <c r="A21" s="25" t="inlineStr">
         <is>
           <t>W5
@@ -1966,12 +1976,12 @@
       </c>
       <c r="B21" s="26" t="inlineStr">
         <is>
-          <t>A · 架构师</t>
+          <t>A·架构+需求</t>
         </is>
       </c>
       <c r="C21" s="27" t="inlineStr">
         <is>
-          <t>① CURATED/SERVE 层设计评审（分区/物化策略）② UC 掩码函数设计（aes_encrypt + is_account_group_member）③ Key Vault 密钥体系（DEK/KEK）④ 附件网络路径确认（Storage Mover / SAS）</t>
+          <t>① CURATED/SERVE 设计评审 ② UC 掩码函数设计（aes_encrypt + is_account_group_member）③ Key Vault 密钥体系 ④ 附件网络路径确认 ⑤ 代码评审</t>
         </is>
       </c>
       <c r="D21" s="28" t="inlineStr">
@@ -1979,7 +1989,7 @@
           <t>🔴</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>掩码函数 ADR；密钥体系设计文档</t>
         </is>
@@ -1995,7 +2005,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="42" customHeight="1">
+    <row r="22" ht="44" customHeight="1">
       <c r="A22" s="25" t="inlineStr">
         <is>
           <t>W5
@@ -2004,12 +2014,12 @@
       </c>
       <c r="B22" s="31" t="inlineStr">
         <is>
-          <t>B · 数据工程</t>
+          <t>B·数据工程</t>
         </is>
       </c>
       <c r="C22" s="27" t="inlineStr">
         <is>
-          <t>① CURATED 层：类型统一/缺失值/SHA-256 台账 SQL ② LAKE 层：业务建模+生命周期分区 ③ SERVE 层：热表物化+Z-Order ④ 四层 Databricks Jobs 创建（多 Task 依赖）</t>
+          <t>① CURATED：类型统一/SHA-256/分区归约 ② LAKE：建模+生命周期分区 ③ SERVE：物化+Z-Order ④ 四层 Jobs（多 Task 依赖）</t>
         </is>
       </c>
       <c r="D22" s="28" t="inlineStr">
@@ -2017,19 +2027,19 @@
           <t>🔴</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>四层转换 Jobs 跑通；SERVE 表可查</t>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>四层转换 Jobs 跑通；SERVE 可查</t>
         </is>
       </c>
       <c r="F22" s="29" t="inlineStr">
         <is>
-          <t>A 的层设计评审通过</t>
+          <t>A 的层设计评审</t>
         </is>
       </c>
       <c r="G22" s="30" t="inlineStr"/>
     </row>
-    <row r="23" ht="42" customHeight="1">
+    <row r="23" ht="44" customHeight="1">
       <c r="A23" s="25" t="inlineStr">
         <is>
           <t>W5
@@ -2038,12 +2048,12 @@
       </c>
       <c r="B23" s="32" t="inlineStr">
         <is>
-          <t>C · 前后端</t>
+          <t>C·全栈+DevOps</t>
         </is>
       </c>
       <c r="C23" s="27" t="inlineStr">
         <is>
-          <t>① 前端配置化查询完善：动态列表格/排序/筛选条件联动 ② 附件预览：图片/音频/视频/文档 ③ 权限渲染：无权限列隐藏 ④ 导出功能完善（Excel）</t>
+          <t>① 前端配置化查询完善（动态列/排序/筛选联动）② 附件预览：图片/音频/视频 ③ 权限渲染（无权限列隐藏）④ CI/CD 完善（多环境 Dev/Staging）</t>
         </is>
       </c>
       <c r="D23" s="28" t="inlineStr">
@@ -2051,19 +2061,19 @@
           <t>🔴</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>前端全功能可用；附件可预览</t>
         </is>
       </c>
       <c r="F23" s="29" t="inlineStr">
         <is>
-          <t>B 的 SERVE 层数据</t>
+          <t>B 的 SERVE 数据</t>
         </is>
       </c>
       <c r="G23" s="30" t="inlineStr"/>
     </row>
-    <row r="24" ht="42" customHeight="1">
+    <row r="24" ht="44" customHeight="1">
       <c r="A24" s="25" t="inlineStr">
         <is>
           <t>W5
@@ -2072,12 +2082,12 @@
       </c>
       <c r="B24" s="33" t="inlineStr">
         <is>
-          <t>D · DevOps/QA</t>
+          <t>D·QA+SLC文档</t>
         </is>
       </c>
       <c r="C24" s="27" t="inlineStr">
         <is>
-          <t>① 功能测试用例扩充（覆盖全部 CRUD + 查询 + 附件 + 权限）② 自动化测试：后端 API 全覆盖 ③ 安全测试：SQL 注入/XSS/越权 ④ 运维文档初稿（监控/告警/故障处理）</t>
+          <t>① 功能测试用例扩充（50+ 场景）② 自动化测试覆盖率 &gt;60% ③ 安全测试（SQL 注入/XSS/越权）④ 详细设计：安全层（认证/授权/加密/审计 + 掩码函数时序图）</t>
         </is>
       </c>
       <c r="D24" s="28" t="inlineStr">
@@ -2085,9 +2095,9 @@
           <t>🟡</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>测试用例 50+；自动化覆盖率 &gt;60%</t>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>测试用例 50+；安全测试报告；安全层设计初稿</t>
         </is>
       </c>
       <c r="F24" s="29" t="inlineStr">
@@ -2097,7 +2107,7 @@
       </c>
       <c r="G24" s="30" t="inlineStr"/>
     </row>
-    <row r="25" ht="42" customHeight="1">
+    <row r="25" ht="44" customHeight="1">
       <c r="A25" s="25" t="inlineStr">
         <is>
           <t>W6
@@ -2106,12 +2116,12 @@
       </c>
       <c r="B25" s="26" t="inlineStr">
         <is>
-          <t>A · 架构师</t>
+          <t>A·架构+需求</t>
         </is>
       </c>
       <c r="C25" s="27" t="inlineStr">
         <is>
-          <t>① 代码评审（四层 SQL + 掩码函数）② 权限端到端测试（有权限见明文/无权限见掩码）③ 附件链路联调（Storage Mover→Blob→SAS→前端预览）④ Sprint 2 验收准备</t>
+          <t>① 代码评审 ② 权限端到端测试（明文/掩码）③ 附件链路联调 ④ Sprint 2 验收 ⑤ 第二系统选型确认 + 源库协调</t>
         </is>
       </c>
       <c r="D25" s="28" t="inlineStr">
@@ -2119,9 +2129,9 @@
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>掩码演示通过；附件端到端预览成功</t>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>掩码演示通过；附件端到端预览；第二系统确认</t>
         </is>
       </c>
       <c r="F25" s="29" t="inlineStr"/>
@@ -2131,7 +2141,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="42" customHeight="1">
+    <row r="26" ht="44" customHeight="1">
       <c r="A26" s="25" t="inlineStr">
         <is>
           <t>W6
@@ -2140,12 +2150,12 @@
       </c>
       <c r="B26" s="31" t="inlineStr">
         <is>
-          <t>B · 数据工程</t>
+          <t>B·数据工程</t>
         </is>
       </c>
       <c r="C26" s="27" t="inlineStr">
         <is>
-          <t>① 附件链路：Storage Mover 任务 + attachment_index 登记 + SHA-256 台账 ② UC 掩码函数部署 + 测试 ③ Compaction/VACUUM 定时 Jobs ④ 四层转换性能优化（并行度/文件大小）</t>
+          <t>① 附件：Storage Mover + attachment_index + SHA-256 ② UC 掩码函数部署 ③ Compaction/VACUUM 定时 ④ 性能优化</t>
         </is>
       </c>
       <c r="D26" s="28" t="inlineStr">
@@ -2153,14 +2163,14 @@
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>附件从源→Blob→前端可预览；掩码查询正常</t>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>附件端到端；掩码查询正常</t>
         </is>
       </c>
       <c r="F26" s="29" t="inlineStr">
         <is>
-          <t>Storage Mover 网络打通</t>
+          <t>Storage Mover 网络</t>
         </is>
       </c>
       <c r="G26" s="30" t="inlineStr">
@@ -2169,7 +2179,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="42" customHeight="1">
+    <row r="27" ht="44" customHeight="1">
       <c r="A27" s="25" t="inlineStr">
         <is>
           <t>W6
@@ -2178,12 +2188,12 @@
       </c>
       <c r="B27" s="32" t="inlineStr">
         <is>
-          <t>C · 前后端</t>
+          <t>C·全栈+DevOps</t>
         </is>
       </c>
       <c r="C27" s="27" t="inlineStr">
         <is>
-          <t>① 前端权限联动：按 UC 返回动态隐藏列 ② 多表 JOIN 查询支持（query_join 配置→动态 SQL）③ 下钻配置（drill_config→父子表导航）④ UI 细节打磨</t>
+          <t>① 多表 JOIN（query_join→动态 SQL）② 下钻（drill_config→父子导航）③ 导出完善 ④ Bug 修复</t>
         </is>
       </c>
       <c r="D27" s="28" t="inlineStr">
@@ -2191,9 +2201,9 @@
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>多表 JOIN + 下钻 + 掩码列隐藏 全部可用</t>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>JOIN+下钻+掩码隐藏全部可用</t>
         </is>
       </c>
       <c r="F27" s="29" t="inlineStr"/>
@@ -2203,7 +2213,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="42" customHeight="1">
+    <row r="28" ht="44" customHeight="1">
       <c r="A28" s="25" t="inlineStr">
         <is>
           <t>W6
@@ -2212,12 +2222,12 @@
       </c>
       <c r="B28" s="33" t="inlineStr">
         <is>
-          <t>D · DevOps/QA</t>
+          <t>D·QA+SLC文档</t>
         </is>
       </c>
       <c r="C28" s="27" t="inlineStr">
         <is>
-          <t>① 功能测试全量执行（Sprint 1+2 合计场景）② 性能测试（100 万行表 SELECT P95 &lt; 5s）③ 安全测试报告 ④ Sprint 2 测试报告 + Bug 清单 ⑤ 运维文档完善</t>
+          <t>① 功能测试全量执行 ② 性能测试（100 万行 P95&lt;5s）③ 详细设计终稿（3 模块合稿：应用+数据+安全）④ 接口文档完善 ⑤ Sprint 2 测试报告</t>
         </is>
       </c>
       <c r="D28" s="28" t="inlineStr">
@@ -2225,14 +2235,14 @@
           <t>🟡</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>性能报告；安全报告；Bug 清单分级</t>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>性能报告；详细设计 3 模块合稿</t>
         </is>
       </c>
       <c r="F28" s="29" t="inlineStr">
         <is>
-          <t>性能测试数据由 B 准备</t>
+          <t>性能数据由 B 准备</t>
         </is>
       </c>
       <c r="G28" s="30" t="inlineStr">
@@ -2241,7 +2251,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="42" customHeight="1">
+    <row r="29" ht="44" customHeight="1">
       <c r="A29" s="25" t="inlineStr">
         <is>
           <t>W7
@@ -2250,12 +2260,12 @@
       </c>
       <c r="B29" s="26" t="inlineStr">
         <is>
-          <t>A · 架构师</t>
+          <t>A·架构+需求</t>
         </is>
       </c>
       <c r="C29" s="27" t="inlineStr">
         <is>
-          <t>① Retention 策略设计（retention_policy/assignment 表→到期计算→触发 Job）② 销毁审批流程设计（destroy_approval + 通知）③ Monitor 告警规则设计（Job 失败/查询超时/存储阈值）④ 第二系统接入排期确认</t>
+          <t>① Retention 策略设计 ② 销毁审批流程设计 ③ Monitor 告警规则 ④ 第二系统源库协调（账号/网络/表结构）</t>
         </is>
       </c>
       <c r="D29" s="28" t="inlineStr">
@@ -2263,7 +2273,7 @@
           <t>🔴</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>Retention 流程图；告警规则清单</t>
         </is>
@@ -2279,7 +2289,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="42" customHeight="1">
+    <row r="30" ht="44" customHeight="1">
       <c r="A30" s="25" t="inlineStr">
         <is>
           <t>W7
@@ -2288,12 +2298,12 @@
       </c>
       <c r="B30" s="31" t="inlineStr">
         <is>
-          <t>B · 数据工程</t>
+          <t>B·数据工程</t>
         </is>
       </c>
       <c r="C30" s="27" t="inlineStr">
         <is>
-          <t>① 到期扫描 Job（读 retention_assignment→计算到期→标记待销毁）② DROP PARTITION + VACUUM 作业（Databricks 原生 cron 调度）③ 销毁结果回写元数据库 + 审计留痕 ④ 通知集成（到期前邮件提醒）</t>
+          <t>① 到期扫描 Job ② DROP PARTITION + VACUUM（Databricks 原生 cron）③ 销毁结果回写 + 审计 ④ 通知集成</t>
         </is>
       </c>
       <c r="D30" s="28" t="inlineStr">
@@ -2301,15 +2311,15 @@
           <t>🔴</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>测试环境完整销毁回路跑通（设 1 天保留期→到期自动删→审计可查）</t>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>测试环境完整销毁回路跑通</t>
         </is>
       </c>
       <c r="F30" s="29" t="inlineStr"/>
       <c r="G30" s="30" t="inlineStr"/>
     </row>
-    <row r="31" ht="42" customHeight="1">
+    <row r="31" ht="44" customHeight="1">
       <c r="A31" s="25" t="inlineStr">
         <is>
           <t>W7
@@ -2318,12 +2328,12 @@
       </c>
       <c r="B31" s="32" t="inlineStr">
         <is>
-          <t>C · 前后端</t>
+          <t>C·全栈+DevOps</t>
         </is>
       </c>
       <c r="C31" s="27" t="inlineStr">
         <is>
-          <t>① Retention 策略配置界面（保留年限/起算日期/到期预警）② 销毁审批界面（审批人操作+留痕）③ 通知中心（站内信+邮件）④ Dashboard：同步活跃度图表（sync_activity）</t>
+          <t>① Retention 策略配置界面 ② 销毁审批界面 ③ 通知中心（站内+邮件）④ Dashboard（同步活跃度图表）</t>
         </is>
       </c>
       <c r="D31" s="28" t="inlineStr">
@@ -2331,19 +2341,19 @@
           <t>🔴</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>Retention 全流程 UI 可操作；审批通过后触发销毁</t>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>Retention 全流程 UI 可操作</t>
         </is>
       </c>
       <c r="F31" s="29" t="inlineStr">
         <is>
-          <t>B 的销毁 Job 就绪</t>
+          <t>B 的销毁 Job</t>
         </is>
       </c>
       <c r="G31" s="30" t="inlineStr"/>
     </row>
-    <row r="32" ht="42" customHeight="1">
+    <row r="32" ht="44" customHeight="1">
       <c r="A32" s="25" t="inlineStr">
         <is>
           <t>W7
@@ -2352,12 +2362,12 @@
       </c>
       <c r="B32" s="33" t="inlineStr">
         <is>
-          <t>D · DevOps/QA</t>
+          <t>D·QA+SLC文档</t>
         </is>
       </c>
       <c r="C32" s="27" t="inlineStr">
         <is>
-          <t>① 销毁流程测试（端到端：设定→到期→审批→执行→审计）② 通知功能测试 ③ Dashboard 数据准确性验证 ④ 第二系统接入测试准备（走零代码流程）</t>
+          <t>① 销毁流程 E2E 测试 ② 通知功能测试 ③ Dashboard 数据验证 ④ 用户手册初稿（含截图 30+）⑤ 第二系统接入测试准备</t>
         </is>
       </c>
       <c r="D32" s="28" t="inlineStr">
@@ -2365,15 +2375,15 @@
           <t>🟡</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>销毁 E2E 测试报告；通知到达率 100%</t>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>销毁 E2E 报告；用户手册初稿（50% 完成）</t>
         </is>
       </c>
       <c r="F32" s="29" t="inlineStr"/>
       <c r="G32" s="30" t="inlineStr"/>
     </row>
-    <row r="33" ht="42" customHeight="1">
+    <row r="33" ht="44" customHeight="1">
       <c r="A33" s="25" t="inlineStr">
         <is>
           <t>W8
@@ -2382,12 +2392,12 @@
       </c>
       <c r="B33" s="26" t="inlineStr">
         <is>
-          <t>A · 架构师</t>
+          <t>A·架构+需求</t>
         </is>
       </c>
       <c r="C33" s="27" t="inlineStr">
         <is>
-          <t>① 第二系统接入（走标准流程验证零代码：建档→连源→勾表→生成任务→数据可查）② 集成测试统筹 ③ 性能瓶颈分析（如有）④ Sprint 3 验收准备</t>
+          <t>① 第二系统零代码接入（标准流程验证）② 集成测试统筹 ③ 性能瓶颈分析 ④ Sprint 3 验收</t>
         </is>
       </c>
       <c r="D33" s="28" t="inlineStr">
@@ -2395,9 +2405,9 @@
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>第二系统全程零代码接入成功（&lt;2 小时）</t>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>第二系统零代码接入成功（&lt;2h）</t>
         </is>
       </c>
       <c r="F33" s="29" t="inlineStr">
@@ -2411,7 +2421,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="42" customHeight="1">
+    <row r="34" ht="44" customHeight="1">
       <c r="A34" s="25" t="inlineStr">
         <is>
           <t>W8
@@ -2420,12 +2430,12 @@
       </c>
       <c r="B34" s="31" t="inlineStr">
         <is>
-          <t>B · 数据工程</t>
+          <t>B·数据工程</t>
         </is>
       </c>
       <c r="C34" s="27" t="inlineStr">
         <is>
-          <t>① 第二系统 SeaTunnel 任务生成+执行 ② 第二系统四层转换+SERVE 物化 ③ 全链路集成测试（两系统数据互查）④ 性能调优（Compaction 频率/分区粒度）</t>
+          <t>① 第二系统 SeaTunnel+四层+SERVE ② 两系统联邦查询 ③ 性能调优</t>
         </is>
       </c>
       <c r="D34" s="28" t="inlineStr">
@@ -2433,23 +2443,19 @@
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>第二系统数据端到端可查</t>
-        </is>
-      </c>
-      <c r="F34" s="29" t="inlineStr">
-        <is>
-          <t>第二系统表结构确认</t>
-        </is>
-      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>第二系统端到端可查</t>
+        </is>
+      </c>
+      <c r="F34" s="29" t="inlineStr"/>
       <c r="G34" s="30" t="inlineStr">
         <is>
           <t>Sprint 3 Review</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="42" customHeight="1">
+    <row r="35" ht="44" customHeight="1">
       <c r="A35" s="25" t="inlineStr">
         <is>
           <t>W8
@@ -2458,12 +2464,12 @@
       </c>
       <c r="B35" s="32" t="inlineStr">
         <is>
-          <t>C · 前后端</t>
+          <t>C·全栈+DevOps</t>
         </is>
       </c>
       <c r="C35" s="27" t="inlineStr">
         <is>
-          <t>① 第二系统前端配置（零代码：配查询字段/筛选/掩码）② 跨系统联邦查询测试（两系统 JOIN）③ 前端性能优化（懒加载/分页）④ Bug 修复</t>
+          <t>① 第二系统前端配置（零代码）② 跨系统联邦查询测试 ③ 前端性能优化 ④ Bug 修复</t>
         </is>
       </c>
       <c r="D35" s="28" t="inlineStr">
@@ -2471,7 +2477,7 @@
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>第二系统查询页零代码上线</t>
         </is>
@@ -2483,7 +2489,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="42" customHeight="1">
+    <row r="36" ht="44" customHeight="1">
       <c r="A36" s="25" t="inlineStr">
         <is>
           <t>W8
@@ -2492,12 +2498,12 @@
       </c>
       <c r="B36" s="33" t="inlineStr">
         <is>
-          <t>D · DevOps/QA</t>
+          <t>D·QA+SLC文档</t>
         </is>
       </c>
       <c r="C36" s="27" t="inlineStr">
         <is>
-          <t>① 全量回归测试（Sprint 1~3 全功能）② 性能测试（20GB 数据量，P95 &lt; 5s）③ 用户手册初稿（面向业务用户）④ Sprint 3 测试报告 ⑤ UAT 场景脚本准备</t>
+          <t>① 全量回归测试（S1+S2+S3）② 性能测试（20GB P95&lt;5s）③ 用户手册完善（80%）④ 运维手册初稿 ⑤ 数据字典初稿 ⑥ Sprint 3 测试报告 ⑦ UAT 场景脚本</t>
         </is>
       </c>
       <c r="D36" s="28" t="inlineStr">
@@ -2505,9 +2511,9 @@
           <t>🟡</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>回归测试全通过；用户手册初稿完成</t>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>回归全通过；用户手册 80%；运维手册初稿；数据字典初稿</t>
         </is>
       </c>
       <c r="F36" s="29" t="inlineStr"/>
@@ -2517,7 +2523,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="42" customHeight="1">
+    <row r="37" ht="44" customHeight="1">
       <c r="A37" s="25" t="inlineStr">
         <is>
           <t>W9
@@ -2526,12 +2532,12 @@
       </c>
       <c r="B37" s="26" t="inlineStr">
         <is>
-          <t>A · 架构师</t>
+          <t>A·架构+需求</t>
         </is>
       </c>
       <c r="C37" s="27" t="inlineStr">
         <is>
-          <t>① 生产环境 Terraform 代码 Review + 与 Dev 环境差异确认 ② 安全评审材料（等保/个保法对照表）③ 生产域名/证书/网络确认 ④ 全量迁移方案（分批 or 一次性）</t>
+          <t>① 生产 Terraform Review + apply ② 安全评审材料（等保/个保法对照表）③ 生产域名/证书/网络确认 ④ 全量迁移方案</t>
         </is>
       </c>
       <c r="D37" s="28" t="inlineStr">
@@ -2539,14 +2545,14 @@
           <t>🔴</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>生产 Terraform plan 通过；安全材料初稿；迁移方案文档</t>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>生产环境就绪；安全材料初稿；迁移方案</t>
         </is>
       </c>
       <c r="F37" s="29" t="inlineStr">
         <is>
-          <t>生产订阅权限；证书申请</t>
+          <t>生产订阅权限；证书</t>
         </is>
       </c>
       <c r="G37" s="30" t="inlineStr">
@@ -2555,7 +2561,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="42" customHeight="1">
+    <row r="38" ht="44" customHeight="1">
       <c r="A38" s="25" t="inlineStr">
         <is>
           <t>W9
@@ -2564,12 +2570,12 @@
       </c>
       <c r="B38" s="31" t="inlineStr">
         <is>
-          <t>B · 数据工程</t>
+          <t>B·数据工程</t>
         </is>
       </c>
       <c r="C38" s="27" t="inlineStr">
         <is>
-          <t>① 首系统全量数据迁移执行（正式，含对账）② 迁移中问题处理 ③ 生产 Databricks Jobs 部署（ETL/Compaction/销毁）④ 生产 UC 权限配置</t>
+          <t>① 首系统全量迁移执行（含对账）② 生产 Jobs 部署 ③ 生产 UC 权限配置</t>
         </is>
       </c>
       <c r="D38" s="28" t="inlineStr">
@@ -2577,19 +2583,19 @@
           <t>🔴</t>
         </is>
       </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>首系统全量数据入湖；对账通过</t>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>首系统全量入湖；对账通过</t>
         </is>
       </c>
       <c r="F38" s="29" t="inlineStr">
         <is>
-          <t>生产环境就绪（A 的 Terraform apply）</t>
+          <t>生产环境就绪</t>
         </is>
       </c>
       <c r="G38" s="30" t="inlineStr"/>
     </row>
-    <row r="39" ht="42" customHeight="1">
+    <row r="39" ht="44" customHeight="1">
       <c r="A39" s="25" t="inlineStr">
         <is>
           <t>W9
@@ -2598,12 +2604,12 @@
       </c>
       <c r="B39" s="32" t="inlineStr">
         <is>
-          <t>C · 前后端</t>
+          <t>C·全栈+DevOps</t>
         </is>
       </c>
       <c r="C39" s="27" t="inlineStr">
         <is>
-          <t>① 生产 AKS 部署（Helm Release）② 生产 SSO 配置（Entra ID 回调域名）③ 首系统查询页生产配置 ④ 性能监控接入</t>
+          <t>① 生产 AKS 部署（Helm Release）② 生产 SSO 配置 ③ 首系统查询页生产配置 ④ 性能监控接入</t>
         </is>
       </c>
       <c r="D39" s="28" t="inlineStr">
@@ -2611,19 +2617,19 @@
           <t>🔴</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>生产环境可访问；SSO 登录正常；查询页可用</t>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>生产可访问；SSO 正常；查询可用</t>
         </is>
       </c>
       <c r="F39" s="29" t="inlineStr">
         <is>
-          <t>生产域名解析</t>
+          <t>生产域名</t>
         </is>
       </c>
       <c r="G39" s="30" t="inlineStr"/>
     </row>
-    <row r="40" ht="42" customHeight="1">
+    <row r="40" ht="44" customHeight="1">
       <c r="A40" s="25" t="inlineStr">
         <is>
           <t>W9
@@ -2632,12 +2638,12 @@
       </c>
       <c r="B40" s="33" t="inlineStr">
         <is>
-          <t>D · DevOps/QA</t>
+          <t>D·QA+SLC文档</t>
         </is>
       </c>
       <c r="C40" s="27" t="inlineStr">
         <is>
-          <t>① 用户手册完善（含截图/FAQ）② 运维手册完善（部署/监控/故障/备份恢复）③ 架构文档（组件清单/网络图/数据流图）④ 审批材料准备（技术方案/安全评估/合规对照）</t>
+          <t>① 文档冲刺启动：用户手册终版 + 运维手册终版 + 数据字典终版 ② 架构图终版（4 张全更新到生产实际）③ 详细设计终版 ④ 接口文档终版 ⑤ 审批材料包准备（技术方案/安全评估/合规对照/验收报告）</t>
         </is>
       </c>
       <c r="D40" s="28" t="inlineStr">
@@ -2645,15 +2651,15 @@
           <t>🔴</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>文档包 V1（用户手册+运维手册+架构文档+审批材料）</t>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>6 套文档进入终审（用户/运维/架构×4/详细设计/接口/数据字典）；审批材料初稿</t>
         </is>
       </c>
       <c r="F40" s="29" t="inlineStr"/>
       <c r="G40" s="30" t="inlineStr"/>
     </row>
-    <row r="41" ht="42" customHeight="1">
+    <row r="41" ht="44" customHeight="1">
       <c r="A41" s="25" t="inlineStr">
         <is>
           <t>W10
@@ -2662,12 +2668,12 @@
       </c>
       <c r="B41" s="26" t="inlineStr">
         <is>
-          <t>A · 架构师</t>
+          <t>A·架构+需求</t>
         </is>
       </c>
       <c r="C41" s="27" t="inlineStr">
         <is>
-          <t>① UAT 组织：5 个核心场景 + 业务方验收 ② UAT 反馈处理（Bug 修复/调整）③ 安全评审提交 ④ 审批文档定稿</t>
+          <t>① UAT 组织（5 核心场景 + 业务方验收）② UAT 反馈处理 ③ 安全评审提交 ④ 审批文档定稿</t>
         </is>
       </c>
       <c r="D41" s="28" t="inlineStr">
@@ -2675,14 +2681,14 @@
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>UAT 签字通过；安全评审提交；审批材料提交</t>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>UAT 签字；安全评审提交；审批材料提交</t>
         </is>
       </c>
       <c r="F41" s="29" t="inlineStr">
         <is>
-          <t>业务方配合 UAT</t>
+          <t>业务方 UAT 配合</t>
         </is>
       </c>
       <c r="G41" s="30" t="inlineStr">
@@ -2691,7 +2697,7 @@
         </is>
       </c>
     </row>
-    <row r="42" ht="42" customHeight="1">
+    <row r="42" ht="44" customHeight="1">
       <c r="A42" s="25" t="inlineStr">
         <is>
           <t>W10
@@ -2700,12 +2706,12 @@
       </c>
       <c r="B42" s="31" t="inlineStr">
         <is>
-          <t>B · 数据工程</t>
+          <t>B·数据工程</t>
         </is>
       </c>
       <c r="C42" s="27" t="inlineStr">
         <is>
-          <t>① UAT 支撑（数据问题排查/修复）② 第二系统全量迁移准备 ③ 生产 Compaction/VACUUM 首次执行 ④ 销毁回路生产验证（用测试数据）</t>
+          <t>① UAT 支撑 ② 第二系统全量迁移准备 ③ 生产 Compaction 首次执行 ④ 销毁回路生产验证</t>
         </is>
       </c>
       <c r="D42" s="28" t="inlineStr">
@@ -2713,9 +2719,9 @@
           <t>🟡</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>UAT 数据问题全部解决；第二系统迁移方案确认</t>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>UAT 数据问题全解决</t>
         </is>
       </c>
       <c r="F42" s="29" t="inlineStr"/>
@@ -2725,7 +2731,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="42" customHeight="1">
+    <row r="43" ht="44" customHeight="1">
       <c r="A43" s="25" t="inlineStr">
         <is>
           <t>W10
@@ -2734,12 +2740,12 @@
       </c>
       <c r="B43" s="32" t="inlineStr">
         <is>
-          <t>C · 前后端</t>
+          <t>C·全栈+DevOps</t>
         </is>
       </c>
       <c r="C43" s="27" t="inlineStr">
         <is>
-          <t>① UAT 反馈 Bug 修复（前端 + 后端）② 生产监控 Dashboard 完善 ③ 性能微调 ④ 文档技术校对（用户手册中截图更新）</t>
+          <t>① UAT Bug 修复 ② 生产监控 Dashboard ③ 性能微调 ④ 文档截图更新</t>
         </is>
       </c>
       <c r="D43" s="28" t="inlineStr">
@@ -2747,9 +2753,9 @@
           <t>🟡</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>UAT Bug 全部关闭；截图与生产一致</t>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>UAT Bug 全关闭；截图一致</t>
         </is>
       </c>
       <c r="F43" s="29" t="inlineStr"/>
@@ -2759,7 +2765,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="42" customHeight="1">
+    <row r="44" ht="44" customHeight="1">
       <c r="A44" s="25" t="inlineStr">
         <is>
           <t>W10
@@ -2768,12 +2774,12 @@
       </c>
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>D · DevOps/QA</t>
+          <t>D·QA+SLC文档</t>
         </is>
       </c>
       <c r="C44" s="27" t="inlineStr">
         <is>
-          <t>① UAT 执行协调 + 结果记录 ② 文档终审（用户/运维/架构/审批 4 套）③ 审批材料跟踪 ④ 上线 Checklist 准备 ⑤ 培训材料准备（面向运维 + 业务）</t>
+          <t>① UAT 执行协调 + 结果记录 ② 文档终审（6 套 + 审批包 = 7 套）③ 上线 Checklist ④ 培训材料（业务用户 + 运维团队）</t>
         </is>
       </c>
       <c r="D44" s="28" t="inlineStr">
@@ -2781,9 +2787,9 @@
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>文档包终版；上线 Checklist 评审通过</t>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>7 套文档终版；上线 Checklist 评审通过；培训 PPT + 演练脚本</t>
         </is>
       </c>
       <c r="F44" s="29" t="inlineStr">
@@ -2797,7 +2803,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="42" customHeight="1">
+    <row r="45" ht="44" customHeight="1">
       <c r="A45" s="25" t="inlineStr">
         <is>
           <t>W11
@@ -2806,12 +2812,12 @@
       </c>
       <c r="B45" s="26" t="inlineStr">
         <is>
-          <t>A · 架构师</t>
+          <t>A·架构+需求</t>
         </is>
       </c>
       <c r="C45" s="27" t="inlineStr">
         <is>
-          <t>① 上线窗口确认 + Go/No-Go 决策 ② 上线指挥（回退方案就绪）③ 知识转移：架构与运维培训（面向运维团队）④ 项目收尾文档启动</t>
+          <t>① Go/No-Go 决策 ② 上线指挥（回退方案就绪）③ 运维培训（架构+UC+权限+监控）④ 项目收尾文档启动</t>
         </is>
       </c>
       <c r="D45" s="28" t="inlineStr">
@@ -2819,19 +2825,19 @@
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>Go/No-Go 会议纪要；上线成功；运维培训完成</t>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>上线成功；运维培训完成</t>
         </is>
       </c>
       <c r="F45" s="29" t="inlineStr"/>
       <c r="G45" s="30" t="inlineStr">
         <is>
-          <t>Go-Live 决策会议</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="42" customHeight="1">
+          <t>Go-Live 决策会</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="44" customHeight="1">
       <c r="A46" s="25" t="inlineStr">
         <is>
           <t>W11
@@ -2840,12 +2846,12 @@
       </c>
       <c r="B46" s="31" t="inlineStr">
         <is>
-          <t>B · 数据工程</t>
+          <t>B·数据工程</t>
         </is>
       </c>
       <c r="C46" s="27" t="inlineStr">
         <is>
-          <t>① 生产运行监控（ETL Job/Compaction/销毁 正常执行）② 异常处理（首周重点）③ 第二系统全量迁移执行 ④ 后续系统接入 SOP 初稿</t>
+          <t>① 生产运行监控（ETL/Compaction/销毁）② 异常处理 ③ 第二系统全量迁移 ④ 接入 SOP 初稿</t>
         </is>
       </c>
       <c r="D46" s="28" t="inlineStr">
@@ -2853,9 +2859,9 @@
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>生产 Jobs 全部正常运行；第二系统数据入湖</t>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>生产 Jobs 正常；第二系统入湖</t>
         </is>
       </c>
       <c r="F46" s="29" t="inlineStr"/>
@@ -2865,7 +2871,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="42" customHeight="1">
+    <row r="47" ht="44" customHeight="1">
       <c r="A47" s="25" t="inlineStr">
         <is>
           <t>W11
@@ -2874,12 +2880,12 @@
       </c>
       <c r="B47" s="32" t="inlineStr">
         <is>
-          <t>C · 前后端</t>
+          <t>C·全栈+DevOps</t>
         </is>
       </c>
       <c r="C47" s="27" t="inlineStr">
         <is>
-          <t>① 生产运行监控（查询性能/前端报错/SSO）② 用户反馈快速响应 ③ 生产配置调优（缓存/连接池）④ 后续系统接入 SOP（前端配置部分）</t>
+          <t>① 生产运行监控（查询/前端/SSO）② 用户反馈响应 ③ 配置调优</t>
         </is>
       </c>
       <c r="D47" s="28" t="inlineStr">
@@ -2887,9 +2893,9 @@
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>生产查询正常；用户可正常使用</t>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>生产查询正常</t>
         </is>
       </c>
       <c r="F47" s="29" t="inlineStr"/>
@@ -2899,7 +2905,7 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="42" customHeight="1">
+    <row r="48" ht="44" customHeight="1">
       <c r="A48" s="25" t="inlineStr">
         <is>
           <t>W11
@@ -2908,12 +2914,12 @@
       </c>
       <c r="B48" s="33" t="inlineStr">
         <is>
-          <t>D · DevOps/QA</t>
+          <t>D·QA+SLC文档</t>
         </is>
       </c>
       <c r="C48" s="27" t="inlineStr">
         <is>
-          <t>① 上线执行（部署顺序/验证步骤/回退点）② 上线后 48h 值守 ③ 监控告警验证（模拟故障）④ 培训交付：业务方用户培训（查询/导出/附件）</t>
+          <t>① 上线执行（部署顺序/验证/回退点）② 48h 值守 ③ 告警验证 ④ 培训交付：业务用户培训（查询/导出/附件）+ 运维培训辅助</t>
         </is>
       </c>
       <c r="D48" s="28" t="inlineStr">
@@ -2921,9 +2927,9 @@
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>上线 Checklist 全部勾选；培训完成；告警可达</t>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>上线 Checklist 全勾；培训完成；告警可达</t>
         </is>
       </c>
       <c r="F48" s="29" t="inlineStr"/>
@@ -2933,7 +2939,7 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="42" customHeight="1">
+    <row r="49" ht="44" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
         <is>
           <t>W12
@@ -2942,12 +2948,12 @@
       </c>
       <c r="B49" s="26" t="inlineStr">
         <is>
-          <t>A · 架构师</t>
+          <t>A·架构+需求</t>
         </is>
       </c>
       <c r="C49" s="27" t="inlineStr">
         <is>
-          <t>① 运维团队独立操作验证（观察 1 周不介入）② 项目关闭报告（范围/成本/质量/风险总结）③ 后续接入排期确认 ④ Retro 团队复盘</t>
+          <t>① 运维团队独立操作验证 ② 项目关闭报告 ③ 后续接入排期 ④ Retro</t>
         </is>
       </c>
       <c r="D49" s="28" t="inlineStr">
@@ -2955,14 +2961,14 @@
           <t>⚪ ★</t>
         </is>
       </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>运维团队可独立处理日常操作；项目关闭报告签字</t>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>运维可独立日常操作；关闭报告签字</t>
         </is>
       </c>
       <c r="F49" s="29" t="inlineStr">
         <is>
-          <t>运维团队意愿确认</t>
+          <t>运维意愿</t>
         </is>
       </c>
       <c r="G49" s="30" t="inlineStr">
@@ -2971,7 +2977,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="42" customHeight="1">
+    <row r="50" ht="44" customHeight="1">
       <c r="A50" s="25" t="inlineStr">
         <is>
           <t>W12
@@ -2980,12 +2986,12 @@
       </c>
       <c r="B50" s="31" t="inlineStr">
         <is>
-          <t>B · 数据工程</t>
+          <t>B·数据工程</t>
         </is>
       </c>
       <c r="C50" s="27" t="inlineStr">
         <is>
-          <t>① 运维团队知识转移（ETL/Compaction/销毁日常操作）② 第三系统接入准备（读源库结构→勾表→生成任务）③ 技术债清单整理 ④ Retro 参与</t>
+          <t>① 运维知识转移（ETL/销毁）② 第三系统 PoC ③ 技术债清单 ④ Retro</t>
         </is>
       </c>
       <c r="D50" s="28" t="inlineStr">
@@ -2993,9 +2999,9 @@
           <t>⚪ ★</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>运维团队可独立跑 ETL + 销毁；第三系统 PoC</t>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>运维可独立跑 ETL+销毁</t>
         </is>
       </c>
       <c r="F50" s="29" t="inlineStr"/>
@@ -3005,7 +3011,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="42" customHeight="1">
+    <row r="51" ht="44" customHeight="1">
       <c r="A51" s="25" t="inlineStr">
         <is>
           <t>W12
@@ -3014,12 +3020,12 @@
       </c>
       <c r="B51" s="32" t="inlineStr">
         <is>
-          <t>C · 前后端</t>
+          <t>C·全栈+DevOps</t>
         </is>
       </c>
       <c r="C51" s="27" t="inlineStr">
         <is>
-          <t>① 运维团队前端/后端知识转移 ② 第三系统前端配置 ③ 代码整理（README/注释/分支清理）④ Retro 参与</t>
+          <t>① 运维知识转移（部署/前端）② 第三系统配置 ③ 代码整理 ④ Retro</t>
         </is>
       </c>
       <c r="D51" s="28" t="inlineStr">
@@ -3027,9 +3033,9 @@
           <t>⚪ ★</t>
         </is>
       </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>运维团队可处理前端配置变更；代码库整洁</t>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>运维可改前端配置；代码整洁</t>
         </is>
       </c>
       <c r="F51" s="29" t="inlineStr"/>
@@ -3039,7 +3045,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="42" customHeight="1">
+    <row r="52" ht="44" customHeight="1">
       <c r="A52" s="25" t="inlineStr">
         <is>
           <t>W12
@@ -3048,12 +3054,12 @@
       </c>
       <c r="B52" s="33" t="inlineStr">
         <is>
-          <t>D · DevOps/QA</t>
+          <t>D·QA+SLC文档</t>
         </is>
       </c>
       <c r="C52" s="27" t="inlineStr">
         <is>
-          <t>① 项目关闭文档包归档 ② 培训视频录制（查询/运维/接入 SOP）③ 后续接入手册终版 ④ Retro 参与 + 行动项记录</t>
+          <t>① 文档包归档（7 套 + 培训视频 + 接入手册）② 培训视频录制 ③ 后续接入手册终版 ④ Retro + 行动项</t>
         </is>
       </c>
       <c r="D52" s="28" t="inlineStr">
@@ -3061,9 +3067,9 @@
           <t>⚪ ★</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>文档包归档完成；培训视频上传；接入手册终版</t>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>全部文档归档；培训视频上传</t>
         </is>
       </c>
       <c r="F52" s="29" t="inlineStr"/>
@@ -3088,7 +3094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3100,16 +3106,16 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>需你确认/决策的事项（按紧急度排序）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>以下事项在对应时间节点前需要确认，否则会阻塞后续工作。🔴=立即需确认 🟡=Sprint 内确认 ⚪=可延后</t>
+      <c r="A2" s="34" t="inlineStr">
+        <is>
+          <t>🔴=立即（W1 内） 🟡=对应 Sprint 内确认 ⚪=可延后到 Sprint 4~5</t>
         </is>
       </c>
     </row>
@@ -3146,396 +3152,424 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
+          <t>首个接入系统选择</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>W1 D3</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Sprint 0~1 全部开发围绕它</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>建议 Dspot（123 表，最小，元数据表可映射）；不建议 CC</t>
+        </is>
+      </c>
+      <c r="F5" s="36" t="inlineStr"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="35" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>源库网络路径 + 只读账号</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>W1 D3</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>SeaTunnel 无法连源库</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>网络团队确认路由；NAT 固定 IP 给源方白名单</t>
+        </is>
+      </c>
+      <c r="F6" s="36" t="inlineStr"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
           <t>Azure 订阅与权限</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>W1 D1</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>Terraform 无法开始</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>需 Owner 或 Contributor 权限；建议用独立订阅避免影响生产</t>
-        </is>
-      </c>
-      <c r="F5" s="35" t="inlineStr"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Terraform/部署全部阻塞</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>需 Owner/Contributor；建议独立订阅</t>
+        </is>
+      </c>
+      <c r="F7" s="36" t="inlineStr"/>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>源库网络路径（ExpressRoute / VPN）</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>W1 D3</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>SeaTunnel 无法连源库</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>网络团队确认路由已通；NAT 固定 IP 需给源方白名单</t>
-        </is>
-      </c>
-      <c r="F6" s="35" t="inlineStr"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Databricks Premium 工作区</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>W1 D5</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>UC/Serverless/NCC 全依赖</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>新建即 Premium（唯一档）；需 Account Admin</t>
+        </is>
+      </c>
+      <c r="F8" s="36" t="inlineStr"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Databricks Premium 工作区</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>W1 D5</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>UC/Serverless/NCC 全部依赖</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>新建工作区即 Premium（唯一档）；需 Account Admin 初始化</t>
-        </is>
-      </c>
-      <c r="F7" s="35" t="inlineStr"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="34" t="inlineStr">
-        <is>
-          <t>🔴</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>首个接入系统选择</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>W1 D5</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>Sprint 1 的全部开发围绕它</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>建议 Dspot（123 表，最小，有元数据表可映射）；不建议 CC（1253 表，太复杂）</t>
-        </is>
-      </c>
-      <c r="F8" s="35" t="inlineStr"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>业务方需求访谈安排</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>W1 D1~D3</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>BRD 无法启动</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>需业务接口人安排 2~3 场访谈（各 1h）</t>
+        </is>
+      </c>
+      <c r="F9" s="36" t="inlineStr"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>🟡</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>UC 命名：catalog-per-system vs schema-per-system</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>UC 命名：catalog vs schema per system</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>W2 D2</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>权限模型和查询路由</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>建议 catalog-per-system（arch_sysXX），权限继承更干净</t>
-        </is>
-      </c>
-      <c r="F9" s="35" t="inlineStr"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>权限模型 + 查询路由</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>建议 catalog-per-system（arch_sysXX）</t>
+        </is>
+      </c>
+      <c r="F10" s="36" t="inlineStr"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="37" t="inlineStr">
         <is>
           <t>🟡</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>PII 字段标记规则（哪些列要掩码）</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>PII 字段标记规则</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>W4 D3</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>UC 掩码函数 + 前端渲染</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>建议：身份证/手机号/邮箱/地址 → 全掩码；姓名 → 部分掩码（姓+**）</t>
-        </is>
-      </c>
-      <c r="F10" s="35" t="inlineStr"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="36" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>UC 掩码 + 前端渲染</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>身份证/手机/邮箱/地址→全掩码；姓名→姓+**</t>
+        </is>
+      </c>
+      <c r="F11" s="36" t="inlineStr"/>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="37" t="inlineStr">
         <is>
           <t>🟡</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>附件是否需要在线预览（图片/音频/视频）</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>附件在线预览范围</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>W4 D3</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>前端开发量 + 附件代理复杂度</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>图片预览建议做；音频/视频建议 V2 再做（浏览器原生支持有限）</t>
-        </is>
-      </c>
-      <c r="F11" s="35" t="inlineStr"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="36" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>前端开发量</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>图片建议做；音频/视频建议 V2</t>
+        </is>
+      </c>
+      <c r="F12" s="36" t="inlineStr"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>🟡</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>销毁是否需要二级审批</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>销毁是否需二级审批</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>W6 D4</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>销毁流程 UI + 合规</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>建议一级审批（运维经理），合规敏感场景可选二级</t>
-        </is>
-      </c>
-      <c r="F12" s="35" t="inlineStr"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="36" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>销毁 UI + 合规</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>建议一级（运维经理）；敏感场景可选二级</t>
+        </is>
+      </c>
+      <c r="F13" s="36" t="inlineStr"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="37" t="inlineStr">
         <is>
           <t>🟡</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>性能验收标准</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>W6 D4</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>测试通过/不通过判定</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>建议：SERVE 层首屏 P95 &lt; 5s；导出 1 万行 &lt; 10s</t>
-        </is>
-      </c>
-      <c r="F13" s="35" t="inlineStr"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="36" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>测试判定</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>首屏 P95&lt;5s；导出 1 万行 &lt;10s</t>
+        </is>
+      </c>
+      <c r="F14" s="36" t="inlineStr"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="37" t="inlineStr">
         <is>
           <t>🟡</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>UAT 验收标准与签字人</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>W8 D5</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>上线 Go/No-Go</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>建议：5 个核心场景全通过 + 业务负责人签字</t>
-        </is>
-      </c>
-      <c r="F14" s="35" t="inlineStr"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="36" t="inlineStr">
-        <is>
-          <t>🟡</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>生产域名与 TLS 证书</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>W9 D1</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>生产部署</t>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Go/No-Go</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>需网络/安全团队申请（内部域名 or 公网域名）</t>
-        </is>
-      </c>
-      <c r="F15" s="35" t="inlineStr"/>
+          <t>5 场景全过 + 业务负责人签字</t>
+        </is>
+      </c>
+      <c r="F15" s="36" t="inlineStr"/>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="37" t="inlineStr">
         <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>生产域名与 TLS 证书</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>W9 D1</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>生产部署</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>需网络/安全团队申请</t>
+        </is>
+      </c>
+      <c r="F16" s="36" t="inlineStr"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="38" t="inlineStr">
+        <is>
           <t>⚪</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>全量迁移是否需要停机窗口</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>全量迁移是否需停机窗口</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>W9 D5</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>上线计划</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>建议：首次迁移可在周末执行；后续增量不停机</t>
-        </is>
-      </c>
-      <c r="F16" s="35" t="inlineStr"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>首次建议周末执行</t>
+        </is>
+      </c>
+      <c r="F17" s="36" t="inlineStr"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="38" t="inlineStr">
         <is>
           <t>⚪</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>运维移交范围（哪些留开发管）</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>运维移交范围</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>W11 D5</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>项目关闭</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>建议：日常监控/告警/ETL 值守移交运维；代码变更留开发</t>
-        </is>
-      </c>
-      <c r="F17" s="35" t="inlineStr"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="37" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>日常监控/告警/ETL 移交运维；代码变更留开发</t>
+        </is>
+      </c>
+      <c r="F18" s="36" t="inlineStr"/>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="38" t="inlineStr">
         <is>
           <t>⚪</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>后续接入排期（第 3~N 系统）</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>W12 D5</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>项目后续规划</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>建议按优先级排序：Dspot → Eflow → 银河 → BPM → DHT → MA → CC</t>
-        </is>
-      </c>
-      <c r="F18" s="35" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>项目后续</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Dspot→Eflow→银河→BPM→DHT→MA→CC</t>
+        </is>
+      </c>
+      <c r="F19" s="36" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/report/项目执行计划.xlsx
+++ b/report/项目执行计划.xlsx
@@ -860,12 +860,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>① 需求分析：BRD、用户故事、验收标准、业务流程图 ② 技术架构：Azure 组件设计、Databricks 湖仓、UC 权限体系 ③ 代码评审与技术决策 ④ IaC（Terraform）⑤ 与业务方/源方/网络团队的沟通协调</t>
+          <t>① 需求分析：BRD、用户故事、验收标准、业务流程图 ② 技术架构：Azure 组件设计、Databricks 湖仓、UC 权限体系 ③ 代码评审与技术决策 ④ Azure 基础设施搭建（Azure CLI / Bicep）⑤ 与业务方/源方/网络团队的沟通协调</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>需求分析 / Databricks / Terraform / Azure 网络 / 架构设计</t>
+          <t>需求分析 / Databricks / Azure CLI / Bicep / Azure 网络 / 架构设计</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>BRD（业务需求文档）、用户故事地图、验收标准、Terraform 模块、UC 权限矩阵、架构决策记录（ADR）、部署手册</t>
+          <t>BRD（业务需求文档）、用户故事地图、验收标准、部署脚本（Azure CLI / Bicep）、UC 权限矩阵、架构决策记录（ADR）、部署手册</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>① A：BRD 初稿 + 用户故事地图 + 验收标准 + 首系统确认 ② A：Terraform 基线（VNet/AKS/ADLS/SQL DB/Key Vault/Databricks）③ B：Databricks 工作区 + UC 初始化 + 源库 PoC ④ C：项目骨架 + CI/CD 流水线 + Docker 本地开发环境 ⑤ D：测试计划 + 架构图初稿（系统上下文图 + 容器图）</t>
+          <t>① A：BRD 初稿 + 用户故事地图 + 验收标准 + 首系统确认 ② A：Azure 环境搭建（CLI/Bicep：VNet/AKS/ADLS/SQL DB/Key Vault/Databricks）③ B：Databricks 工作区 + UC 初始化 + 源库 PoC ④ C：项目骨架 + CI/CD 流水线 + Docker 本地开发环境 ⑤ D：测试计划 + 架构图初稿（系统上下文图 + 容器图）</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>① A：生产 Terraform apply + 安全评审材料 ② B：首系统全量迁移 + 生产 Jobs 部署 ③ C：生产 AKS 部署 + SSO + 监控接入 ④ D：文档冲刺（用户手册终版 + 运维手册终版 + 架构图终版 + 详细设计终版 + 接口文档终版 + 审批材料包）+ UAT 执行</t>
+          <t>① A：生产环境部署（CLI/Bicep）+ 安全评审材料 ② B：首系统全量迁移 + 生产 Jobs 部署 ③ C：生产 AKS 部署 + SSO + 监控接入 ④ D：文档冲刺（用户手册终版 + 运维手册终版 + 架构图终版 + 详细设计终版 + 接口文档终版 + 审批材料包）+ UAT 执行</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="F7" s="29" t="inlineStr">
         <is>
-          <t>ACR 先建好（A 的 Terraform）</t>
+          <t>ACR 先建好（A 的 CLI 脚本）</t>
         </is>
       </c>
       <c r="G7" s="30" t="inlineStr"/>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>① BRD 评审会（业务方确认）→ 定稿 ② 用户故事地图 + Sprint 1~6 验收标准 ③ Terraform 完整基线：VNet/AKS/ADLS/SQL DB/Key Vault/AppGateway+WAF/PE/NCC ④ IaC 部署到 Dev 环境 ⑤ UC 权限矩阵</t>
+          <t>① BRD 评审会（业务方确认）→ 定稿 ② 用户故事地图 + Sprint 1~6 验收标准 ③ Azure CLI 完整脚本：VNet/AKS/ADLS/SQL DB/Key Vault/AppGateway+WAF/PE/NCC ④ 部署到 Dev 环境 ⑤ UC 权限矩阵</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="C37" s="27" t="inlineStr">
         <is>
-          <t>① 生产 Terraform Review + apply ② 安全评审材料（等保/个保法对照表）③ 生产域名/证书/网络确认 ④ 全量迁移方案</t>
+          <t>① 生产环境部署（CLI/Bicep 脚本执行）② 安全评审材料（等保/个保法对照表）③ 生产域名/证书/网络确认 ④ 全量迁移方案</t>
         </is>
       </c>
       <c r="D37" s="28" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Terraform/部署全部阻塞</t>
+          <t>Azure 环境搭建/部署全部阻塞</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">

--- a/report/项目执行计划.xlsx
+++ b/report/项目执行计划.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="34">
+  <fonts count="39">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -212,6 +212,36 @@
       <color rgb="000F172A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="0064748b"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="000284c7"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00d97706"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00dc2626"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -281,7 +311,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -303,11 +333,12 @@
         <color rgb="00CBD5E1"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -411,6 +442,28 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -778,7 +831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -794,14 +847,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>B2 湖仓归档平台 · 项目执行计划 V2（4 人 × 12 周 Agile）</t>
+          <t>B2 湖仓归档平台 · 项目执行计划 V3（4 人 × 12 周 Agile）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>修订：① C 角色 = 前后端 + DevOps  ② D 角色 = QA + SLC 全生命周期文档  ③ A 角色 = 架构师 + 需求分析  ④ Sprint 0 前两周加需求确认，不是直接搭环境</t>
+          <t>V3 修订：① A = 专职需求分析师（BRD / 用户故事 / 验收标准 / 业务协调），兼架构设计（前期）与前后端功能开发分担（后期）　② 周次与 Sprint 拆为两列　③ 不用 Terraform（Azure CLI / Bicep）</t>
         </is>
       </c>
     </row>
@@ -846,8 +899,9 @@
           <t>备注</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
+      <c r="I4" s="39" t="n"/>
+    </row>
+    <row r="5" ht="62" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>A</t>
@@ -855,17 +909,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>架构师 / 需求分析师 / 技术负责人</t>
+          <t>需求分析师（兼架构 + 开发分担）</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>① 需求分析：BRD、用户故事、验收标准、业务流程图 ② 技术架构：Azure 组件设计、Databricks 湖仓、UC 权限体系 ③ 代码评审与技术决策 ④ Azure 基础设施搭建（Azure CLI / Bicep）⑤ 与业务方/源方/网络团队的沟通协调</t>
+          <t>前期（W1~W4）：① 需求访谈与 BRD ② 用户故事地图与验收标准 ③ 架构设计（Azure 组件 / Databricks 湖仓 / UC 权限体系）④ Azure 环境搭建（CLI/Bicep）。后期（W5~W12）：⑤ 分担前后端功能开发（查询页 / 配置页 / Retention 界面等）⑥ 代码评审 ⑦ 业务方/源方/网络团队协调</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>需求分析 / Databricks / Azure CLI / Bicep / Azure 网络 / 架构设计</t>
+          <t>需求分析 / 业务流程建模 / Databricks / Azure CLI / .NET 或 React（至少一头）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -875,21 +929,22 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>BRD（业务需求文档）、用户故事地图、验收标准、部署脚本（Azure CLI / Bicep）、UC 权限矩阵、架构决策记录（ADR）、部署手册</t>
+          <t>BRD、用户故事地图、验收标准、架构设计文档、Azure 部署脚本、分担开发的功能模块、ADR</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>需要 Azure 订阅 Owner；源库账号与网络路径需多团队协调</t>
+          <t>需求不清晰会阻塞全员；一人身兼三职需严格管理切换时间</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>前 2 周偏需求，之后偏架构；全程做代码评审</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
+          <t>W1~W4 需求+架构为主（60/40）；W5 起转入开发（80% 开发 + 20% 评审协调）</t>
+        </is>
+      </c>
+      <c r="I5" s="39" t="n"/>
+    </row>
+    <row r="6" ht="62" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>B</t>
@@ -930,8 +985,9 @@
           <t>核心开发角色，代码量最大</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
+      <c r="I6" s="39" t="n"/>
+    </row>
+    <row r="7" ht="62" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
           <t>C</t>
@@ -944,7 +1000,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>① .NET 10 后端（元数据/查询代理/附件/权限/审计/调度）② React 前端（配置化查询平台）③ CI/CD 流水线（GitHub Actions）④ Docker 镜像构建 + Helm Chart + AKS 部署 ⑤ SSO（Entra ID OIDC）</t>
+          <t>① .NET 10 后端（元数据/查询代理/附件/权限/审计/调度）② React 前端（配置化查询平台）③ CI/CD 流水线（GitHub Actions）④ Docker 镜像 + Helm Chart + AKS 部署 ⑤ SSO（Entra ID OIDC）</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -959,21 +1015,22 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>后端 API（15+ 接口）、React 前端、CI/CD 流水线、Helm Chart、Docker Compose（本地开发）、SSO 集成</t>
+          <t>后端 API（15+ 接口）、React 前端、CI/CD 流水线、Helm Chart、SSO 集成</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>前后端 + DevOps 一人扛，压力最大；元数据库 35 张表需 A 先建</t>
+          <t>前后端 + DevOps 一人扛，压力最大</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>前 4 周偏 DevOps（搭 CI/CD），之后偏开发；建议 W5 后请求支援或简化 DevOps 任务</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
+          <t>W5 后 A 加入分担开发，压力缓解</t>
+        </is>
+      </c>
+      <c r="I7" s="39" t="n"/>
+    </row>
+    <row r="8" ht="62" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
           <t>D</t>
@@ -986,12 +1043,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>① 测试策略与计划 ② 功能测试 / 集成测试 / 性能测试 / 安全测试 / UAT 协调 ③ 缺陷管理与跟踪 ④ SLC 文档：架构图（C4/时序/部署图）、详细设计文档、接口文档、数据字典、用户手册、运维手册、审批材料包 ⑤ 培训材料与培训交付</t>
+          <t>① 测试策略与计划 ② 功能/集成/性能/安全测试 + UAT 协调 ③ 缺陷管理 ④ SLC 文档：架构图（C4 四层）、详细设计（3 模块）、接口文档、数据字典、用户手册、运维手册、审批材料包 ⑤ 培训材料与交付</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>测试设计 / 自动化测试 / 技术写作 / Visio/Draw.io / 文档管理</t>
+          <t>测试设计 / 自动化测试 / 技术写作 / Draw.io / 文档管理</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -1001,19 +1058,31 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>测试计划、测试用例（80+）、自动化测试套件、测试报告（Sprint 每轮）、架构图（4 张）、详细设计（3 模块）、接口文档、用户手册、运维手册、审批文档包、培训材料</t>
+          <t>测试计划、测试用例（80+）、自动化测试、测试报告、架构图×4、详细设计×3、接口文档、数据字典、用户手册、运维手册、审批包、培训材料</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>文档量极大（≈40% 工作量）；测试数据依赖 B 的链路就绪；审批流程依赖业务方</t>
+          <t>文档量 ≈40% 工作量；测试数据依赖 B 的链路就绪</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>前 3 周偏测试框架搭建，W4 起文档与测试并重，W9~10 文档冲刺</t>
-        </is>
-      </c>
+          <t>前 3 周偏测试框架，W4 起文档与测试并重，W9~10 文档冲刺</t>
+        </is>
+      </c>
+      <c r="I8" s="39" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="39" t="n"/>
+      <c r="B9" s="39" t="n"/>
+      <c r="C9" s="39" t="n"/>
+      <c r="D9" s="39" t="n"/>
+      <c r="E9" s="39" t="n"/>
+      <c r="F9" s="39" t="n"/>
+      <c r="G9" s="39" t="n"/>
+      <c r="H9" s="39" t="n"/>
+      <c r="I9" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1045,7 +1114,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>12 周 Sprint 计划（双周 × 6）· V2 修订版</t>
+          <t>12 周 Sprint 计划（双周 × 6）· V3</t>
         </is>
       </c>
     </row>
@@ -1328,22 +1397,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="38" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>周计划明细 · 4 人 × 12 周（V2 修订版）</t>
+          <t>周计划明细 · 4 人 × 12 周（V3：周次与 Sprint 分列 · A=需求+架构+开发分担）</t>
         </is>
       </c>
     </row>
@@ -1357,1727 +1427,1994 @@
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>周次 / Sprint</t>
+          <t>周次</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>角色</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>本周核心任务</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>产出物 / 验收标准</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>依赖/阻塞</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>会议/仪式</t>
         </is>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
-        <is>
-          <t>W1
-S0</t>
-        </is>
-      </c>
-      <c r="B5" s="26" t="inlineStr">
-        <is>
-          <t>A·架构+需求</t>
-        </is>
-      </c>
-      <c r="C5" s="27" t="inlineStr">
-        <is>
-          <t>① 需求访谈（业务方：查询场景/附件/保留期/权限/审计）② BRD 初稿（业务流程图 + 功能清单 + 非功能需求）③ 首个接入系统选定（建议 Dspot）④ Azure 订阅与权限确认 ⑤ 与网络/源方/安全团队的协调会</t>
-        </is>
-      </c>
-      <c r="D5" s="28" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="B5" s="41" t="inlineStr">
+        <is>
+          <t>Sprint 0</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>A·需求+架构+开发</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>① 需求访谈×3 场（查询场景/附件/保留期/权限/审计）② BRD 初稿：业务流程图+功能清单+非功能需求 ③ 首系统选定（建议 Dspot）④ Azure 订阅确认</t>
+        </is>
+      </c>
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>BRD 初稿（可评审）；首系统确认；订阅就绪</t>
-        </is>
-      </c>
-      <c r="F5" s="29" t="inlineStr">
-        <is>
-          <t>业务方安排访谈时间</t>
-        </is>
-      </c>
-      <c r="G5" s="30" t="inlineStr">
-        <is>
-          <t>Kick-off；需求访谈 × 3 场</t>
-        </is>
-      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>BRD 初稿可评审；首系统确认；订阅就绪</t>
+        </is>
+      </c>
+      <c r="G5" s="29" t="inlineStr">
+        <is>
+          <t>业务方安排访谈</t>
+        </is>
+      </c>
+      <c r="H5" s="30" t="inlineStr">
+        <is>
+          <t>Kick-off；需求访谈×3</t>
+        </is>
+      </c>
+      <c r="I5" s="39" t="n"/>
     </row>
     <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>W1
-S0</t>
-        </is>
-      </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="B6" s="41" t="inlineStr">
+        <is>
+          <t>Sprint 0</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>B·数据工程</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>① Databricks Premium 工作区创建（或确认已有）② UC Catalog 结构设计 ③ Iceberg 分区策略设计 ④ SeaTunnel 本地 PoC 准备</t>
         </is>
       </c>
-      <c r="D6" s="28" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>UC 结构设计文档；SeaTunnel 本地→Iceberg PoC 通过</t>
         </is>
       </c>
-      <c r="F6" s="29" t="inlineStr">
+      <c r="G6" s="29" t="inlineStr">
         <is>
           <t>Databricks 开通周期</t>
         </is>
       </c>
-      <c r="G6" s="30" t="inlineStr"/>
+      <c r="H6" s="30" t="n"/>
+      <c r="I6" s="39" t="n"/>
     </row>
     <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="25" t="inlineStr">
-        <is>
-          <t>W1
-S0</t>
-        </is>
-      </c>
-      <c r="B7" s="32" t="inlineStr">
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>Sprint 0</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>C·全栈+DevOps</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>① .NET 10 项目骨架 + Clean Architecture ② React 前端骨架 + 路由/布局 ③ Docker Compose 本地开发环境（SQL Server + Azurite 模拟 ADLS）④ GitHub Actions CI 骨架（build + test + push ACR）</t>
         </is>
       </c>
-      <c r="D7" s="28" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>本地可开发（docker compose up）；CI 推镜像成功</t>
         </is>
       </c>
-      <c r="F7" s="29" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t>ACR 先建好（A 的 CLI 脚本）</t>
         </is>
       </c>
-      <c r="G7" s="30" t="inlineStr"/>
+      <c r="H7" s="30" t="n"/>
+      <c r="I7" s="39" t="n"/>
     </row>
     <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="25" t="inlineStr">
-        <is>
-          <t>W1
-S0</t>
-        </is>
-      </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="A8" s="40" t="inlineStr">
+        <is>
+          <t>W1</t>
+        </is>
+      </c>
+      <c r="B8" s="41" t="inlineStr">
+        <is>
+          <t>Sprint 0</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>D·QA+SLC文档</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>① 测试计划初稿（功能/集成/性能/安全/UAT）② 架构图初稿：系统上下文图（C4-L1）+ 容器图（C4-L2）③ 项目文档模板定稿（详细设计/接口/用户手册/运维手册 4 套模板）④ UAT 场景清单初稿</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>🟡</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>测试计划初稿；架构图 2 张初稿；文档模板 4 套</t>
         </is>
       </c>
-      <c r="F8" s="29" t="inlineStr">
+      <c r="G8" s="29" t="inlineStr">
         <is>
           <t>A 的 BRD 初稿（了解需求范围）</t>
         </is>
       </c>
-      <c r="G8" s="30" t="inlineStr">
+      <c r="H8" s="30" t="inlineStr">
         <is>
           <t>Kick-off 参加</t>
         </is>
       </c>
+      <c r="I8" s="39" t="n"/>
     </row>
     <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>W2
-S0</t>
-        </is>
-      </c>
-      <c r="B9" s="26" t="inlineStr">
-        <is>
-          <t>A·架构+需求</t>
-        </is>
-      </c>
-      <c r="C9" s="27" t="inlineStr">
-        <is>
-          <t>① BRD 评审会（业务方确认）→ 定稿 ② 用户故事地图 + Sprint 1~6 验收标准 ③ Azure CLI 完整脚本：VNet/AKS/ADLS/SQL DB/Key Vault/AppGateway+WAF/PE/NCC ④ 部署到 Dev 环境 ⑤ UC 权限矩阵</t>
-        </is>
-      </c>
-      <c r="D9" s="28" t="inlineStr">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="B9" s="41" t="inlineStr">
+        <is>
+          <t>Sprint 0</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>A·需求+架构+开发</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>① BRD 评审→定稿签字 ② 用户故事地图 + Sprint 1~6 验收标准 ③ 架构设计定稿（组件清单/网络拓扑/UC 结构）④ Azure CLI 完整脚本→Dev 部署（VNet/AKS/ADLS/SQL/KeyVault/AGW/PE/NCC）</t>
+        </is>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>BRD 签字；Dev 环境全套组件部署成功；UC 权限矩阵</t>
-        </is>
-      </c>
-      <c r="F9" s="29" t="inlineStr">
-        <is>
-          <t>网络团队 NCC 路由；BRD 评审会业务方到场</t>
-        </is>
-      </c>
-      <c r="G9" s="30" t="inlineStr">
-        <is>
-          <t>BRD 评审会；Sprint 0 Review；Sprint 1 Planning</t>
-        </is>
-      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>BRD 签字；架构文档；Dev 全套组件就绪</t>
+        </is>
+      </c>
+      <c r="G9" s="29" t="inlineStr">
+        <is>
+          <t>网络团队 NCC 路由</t>
+        </is>
+      </c>
+      <c r="H9" s="30" t="inlineStr">
+        <is>
+          <t>BRD 评审；S0 Review；S1 Planning</t>
+        </is>
+      </c>
+      <c r="I9" s="39" t="n"/>
     </row>
     <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="25" t="inlineStr">
-        <is>
-          <t>W2
-S0</t>
-        </is>
-      </c>
-      <c r="B10" s="31" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="B10" s="41" t="inlineStr">
+        <is>
+          <t>Sprint 0</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t>B·数据工程</t>
         </is>
       </c>
-      <c r="C10" s="27" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>① SeaTunnel→Iceberg PoC（连真实源库 SQL Server，Dspot）② RAW 层表创建 + 写入验证 ③ SQL Warehouse 查询验证 ④ PoC 结论记录</t>
         </is>
       </c>
-      <c r="D10" s="28" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>PoC 端到端：源库→SeaTunnel→Iceberg→SQL Warehouse 可查</t>
         </is>
       </c>
-      <c r="F10" s="29" t="inlineStr">
+      <c r="G10" s="29" t="inlineStr">
         <is>
           <t>源库只读账号 + NAT IP 白名单</t>
         </is>
       </c>
-      <c r="G10" s="30" t="inlineStr">
+      <c r="H10" s="30" t="inlineStr">
         <is>
           <t>Sprint 0 Review</t>
         </is>
       </c>
+      <c r="I10" s="39" t="n"/>
     </row>
     <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="25" t="inlineStr">
-        <is>
-          <t>W2
-S0</t>
-        </is>
-      </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="A11" s="40" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="B11" s="41" t="inlineStr">
+        <is>
+          <t>Sprint 0</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="inlineStr">
         <is>
           <t>C·全栈+DevOps</t>
         </is>
       </c>
-      <c r="C11" s="27" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>① CI/CD 完整流水线（自动测试→构建→推镜像→Helm 部署 AKS Dev）② Entra ID 应用注册 + OIDC ③ 后端认证中间件 ④ 前端登录页 + 系统列表页 ⑤ Helm Chart 初版</t>
         </is>
       </c>
-      <c r="D11" s="28" t="inlineStr">
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>Pipeline 端到端自动部署成功；浏览器可登录看到列表页</t>
         </is>
       </c>
-      <c r="F11" s="29" t="inlineStr">
+      <c r="G11" s="29" t="inlineStr">
         <is>
           <t>Entra ID 管理员；AKS Dev 就绪</t>
         </is>
       </c>
-      <c r="G11" s="30" t="inlineStr">
+      <c r="H11" s="30" t="inlineStr">
         <is>
           <t>Sprint 0 Review</t>
         </is>
       </c>
+      <c r="I11" s="39" t="n"/>
     </row>
     <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="25" t="inlineStr">
-        <is>
-          <t>W2
-S0</t>
-        </is>
-      </c>
-      <c r="B12" s="33" t="inlineStr">
+      <c r="A12" s="40" t="inlineStr">
+        <is>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="B12" s="41" t="inlineStr">
+        <is>
+          <t>Sprint 0</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>D·QA+SLC文档</t>
         </is>
       </c>
-      <c r="C12" s="27" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>① 架构图完善：组件图（C4-L3）+ 部署图（Azure 拓扑）② 接口文档初稿（API 列表 + 请求/响应示例）③ 测试环境搭建（测试数据准备方案）④ 需求可追溯矩阵（BRD→测试用例映射）</t>
         </is>
       </c>
-      <c r="D12" s="28" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>🟡</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>架构图 4 张初稿（上下文/容器/组件/部署）；接口文档初稿</t>
         </is>
       </c>
-      <c r="F12" s="29" t="inlineStr">
+      <c r="G12" s="29" t="inlineStr">
         <is>
           <t>A 的 BRD 定稿；C 的 API 骨架</t>
         </is>
       </c>
-      <c r="G12" s="30" t="inlineStr">
+      <c r="H12" s="30" t="inlineStr">
         <is>
           <t>Sprint 0 Review</t>
         </is>
       </c>
+      <c r="I12" s="39" t="n"/>
     </row>
     <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="25" t="inlineStr">
-        <is>
-          <t>W3
-S1</t>
-        </is>
-      </c>
-      <c r="B13" s="26" t="inlineStr">
-        <is>
-          <t>A·架构+需求</t>
-        </is>
-      </c>
-      <c r="C13" s="27" t="inlineStr">
-        <is>
-          <t>① 代码评审（B 的生成器 + C 的 API）② Databricks Jobs API 触发方案（后端 REST 调用）③ 查询 SQL 安全方案（表名白名单/参数化）④ 用户故事拆分到 Sprint 1 任务</t>
-        </is>
-      </c>
-      <c r="D13" s="28" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="B13" s="42" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>A·需求+架构+开发</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>① Sprint 2 需求澄清（附件/掩码/多表 JOIN 细节）② 代码评审（B 生成器 + C API）③ Jobs API 触发方案 + SQL 安全方案 ④ 开始接手前端查询配置页开发</t>
+        </is>
+      </c>
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t>🟡</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>ADR：Jobs 触发方式；SQL 安全评审意见</t>
-        </is>
-      </c>
-      <c r="F13" s="29" t="inlineStr"/>
-      <c r="G13" s="30" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 2 需求就绪；ADR×2；查询配置页开发中</t>
+        </is>
+      </c>
+      <c r="G13" s="29" t="inlineStr"/>
+      <c r="H13" s="30" t="inlineStr">
         <is>
           <t>Daily Standup</t>
         </is>
       </c>
+      <c r="I13" s="39" t="n"/>
     </row>
     <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="25" t="inlineStr">
-        <is>
-          <t>W3
-S1</t>
-        </is>
-      </c>
-      <c r="B14" s="31" t="inlineStr">
+      <c r="A14" s="40" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="B14" s="42" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="C14" s="31" t="inlineStr">
         <is>
           <t>B·数据工程</t>
         </is>
       </c>
-      <c r="C14" s="27" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>① SeaTunnel 配置生成器（读 source_table→生成 .conf→提交 K8s Job）② RAW→LAKE 直达转换 ③ 触发方式（后端调 K8s API 或 ADF）</t>
         </is>
       </c>
-      <c r="D14" s="28" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>配置生成器跑通：选表→生成任务→数据进 RAW</t>
         </is>
       </c>
-      <c r="F14" s="29" t="inlineStr">
+      <c r="G14" s="29" t="inlineStr">
         <is>
           <t>元数据库有测试数据</t>
         </is>
       </c>
-      <c r="G14" s="30" t="inlineStr"/>
+      <c r="H14" s="30" t="n"/>
+      <c r="I14" s="39" t="n"/>
     </row>
     <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="25" t="inlineStr">
-        <is>
-          <t>W3
-S1</t>
-        </is>
-      </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="A15" s="40" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="B15" s="42" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
         <is>
           <t>C·全栈+DevOps</t>
         </is>
       </c>
-      <c r="C15" s="27" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>① 核心 CRUD API：系统/源库/表清单/查询配置 ② 查询代理 API（→SQL Warehouse）③ Helm Chart 完善（后端+前端+Service+Ingress）④ 前端：查询配置管理页</t>
         </is>
       </c>
-      <c r="D15" s="28" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>Postman API 全通；前端可配置查询字段</t>
         </is>
       </c>
-      <c r="F15" s="29" t="inlineStr">
+      <c r="G15" s="29" t="inlineStr">
         <is>
           <t>SQL Warehouse 连接串</t>
         </is>
       </c>
-      <c r="G15" s="30" t="inlineStr"/>
+      <c r="H15" s="30" t="n"/>
+      <c r="I15" s="39" t="n"/>
     </row>
     <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="25" t="inlineStr">
-        <is>
-          <t>W3
-S1</t>
-        </is>
-      </c>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="A16" s="40" t="inlineStr">
+        <is>
+          <t>W3</t>
+        </is>
+      </c>
+      <c r="B16" s="42" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>D·QA+SLC文档</t>
         </is>
       </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>① 单元测试框架搭建（xUnit + Mock）② API 集成测试（10 核心场景）③ E2E 测试骨架（Playwright）④ 详细设计文档初稿：应用层（API 设计 + 类图 + 时序图）</t>
         </is>
       </c>
-      <c r="D16" s="28" t="inlineStr">
+      <c r="E16" s="28" t="inlineStr">
         <is>
           <t>🟡</t>
         </is>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>CI 里自动跑测试 &gt;80%；应用层详细设计初稿</t>
         </is>
       </c>
-      <c r="F16" s="29" t="inlineStr">
+      <c r="G16" s="29" t="inlineStr">
         <is>
           <t>C 的 API 稳定</t>
         </is>
       </c>
-      <c r="G16" s="30" t="inlineStr"/>
+      <c r="H16" s="30" t="n"/>
+      <c r="I16" s="39" t="n"/>
     </row>
     <row r="17" ht="44" customHeight="1">
-      <c r="A17" s="25" t="inlineStr">
-        <is>
-          <t>W4
-S1</t>
-        </is>
-      </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>A·架构+需求</t>
-        </is>
-      </c>
-      <c r="C17" s="27" t="inlineStr">
-        <is>
-          <t>① 端到端联调 ② UC 权限落地（SP-query/SP-audit）③ 性能基线测试（10 万行 &lt;3s）④ Sprint 1 验收准备 ⑤ 下一个 Sprint 的需求澄清（附件/掩码/多表 JOIN）</t>
-        </is>
-      </c>
-      <c r="D17" s="28" t="inlineStr">
+      <c r="A17" s="40" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="B17" s="42" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>A·需求+架构+开发</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>① 端到端联调支撑 ② UC 权限落地（SP-query/SP-audit）③ 完成查询配置页开发并提测 ④ Sprint 3 需求澄清（Retention/审批/通知）</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="inlineStr">
+        <is>
+          <t>🔴 ★</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>UC GRANT 成功；查询配置页上线；S3 需求就绪</t>
+        </is>
+      </c>
+      <c r="G17" s="29" t="inlineStr">
+        <is>
+          <t>B 数据链路</t>
+        </is>
+      </c>
+      <c r="H17" s="30" t="inlineStr">
+        <is>
+          <t>S1 Review ★；S2 Planning</t>
+        </is>
+      </c>
+      <c r="I17" s="39" t="n"/>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="40" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="B18" s="42" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="inlineStr">
+        <is>
+          <t>B·数据工程</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>① 端到端联调：源→SeaTunnel→RAW→LAKE→查询代理 ② 对账脚本（行数+校验和）③ Compaction 初版 ④ 增量方案确认</t>
+        </is>
+      </c>
+      <c r="E18" s="28" t="inlineStr">
+        <is>
+          <t>🔴 ★</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>1 张表端到端：源→查询页可查</t>
+        </is>
+      </c>
+      <c r="G18" s="29" t="n"/>
+      <c r="H18" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 1 Review</t>
+        </is>
+      </c>
+      <c r="I18" s="39" t="n"/>
+    </row>
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="40" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="B19" s="42" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>C·全栈+DevOps</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>① 前端查询页（元数据驱动渲染：筛选/表格/分页）② 查询结果导出 CSV ③ 附件 URL 生成框架 ④ 前后端联调</t>
+        </is>
+      </c>
+      <c r="E19" s="28" t="inlineStr">
+        <is>
+          <t>🔴 ★</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>登录→选系统→查表→看到数据</t>
+        </is>
+      </c>
+      <c r="G19" s="29" t="inlineStr">
+        <is>
+          <t>查询代理就绪</t>
+        </is>
+      </c>
+      <c r="H19" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 1 Review ★ MVP 演示</t>
+        </is>
+      </c>
+      <c r="I19" s="39" t="n"/>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="40" t="inlineStr">
+        <is>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="B20" s="42" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="C20" s="33" t="inlineStr">
+        <is>
+          <t>D·QA+SLC文档</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>① 集成测试执行 + Bug 跟踪 ② 详细设计初稿：数据层（Iceberg 表结构 + 四层转换逻辑 + ER 图）③ Sprint 1 测试报告 ④ 架构图更新（反映实际部署）</t>
+        </is>
+      </c>
+      <c r="E20" s="28" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>测试报告；数据层详细设计初稿</t>
+        </is>
+      </c>
+      <c r="G20" s="29" t="n"/>
+      <c r="H20" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 1 Review</t>
+        </is>
+      </c>
+      <c r="I20" s="39" t="n"/>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="40" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="B21" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>A·需求+架构+开发</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>① 开发分担：前端附件预览模块（图片/音频/视频）② 代码评审（四层 SQL + 掩码函数）③ Sprint 4 需求澄清（UAT 场景/审批流程）</t>
+        </is>
+      </c>
+      <c r="E21" s="28" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>UC GRANT 成功；性能基线报告；Sprint 2 需求就绪</t>
-        </is>
-      </c>
-      <c r="F17" s="29" t="inlineStr">
-        <is>
-          <t>B 数据链路就绪</t>
-        </is>
-      </c>
-      <c r="G17" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 1 Review ★ MVP 演示；Sprint 2 Planning</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="25" t="inlineStr">
-        <is>
-          <t>W4
-S1</t>
-        </is>
-      </c>
-      <c r="B18" s="31" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>附件预览模块提测；S4 需求就绪</t>
+        </is>
+      </c>
+      <c r="G21" s="29" t="inlineStr">
+        <is>
+          <t>B 的 SERVE 数据</t>
+        </is>
+      </c>
+      <c r="H21" s="30" t="inlineStr">
+        <is>
+          <t>Daily Standup</t>
+        </is>
+      </c>
+      <c r="I21" s="39" t="n"/>
+    </row>
+    <row r="22" ht="44" customHeight="1">
+      <c r="A22" s="40" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="B22" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="inlineStr">
         <is>
           <t>B·数据工程</t>
         </is>
       </c>
-      <c r="C18" s="27" t="inlineStr">
-        <is>
-          <t>① 端到端联调：源→SeaTunnel→RAW→LAKE→查询代理 ② 对账脚本（行数+校验和）③ Compaction 初版 ④ 增量方案确认</t>
-        </is>
-      </c>
-      <c r="D18" s="28" t="inlineStr">
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>① CURATED：类型统一/SHA-256/分区归约 ② LAKE：建模+生命周期分区 ③ SERVE：物化+Z-Order ④ 四层 Jobs（多 Task 依赖）</t>
+        </is>
+      </c>
+      <c r="E22" s="28" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>四层转换 Jobs 跑通；SERVE 可查</t>
+        </is>
+      </c>
+      <c r="G22" s="29" t="inlineStr">
+        <is>
+          <t>A 的层设计评审</t>
+        </is>
+      </c>
+      <c r="H22" s="30" t="n"/>
+      <c r="I22" s="39" t="n"/>
+    </row>
+    <row r="23" ht="44" customHeight="1">
+      <c r="A23" s="40" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="B23" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>C·全栈+DevOps</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>① 前端配置化查询完善（动态列/排序/筛选联动）② 附件预览：图片/音频/视频 ③ 权限渲染（无权限列隐藏）④ CI/CD 完善（多环境 Dev/Staging）</t>
+        </is>
+      </c>
+      <c r="E23" s="28" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>前端全功能可用；附件可预览</t>
+        </is>
+      </c>
+      <c r="G23" s="29" t="inlineStr">
+        <is>
+          <t>B 的 SERVE 数据</t>
+        </is>
+      </c>
+      <c r="H23" s="30" t="n"/>
+      <c r="I23" s="39" t="n"/>
+    </row>
+    <row r="24" ht="44" customHeight="1">
+      <c r="A24" s="40" t="inlineStr">
+        <is>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="B24" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C24" s="33" t="inlineStr">
+        <is>
+          <t>D·QA+SLC文档</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="inlineStr">
+        <is>
+          <t>① 功能测试用例扩充（50+ 场景）② 自动化测试覆盖率 &gt;60% ③ 安全测试（SQL 注入/XSS/越权）④ 详细设计：安全层（认证/授权/加密/审计 + 掩码函数时序图）</t>
+        </is>
+      </c>
+      <c r="E24" s="28" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>测试用例 50+；安全测试报告；安全层设计初稿</t>
+        </is>
+      </c>
+      <c r="G24" s="29" t="inlineStr">
+        <is>
+          <t>C 的功能可用</t>
+        </is>
+      </c>
+      <c r="H24" s="30" t="n"/>
+      <c r="I24" s="39" t="n"/>
+    </row>
+    <row r="25" ht="44" customHeight="1">
+      <c r="A25" s="40" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="B25" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>A·需求+架构+开发</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="inlineStr">
+        <is>
+          <t>① 开发分担：多表 JOIN 前端渲染 ② 权限端到端测试组织（明文/掩码）③ 第二系统选型确认 + 源库协调 ④ Sprint 2 验收支撑</t>
+        </is>
+      </c>
+      <c r="E25" s="28" t="inlineStr">
         <is>
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>1 张表端到端：源→查询页可查</t>
-        </is>
-      </c>
-      <c r="F18" s="29" t="inlineStr"/>
-      <c r="G18" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 1 Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="44" customHeight="1">
-      <c r="A19" s="25" t="inlineStr">
-        <is>
-          <t>W4
-S1</t>
-        </is>
-      </c>
-      <c r="B19" s="32" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>JOIN 渲染提测；第二系统确认</t>
+        </is>
+      </c>
+      <c r="G25" s="29" t="inlineStr"/>
+      <c r="H25" s="30" t="inlineStr">
+        <is>
+          <t>S2 Review；S3 Planning</t>
+        </is>
+      </c>
+      <c r="I25" s="39" t="n"/>
+    </row>
+    <row r="26" ht="44" customHeight="1">
+      <c r="A26" s="40" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="B26" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="inlineStr">
+        <is>
+          <t>B·数据工程</t>
+        </is>
+      </c>
+      <c r="D26" s="27" t="inlineStr">
+        <is>
+          <t>① 附件：Storage Mover + attachment_index + SHA-256 ② UC 掩码函数部署 ③ Compaction/VACUUM 定时 ④ 性能优化</t>
+        </is>
+      </c>
+      <c r="E26" s="28" t="inlineStr">
+        <is>
+          <t>🔴 ★</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>附件端到端；掩码查询正常</t>
+        </is>
+      </c>
+      <c r="G26" s="29" t="inlineStr">
+        <is>
+          <t>Storage Mover 网络</t>
+        </is>
+      </c>
+      <c r="H26" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 2 Review</t>
+        </is>
+      </c>
+      <c r="I26" s="39" t="n"/>
+    </row>
+    <row r="27" ht="44" customHeight="1">
+      <c r="A27" s="40" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="B27" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="inlineStr">
         <is>
           <t>C·全栈+DevOps</t>
         </is>
       </c>
-      <c r="C19" s="27" t="inlineStr">
-        <is>
-          <t>① 前端查询页（元数据驱动渲染：筛选/表格/分页）② 查询结果导出 CSV ③ 附件 URL 生成框架 ④ 前后端联调</t>
-        </is>
-      </c>
-      <c r="D19" s="28" t="inlineStr">
+      <c r="D27" s="27" t="inlineStr">
+        <is>
+          <t>① 多表 JOIN（query_join→动态 SQL）② 下钻（drill_config→父子导航）③ 导出完善 ④ Bug 修复</t>
+        </is>
+      </c>
+      <c r="E27" s="28" t="inlineStr">
         <is>
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>登录→选系统→查表→看到数据</t>
-        </is>
-      </c>
-      <c r="F19" s="29" t="inlineStr">
-        <is>
-          <t>查询代理就绪</t>
-        </is>
-      </c>
-      <c r="G19" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 1 Review ★ MVP 演示</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="44" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>W4
-S1</t>
-        </is>
-      </c>
-      <c r="B20" s="33" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>JOIN+下钻+掩码隐藏全部可用</t>
+        </is>
+      </c>
+      <c r="G27" s="29" t="n"/>
+      <c r="H27" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 2 Review</t>
+        </is>
+      </c>
+      <c r="I27" s="39" t="n"/>
+    </row>
+    <row r="28" ht="44" customHeight="1">
+      <c r="A28" s="40" t="inlineStr">
+        <is>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="B28" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C28" s="33" t="inlineStr">
         <is>
           <t>D·QA+SLC文档</t>
         </is>
       </c>
-      <c r="C20" s="27" t="inlineStr">
-        <is>
-          <t>① 集成测试执行 + Bug 跟踪 ② 详细设计初稿：数据层（Iceberg 表结构 + 四层转换逻辑 + ER 图）③ Sprint 1 测试报告 ④ 架构图更新（反映实际部署）</t>
-        </is>
-      </c>
-      <c r="D20" s="28" t="inlineStr">
+      <c r="D28" s="27" t="inlineStr">
+        <is>
+          <t>① 功能测试全量执行 ② 性能测试（100 万行 P95&lt;5s）③ 详细设计终稿（3 模块合稿：应用+数据+安全）④ 接口文档完善 ⑤ Sprint 2 测试报告</t>
+        </is>
+      </c>
+      <c r="E28" s="28" t="inlineStr">
         <is>
           <t>🟡</t>
         </is>
       </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>测试报告；数据层详细设计初稿</t>
-        </is>
-      </c>
-      <c r="F20" s="29" t="inlineStr"/>
-      <c r="G20" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 1 Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="44" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>W5
-S2</t>
-        </is>
-      </c>
-      <c r="B21" s="26" t="inlineStr">
-        <is>
-          <t>A·架构+需求</t>
-        </is>
-      </c>
-      <c r="C21" s="27" t="inlineStr">
-        <is>
-          <t>① CURATED/SERVE 设计评审 ② UC 掩码函数设计（aes_encrypt + is_account_group_member）③ Key Vault 密钥体系 ④ 附件网络路径确认 ⑤ 代码评审</t>
-        </is>
-      </c>
-      <c r="D21" s="28" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>性能报告；详细设计 3 模块合稿</t>
+        </is>
+      </c>
+      <c r="G28" s="29" t="inlineStr">
+        <is>
+          <t>性能数据由 B 准备</t>
+        </is>
+      </c>
+      <c r="H28" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 2 Review</t>
+        </is>
+      </c>
+      <c r="I28" s="39" t="n"/>
+    </row>
+    <row r="29" ht="44" customHeight="1">
+      <c r="A29" s="40" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B29" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>A·需求+架构+开发</t>
+        </is>
+      </c>
+      <c r="D29" s="27" t="inlineStr">
+        <is>
+          <t>① 开发分担：Retention 策略配置界面（后端 API + 前端）② Retention 流程评审（含销毁审批设计）③ 业务方确认保留期合规底线</t>
+        </is>
+      </c>
+      <c r="E29" s="28" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>掩码函数 ADR；密钥体系设计文档</t>
-        </is>
-      </c>
-      <c r="F21" s="29" t="inlineStr">
-        <is>
-          <t>Key Vault 权限</t>
-        </is>
-      </c>
-      <c r="G21" s="30" t="inlineStr">
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Retention 界面开发中；流程评审通过</t>
+        </is>
+      </c>
+      <c r="G29" s="29" t="inlineStr">
+        <is>
+          <t>法务保留期底线</t>
+        </is>
+      </c>
+      <c r="H29" s="30" t="inlineStr">
         <is>
           <t>Daily Standup</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="44" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
-        <is>
-          <t>W5
-S2</t>
-        </is>
-      </c>
-      <c r="B22" s="31" t="inlineStr">
+      <c r="I29" s="39" t="n"/>
+    </row>
+    <row r="30" ht="44" customHeight="1">
+      <c r="A30" s="40" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B30" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="inlineStr">
         <is>
           <t>B·数据工程</t>
         </is>
       </c>
-      <c r="C22" s="27" t="inlineStr">
-        <is>
-          <t>① CURATED：类型统一/SHA-256/分区归约 ② LAKE：建模+生命周期分区 ③ SERVE：物化+Z-Order ④ 四层 Jobs（多 Task 依赖）</t>
-        </is>
-      </c>
-      <c r="D22" s="28" t="inlineStr">
+      <c r="D30" s="27" t="inlineStr">
+        <is>
+          <t>① 到期扫描 Job ② DROP PARTITION + VACUUM（Databricks 原生 cron）③ 销毁结果回写 + 审计 ④ 通知集成</t>
+        </is>
+      </c>
+      <c r="E30" s="28" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
       </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>四层转换 Jobs 跑通；SERVE 可查</t>
-        </is>
-      </c>
-      <c r="F22" s="29" t="inlineStr">
-        <is>
-          <t>A 的层设计评审</t>
-        </is>
-      </c>
-      <c r="G22" s="30" t="inlineStr"/>
-    </row>
-    <row r="23" ht="44" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
-        <is>
-          <t>W5
-S2</t>
-        </is>
-      </c>
-      <c r="B23" s="32" t="inlineStr">
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>测试环境完整销毁回路跑通</t>
+        </is>
+      </c>
+      <c r="G30" s="29" t="n"/>
+      <c r="H30" s="30" t="n"/>
+      <c r="I30" s="39" t="n"/>
+    </row>
+    <row r="31" ht="44" customHeight="1">
+      <c r="A31" s="40" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B31" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="inlineStr">
         <is>
           <t>C·全栈+DevOps</t>
         </is>
       </c>
-      <c r="C23" s="27" t="inlineStr">
-        <is>
-          <t>① 前端配置化查询完善（动态列/排序/筛选联动）② 附件预览：图片/音频/视频 ③ 权限渲染（无权限列隐藏）④ CI/CD 完善（多环境 Dev/Staging）</t>
-        </is>
-      </c>
-      <c r="D23" s="28" t="inlineStr">
+      <c r="D31" s="27" t="inlineStr">
+        <is>
+          <t>① Retention 策略配置界面 ② 销毁审批界面 ③ 通知中心（站内+邮件）④ Dashboard（同步活跃度图表）</t>
+        </is>
+      </c>
+      <c r="E31" s="28" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>前端全功能可用；附件可预览</t>
-        </is>
-      </c>
-      <c r="F23" s="29" t="inlineStr">
-        <is>
-          <t>B 的 SERVE 数据</t>
-        </is>
-      </c>
-      <c r="G23" s="30" t="inlineStr"/>
-    </row>
-    <row r="24" ht="44" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
-        <is>
-          <t>W5
-S2</t>
-        </is>
-      </c>
-      <c r="B24" s="33" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>Retention 全流程 UI 可操作</t>
+        </is>
+      </c>
+      <c r="G31" s="29" t="inlineStr">
+        <is>
+          <t>B 的销毁 Job</t>
+        </is>
+      </c>
+      <c r="H31" s="30" t="n"/>
+      <c r="I31" s="39" t="n"/>
+    </row>
+    <row r="32" ht="44" customHeight="1">
+      <c r="A32" s="40" t="inlineStr">
+        <is>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B32" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C32" s="33" t="inlineStr">
         <is>
           <t>D·QA+SLC文档</t>
         </is>
       </c>
-      <c r="C24" s="27" t="inlineStr">
-        <is>
-          <t>① 功能测试用例扩充（50+ 场景）② 自动化测试覆盖率 &gt;60% ③ 安全测试（SQL 注入/XSS/越权）④ 详细设计：安全层（认证/授权/加密/审计 + 掩码函数时序图）</t>
-        </is>
-      </c>
-      <c r="D24" s="28" t="inlineStr">
+      <c r="D32" s="27" t="inlineStr">
+        <is>
+          <t>① 销毁流程 E2E 测试 ② 通知功能测试 ③ Dashboard 数据验证 ④ 用户手册初稿（含截图 30+）⑤ 第二系统接入测试准备</t>
+        </is>
+      </c>
+      <c r="E32" s="28" t="inlineStr">
         <is>
           <t>🟡</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>测试用例 50+；安全测试报告；安全层设计初稿</t>
-        </is>
-      </c>
-      <c r="F24" s="29" t="inlineStr">
-        <is>
-          <t>C 的功能可用</t>
-        </is>
-      </c>
-      <c r="G24" s="30" t="inlineStr"/>
-    </row>
-    <row r="25" ht="44" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
-        <is>
-          <t>W6
-S2</t>
-        </is>
-      </c>
-      <c r="B25" s="26" t="inlineStr">
-        <is>
-          <t>A·架构+需求</t>
-        </is>
-      </c>
-      <c r="C25" s="27" t="inlineStr">
-        <is>
-          <t>① 代码评审 ② 权限端到端测试（明文/掩码）③ 附件链路联调 ④ Sprint 2 验收 ⑤ 第二系统选型确认 + 源库协调</t>
-        </is>
-      </c>
-      <c r="D25" s="28" t="inlineStr">
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>销毁 E2E 报告；用户手册初稿（50% 完成）</t>
+        </is>
+      </c>
+      <c r="G32" s="29" t="n"/>
+      <c r="H32" s="30" t="n"/>
+      <c r="I32" s="39" t="n"/>
+    </row>
+    <row r="33" ht="44" customHeight="1">
+      <c r="A33" s="40" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="B33" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>A·需求+架构+开发</t>
+        </is>
+      </c>
+      <c r="D33" s="27" t="inlineStr">
+        <is>
+          <t>① 完成 Retention + 审批界面并提测 ② 第二系统零代码接入验证（标准流程走一遍）③ 集成测试统筹</t>
+        </is>
+      </c>
+      <c r="E33" s="28" t="inlineStr">
         <is>
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>掩码演示通过；附件端到端预览；第二系统确认</t>
-        </is>
-      </c>
-      <c r="F25" s="29" t="inlineStr"/>
-      <c r="G25" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 2 Review；Sprint 3 Planning</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="44" customHeight="1">
-      <c r="A26" s="25" t="inlineStr">
-        <is>
-          <t>W6
-S2</t>
-        </is>
-      </c>
-      <c r="B26" s="31" t="inlineStr">
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>第二系统零代码接入 &lt;2h；Retention 全流程可测</t>
+        </is>
+      </c>
+      <c r="G33" s="29" t="inlineStr">
+        <is>
+          <t>第二系统账号</t>
+        </is>
+      </c>
+      <c r="H33" s="30" t="inlineStr">
+        <is>
+          <t>S3 Review；S4 Planning</t>
+        </is>
+      </c>
+      <c r="I33" s="39" t="n"/>
+    </row>
+    <row r="34" ht="44" customHeight="1">
+      <c r="A34" s="40" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="B34" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C34" s="31" t="inlineStr">
         <is>
           <t>B·数据工程</t>
         </is>
       </c>
-      <c r="C26" s="27" t="inlineStr">
-        <is>
-          <t>① 附件：Storage Mover + attachment_index + SHA-256 ② UC 掩码函数部署 ③ Compaction/VACUUM 定时 ④ 性能优化</t>
-        </is>
-      </c>
-      <c r="D26" s="28" t="inlineStr">
+      <c r="D34" s="27" t="inlineStr">
+        <is>
+          <t>① 第二系统 SeaTunnel+四层+SERVE ② 两系统联邦查询 ③ 性能调优</t>
+        </is>
+      </c>
+      <c r="E34" s="28" t="inlineStr">
         <is>
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>附件端到端；掩码查询正常</t>
-        </is>
-      </c>
-      <c r="F26" s="29" t="inlineStr">
-        <is>
-          <t>Storage Mover 网络</t>
-        </is>
-      </c>
-      <c r="G26" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 2 Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="44" customHeight="1">
-      <c r="A27" s="25" t="inlineStr">
-        <is>
-          <t>W6
-S2</t>
-        </is>
-      </c>
-      <c r="B27" s="32" t="inlineStr">
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>第二系统端到端可查</t>
+        </is>
+      </c>
+      <c r="G34" s="29" t="n"/>
+      <c r="H34" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 3 Review</t>
+        </is>
+      </c>
+      <c r="I34" s="39" t="n"/>
+    </row>
+    <row r="35" ht="44" customHeight="1">
+      <c r="A35" s="40" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="B35" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C35" s="32" t="inlineStr">
         <is>
           <t>C·全栈+DevOps</t>
         </is>
       </c>
-      <c r="C27" s="27" t="inlineStr">
-        <is>
-          <t>① 多表 JOIN（query_join→动态 SQL）② 下钻（drill_config→父子导航）③ 导出完善 ④ Bug 修复</t>
-        </is>
-      </c>
-      <c r="D27" s="28" t="inlineStr">
+      <c r="D35" s="27" t="inlineStr">
+        <is>
+          <t>① 第二系统前端配置（零代码）② 跨系统联邦查询测试 ③ 前端性能优化 ④ Bug 修复</t>
+        </is>
+      </c>
+      <c r="E35" s="28" t="inlineStr">
         <is>
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>JOIN+下钻+掩码隐藏全部可用</t>
-        </is>
-      </c>
-      <c r="F27" s="29" t="inlineStr"/>
-      <c r="G27" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 2 Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="44" customHeight="1">
-      <c r="A28" s="25" t="inlineStr">
-        <is>
-          <t>W6
-S2</t>
-        </is>
-      </c>
-      <c r="B28" s="33" t="inlineStr">
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>第二系统查询页零代码上线</t>
+        </is>
+      </c>
+      <c r="G35" s="29" t="n"/>
+      <c r="H35" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 3 Review</t>
+        </is>
+      </c>
+      <c r="I35" s="39" t="n"/>
+    </row>
+    <row r="36" ht="44" customHeight="1">
+      <c r="A36" s="40" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="B36" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C36" s="33" t="inlineStr">
         <is>
           <t>D·QA+SLC文档</t>
         </is>
       </c>
-      <c r="C28" s="27" t="inlineStr">
-        <is>
-          <t>① 功能测试全量执行 ② 性能测试（100 万行 P95&lt;5s）③ 详细设计终稿（3 模块合稿：应用+数据+安全）④ 接口文档完善 ⑤ Sprint 2 测试报告</t>
-        </is>
-      </c>
-      <c r="D28" s="28" t="inlineStr">
+      <c r="D36" s="27" t="inlineStr">
+        <is>
+          <t>① 全量回归测试（S1+S2+S3）② 性能测试（20GB P95&lt;5s）③ 用户手册完善（80%）④ 运维手册初稿 ⑤ 数据字典初稿 ⑥ Sprint 3 测试报告 ⑦ UAT 场景脚本</t>
+        </is>
+      </c>
+      <c r="E36" s="28" t="inlineStr">
         <is>
           <t>🟡</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>性能报告；详细设计 3 模块合稿</t>
-        </is>
-      </c>
-      <c r="F28" s="29" t="inlineStr">
-        <is>
-          <t>性能数据由 B 准备</t>
-        </is>
-      </c>
-      <c r="G28" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 2 Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="44" customHeight="1">
-      <c r="A29" s="25" t="inlineStr">
-        <is>
-          <t>W7
-S3</t>
-        </is>
-      </c>
-      <c r="B29" s="26" t="inlineStr">
-        <is>
-          <t>A·架构+需求</t>
-        </is>
-      </c>
-      <c r="C29" s="27" t="inlineStr">
-        <is>
-          <t>① Retention 策略设计 ② 销毁审批流程设计 ③ Monitor 告警规则 ④ 第二系统源库协调（账号/网络/表结构）</t>
-        </is>
-      </c>
-      <c r="D29" s="28" t="inlineStr">
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>回归全通过；用户手册 80%；运维手册初稿；数据字典初稿</t>
+        </is>
+      </c>
+      <c r="G36" s="29" t="n"/>
+      <c r="H36" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 3 Review</t>
+        </is>
+      </c>
+      <c r="I36" s="39" t="n"/>
+    </row>
+    <row r="37" ht="44" customHeight="1">
+      <c r="A37" s="40" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="B37" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>A·需求+架构+开发</t>
+        </is>
+      </c>
+      <c r="D37" s="27" t="inlineStr">
+        <is>
+          <t>① 生产环境部署（CLI 脚本执行 + 验证）② 安全评审材料（等保/个保法对照表）③ 生产域名/证书/网络确认 ④ 全量迁移方案定稿</t>
+        </is>
+      </c>
+      <c r="E37" s="28" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>Retention 流程图；告警规则清单</t>
-        </is>
-      </c>
-      <c r="F29" s="29" t="inlineStr">
-        <is>
-          <t>法务确认保留期底线</t>
-        </is>
-      </c>
-      <c r="G29" s="30" t="inlineStr">
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>生产就绪；安全材料初稿；迁移方案</t>
+        </is>
+      </c>
+      <c r="G37" s="29" t="inlineStr">
+        <is>
+          <t>生产订阅；证书</t>
+        </is>
+      </c>
+      <c r="H37" s="30" t="inlineStr">
         <is>
           <t>Daily Standup</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="44" customHeight="1">
-      <c r="A30" s="25" t="inlineStr">
-        <is>
-          <t>W7
-S3</t>
-        </is>
-      </c>
-      <c r="B30" s="31" t="inlineStr">
+      <c r="I37" s="39" t="n"/>
+    </row>
+    <row r="38" ht="44" customHeight="1">
+      <c r="A38" s="40" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="B38" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C38" s="31" t="inlineStr">
         <is>
           <t>B·数据工程</t>
         </is>
       </c>
-      <c r="C30" s="27" t="inlineStr">
-        <is>
-          <t>① 到期扫描 Job ② DROP PARTITION + VACUUM（Databricks 原生 cron）③ 销毁结果回写 + 审计 ④ 通知集成</t>
-        </is>
-      </c>
-      <c r="D30" s="28" t="inlineStr">
+      <c r="D38" s="27" t="inlineStr">
+        <is>
+          <t>① 首系统全量迁移执行（含对账）② 生产 Jobs 部署 ③ 生产 UC 权限配置</t>
+        </is>
+      </c>
+      <c r="E38" s="28" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>测试环境完整销毁回路跑通</t>
-        </is>
-      </c>
-      <c r="F30" s="29" t="inlineStr"/>
-      <c r="G30" s="30" t="inlineStr"/>
-    </row>
-    <row r="31" ht="44" customHeight="1">
-      <c r="A31" s="25" t="inlineStr">
-        <is>
-          <t>W7
-S3</t>
-        </is>
-      </c>
-      <c r="B31" s="32" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>首系统全量入湖；对账通过</t>
+        </is>
+      </c>
+      <c r="G38" s="29" t="inlineStr">
+        <is>
+          <t>生产环境就绪</t>
+        </is>
+      </c>
+      <c r="H38" s="30" t="n"/>
+      <c r="I38" s="39" t="n"/>
+    </row>
+    <row r="39" ht="44" customHeight="1">
+      <c r="A39" s="40" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="B39" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C39" s="32" t="inlineStr">
         <is>
           <t>C·全栈+DevOps</t>
         </is>
       </c>
-      <c r="C31" s="27" t="inlineStr">
-        <is>
-          <t>① Retention 策略配置界面 ② 销毁审批界面 ③ 通知中心（站内+邮件）④ Dashboard（同步活跃度图表）</t>
-        </is>
-      </c>
-      <c r="D31" s="28" t="inlineStr">
+      <c r="D39" s="27" t="inlineStr">
+        <is>
+          <t>① 生产 AKS 部署（Helm Release）② 生产 SSO 配置 ③ 首系统查询页生产配置 ④ 性能监控接入</t>
+        </is>
+      </c>
+      <c r="E39" s="28" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>Retention 全流程 UI 可操作</t>
-        </is>
-      </c>
-      <c r="F31" s="29" t="inlineStr">
-        <is>
-          <t>B 的销毁 Job</t>
-        </is>
-      </c>
-      <c r="G31" s="30" t="inlineStr"/>
-    </row>
-    <row r="32" ht="44" customHeight="1">
-      <c r="A32" s="25" t="inlineStr">
-        <is>
-          <t>W7
-S3</t>
-        </is>
-      </c>
-      <c r="B32" s="33" t="inlineStr">
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>生产可访问；SSO 正常；查询可用</t>
+        </is>
+      </c>
+      <c r="G39" s="29" t="inlineStr">
+        <is>
+          <t>生产域名</t>
+        </is>
+      </c>
+      <c r="H39" s="30" t="n"/>
+      <c r="I39" s="39" t="n"/>
+    </row>
+    <row r="40" ht="44" customHeight="1">
+      <c r="A40" s="40" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="B40" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C40" s="33" t="inlineStr">
         <is>
           <t>D·QA+SLC文档</t>
         </is>
       </c>
-      <c r="C32" s="27" t="inlineStr">
-        <is>
-          <t>① 销毁流程 E2E 测试 ② 通知功能测试 ③ Dashboard 数据验证 ④ 用户手册初稿（含截图 30+）⑤ 第二系统接入测试准备</t>
-        </is>
-      </c>
-      <c r="D32" s="28" t="inlineStr">
+      <c r="D40" s="27" t="inlineStr">
+        <is>
+          <t>① 文档冲刺启动：用户手册终版 + 运维手册终版 + 数据字典终版 ② 架构图终版（4 张全更新到生产实际）③ 详细设计终版 ④ 接口文档终版 ⑤ 审批材料包准备（技术方案/安全评估/合规对照/验收报告）</t>
+        </is>
+      </c>
+      <c r="E40" s="28" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>6 套文档进入终审（用户/运维/架构×4/详细设计/接口/数据字典）；审批材料初稿</t>
+        </is>
+      </c>
+      <c r="G40" s="29" t="n"/>
+      <c r="H40" s="30" t="n"/>
+      <c r="I40" s="39" t="n"/>
+    </row>
+    <row r="41" ht="44" customHeight="1">
+      <c r="A41" s="40" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="B41" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>A·需求+架构+开发</t>
+        </is>
+      </c>
+      <c r="D41" s="27" t="inlineStr">
+        <is>
+          <t>① UAT 组织（5 场景 + 业务方验收）② UAT 反馈处理与优先级排序 ③ 安全评审提交 ④ 审批文档定稿</t>
+        </is>
+      </c>
+      <c r="E41" s="28" t="inlineStr">
+        <is>
+          <t>🔴 ★</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>UAT 签字；审批材料提交</t>
+        </is>
+      </c>
+      <c r="G41" s="29" t="inlineStr">
+        <is>
+          <t>业务方 UAT</t>
+        </is>
+      </c>
+      <c r="H41" s="30" t="inlineStr">
+        <is>
+          <t>S4 Review（UAT）；S5 Planning</t>
+        </is>
+      </c>
+      <c r="I41" s="39" t="n"/>
+    </row>
+    <row r="42" ht="44" customHeight="1">
+      <c r="A42" s="40" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="B42" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C42" s="31" t="inlineStr">
+        <is>
+          <t>B·数据工程</t>
+        </is>
+      </c>
+      <c r="D42" s="27" t="inlineStr">
+        <is>
+          <t>① UAT 支撑 ② 第二系统全量迁移准备 ③ 生产 Compaction 首次执行 ④ 销毁回路生产验证</t>
+        </is>
+      </c>
+      <c r="E42" s="28" t="inlineStr">
         <is>
           <t>🟡</t>
         </is>
       </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>销毁 E2E 报告；用户手册初稿（50% 完成）</t>
-        </is>
-      </c>
-      <c r="F32" s="29" t="inlineStr"/>
-      <c r="G32" s="30" t="inlineStr"/>
-    </row>
-    <row r="33" ht="44" customHeight="1">
-      <c r="A33" s="25" t="inlineStr">
-        <is>
-          <t>W8
-S3</t>
-        </is>
-      </c>
-      <c r="B33" s="26" t="inlineStr">
-        <is>
-          <t>A·架构+需求</t>
-        </is>
-      </c>
-      <c r="C33" s="27" t="inlineStr">
-        <is>
-          <t>① 第二系统零代码接入（标准流程验证）② 集成测试统筹 ③ 性能瓶颈分析 ④ Sprint 3 验收</t>
-        </is>
-      </c>
-      <c r="D33" s="28" t="inlineStr">
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>UAT 数据问题全解决</t>
+        </is>
+      </c>
+      <c r="G42" s="29" t="n"/>
+      <c r="H42" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 4 Review</t>
+        </is>
+      </c>
+      <c r="I42" s="39" t="n"/>
+    </row>
+    <row r="43" ht="44" customHeight="1">
+      <c r="A43" s="40" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="B43" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C43" s="32" t="inlineStr">
+        <is>
+          <t>C·全栈+DevOps</t>
+        </is>
+      </c>
+      <c r="D43" s="27" t="inlineStr">
+        <is>
+          <t>① UAT Bug 修复 ② 生产监控 Dashboard ③ 性能微调 ④ 文档截图更新</t>
+        </is>
+      </c>
+      <c r="E43" s="28" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>UAT Bug 全关闭；截图一致</t>
+        </is>
+      </c>
+      <c r="G43" s="29" t="n"/>
+      <c r="H43" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 4 Review</t>
+        </is>
+      </c>
+      <c r="I43" s="39" t="n"/>
+    </row>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="40" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="B44" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C44" s="33" t="inlineStr">
+        <is>
+          <t>D·QA+SLC文档</t>
+        </is>
+      </c>
+      <c r="D44" s="27" t="inlineStr">
+        <is>
+          <t>① UAT 执行协调 + 结果记录 ② 文档终审（6 套 + 审批包 = 7 套）③ 上线 Checklist ④ 培训材料（业务用户 + 运维团队）</t>
+        </is>
+      </c>
+      <c r="E44" s="28" t="inlineStr">
         <is>
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>第二系统零代码接入成功（&lt;2h）</t>
-        </is>
-      </c>
-      <c r="F33" s="29" t="inlineStr">
-        <is>
-          <t>第二系统源库账号</t>
-        </is>
-      </c>
-      <c r="G33" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 3 Review；Sprint 4 Planning</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="44" customHeight="1">
-      <c r="A34" s="25" t="inlineStr">
-        <is>
-          <t>W8
-S3</t>
-        </is>
-      </c>
-      <c r="B34" s="31" t="inlineStr">
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>7 套文档终版；上线 Checklist 评审通过；培训 PPT + 演练脚本</t>
+        </is>
+      </c>
+      <c r="G44" s="29" t="inlineStr">
+        <is>
+          <t>审批方反馈</t>
+        </is>
+      </c>
+      <c r="H44" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 4 Review</t>
+        </is>
+      </c>
+      <c r="I44" s="39" t="n"/>
+    </row>
+    <row r="45" ht="44" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="B45" s="46" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>A·需求+架构+开发</t>
+        </is>
+      </c>
+      <c r="D45" s="27" t="inlineStr">
+        <is>
+          <t>① Go/No-Go 决策 ② 上线指挥（回退方案就绪）③ 运维培训（架构+UC+权限+监控）④ 项目收尾文档启动</t>
+        </is>
+      </c>
+      <c r="E45" s="28" t="inlineStr">
+        <is>
+          <t>🔴 ★</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>上线成功；运维培训完成</t>
+        </is>
+      </c>
+      <c r="G45" s="29" t="inlineStr"/>
+      <c r="H45" s="30" t="inlineStr">
+        <is>
+          <t>Go-Live 决策会</t>
+        </is>
+      </c>
+      <c r="I45" s="39" t="n"/>
+    </row>
+    <row r="46" ht="44" customHeight="1">
+      <c r="A46" s="40" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="B46" s="46" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C46" s="31" t="inlineStr">
         <is>
           <t>B·数据工程</t>
         </is>
       </c>
-      <c r="C34" s="27" t="inlineStr">
-        <is>
-          <t>① 第二系统 SeaTunnel+四层+SERVE ② 两系统联邦查询 ③ 性能调优</t>
-        </is>
-      </c>
-      <c r="D34" s="28" t="inlineStr">
+      <c r="D46" s="27" t="inlineStr">
+        <is>
+          <t>① 生产运行监控（ETL/Compaction/销毁）② 异常处理 ③ 第二系统全量迁移 ④ 接入 SOP 初稿</t>
+        </is>
+      </c>
+      <c r="E46" s="28" t="inlineStr">
         <is>
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>第二系统端到端可查</t>
-        </is>
-      </c>
-      <c r="F34" s="29" t="inlineStr"/>
-      <c r="G34" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 3 Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="44" customHeight="1">
-      <c r="A35" s="25" t="inlineStr">
-        <is>
-          <t>W8
-S3</t>
-        </is>
-      </c>
-      <c r="B35" s="32" t="inlineStr">
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>生产 Jobs 正常；第二系统入湖</t>
+        </is>
+      </c>
+      <c r="G46" s="29" t="n"/>
+      <c r="H46" s="30" t="inlineStr">
+        <is>
+          <t>Go-Live</t>
+        </is>
+      </c>
+      <c r="I46" s="39" t="n"/>
+    </row>
+    <row r="47" ht="44" customHeight="1">
+      <c r="A47" s="40" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="B47" s="46" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C47" s="32" t="inlineStr">
         <is>
           <t>C·全栈+DevOps</t>
         </is>
       </c>
-      <c r="C35" s="27" t="inlineStr">
-        <is>
-          <t>① 第二系统前端配置（零代码）② 跨系统联邦查询测试 ③ 前端性能优化 ④ Bug 修复</t>
-        </is>
-      </c>
-      <c r="D35" s="28" t="inlineStr">
+      <c r="D47" s="27" t="inlineStr">
+        <is>
+          <t>① 生产运行监控（查询/前端/SSO）② 用户反馈响应 ③ 配置调优</t>
+        </is>
+      </c>
+      <c r="E47" s="28" t="inlineStr">
         <is>
           <t>🔴 ★</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>第二系统查询页零代码上线</t>
-        </is>
-      </c>
-      <c r="F35" s="29" t="inlineStr"/>
-      <c r="G35" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 3 Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="44" customHeight="1">
-      <c r="A36" s="25" t="inlineStr">
-        <is>
-          <t>W8
-S3</t>
-        </is>
-      </c>
-      <c r="B36" s="33" t="inlineStr">
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>生产查询正常</t>
+        </is>
+      </c>
+      <c r="G47" s="29" t="n"/>
+      <c r="H47" s="30" t="inlineStr">
+        <is>
+          <t>Go-Live</t>
+        </is>
+      </c>
+      <c r="I47" s="39" t="n"/>
+    </row>
+    <row r="48" ht="44" customHeight="1">
+      <c r="A48" s="40" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="B48" s="46" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C48" s="33" t="inlineStr">
         <is>
           <t>D·QA+SLC文档</t>
         </is>
       </c>
-      <c r="C36" s="27" t="inlineStr">
-        <is>
-          <t>① 全量回归测试（S1+S2+S3）② 性能测试（20GB P95&lt;5s）③ 用户手册完善（80%）④ 运维手册初稿 ⑤ 数据字典初稿 ⑥ Sprint 3 测试报告 ⑦ UAT 场景脚本</t>
-        </is>
-      </c>
-      <c r="D36" s="28" t="inlineStr">
-        <is>
-          <t>🟡</t>
-        </is>
-      </c>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>回归全通过；用户手册 80%；运维手册初稿；数据字典初稿</t>
-        </is>
-      </c>
-      <c r="F36" s="29" t="inlineStr"/>
-      <c r="G36" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 3 Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="44" customHeight="1">
-      <c r="A37" s="25" t="inlineStr">
-        <is>
-          <t>W9
-S4</t>
-        </is>
-      </c>
-      <c r="B37" s="26" t="inlineStr">
-        <is>
-          <t>A·架构+需求</t>
-        </is>
-      </c>
-      <c r="C37" s="27" t="inlineStr">
-        <is>
-          <t>① 生产环境部署（CLI/Bicep 脚本执行）② 安全评审材料（等保/个保法对照表）③ 生产域名/证书/网络确认 ④ 全量迁移方案</t>
-        </is>
-      </c>
-      <c r="D37" s="28" t="inlineStr">
-        <is>
-          <t>🔴</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>生产环境就绪；安全材料初稿；迁移方案</t>
-        </is>
-      </c>
-      <c r="F37" s="29" t="inlineStr">
-        <is>
-          <t>生产订阅权限；证书</t>
-        </is>
-      </c>
-      <c r="G37" s="30" t="inlineStr">
-        <is>
-          <t>Daily Standup</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="44" customHeight="1">
-      <c r="A38" s="25" t="inlineStr">
-        <is>
-          <t>W9
-S4</t>
-        </is>
-      </c>
-      <c r="B38" s="31" t="inlineStr">
+      <c r="D48" s="27" t="inlineStr">
+        <is>
+          <t>① 上线执行（部署顺序/验证/回退点）② 48h 值守 ③ 告警验证 ④ 培训交付：业务用户培训（查询/导出/附件）+ 运维培训辅助</t>
+        </is>
+      </c>
+      <c r="E48" s="28" t="inlineStr">
+        <is>
+          <t>🔴 ★</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>上线 Checklist 全勾；培训完成；告警可达</t>
+        </is>
+      </c>
+      <c r="G48" s="29" t="n"/>
+      <c r="H48" s="30" t="inlineStr">
+        <is>
+          <t>Go-Live；培训</t>
+        </is>
+      </c>
+      <c r="I48" s="39" t="n"/>
+    </row>
+    <row r="49" ht="44" customHeight="1">
+      <c r="A49" s="40" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="B49" s="46" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>A·需求+架构+开发</t>
+        </is>
+      </c>
+      <c r="D49" s="27" t="inlineStr">
+        <is>
+          <t>① 运维团队独立操作验证 ② 项目关闭报告 ③ 后续系统接入排期（与业务方）④ Retro</t>
+        </is>
+      </c>
+      <c r="E49" s="28" t="inlineStr">
+        <is>
+          <t>⚪ ★</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>运维可独立日常操作；关闭报告签字</t>
+        </is>
+      </c>
+      <c r="G49" s="29" t="inlineStr">
+        <is>
+          <t>运维意愿</t>
+        </is>
+      </c>
+      <c r="H49" s="30" t="inlineStr">
+        <is>
+          <t>Retro；项目关闭会</t>
+        </is>
+      </c>
+      <c r="I49" s="39" t="n"/>
+    </row>
+    <row r="50" ht="44" customHeight="1">
+      <c r="A50" s="40" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="B50" s="46" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C50" s="31" t="inlineStr">
         <is>
           <t>B·数据工程</t>
         </is>
       </c>
-      <c r="C38" s="27" t="inlineStr">
-        <is>
-          <t>① 首系统全量迁移执行（含对账）② 生产 Jobs 部署 ③ 生产 UC 权限配置</t>
-        </is>
-      </c>
-      <c r="D38" s="28" t="inlineStr">
-        <is>
-          <t>🔴</t>
-        </is>
-      </c>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>首系统全量入湖；对账通过</t>
-        </is>
-      </c>
-      <c r="F38" s="29" t="inlineStr">
-        <is>
-          <t>生产环境就绪</t>
-        </is>
-      </c>
-      <c r="G38" s="30" t="inlineStr"/>
-    </row>
-    <row r="39" ht="44" customHeight="1">
-      <c r="A39" s="25" t="inlineStr">
-        <is>
-          <t>W9
-S4</t>
-        </is>
-      </c>
-      <c r="B39" s="32" t="inlineStr">
+      <c r="D50" s="27" t="inlineStr">
+        <is>
+          <t>① 运维知识转移（ETL/销毁）② 第三系统 PoC ③ 技术债清单 ④ Retro</t>
+        </is>
+      </c>
+      <c r="E50" s="28" t="inlineStr">
+        <is>
+          <t>⚪ ★</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>运维可独立跑 ETL+销毁</t>
+        </is>
+      </c>
+      <c r="G50" s="29" t="n"/>
+      <c r="H50" s="30" t="inlineStr">
+        <is>
+          <t>Retro</t>
+        </is>
+      </c>
+      <c r="I50" s="39" t="n"/>
+    </row>
+    <row r="51" ht="44" customHeight="1">
+      <c r="A51" s="40" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="B51" s="46" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C51" s="32" t="inlineStr">
         <is>
           <t>C·全栈+DevOps</t>
         </is>
       </c>
-      <c r="C39" s="27" t="inlineStr">
-        <is>
-          <t>① 生产 AKS 部署（Helm Release）② 生产 SSO 配置 ③ 首系统查询页生产配置 ④ 性能监控接入</t>
-        </is>
-      </c>
-      <c r="D39" s="28" t="inlineStr">
-        <is>
-          <t>🔴</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>生产可访问；SSO 正常；查询可用</t>
-        </is>
-      </c>
-      <c r="F39" s="29" t="inlineStr">
-        <is>
-          <t>生产域名</t>
-        </is>
-      </c>
-      <c r="G39" s="30" t="inlineStr"/>
-    </row>
-    <row r="40" ht="44" customHeight="1">
-      <c r="A40" s="25" t="inlineStr">
-        <is>
-          <t>W9
-S4</t>
-        </is>
-      </c>
-      <c r="B40" s="33" t="inlineStr">
+      <c r="D51" s="27" t="inlineStr">
+        <is>
+          <t>① 运维知识转移（部署/前端）② 第三系统配置 ③ 代码整理 ④ Retro</t>
+        </is>
+      </c>
+      <c r="E51" s="28" t="inlineStr">
+        <is>
+          <t>⚪ ★</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>运维可改前端配置；代码整洁</t>
+        </is>
+      </c>
+      <c r="G51" s="29" t="n"/>
+      <c r="H51" s="30" t="inlineStr">
+        <is>
+          <t>Retro</t>
+        </is>
+      </c>
+      <c r="I51" s="39" t="n"/>
+    </row>
+    <row r="52" ht="44" customHeight="1">
+      <c r="A52" s="40" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="B52" s="46" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C52" s="33" t="inlineStr">
         <is>
           <t>D·QA+SLC文档</t>
         </is>
       </c>
-      <c r="C40" s="27" t="inlineStr">
-        <is>
-          <t>① 文档冲刺启动：用户手册终版 + 运维手册终版 + 数据字典终版 ② 架构图终版（4 张全更新到生产实际）③ 详细设计终版 ④ 接口文档终版 ⑤ 审批材料包准备（技术方案/安全评估/合规对照/验收报告）</t>
-        </is>
-      </c>
-      <c r="D40" s="28" t="inlineStr">
-        <is>
-          <t>🔴</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>6 套文档进入终审（用户/运维/架构×4/详细设计/接口/数据字典）；审批材料初稿</t>
-        </is>
-      </c>
-      <c r="F40" s="29" t="inlineStr"/>
-      <c r="G40" s="30" t="inlineStr"/>
-    </row>
-    <row r="41" ht="44" customHeight="1">
-      <c r="A41" s="25" t="inlineStr">
-        <is>
-          <t>W10
-S4</t>
-        </is>
-      </c>
-      <c r="B41" s="26" t="inlineStr">
-        <is>
-          <t>A·架构+需求</t>
-        </is>
-      </c>
-      <c r="C41" s="27" t="inlineStr">
-        <is>
-          <t>① UAT 组织（5 核心场景 + 业务方验收）② UAT 反馈处理 ③ 安全评审提交 ④ 审批文档定稿</t>
-        </is>
-      </c>
-      <c r="D41" s="28" t="inlineStr">
-        <is>
-          <t>🔴 ★</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>UAT 签字；安全评审提交；审批材料提交</t>
-        </is>
-      </c>
-      <c r="F41" s="29" t="inlineStr">
-        <is>
-          <t>业务方 UAT 配合</t>
-        </is>
-      </c>
-      <c r="G41" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 4 Review（UAT 报告）；Sprint 5 Planning</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="44" customHeight="1">
-      <c r="A42" s="25" t="inlineStr">
-        <is>
-          <t>W10
-S4</t>
-        </is>
-      </c>
-      <c r="B42" s="31" t="inlineStr">
-        <is>
-          <t>B·数据工程</t>
-        </is>
-      </c>
-      <c r="C42" s="27" t="inlineStr">
-        <is>
-          <t>① UAT 支撑 ② 第二系统全量迁移准备 ③ 生产 Compaction 首次执行 ④ 销毁回路生产验证</t>
-        </is>
-      </c>
-      <c r="D42" s="28" t="inlineStr">
-        <is>
-          <t>🟡</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>UAT 数据问题全解决</t>
-        </is>
-      </c>
-      <c r="F42" s="29" t="inlineStr"/>
-      <c r="G42" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 4 Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="44" customHeight="1">
-      <c r="A43" s="25" t="inlineStr">
-        <is>
-          <t>W10
-S4</t>
-        </is>
-      </c>
-      <c r="B43" s="32" t="inlineStr">
-        <is>
-          <t>C·全栈+DevOps</t>
-        </is>
-      </c>
-      <c r="C43" s="27" t="inlineStr">
-        <is>
-          <t>① UAT Bug 修复 ② 生产监控 Dashboard ③ 性能微调 ④ 文档截图更新</t>
-        </is>
-      </c>
-      <c r="D43" s="28" t="inlineStr">
-        <is>
-          <t>🟡</t>
-        </is>
-      </c>
-      <c r="E43" s="9" t="inlineStr">
-        <is>
-          <t>UAT Bug 全关闭；截图一致</t>
-        </is>
-      </c>
-      <c r="F43" s="29" t="inlineStr"/>
-      <c r="G43" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 4 Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="44" customHeight="1">
-      <c r="A44" s="25" t="inlineStr">
-        <is>
-          <t>W10
-S4</t>
-        </is>
-      </c>
-      <c r="B44" s="33" t="inlineStr">
-        <is>
-          <t>D·QA+SLC文档</t>
-        </is>
-      </c>
-      <c r="C44" s="27" t="inlineStr">
-        <is>
-          <t>① UAT 执行协调 + 结果记录 ② 文档终审（6 套 + 审批包 = 7 套）③ 上线 Checklist ④ 培训材料（业务用户 + 运维团队）</t>
-        </is>
-      </c>
-      <c r="D44" s="28" t="inlineStr">
-        <is>
-          <t>🔴 ★</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>7 套文档终版；上线 Checklist 评审通过；培训 PPT + 演练脚本</t>
-        </is>
-      </c>
-      <c r="F44" s="29" t="inlineStr">
-        <is>
-          <t>审批方反馈</t>
-        </is>
-      </c>
-      <c r="G44" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 4 Review</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="44" customHeight="1">
-      <c r="A45" s="25" t="inlineStr">
-        <is>
-          <t>W11
-S5</t>
-        </is>
-      </c>
-      <c r="B45" s="26" t="inlineStr">
-        <is>
-          <t>A·架构+需求</t>
-        </is>
-      </c>
-      <c r="C45" s="27" t="inlineStr">
-        <is>
-          <t>① Go/No-Go 决策 ② 上线指挥（回退方案就绪）③ 运维培训（架构+UC+权限+监控）④ 项目收尾文档启动</t>
-        </is>
-      </c>
-      <c r="D45" s="28" t="inlineStr">
-        <is>
-          <t>🔴 ★</t>
-        </is>
-      </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>上线成功；运维培训完成</t>
-        </is>
-      </c>
-      <c r="F45" s="29" t="inlineStr"/>
-      <c r="G45" s="30" t="inlineStr">
-        <is>
-          <t>Go-Live 决策会</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="44" customHeight="1">
-      <c r="A46" s="25" t="inlineStr">
-        <is>
-          <t>W11
-S5</t>
-        </is>
-      </c>
-      <c r="B46" s="31" t="inlineStr">
-        <is>
-          <t>B·数据工程</t>
-        </is>
-      </c>
-      <c r="C46" s="27" t="inlineStr">
-        <is>
-          <t>① 生产运行监控（ETL/Compaction/销毁）② 异常处理 ③ 第二系统全量迁移 ④ 接入 SOP 初稿</t>
-        </is>
-      </c>
-      <c r="D46" s="28" t="inlineStr">
-        <is>
-          <t>🔴 ★</t>
-        </is>
-      </c>
-      <c r="E46" s="9" t="inlineStr">
-        <is>
-          <t>生产 Jobs 正常；第二系统入湖</t>
-        </is>
-      </c>
-      <c r="F46" s="29" t="inlineStr"/>
-      <c r="G46" s="30" t="inlineStr">
-        <is>
-          <t>Go-Live</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="44" customHeight="1">
-      <c r="A47" s="25" t="inlineStr">
-        <is>
-          <t>W11
-S5</t>
-        </is>
-      </c>
-      <c r="B47" s="32" t="inlineStr">
-        <is>
-          <t>C·全栈+DevOps</t>
-        </is>
-      </c>
-      <c r="C47" s="27" t="inlineStr">
-        <is>
-          <t>① 生产运行监控（查询/前端/SSO）② 用户反馈响应 ③ 配置调优</t>
-        </is>
-      </c>
-      <c r="D47" s="28" t="inlineStr">
-        <is>
-          <t>🔴 ★</t>
-        </is>
-      </c>
-      <c r="E47" s="9" t="inlineStr">
-        <is>
-          <t>生产查询正常</t>
-        </is>
-      </c>
-      <c r="F47" s="29" t="inlineStr"/>
-      <c r="G47" s="30" t="inlineStr">
-        <is>
-          <t>Go-Live</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="44" customHeight="1">
-      <c r="A48" s="25" t="inlineStr">
-        <is>
-          <t>W11
-S5</t>
-        </is>
-      </c>
-      <c r="B48" s="33" t="inlineStr">
-        <is>
-          <t>D·QA+SLC文档</t>
-        </is>
-      </c>
-      <c r="C48" s="27" t="inlineStr">
-        <is>
-          <t>① 上线执行（部署顺序/验证/回退点）② 48h 值守 ③ 告警验证 ④ 培训交付：业务用户培训（查询/导出/附件）+ 运维培训辅助</t>
-        </is>
-      </c>
-      <c r="D48" s="28" t="inlineStr">
-        <is>
-          <t>🔴 ★</t>
-        </is>
-      </c>
-      <c r="E48" s="9" t="inlineStr">
-        <is>
-          <t>上线 Checklist 全勾；培训完成；告警可达</t>
-        </is>
-      </c>
-      <c r="F48" s="29" t="inlineStr"/>
-      <c r="G48" s="30" t="inlineStr">
-        <is>
-          <t>Go-Live；培训</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="44" customHeight="1">
-      <c r="A49" s="25" t="inlineStr">
-        <is>
-          <t>W12
-S5</t>
-        </is>
-      </c>
-      <c r="B49" s="26" t="inlineStr">
-        <is>
-          <t>A·架构+需求</t>
-        </is>
-      </c>
-      <c r="C49" s="27" t="inlineStr">
-        <is>
-          <t>① 运维团队独立操作验证 ② 项目关闭报告 ③ 后续接入排期 ④ Retro</t>
-        </is>
-      </c>
-      <c r="D49" s="28" t="inlineStr">
+      <c r="D52" s="27" t="inlineStr">
+        <is>
+          <t>① 文档包归档（7 套 + 培训视频 + 接入手册）② 培训视频录制 ③ 后续接入手册终版 ④ Retro + 行动项</t>
+        </is>
+      </c>
+      <c r="E52" s="28" t="inlineStr">
         <is>
           <t>⚪ ★</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr">
-        <is>
-          <t>运维可独立日常操作；关闭报告签字</t>
-        </is>
-      </c>
-      <c r="F49" s="29" t="inlineStr">
-        <is>
-          <t>运维意愿</t>
-        </is>
-      </c>
-      <c r="G49" s="30" t="inlineStr">
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>全部文档归档；培训视频上传</t>
+        </is>
+      </c>
+      <c r="G52" s="29" t="n"/>
+      <c r="H52" s="30" t="inlineStr">
         <is>
           <t>Retro；项目关闭会</t>
         </is>
       </c>
-    </row>
-    <row r="50" ht="44" customHeight="1">
-      <c r="A50" s="25" t="inlineStr">
-        <is>
-          <t>W12
-S5</t>
-        </is>
-      </c>
-      <c r="B50" s="31" t="inlineStr">
-        <is>
-          <t>B·数据工程</t>
-        </is>
-      </c>
-      <c r="C50" s="27" t="inlineStr">
-        <is>
-          <t>① 运维知识转移（ETL/销毁）② 第三系统 PoC ③ 技术债清单 ④ Retro</t>
-        </is>
-      </c>
-      <c r="D50" s="28" t="inlineStr">
-        <is>
-          <t>⚪ ★</t>
-        </is>
-      </c>
-      <c r="E50" s="9" t="inlineStr">
-        <is>
-          <t>运维可独立跑 ETL+销毁</t>
-        </is>
-      </c>
-      <c r="F50" s="29" t="inlineStr"/>
-      <c r="G50" s="30" t="inlineStr">
-        <is>
-          <t>Retro</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="44" customHeight="1">
-      <c r="A51" s="25" t="inlineStr">
-        <is>
-          <t>W12
-S5</t>
-        </is>
-      </c>
-      <c r="B51" s="32" t="inlineStr">
-        <is>
-          <t>C·全栈+DevOps</t>
-        </is>
-      </c>
-      <c r="C51" s="27" t="inlineStr">
-        <is>
-          <t>① 运维知识转移（部署/前端）② 第三系统配置 ③ 代码整理 ④ Retro</t>
-        </is>
-      </c>
-      <c r="D51" s="28" t="inlineStr">
-        <is>
-          <t>⚪ ★</t>
-        </is>
-      </c>
-      <c r="E51" s="9" t="inlineStr">
-        <is>
-          <t>运维可改前端配置；代码整洁</t>
-        </is>
-      </c>
-      <c r="F51" s="29" t="inlineStr"/>
-      <c r="G51" s="30" t="inlineStr">
-        <is>
-          <t>Retro</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="44" customHeight="1">
-      <c r="A52" s="25" t="inlineStr">
-        <is>
-          <t>W12
-S5</t>
-        </is>
-      </c>
-      <c r="B52" s="33" t="inlineStr">
-        <is>
-          <t>D·QA+SLC文档</t>
-        </is>
-      </c>
-      <c r="C52" s="27" t="inlineStr">
-        <is>
-          <t>① 文档包归档（7 套 + 培训视频 + 接入手册）② 培训视频录制 ③ 后续接入手册终版 ④ Retro + 行动项</t>
-        </is>
-      </c>
-      <c r="D52" s="28" t="inlineStr">
-        <is>
-          <t>⚪ ★</t>
-        </is>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>全部文档归档；培训视频上传</t>
-        </is>
-      </c>
-      <c r="F52" s="29" t="inlineStr"/>
-      <c r="G52" s="30" t="inlineStr">
-        <is>
-          <t>Retro；项目关闭会</t>
-        </is>
-      </c>
+      <c r="I52" s="39" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="39" t="n"/>
+      <c r="B53" s="39" t="n"/>
+      <c r="C53" s="39" t="n"/>
+      <c r="D53" s="39" t="n"/>
+      <c r="E53" s="39" t="n"/>
+      <c r="F53" s="39" t="n"/>
+      <c r="G53" s="39" t="n"/>
+      <c r="H53" s="39" t="n"/>
+      <c r="I53" s="39" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="39" t="n"/>
+      <c r="B54" s="39" t="n"/>
+      <c r="C54" s="39" t="n"/>
+      <c r="D54" s="39" t="n"/>
+      <c r="E54" s="39" t="n"/>
+      <c r="F54" s="39" t="n"/>
+      <c r="G54" s="39" t="n"/>
+      <c r="H54" s="39" t="n"/>
+      <c r="I54" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/report/项目执行计划.xlsx
+++ b/report/项目执行计划.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="39">
+  <fonts count="41">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -242,8 +242,20 @@
       <color rgb="00dc2626"/>
       <sz val="8.5"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00c2410c"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00c2410c"/>
+      <sz val="8.5"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -310,6 +322,11 @@
         <fgColor rgb="00E2E8F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEDD5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -338,7 +355,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -464,6 +481,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -831,7 +854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -847,14 +870,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>B2 湖仓归档平台 · 项目执行计划 V3（4 人 × 12 周 Agile）</t>
+          <t>B2 湖仓归档平台 · 项目执行计划 V4（Agile）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>V3 修订：① A = 专职需求分析师（BRD / 用户故事 / 验收标准 / 业务协调），兼架构设计（前期）与前后端功能开发分担（后期）　② 周次与 Sprint 拆为两列　③ 不用 Terraform（Azure CLI / Bicep）</t>
+          <t>V4 修订：① 需求与架构彻底分离——A=专职需求分析师（50% 投入），不再兼架构与开发　② 新增 E=架构师（兼职功能开发）：负责技术架构 + Azure 环境 + 分担前后端开发　③ 其余角色不变（B 数据工程 / C 全栈+DevOps / D QA+SLC 文档）</t>
         </is>
       </c>
     </row>
@@ -909,180 +932,223 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>需求分析师（兼架构 + 开发分担）</t>
+          <t>需求分析师（专职，50% 投入）</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>前期（W1~W4）：① 需求访谈与 BRD ② 用户故事地图与验收标准 ③ 架构设计（Azure 组件 / Databricks 湖仓 / UC 权限体系）④ Azure 环境搭建（CLI/Bicep）。后期（W5~W12）：⑤ 分担前后端功能开发（查询页 / 配置页 / Retention 界面等）⑥ 代码评审 ⑦ 业务方/源方/网络团队协调</t>
+          <t>① 需求访谈与引导（业务方/源方）② BRD：业务流程图 + 功能清单 + 非功能需求 ③ 用户故事地图与验收标准（每 Sprint 更新）④ UAT 场景设计与组织 ⑤ 需求变更管理与优先级排序 ⑥ 业务方/源方/法务的沟通协调</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>需求分析 / 业务流程建模 / Databricks / Azure CLI / .NET 或 React（至少一头）</t>
+          <t>需求分析 / 业务流程建模 / 用户故事 / 原型草图（可选）</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>BRD、用户故事地图、验收标准、UAT 场景脚本、需求变更记录</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>需求不清晰阻塞全员；访谈需业务方配合</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>W1~W2 密集（BRD）；之后每 Sprint 前做需求澄清、Sprint 后做验收；空档期可支持 UAT/Bug 复核（不再写代码）</t>
+        </is>
+      </c>
+      <c r="I5" s="39" t="n"/>
+    </row>
+    <row r="6" ht="62" customHeight="1">
+      <c r="A6" s="47" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>架构师（兼职功能开发）</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>① 技术架构：Azure 组件设计、Databricks 湖仓四层、UC 权限体系、网络与安全 ② Azure 环境搭建（CLI/Bicep）③ 技术决策与代码评审 ④ 兼职功能开发：W4 起分担前后端开发（与 C 组成开发双前线）</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Databricks / Azure 网络 / .NET 或 React（至少一头）/ 系统设计</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>50% 架构 + 50% 开发</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>架构设计文档、Azure 部署脚本、UC 权限矩阵、ADR、分担开发的功能模块（查询配置页/附件预览/Retention 界面等）</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>前期架构决策阻塞 B/C；后期开发与评审争时间</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>W1~W3 架构为主；W4 起开发为主（架构只剩评审与决策）</t>
+        </is>
+      </c>
+      <c r="I6" s="39" t="n"/>
+    </row>
+    <row r="7" ht="62" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>数据工程师（ETL / 湖仓开发）</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>① SeaTunnel 抽取链路与配置生成器 ② Iceberg 四层建模（RAW→CURATED→LAKE→SERVE）③ Databricks Jobs 开发（ETL/Compaction/VACUUM/销毁）④ 数据对账脚本 ⑤ 性能调优</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Python / Spark SQL / SeaTunnel / Iceberg / Databricks SDK</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>BRD、用户故事地图、验收标准、架构设计文档、Azure 部署脚本、分担开发的功能模块、ADR</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>需求不清晰会阻塞全员；一人身兼三职需严格管理切换时间</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>W1~W4 需求+架构为主（60/40）；W5 起转入开发（80% 开发 + 20% 评审协调）</t>
-        </is>
-      </c>
-      <c r="I5" s="39" t="n"/>
-    </row>
-    <row r="6" ht="62" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>数据工程师（ETL / 湖仓开发）</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>① SeaTunnel 抽取链路与配置生成器 ② Iceberg 四层建模（RAW→CURATED→LAKE→SERVE）③ Databricks Jobs 开发（ETL/Compaction/VACUUM/销毁）④ 数据对账脚本 ⑤ 性能调优</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Python / Spark SQL / SeaTunnel / Iceberg / Databricks SDK</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>SeaTunnel 配置生成器、四层转换 SQL、销毁作业、Compaction 调度、对账脚本、性能基准报告</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>源库连接依赖源方配合；Databricks Premium 需提前开通</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>核心开发角色，代码量最大</t>
+        </is>
+      </c>
+      <c r="I7" s="39" t="n"/>
+    </row>
+    <row r="8" ht="62" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>全栈开发 + DevOps</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>① .NET 10 后端（元数据/查询代理/附件/权限/审计/调度）② React 前端（配置化查询平台）③ CI/CD 流水线（GitHub Actions）④ Docker 镜像 + Helm Chart + AKS 部署 ⑤ SSO（Entra ID OIDC）</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>.NET 10 / React / TypeScript / Docker / Helm / GitHub Actions / AKS / OIDC</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>SeaTunnel 配置生成器、四层转换 SQL、销毁作业、Compaction 调度、对账脚本、性能基准报告</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>源库连接依赖源方配合；Databricks Premium 需提前开通</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t>核心开发角色，代码量最大</t>
-        </is>
-      </c>
-      <c r="I6" s="39" t="n"/>
-    </row>
-    <row r="7" ht="62" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>全栈开发 + DevOps</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>① .NET 10 后端（元数据/查询代理/附件/权限/审计/调度）② React 前端（配置化查询平台）③ CI/CD 流水线（GitHub Actions）④ Docker 镜像 + Helm Chart + AKS 部署 ⑤ SSO（Entra ID OIDC）</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>.NET 10 / React / TypeScript / Docker / Helm / GitHub Actions / AKS / OIDC</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>后端 API（15+ 接口）、React 前端、CI/CD 流水线、Helm Chart、SSO 集成</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>前后端 + DevOps 一人扛，压力最大</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>W4 后 E 加入分担开发，压力缓解</t>
+        </is>
+      </c>
+      <c r="I8" s="39" t="n"/>
+    </row>
+    <row r="9" ht="62" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>QA 测试 + SLC 全生命周期文档</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>① 测试策略与计划 ② 功能/集成/性能/安全测试 + UAT 协调 ③ 缺陷管理 ④ SLC 文档：架构图（C4 四层）、详细设计（3 模块）、接口文档、数据字典、用户手册、运维手册、审批材料包 ⑤ 培训材料与交付</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>测试设计 / 自动化测试 / 技术写作 / Draw.io / 文档管理</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>后端 API（15+ 接口）、React 前端、CI/CD 流水线、Helm Chart、SSO 集成</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>前后端 + DevOps 一人扛，压力最大</t>
-        </is>
-      </c>
-      <c r="H7" s="11" t="inlineStr">
-        <is>
-          <t>W5 后 A 加入分担开发，压力缓解</t>
-        </is>
-      </c>
-      <c r="I7" s="39" t="n"/>
-    </row>
-    <row r="8" ht="62" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>QA 测试 + SLC 全生命周期文档</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>① 测试策略与计划 ② 功能/集成/性能/安全测试 + UAT 协调 ③ 缺陷管理 ④ SLC 文档：架构图（C4 四层）、详细设计（3 模块）、接口文档、数据字典、用户手册、运维手册、审批材料包 ⑤ 培训材料与交付</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>测试设计 / 自动化测试 / 技术写作 / Draw.io / 文档管理</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>测试计划、测试用例（80+）、自动化测试、测试报告、架构图×4、详细设计×3、接口文档、数据字典、用户手册、运维手册、审批包、培训材料</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>文档量 ≈40% 工作量；测试数据依赖 B 的链路就绪</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>前 3 周偏测试框架，W4 起文档与测试并重，W9~10 文档冲刺</t>
         </is>
       </c>
-      <c r="I8" s="39" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="39" t="n"/>
-      <c r="B9" s="39" t="n"/>
-      <c r="C9" s="39" t="n"/>
-      <c r="D9" s="39" t="n"/>
-      <c r="E9" s="39" t="n"/>
-      <c r="F9" s="39" t="n"/>
-      <c r="G9" s="39" t="n"/>
-      <c r="H9" s="39" t="n"/>
       <c r="I9" s="39" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="39" t="n"/>
+      <c r="B10" s="39" t="n"/>
+      <c r="C10" s="39" t="n"/>
+      <c r="D10" s="39" t="n"/>
+      <c r="E10" s="39" t="n"/>
+      <c r="F10" s="39" t="n"/>
+      <c r="G10" s="39" t="n"/>
+      <c r="H10" s="39" t="n"/>
+      <c r="I10" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1397,7 +1463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1413,7 +1479,7 @@
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>周计划明细 · 4 人 × 12 周（V3：周次与 Sprint 分列 · A=需求+架构+开发分担）</t>
+          <t>周计划明细（V4：A=需求50% · E=架构+开发 · B/C/D 不变）※ 5 个角色 = 4 人编制（A 为 50% 投入），如需全职请确认</t>
         </is>
       </c>
     </row>
@@ -1479,12 +1545,12 @@
       </c>
       <c r="C5" s="26" t="inlineStr">
         <is>
-          <t>A·需求+架构+开发</t>
+          <t>A·需求(50%)</t>
         </is>
       </c>
       <c r="D5" s="27" t="inlineStr">
         <is>
-          <t>① 需求访谈×3 场（查询场景/附件/保留期/权限/审计）② BRD 初稿：业务流程图+功能清单+非功能需求 ③ 首系统选定（建议 Dspot）④ Azure 订阅确认</t>
+          <t>① 需求访谈×3 场（查询/附件/保留期/权限/审计）② BRD 初稿：流程图+功能清单+非功能需求 ③ 首系统选定（建议 Dspot）</t>
         </is>
       </c>
       <c r="E5" s="28" t="inlineStr">
@@ -1494,7 +1560,7 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>BRD 初稿可评审；首系统确认；订阅就绪</t>
+          <t>BRD 初稿可评审；首系统确认</t>
         </is>
       </c>
       <c r="G5" s="29" t="inlineStr">
@@ -1520,14 +1586,14 @@
           <t>Sprint 0</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
-        <is>
-          <t>B·数据工程</t>
+      <c r="C6" s="48" t="inlineStr">
+        <is>
+          <t>E·架构+开发</t>
         </is>
       </c>
       <c r="D6" s="27" t="inlineStr">
         <is>
-          <t>① Databricks Premium 工作区创建（或确认已有）② UC Catalog 结构设计 ③ Iceberg 分区策略设计 ④ SeaTunnel 本地 PoC 准备</t>
+          <t>① Azure 订阅与权限确认 ② 架构设计启动：组件清单/网络拓扑/UC 结构 ③ Azure CLI 脚本初始化（资源组/VNet/NAT）④ 与网络团队确认源库路径</t>
         </is>
       </c>
       <c r="E6" s="28" t="inlineStr">
@@ -1537,15 +1603,19 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>UC 结构设计文档；SeaTunnel 本地→Iceberg PoC 通过</t>
+          <t>架构文档初稿；CLI 骨架；网络方案确认</t>
         </is>
       </c>
       <c r="G6" s="29" t="inlineStr">
         <is>
-          <t>Databricks 开通周期</t>
-        </is>
-      </c>
-      <c r="H6" s="30" t="n"/>
+          <t>订阅权限</t>
+        </is>
+      </c>
+      <c r="H6" s="30" t="inlineStr">
+        <is>
+          <t>Kick-off</t>
+        </is>
+      </c>
       <c r="I6" s="39" t="n"/>
     </row>
     <row r="7" ht="44" customHeight="1">
@@ -1559,14 +1629,14 @@
           <t>Sprint 0</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
-        <is>
-          <t>C·全栈+DevOps</t>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>B·数据工程</t>
         </is>
       </c>
       <c r="D7" s="27" t="inlineStr">
         <is>
-          <t>① .NET 10 项目骨架 + Clean Architecture ② React 前端骨架 + 路由/布局 ③ Docker Compose 本地开发环境（SQL Server + Azurite 模拟 ADLS）④ GitHub Actions CI 骨架（build + test + push ACR）</t>
+          <t>① Databricks Premium 工作区创建（或确认已有）② UC Catalog 结构设计 ③ Iceberg 分区策略设计 ④ SeaTunnel 本地 PoC 准备</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
@@ -1576,12 +1646,12 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>本地可开发（docker compose up）；CI 推镜像成功</t>
+          <t>UC 结构设计文档；SeaTunnel 本地→Iceberg PoC 通过</t>
         </is>
       </c>
       <c r="G7" s="29" t="inlineStr">
         <is>
-          <t>ACR 先建好（A 的 CLI 脚本）</t>
+          <t>Databricks 开通周期</t>
         </is>
       </c>
       <c r="H7" s="30" t="n"/>
@@ -1598,42 +1668,38 @@
           <t>Sprint 0</t>
         </is>
       </c>
-      <c r="C8" s="33" t="inlineStr">
-        <is>
-          <t>D·QA+SLC文档</t>
+      <c r="C8" s="32" t="inlineStr">
+        <is>
+          <t>C·全栈+DevOps</t>
         </is>
       </c>
       <c r="D8" s="27" t="inlineStr">
         <is>
-          <t>① 测试计划初稿（功能/集成/性能/安全/UAT）② 架构图初稿：系统上下文图（C4-L1）+ 容器图（C4-L2）③ 项目文档模板定稿（详细设计/接口/用户手册/运维手册 4 套模板）④ UAT 场景清单初稿</t>
+          <t>① .NET 10 项目骨架 + Clean Architecture ② React 前端骨架 + 路由/布局 ③ Docker Compose 本地开发环境（SQL Server + Azurite 模拟 ADLS）④ GitHub Actions CI 骨架（build + test + push ACR）</t>
         </is>
       </c>
       <c r="E8" s="28" t="inlineStr">
         <is>
-          <t>🟡</t>
+          <t>🔴</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>测试计划初稿；架构图 2 张初稿；文档模板 4 套</t>
+          <t>本地可开发（docker compose up）；CI 推镜像成功</t>
         </is>
       </c>
       <c r="G8" s="29" t="inlineStr">
         <is>
-          <t>A 的 BRD 初稿（了解需求范围）</t>
-        </is>
-      </c>
-      <c r="H8" s="30" t="inlineStr">
-        <is>
-          <t>Kick-off 参加</t>
-        </is>
-      </c>
+          <t>ACR 先建好（A 的 CLI 脚本）</t>
+        </is>
+      </c>
+      <c r="H8" s="30" t="n"/>
       <c r="I8" s="39" t="n"/>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="40" t="inlineStr">
         <is>
-          <t>W2</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B9" s="41" t="inlineStr">
@@ -1641,34 +1707,34 @@
           <t>Sprint 0</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>A·需求+架构+开发</t>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>D·QA+SLC文档</t>
         </is>
       </c>
       <c r="D9" s="27" t="inlineStr">
         <is>
-          <t>① BRD 评审→定稿签字 ② 用户故事地图 + Sprint 1~6 验收标准 ③ 架构设计定稿（组件清单/网络拓扑/UC 结构）④ Azure CLI 完整脚本→Dev 部署（VNet/AKS/ADLS/SQL/KeyVault/AGW/PE/NCC）</t>
+          <t>① 测试计划初稿（功能/集成/性能/安全/UAT）② 架构图初稿：系统上下文图（C4-L1）+ 容器图（C4-L2）③ 项目文档模板定稿（详细设计/接口/用户手册/运维手册 4 套模板）④ UAT 场景清单初稿</t>
         </is>
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>🔴 ★</t>
+          <t>🟡</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>BRD 签字；架构文档；Dev 全套组件就绪</t>
+          <t>测试计划初稿；架构图 2 张初稿；文档模板 4 套</t>
         </is>
       </c>
       <c r="G9" s="29" t="inlineStr">
         <is>
-          <t>网络团队 NCC 路由</t>
+          <t>A 的 BRD 初稿（了解需求范围）</t>
         </is>
       </c>
       <c r="H9" s="30" t="inlineStr">
         <is>
-          <t>BRD 评审；S0 Review；S1 Planning</t>
+          <t>Kick-off 参加</t>
         </is>
       </c>
       <c r="I9" s="39" t="n"/>
@@ -1684,14 +1750,14 @@
           <t>Sprint 0</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
-        <is>
-          <t>B·数据工程</t>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>A·需求(50%)</t>
         </is>
       </c>
       <c r="D10" s="27" t="inlineStr">
         <is>
-          <t>① SeaTunnel→Iceberg PoC（连真实源库 SQL Server，Dspot）② RAW 层表创建 + 写入验证 ③ SQL Warehouse 查询验证 ④ PoC 结论记录</t>
+          <t>① BRD 评审→定稿签字 ② 用户故事地图 + Sprint 1~6 验收标准 ③ 优先级排序（MoSCoW）</t>
         </is>
       </c>
       <c r="E10" s="28" t="inlineStr">
@@ -1701,17 +1767,17 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>PoC 端到端：源库→SeaTunnel→Iceberg→SQL Warehouse 可查</t>
+          <t>BRD 签字；用户故事地图</t>
         </is>
       </c>
       <c r="G10" s="29" t="inlineStr">
         <is>
-          <t>源库只读账号 + NAT IP 白名单</t>
+          <t>业务方到场</t>
         </is>
       </c>
       <c r="H10" s="30" t="inlineStr">
         <is>
-          <t>Sprint 0 Review</t>
+          <t>BRD 评审；S0 Review</t>
         </is>
       </c>
       <c r="I10" s="39" t="n"/>
@@ -1727,14 +1793,14 @@
           <t>Sprint 0</t>
         </is>
       </c>
-      <c r="C11" s="32" t="inlineStr">
-        <is>
-          <t>C·全栈+DevOps</t>
+      <c r="C11" s="48" t="inlineStr">
+        <is>
+          <t>E·架构+开发</t>
         </is>
       </c>
       <c r="D11" s="27" t="inlineStr">
         <is>
-          <t>① CI/CD 完整流水线（自动测试→构建→推镜像→Helm 部署 AKS Dev）② Entra ID 应用注册 + OIDC ③ 后端认证中间件 ④ 前端登录页 + 系统列表页 ⑤ Helm Chart 初版</t>
+          <t>① 架构设计定稿（含部署图）② Azure CLI 完整脚本→Dev 部署（AKS/ADLS/SQL/KeyVault/AGW/PE/NCC）③ UC 权限矩阵（SP-query/SP-audit）</t>
         </is>
       </c>
       <c r="E11" s="28" t="inlineStr">
@@ -1744,17 +1810,17 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Pipeline 端到端自动部署成功；浏览器可登录看到列表页</t>
+          <t>架构文档 V1；Dev 全套组件就绪；UC 权限矩阵</t>
         </is>
       </c>
       <c r="G11" s="29" t="inlineStr">
         <is>
-          <t>Entra ID 管理员；AKS Dev 就绪</t>
+          <t>网络团队 NCC</t>
         </is>
       </c>
       <c r="H11" s="30" t="inlineStr">
         <is>
-          <t>Sprint 0 Review</t>
+          <t>S0 Review；S1 Planning</t>
         </is>
       </c>
       <c r="I11" s="39" t="n"/>
@@ -1770,29 +1836,29 @@
           <t>Sprint 0</t>
         </is>
       </c>
-      <c r="C12" s="33" t="inlineStr">
-        <is>
-          <t>D·QA+SLC文档</t>
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>B·数据工程</t>
         </is>
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>① 架构图完善：组件图（C4-L3）+ 部署图（Azure 拓扑）② 接口文档初稿（API 列表 + 请求/响应示例）③ 测试环境搭建（测试数据准备方案）④ 需求可追溯矩阵（BRD→测试用例映射）</t>
+          <t>① SeaTunnel→Iceberg PoC（连真实源库 SQL Server，Dspot）② RAW 层表创建 + 写入验证 ③ SQL Warehouse 查询验证 ④ PoC 结论记录</t>
         </is>
       </c>
       <c r="E12" s="28" t="inlineStr">
         <is>
-          <t>🟡</t>
+          <t>🔴 ★</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>架构图 4 张初稿（上下文/容器/组件/部署）；接口文档初稿</t>
+          <t>PoC 端到端：源库→SeaTunnel→Iceberg→SQL Warehouse 可查</t>
         </is>
       </c>
       <c r="G12" s="29" t="inlineStr">
         <is>
-          <t>A 的 BRD 定稿；C 的 API 骨架</t>
+          <t>源库只读账号 + NAT IP 白名单</t>
         </is>
       </c>
       <c r="H12" s="30" t="inlineStr">
@@ -1805,38 +1871,42 @@
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="40" t="inlineStr">
         <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="B13" s="42" t="inlineStr">
-        <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="C13" s="26" t="inlineStr">
-        <is>
-          <t>A·需求+架构+开发</t>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="B13" s="41" t="inlineStr">
+        <is>
+          <t>Sprint 0</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>C·全栈+DevOps</t>
         </is>
       </c>
       <c r="D13" s="27" t="inlineStr">
         <is>
-          <t>① Sprint 2 需求澄清（附件/掩码/多表 JOIN 细节）② 代码评审（B 生成器 + C API）③ Jobs API 触发方案 + SQL 安全方案 ④ 开始接手前端查询配置页开发</t>
+          <t>① CI/CD 完整流水线（自动测试→构建→推镜像→Helm 部署 AKS Dev）② Entra ID 应用注册 + OIDC ③ 后端认证中间件 ④ 前端登录页 + 系统列表页 ⑤ Helm Chart 初版</t>
         </is>
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>🟡</t>
+          <t>🔴 ★</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Sprint 2 需求就绪；ADR×2；查询配置页开发中</t>
-        </is>
-      </c>
-      <c r="G13" s="29" t="inlineStr"/>
+          <t>Pipeline 端到端自动部署成功；浏览器可登录看到列表页</t>
+        </is>
+      </c>
+      <c r="G13" s="29" t="inlineStr">
+        <is>
+          <t>Entra ID 管理员；AKS Dev 就绪</t>
+        </is>
+      </c>
       <c r="H13" s="30" t="inlineStr">
         <is>
-          <t>Daily Standup</t>
+          <t>Sprint 0 Review</t>
         </is>
       </c>
       <c r="I13" s="39" t="n"/>
@@ -1844,40 +1914,44 @@
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="40" t="inlineStr">
         <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="B14" s="42" t="inlineStr">
-        <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="C14" s="31" t="inlineStr">
-        <is>
-          <t>B·数据工程</t>
+          <t>W2</t>
+        </is>
+      </c>
+      <c r="B14" s="41" t="inlineStr">
+        <is>
+          <t>Sprint 0</t>
+        </is>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>D·QA+SLC文档</t>
         </is>
       </c>
       <c r="D14" s="27" t="inlineStr">
         <is>
-          <t>① SeaTunnel 配置生成器（读 source_table→生成 .conf→提交 K8s Job）② RAW→LAKE 直达转换 ③ 触发方式（后端调 K8s API 或 ADF）</t>
+          <t>① 架构图完善：组件图（C4-L3）+ 部署图（Azure 拓扑）② 接口文档初稿（API 列表 + 请求/响应示例）③ 测试环境搭建（测试数据准备方案）④ 需求可追溯矩阵（BRD→测试用例映射）</t>
         </is>
       </c>
       <c r="E14" s="28" t="inlineStr">
         <is>
-          <t>🔴</t>
+          <t>🟡</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>配置生成器跑通：选表→生成任务→数据进 RAW</t>
+          <t>架构图 4 张初稿（上下文/容器/组件/部署）；接口文档初稿</t>
         </is>
       </c>
       <c r="G14" s="29" t="inlineStr">
         <is>
-          <t>元数据库有测试数据</t>
-        </is>
-      </c>
-      <c r="H14" s="30" t="n"/>
+          <t>A 的 BRD 定稿；C 的 API 骨架</t>
+        </is>
+      </c>
+      <c r="H14" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 0 Review</t>
+        </is>
+      </c>
       <c r="I14" s="39" t="n"/>
     </row>
     <row r="15" ht="44" customHeight="1">
@@ -1891,32 +1965,32 @@
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="C15" s="32" t="inlineStr">
-        <is>
-          <t>C·全栈+DevOps</t>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>A·需求(50%)</t>
         </is>
       </c>
       <c r="D15" s="27" t="inlineStr">
         <is>
-          <t>① 核心 CRUD API：系统/源库/表清单/查询配置 ② 查询代理 API（→SQL Warehouse）③ Helm Chart 完善（后端+前端+Service+Ingress）④ 前端：查询配置管理页</t>
+          <t>① Sprint 2 需求澄清（附件/掩码/JOIN 细节）② 原型草图确认（查询页/配置页交互）</t>
         </is>
       </c>
       <c r="E15" s="28" t="inlineStr">
         <is>
-          <t>🔴</t>
+          <t>🟡</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>Postman API 全通；前端可配置查询字段</t>
-        </is>
-      </c>
-      <c r="G15" s="29" t="inlineStr">
-        <is>
-          <t>SQL Warehouse 连接串</t>
-        </is>
-      </c>
-      <c r="H15" s="30" t="n"/>
+          <t>S2 需求就绪；原型确认</t>
+        </is>
+      </c>
+      <c r="G15" s="29" t="inlineStr"/>
+      <c r="H15" s="30" t="inlineStr">
+        <is>
+          <t>S1 Planning</t>
+        </is>
+      </c>
       <c r="I15" s="39" t="n"/>
     </row>
     <row r="16" ht="44" customHeight="1">
@@ -1930,14 +2004,14 @@
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="C16" s="33" t="inlineStr">
-        <is>
-          <t>D·QA+SLC文档</t>
+      <c r="C16" s="48" t="inlineStr">
+        <is>
+          <t>E·架构+开发</t>
         </is>
       </c>
       <c r="D16" s="27" t="inlineStr">
         <is>
-          <t>① 单元测试框架搭建（xUnit + Mock）② API 集成测试（10 核心场景）③ E2E 测试骨架（Playwright）④ 详细设计文档初稿：应用层（API 设计 + 类图 + 时序图）</t>
+          <t>① 代码评审（B 生成器 + C API）② ADR：Jobs 触发方式 + SQL 安全方案 ③ 开始接手前端查询配置页开发</t>
         </is>
       </c>
       <c r="E16" s="28" t="inlineStr">
@@ -1947,21 +2021,21 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>CI 里自动跑测试 &gt;80%；应用层详细设计初稿</t>
-        </is>
-      </c>
-      <c r="G16" s="29" t="inlineStr">
-        <is>
-          <t>C 的 API 稳定</t>
-        </is>
-      </c>
-      <c r="H16" s="30" t="n"/>
+          <t>ADR×2；查询配置页开发中</t>
+        </is>
+      </c>
+      <c r="G16" s="29" t="inlineStr"/>
+      <c r="H16" s="30" t="inlineStr">
+        <is>
+          <t>Daily Standup</t>
+        </is>
+      </c>
       <c r="I16" s="39" t="n"/>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="40" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B17" s="42" t="inlineStr">
@@ -1969,42 +2043,38 @@
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
-        <is>
-          <t>A·需求+架构+开发</t>
+      <c r="C17" s="31" t="inlineStr">
+        <is>
+          <t>B·数据工程</t>
         </is>
       </c>
       <c r="D17" s="27" t="inlineStr">
         <is>
-          <t>① 端到端联调支撑 ② UC 权限落地（SP-query/SP-audit）③ 完成查询配置页开发并提测 ④ Sprint 3 需求澄清（Retention/审批/通知）</t>
+          <t>① SeaTunnel 配置生成器（读 source_table→生成 .conf→提交 K8s Job）② RAW→LAKE 直达转换 ③ 触发方式（后端调 K8s API 或 ADF）</t>
         </is>
       </c>
       <c r="E17" s="28" t="inlineStr">
         <is>
-          <t>🔴 ★</t>
+          <t>🔴</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>UC GRANT 成功；查询配置页上线；S3 需求就绪</t>
+          <t>配置生成器跑通：选表→生成任务→数据进 RAW</t>
         </is>
       </c>
       <c r="G17" s="29" t="inlineStr">
         <is>
-          <t>B 数据链路</t>
-        </is>
-      </c>
-      <c r="H17" s="30" t="inlineStr">
-        <is>
-          <t>S1 Review ★；S2 Planning</t>
-        </is>
-      </c>
+          <t>元数据库有测试数据</t>
+        </is>
+      </c>
+      <c r="H17" s="30" t="n"/>
       <c r="I17" s="39" t="n"/>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="40" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B18" s="42" t="inlineStr">
@@ -2012,38 +2082,38 @@
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="C18" s="31" t="inlineStr">
-        <is>
-          <t>B·数据工程</t>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>C·全栈+DevOps</t>
         </is>
       </c>
       <c r="D18" s="27" t="inlineStr">
         <is>
-          <t>① 端到端联调：源→SeaTunnel→RAW→LAKE→查询代理 ② 对账脚本（行数+校验和）③ Compaction 初版 ④ 增量方案确认</t>
+          <t>① 核心 CRUD API：系统/源库/表清单/查询配置 ② 查询代理 API（→SQL Warehouse）③ Helm Chart 完善（后端+前端+Service+Ingress）④ 前端：查询配置管理页</t>
         </is>
       </c>
       <c r="E18" s="28" t="inlineStr">
         <is>
-          <t>🔴 ★</t>
+          <t>🔴</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>1 张表端到端：源→查询页可查</t>
-        </is>
-      </c>
-      <c r="G18" s="29" t="n"/>
-      <c r="H18" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 1 Review</t>
-        </is>
-      </c>
+          <t>Postman API 全通；前端可配置查询字段</t>
+        </is>
+      </c>
+      <c r="G18" s="29" t="inlineStr">
+        <is>
+          <t>SQL Warehouse 连接串</t>
+        </is>
+      </c>
+      <c r="H18" s="30" t="n"/>
       <c r="I18" s="39" t="n"/>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="40" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B19" s="42" t="inlineStr">
@@ -2051,36 +2121,32 @@
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="C19" s="32" t="inlineStr">
-        <is>
-          <t>C·全栈+DevOps</t>
+      <c r="C19" s="33" t="inlineStr">
+        <is>
+          <t>D·QA+SLC文档</t>
         </is>
       </c>
       <c r="D19" s="27" t="inlineStr">
         <is>
-          <t>① 前端查询页（元数据驱动渲染：筛选/表格/分页）② 查询结果导出 CSV ③ 附件 URL 生成框架 ④ 前后端联调</t>
+          <t>① 单元测试框架搭建（xUnit + Mock）② API 集成测试（10 核心场景）③ E2E 测试骨架（Playwright）④ 详细设计文档初稿：应用层（API 设计 + 类图 + 时序图）</t>
         </is>
       </c>
       <c r="E19" s="28" t="inlineStr">
         <is>
-          <t>🔴 ★</t>
+          <t>🟡</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>登录→选系统→查表→看到数据</t>
+          <t>CI 里自动跑测试 &gt;80%；应用层详细设计初稿</t>
         </is>
       </c>
       <c r="G19" s="29" t="inlineStr">
         <is>
-          <t>查询代理就绪</t>
-        </is>
-      </c>
-      <c r="H19" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 1 Review ★ MVP 演示</t>
-        </is>
-      </c>
+          <t>C 的 API 稳定</t>
+        </is>
+      </c>
+      <c r="H19" s="30" t="n"/>
       <c r="I19" s="39" t="n"/>
     </row>
     <row r="20" ht="44" customHeight="1">
@@ -2094,30 +2160,30 @@
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="C20" s="33" t="inlineStr">
-        <is>
-          <t>D·QA+SLC文档</t>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>A·需求(50%)</t>
         </is>
       </c>
       <c r="D20" s="27" t="inlineStr">
         <is>
-          <t>① 集成测试执行 + Bug 跟踪 ② 详细设计初稿：数据层（Iceberg 表结构 + 四层转换逻辑 + ER 图）③ Sprint 1 测试报告 ④ 架构图更新（反映实际部署）</t>
+          <t>① Sprint 3 需求澄清（Retention/审批/通知）② 验收 Sprint 1 交付（对照用户故事）</t>
         </is>
       </c>
       <c r="E20" s="28" t="inlineStr">
         <is>
-          <t>🟡</t>
+          <t>🔴</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>测试报告；数据层详细设计初稿</t>
-        </is>
-      </c>
-      <c r="G20" s="29" t="n"/>
+          <t>S3 需求就绪；S1 验收记录</t>
+        </is>
+      </c>
+      <c r="G20" s="29" t="inlineStr"/>
       <c r="H20" s="30" t="inlineStr">
         <is>
-          <t>Sprint 1 Review</t>
+          <t>S1 Review ★</t>
         </is>
       </c>
       <c r="I20" s="39" t="n"/>
@@ -2125,42 +2191,42 @@
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="40" t="inlineStr">
         <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="B21" s="43" t="inlineStr">
-        <is>
-          <t>Sprint 2</t>
-        </is>
-      </c>
-      <c r="C21" s="26" t="inlineStr">
-        <is>
-          <t>A·需求+架构+开发</t>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="B21" s="42" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="C21" s="48" t="inlineStr">
+        <is>
+          <t>E·架构+开发</t>
         </is>
       </c>
       <c r="D21" s="27" t="inlineStr">
         <is>
-          <t>① 开发分担：前端附件预览模块（图片/音频/视频）② 代码评审（四层 SQL + 掩码函数）③ Sprint 4 需求澄清（UAT 场景/审批流程）</t>
+          <t>① UC 权限落地（GRANT 执行）② 完成查询配置页并提测 ③ 端到端联调支撑</t>
         </is>
       </c>
       <c r="E21" s="28" t="inlineStr">
         <is>
-          <t>🔴</t>
+          <t>🔴 ★</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>附件预览模块提测；S4 需求就绪</t>
+          <t>UC GRANT 成功；配置页提测</t>
         </is>
       </c>
       <c r="G21" s="29" t="inlineStr">
         <is>
-          <t>B 的 SERVE 数据</t>
+          <t>B 数据链路</t>
         </is>
       </c>
       <c r="H21" s="30" t="inlineStr">
         <is>
-          <t>Daily Standup</t>
+          <t>S1 Review ★</t>
         </is>
       </c>
       <c r="I21" s="39" t="n"/>
@@ -2168,12 +2234,12 @@
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="40" t="inlineStr">
         <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="B22" s="43" t="inlineStr">
-        <is>
-          <t>Sprint 2</t>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="B22" s="42" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
         </is>
       </c>
       <c r="C22" s="31" t="inlineStr">
@@ -2183,36 +2249,36 @@
       </c>
       <c r="D22" s="27" t="inlineStr">
         <is>
-          <t>① CURATED：类型统一/SHA-256/分区归约 ② LAKE：建模+生命周期分区 ③ SERVE：物化+Z-Order ④ 四层 Jobs（多 Task 依赖）</t>
+          <t>① 端到端联调：源→SeaTunnel→RAW→LAKE→查询代理 ② 对账脚本（行数+校验和）③ Compaction 初版 ④ 增量方案确认</t>
         </is>
       </c>
       <c r="E22" s="28" t="inlineStr">
         <is>
-          <t>🔴</t>
+          <t>🔴 ★</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>四层转换 Jobs 跑通；SERVE 可查</t>
-        </is>
-      </c>
-      <c r="G22" s="29" t="inlineStr">
-        <is>
-          <t>A 的层设计评审</t>
-        </is>
-      </c>
-      <c r="H22" s="30" t="n"/>
+          <t>1 张表端到端：源→查询页可查</t>
+        </is>
+      </c>
+      <c r="G22" s="29" t="n"/>
+      <c r="H22" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 1 Review</t>
+        </is>
+      </c>
       <c r="I22" s="39" t="n"/>
     </row>
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="40" t="inlineStr">
         <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="B23" s="43" t="inlineStr">
-        <is>
-          <t>Sprint 2</t>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="B23" s="42" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
         </is>
       </c>
       <c r="C23" s="32" t="inlineStr">
@@ -2222,36 +2288,40 @@
       </c>
       <c r="D23" s="27" t="inlineStr">
         <is>
-          <t>① 前端配置化查询完善（动态列/排序/筛选联动）② 附件预览：图片/音频/视频 ③ 权限渲染（无权限列隐藏）④ CI/CD 完善（多环境 Dev/Staging）</t>
+          <t>① 前端查询页（元数据驱动渲染：筛选/表格/分页）② 查询结果导出 CSV ③ 附件 URL 生成框架 ④ 前后端联调</t>
         </is>
       </c>
       <c r="E23" s="28" t="inlineStr">
         <is>
-          <t>🔴</t>
+          <t>🔴 ★</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>前端全功能可用；附件可预览</t>
+          <t>登录→选系统→查表→看到数据</t>
         </is>
       </c>
       <c r="G23" s="29" t="inlineStr">
         <is>
-          <t>B 的 SERVE 数据</t>
-        </is>
-      </c>
-      <c r="H23" s="30" t="n"/>
+          <t>查询代理就绪</t>
+        </is>
+      </c>
+      <c r="H23" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 1 Review ★ MVP 演示</t>
+        </is>
+      </c>
       <c r="I23" s="39" t="n"/>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="40" t="inlineStr">
         <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="B24" s="43" t="inlineStr">
-        <is>
-          <t>Sprint 2</t>
+          <t>W4</t>
+        </is>
+      </c>
+      <c r="B24" s="42" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
         </is>
       </c>
       <c r="C24" s="33" t="inlineStr">
@@ -2261,7 +2331,7 @@
       </c>
       <c r="D24" s="27" t="inlineStr">
         <is>
-          <t>① 功能测试用例扩充（50+ 场景）② 自动化测试覆盖率 &gt;60% ③ 安全测试（SQL 注入/XSS/越权）④ 详细设计：安全层（认证/授权/加密/审计 + 掩码函数时序图）</t>
+          <t>① 集成测试执行 + Bug 跟踪 ② 详细设计初稿：数据层（Iceberg 表结构 + 四层转换逻辑 + ER 图）③ Sprint 1 测试报告 ④ 架构图更新（反映实际部署）</t>
         </is>
       </c>
       <c r="E24" s="28" t="inlineStr">
@@ -2271,21 +2341,21 @@
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>测试用例 50+；安全测试报告；安全层设计初稿</t>
-        </is>
-      </c>
-      <c r="G24" s="29" t="inlineStr">
-        <is>
-          <t>C 的功能可用</t>
-        </is>
-      </c>
-      <c r="H24" s="30" t="n"/>
+          <t>测试报告；数据层详细设计初稿</t>
+        </is>
+      </c>
+      <c r="G24" s="29" t="n"/>
+      <c r="H24" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 1 Review</t>
+        </is>
+      </c>
       <c r="I24" s="39" t="n"/>
     </row>
     <row r="25" ht="44" customHeight="1">
       <c r="A25" s="40" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B25" s="43" t="inlineStr">
@@ -2295,28 +2365,28 @@
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>A·需求+架构+开发</t>
+          <t>A·需求(50%)</t>
         </is>
       </c>
       <c r="D25" s="27" t="inlineStr">
         <is>
-          <t>① 开发分担：多表 JOIN 前端渲染 ② 权限端到端测试组织（明文/掩码）③ 第二系统选型确认 + 源库协调 ④ Sprint 2 验收支撑</t>
+          <t>① Sprint 4 需求澄清（UAT 场景/审批流程）② 验收 Sprint 2 交付</t>
         </is>
       </c>
       <c r="E25" s="28" t="inlineStr">
         <is>
-          <t>🔴 ★</t>
+          <t>🟡</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>JOIN 渲染提测；第二系统确认</t>
+          <t>S4 需求就绪；S2 验收记录</t>
         </is>
       </c>
       <c r="G25" s="29" t="inlineStr"/>
       <c r="H25" s="30" t="inlineStr">
         <is>
-          <t>S2 Review；S3 Planning</t>
+          <t>S2 Review</t>
         </is>
       </c>
       <c r="I25" s="39" t="n"/>
@@ -2324,7 +2394,7 @@
     <row r="26" ht="44" customHeight="1">
       <c r="A26" s="40" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B26" s="43" t="inlineStr">
@@ -2332,34 +2402,30 @@
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="C26" s="31" t="inlineStr">
-        <is>
-          <t>B·数据工程</t>
+      <c r="C26" s="48" t="inlineStr">
+        <is>
+          <t>E·架构+开发</t>
         </is>
       </c>
       <c r="D26" s="27" t="inlineStr">
         <is>
-          <t>① 附件：Storage Mover + attachment_index + SHA-256 ② UC 掩码函数部署 ③ Compaction/VACUUM 定时 ④ 性能优化</t>
+          <t>① 开发分担：前端附件预览模块 ② 代码评审（四层 SQL + 掩码函数）③ 密钥体系设计（Key Vault DEK/KEK）</t>
         </is>
       </c>
       <c r="E26" s="28" t="inlineStr">
         <is>
-          <t>🔴 ★</t>
+          <t>🔴</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>附件端到端；掩码查询正常</t>
-        </is>
-      </c>
-      <c r="G26" s="29" t="inlineStr">
-        <is>
-          <t>Storage Mover 网络</t>
-        </is>
-      </c>
+          <t>附件预览提测；密钥设计文档</t>
+        </is>
+      </c>
+      <c r="G26" s="29" t="inlineStr"/>
       <c r="H26" s="30" t="inlineStr">
         <is>
-          <t>Sprint 2 Review</t>
+          <t>Daily Standup</t>
         </is>
       </c>
       <c r="I26" s="39" t="n"/>
@@ -2367,7 +2433,7 @@
     <row r="27" ht="44" customHeight="1">
       <c r="A27" s="40" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B27" s="43" t="inlineStr">
@@ -2375,38 +2441,38 @@
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="C27" s="32" t="inlineStr">
-        <is>
-          <t>C·全栈+DevOps</t>
+      <c r="C27" s="31" t="inlineStr">
+        <is>
+          <t>B·数据工程</t>
         </is>
       </c>
       <c r="D27" s="27" t="inlineStr">
         <is>
-          <t>① 多表 JOIN（query_join→动态 SQL）② 下钻（drill_config→父子导航）③ 导出完善 ④ Bug 修复</t>
+          <t>① CURATED：类型统一/SHA-256/分区归约 ② LAKE：建模+生命周期分区 ③ SERVE：物化+Z-Order ④ 四层 Jobs（多 Task 依赖）</t>
         </is>
       </c>
       <c r="E27" s="28" t="inlineStr">
         <is>
-          <t>🔴 ★</t>
+          <t>🔴</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>JOIN+下钻+掩码隐藏全部可用</t>
-        </is>
-      </c>
-      <c r="G27" s="29" t="n"/>
-      <c r="H27" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 2 Review</t>
-        </is>
-      </c>
+          <t>四层转换 Jobs 跑通；SERVE 可查</t>
+        </is>
+      </c>
+      <c r="G27" s="29" t="inlineStr">
+        <is>
+          <t>A 的层设计评审</t>
+        </is>
+      </c>
+      <c r="H27" s="30" t="n"/>
       <c r="I27" s="39" t="n"/>
     </row>
     <row r="28" ht="44" customHeight="1">
       <c r="A28" s="40" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="B28" s="43" t="inlineStr">
@@ -2414,100 +2480,92 @@
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="C28" s="33" t="inlineStr">
-        <is>
-          <t>D·QA+SLC文档</t>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>C·全栈+DevOps</t>
         </is>
       </c>
       <c r="D28" s="27" t="inlineStr">
         <is>
-          <t>① 功能测试全量执行 ② 性能测试（100 万行 P95&lt;5s）③ 详细设计终稿（3 模块合稿：应用+数据+安全）④ 接口文档完善 ⑤ Sprint 2 测试报告</t>
+          <t>① 前端配置化查询完善（动态列/排序/筛选联动）② 附件预览：图片/音频/视频 ③ 权限渲染（无权限列隐藏）④ CI/CD 完善（多环境 Dev/Staging）</t>
         </is>
       </c>
       <c r="E28" s="28" t="inlineStr">
         <is>
-          <t>🟡</t>
+          <t>🔴</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
         <is>
-          <t>性能报告；详细设计 3 模块合稿</t>
+          <t>前端全功能可用；附件可预览</t>
         </is>
       </c>
       <c r="G28" s="29" t="inlineStr">
         <is>
-          <t>性能数据由 B 准备</t>
-        </is>
-      </c>
-      <c r="H28" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 2 Review</t>
-        </is>
-      </c>
+          <t>B 的 SERVE 数据</t>
+        </is>
+      </c>
+      <c r="H28" s="30" t="n"/>
       <c r="I28" s="39" t="n"/>
     </row>
     <row r="29" ht="44" customHeight="1">
       <c r="A29" s="40" t="inlineStr">
         <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B29" s="44" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="C29" s="26" t="inlineStr">
-        <is>
-          <t>A·需求+架构+开发</t>
+          <t>W5</t>
+        </is>
+      </c>
+      <c r="B29" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C29" s="33" t="inlineStr">
+        <is>
+          <t>D·QA+SLC文档</t>
         </is>
       </c>
       <c r="D29" s="27" t="inlineStr">
         <is>
-          <t>① 开发分担：Retention 策略配置界面（后端 API + 前端）② Retention 流程评审（含销毁审批设计）③ 业务方确认保留期合规底线</t>
+          <t>① 功能测试用例扩充（50+ 场景）② 自动化测试覆盖率 &gt;60% ③ 安全测试（SQL 注入/XSS/越权）④ 详细设计：安全层（认证/授权/加密/审计 + 掩码函数时序图）</t>
         </is>
       </c>
       <c r="E29" s="28" t="inlineStr">
         <is>
-          <t>🔴</t>
+          <t>🟡</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Retention 界面开发中；流程评审通过</t>
+          <t>测试用例 50+；安全测试报告；安全层设计初稿</t>
         </is>
       </c>
       <c r="G29" s="29" t="inlineStr">
         <is>
-          <t>法务保留期底线</t>
-        </is>
-      </c>
-      <c r="H29" s="30" t="inlineStr">
-        <is>
-          <t>Daily Standup</t>
-        </is>
-      </c>
+          <t>C 的功能可用</t>
+        </is>
+      </c>
+      <c r="H29" s="30" t="n"/>
       <c r="I29" s="39" t="n"/>
     </row>
     <row r="30" ht="44" customHeight="1">
       <c r="A30" s="40" t="inlineStr">
         <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B30" s="44" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="C30" s="31" t="inlineStr">
-        <is>
-          <t>B·数据工程</t>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="B30" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>A·需求(50%)</t>
         </is>
       </c>
       <c r="D30" s="27" t="inlineStr">
         <is>
-          <t>① 到期扫描 Job ② DROP PARTITION + VACUUM（Databricks 原生 cron）③ 销毁结果回写 + 审计 ④ 通知集成</t>
+          <t>① 第二系统选型协调（业务方确认+源库对接）② 验收 Sprint 2 剩余项</t>
         </is>
       </c>
       <c r="E30" s="28" t="inlineStr">
@@ -2517,106 +2575,118 @@
       </c>
       <c r="F30" s="9" t="inlineStr">
         <is>
-          <t>测试环境完整销毁回路跑通</t>
-        </is>
-      </c>
-      <c r="G30" s="29" t="n"/>
-      <c r="H30" s="30" t="n"/>
+          <t>第二系统确认</t>
+        </is>
+      </c>
+      <c r="G30" s="29" t="inlineStr"/>
+      <c r="H30" s="30" t="inlineStr">
+        <is>
+          <t>S3 Planning</t>
+        </is>
+      </c>
       <c r="I30" s="39" t="n"/>
     </row>
     <row r="31" ht="44" customHeight="1">
       <c r="A31" s="40" t="inlineStr">
         <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B31" s="44" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="C31" s="32" t="inlineStr">
-        <is>
-          <t>C·全栈+DevOps</t>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="B31" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C31" s="48" t="inlineStr">
+        <is>
+          <t>E·架构+开发</t>
         </is>
       </c>
       <c r="D31" s="27" t="inlineStr">
         <is>
-          <t>① Retention 策略配置界面 ② 销毁审批界面 ③ 通知中心（站内+邮件）④ Dashboard（同步活跃度图表）</t>
+          <t>① 开发分担：多表 JOIN 前端渲染 ② 权限端到端测试组织 ③ Sprint 2 架构支撑</t>
         </is>
       </c>
       <c r="E31" s="28" t="inlineStr">
         <is>
-          <t>🔴</t>
+          <t>🔴 ★</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Retention 全流程 UI 可操作</t>
-        </is>
-      </c>
-      <c r="G31" s="29" t="inlineStr">
-        <is>
-          <t>B 的销毁 Job</t>
-        </is>
-      </c>
-      <c r="H31" s="30" t="n"/>
+          <t>JOIN 渲染提测</t>
+        </is>
+      </c>
+      <c r="G31" s="29" t="inlineStr"/>
+      <c r="H31" s="30" t="inlineStr">
+        <is>
+          <t>S2 Review；S3 Planning</t>
+        </is>
+      </c>
       <c r="I31" s="39" t="n"/>
     </row>
     <row r="32" ht="44" customHeight="1">
       <c r="A32" s="40" t="inlineStr">
         <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B32" s="44" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="C32" s="33" t="inlineStr">
-        <is>
-          <t>D·QA+SLC文档</t>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="B32" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="inlineStr">
+        <is>
+          <t>B·数据工程</t>
         </is>
       </c>
       <c r="D32" s="27" t="inlineStr">
         <is>
-          <t>① 销毁流程 E2E 测试 ② 通知功能测试 ③ Dashboard 数据验证 ④ 用户手册初稿（含截图 30+）⑤ 第二系统接入测试准备</t>
+          <t>① 附件：Storage Mover + attachment_index + SHA-256 ② UC 掩码函数部署 ③ Compaction/VACUUM 定时 ④ 性能优化</t>
         </is>
       </c>
       <c r="E32" s="28" t="inlineStr">
         <is>
-          <t>🟡</t>
+          <t>🔴 ★</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>销毁 E2E 报告；用户手册初稿（50% 完成）</t>
-        </is>
-      </c>
-      <c r="G32" s="29" t="n"/>
-      <c r="H32" s="30" t="n"/>
+          <t>附件端到端；掩码查询正常</t>
+        </is>
+      </c>
+      <c r="G32" s="29" t="inlineStr">
+        <is>
+          <t>Storage Mover 网络</t>
+        </is>
+      </c>
+      <c r="H32" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 2 Review</t>
+        </is>
+      </c>
       <c r="I32" s="39" t="n"/>
     </row>
     <row r="33" ht="44" customHeight="1">
       <c r="A33" s="40" t="inlineStr">
         <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B33" s="44" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="C33" s="26" t="inlineStr">
-        <is>
-          <t>A·需求+架构+开发</t>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="B33" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="inlineStr">
+        <is>
+          <t>C·全栈+DevOps</t>
         </is>
       </c>
       <c r="D33" s="27" t="inlineStr">
         <is>
-          <t>① 完成 Retention + 审批界面并提测 ② 第二系统零代码接入验证（标准流程走一遍）③ 集成测试统筹</t>
+          <t>① 多表 JOIN（query_join→动态 SQL）② 下钻（drill_config→父子导航）③ 导出完善 ④ Bug 修复</t>
         </is>
       </c>
       <c r="E33" s="28" t="inlineStr">
@@ -2626,17 +2696,13 @@
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>第二系统零代码接入 &lt;2h；Retention 全流程可测</t>
-        </is>
-      </c>
-      <c r="G33" s="29" t="inlineStr">
-        <is>
-          <t>第二系统账号</t>
-        </is>
-      </c>
+          <t>JOIN+下钻+掩码隐藏全部可用</t>
+        </is>
+      </c>
+      <c r="G33" s="29" t="n"/>
       <c r="H33" s="30" t="inlineStr">
         <is>
-          <t>S3 Review；S4 Planning</t>
+          <t>Sprint 2 Review</t>
         </is>
       </c>
       <c r="I33" s="39" t="n"/>
@@ -2644,38 +2710,42 @@
     <row r="34" ht="44" customHeight="1">
       <c r="A34" s="40" t="inlineStr">
         <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B34" s="44" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="C34" s="31" t="inlineStr">
-        <is>
-          <t>B·数据工程</t>
+          <t>W6</t>
+        </is>
+      </c>
+      <c r="B34" s="43" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="C34" s="33" t="inlineStr">
+        <is>
+          <t>D·QA+SLC文档</t>
         </is>
       </c>
       <c r="D34" s="27" t="inlineStr">
         <is>
-          <t>① 第二系统 SeaTunnel+四层+SERVE ② 两系统联邦查询 ③ 性能调优</t>
+          <t>① 功能测试全量执行 ② 性能测试（100 万行 P95&lt;5s）③ 详细设计终稿（3 模块合稿：应用+数据+安全）④ 接口文档完善 ⑤ Sprint 2 测试报告</t>
         </is>
       </c>
       <c r="E34" s="28" t="inlineStr">
         <is>
-          <t>🔴 ★</t>
+          <t>🟡</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>第二系统端到端可查</t>
-        </is>
-      </c>
-      <c r="G34" s="29" t="n"/>
+          <t>性能报告；详细设计 3 模块合稿</t>
+        </is>
+      </c>
+      <c r="G34" s="29" t="inlineStr">
+        <is>
+          <t>性能数据由 B 准备</t>
+        </is>
+      </c>
       <c r="H34" s="30" t="inlineStr">
         <is>
-          <t>Sprint 3 Review</t>
+          <t>Sprint 2 Review</t>
         </is>
       </c>
       <c r="I34" s="39" t="n"/>
@@ -2683,7 +2753,7 @@
     <row r="35" ht="44" customHeight="1">
       <c r="A35" s="40" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B35" s="44" t="inlineStr">
@@ -2691,30 +2761,34 @@
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="C35" s="32" t="inlineStr">
-        <is>
-          <t>C·全栈+DevOps</t>
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>A·需求(50%)</t>
         </is>
       </c>
       <c r="D35" s="27" t="inlineStr">
         <is>
-          <t>① 第二系统前端配置（零代码）② 跨系统联邦查询测试 ③ 前端性能优化 ④ Bug 修复</t>
+          <t>① 验收 Sprint 3 交付（销毁流程对照合规要求）② UAT 场景脚本初稿</t>
         </is>
       </c>
       <c r="E35" s="28" t="inlineStr">
         <is>
-          <t>🔴 ★</t>
+          <t>🔴</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>第二系统查询页零代码上线</t>
-        </is>
-      </c>
-      <c r="G35" s="29" t="n"/>
+          <t>S3 验收记录；UAT 脚本初稿</t>
+        </is>
+      </c>
+      <c r="G35" s="29" t="inlineStr">
+        <is>
+          <t>法务保留期底线</t>
+        </is>
+      </c>
       <c r="H35" s="30" t="inlineStr">
         <is>
-          <t>Sprint 3 Review</t>
+          <t>Daily Standup</t>
         </is>
       </c>
       <c r="I35" s="39" t="n"/>
@@ -2722,7 +2796,7 @@
     <row r="36" ht="44" customHeight="1">
       <c r="A36" s="40" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B36" s="44" t="inlineStr">
@@ -2730,30 +2804,30 @@
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="C36" s="33" t="inlineStr">
-        <is>
-          <t>D·QA+SLC文档</t>
+      <c r="C36" s="48" t="inlineStr">
+        <is>
+          <t>E·架构+开发</t>
         </is>
       </c>
       <c r="D36" s="27" t="inlineStr">
         <is>
-          <t>① 全量回归测试（S1+S2+S3）② 性能测试（20GB P95&lt;5s）③ 用户手册完善（80%）④ 运维手册初稿 ⑤ 数据字典初稿 ⑥ Sprint 3 测试报告 ⑦ UAT 场景脚本</t>
+          <t>① 开发分担：Retention 后端 API ② Retention 流程架构评审 ③ Monitor 告警规则设计</t>
         </is>
       </c>
       <c r="E36" s="28" t="inlineStr">
         <is>
-          <t>🟡</t>
+          <t>🔴</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
         <is>
-          <t>回归全通过；用户手册 80%；运维手册初稿；数据字典初稿</t>
-        </is>
-      </c>
-      <c r="G36" s="29" t="n"/>
+          <t>Retention API 提测；告警规则清单</t>
+        </is>
+      </c>
+      <c r="G36" s="29" t="inlineStr"/>
       <c r="H36" s="30" t="inlineStr">
         <is>
-          <t>Sprint 3 Review</t>
+          <t>Daily Standup</t>
         </is>
       </c>
       <c r="I36" s="39" t="n"/>
@@ -2761,22 +2835,22 @@
     <row r="37" ht="44" customHeight="1">
       <c r="A37" s="40" t="inlineStr">
         <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B37" s="45" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>A·需求+架构+开发</t>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B37" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C37" s="31" t="inlineStr">
+        <is>
+          <t>B·数据工程</t>
         </is>
       </c>
       <c r="D37" s="27" t="inlineStr">
         <is>
-          <t>① 生产环境部署（CLI 脚本执行 + 验证）② 安全评审材料（等保/个保法对照表）③ 生产域名/证书/网络确认 ④ 全量迁移方案定稿</t>
+          <t>① 到期扫描 Job ② DROP PARTITION + VACUUM（Databricks 原生 cron）③ 销毁结果回写 + 审计 ④ 通知集成</t>
         </is>
       </c>
       <c r="E37" s="28" t="inlineStr">
@@ -2786,40 +2860,32 @@
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>生产就绪；安全材料初稿；迁移方案</t>
-        </is>
-      </c>
-      <c r="G37" s="29" t="inlineStr">
-        <is>
-          <t>生产订阅；证书</t>
-        </is>
-      </c>
-      <c r="H37" s="30" t="inlineStr">
-        <is>
-          <t>Daily Standup</t>
-        </is>
-      </c>
+          <t>测试环境完整销毁回路跑通</t>
+        </is>
+      </c>
+      <c r="G37" s="29" t="n"/>
+      <c r="H37" s="30" t="n"/>
       <c r="I37" s="39" t="n"/>
     </row>
     <row r="38" ht="44" customHeight="1">
       <c r="A38" s="40" t="inlineStr">
         <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B38" s="45" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="C38" s="31" t="inlineStr">
-        <is>
-          <t>B·数据工程</t>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B38" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C38" s="32" t="inlineStr">
+        <is>
+          <t>C·全栈+DevOps</t>
         </is>
       </c>
       <c r="D38" s="27" t="inlineStr">
         <is>
-          <t>① 首系统全量迁移执行（含对账）② 生产 Jobs 部署 ③ 生产 UC 权限配置</t>
+          <t>① Retention 策略配置界面 ② 销毁审批界面 ③ 通知中心（站内+邮件）④ Dashboard（同步活跃度图表）</t>
         </is>
       </c>
       <c r="E38" s="28" t="inlineStr">
@@ -2829,12 +2895,12 @@
       </c>
       <c r="F38" s="9" t="inlineStr">
         <is>
-          <t>首系统全量入湖；对账通过</t>
+          <t>Retention 全流程 UI 可操作</t>
         </is>
       </c>
       <c r="G38" s="29" t="inlineStr">
         <is>
-          <t>生产环境就绪</t>
+          <t>B 的销毁 Job</t>
         </is>
       </c>
       <c r="H38" s="30" t="n"/>
@@ -2843,96 +2909,96 @@
     <row r="39" ht="44" customHeight="1">
       <c r="A39" s="40" t="inlineStr">
         <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B39" s="45" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="C39" s="32" t="inlineStr">
-        <is>
-          <t>C·全栈+DevOps</t>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="B39" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C39" s="33" t="inlineStr">
+        <is>
+          <t>D·QA+SLC文档</t>
         </is>
       </c>
       <c r="D39" s="27" t="inlineStr">
         <is>
-          <t>① 生产 AKS 部署（Helm Release）② 生产 SSO 配置 ③ 首系统查询页生产配置 ④ 性能监控接入</t>
+          <t>① 销毁流程 E2E 测试 ② 通知功能测试 ③ Dashboard 数据验证 ④ 用户手册初稿（含截图 30+）⑤ 第二系统接入测试准备</t>
         </is>
       </c>
       <c r="E39" s="28" t="inlineStr">
         <is>
-          <t>🔴</t>
+          <t>🟡</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>生产可访问；SSO 正常；查询可用</t>
-        </is>
-      </c>
-      <c r="G39" s="29" t="inlineStr">
-        <is>
-          <t>生产域名</t>
-        </is>
-      </c>
+          <t>销毁 E2E 报告；用户手册初稿（50% 完成）</t>
+        </is>
+      </c>
+      <c r="G39" s="29" t="n"/>
       <c r="H39" s="30" t="n"/>
       <c r="I39" s="39" t="n"/>
     </row>
     <row r="40" ht="44" customHeight="1">
       <c r="A40" s="40" t="inlineStr">
         <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B40" s="45" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="C40" s="33" t="inlineStr">
-        <is>
-          <t>D·QA+SLC文档</t>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="B40" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>A·需求(50%)</t>
         </is>
       </c>
       <c r="D40" s="27" t="inlineStr">
         <is>
-          <t>① 文档冲刺启动：用户手册终版 + 运维手册终版 + 数据字典终版 ② 架构图终版（4 张全更新到生产实际）③ 详细设计终版 ④ 接口文档终版 ⑤ 审批材料包准备（技术方案/安全评估/合规对照/验收报告）</t>
+          <t>① UAT 场景脚本定稿（5 场景+步骤+期望结果）② 验收 Sprint 3 剩余项</t>
         </is>
       </c>
       <c r="E40" s="28" t="inlineStr">
         <is>
-          <t>🔴</t>
+          <t>🟡</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>6 套文档进入终审（用户/运维/架构×4/详细设计/接口/数据字典）；审批材料初稿</t>
-        </is>
-      </c>
-      <c r="G40" s="29" t="n"/>
-      <c r="H40" s="30" t="n"/>
+          <t>UAT 脚本定稿</t>
+        </is>
+      </c>
+      <c r="G40" s="29" t="inlineStr"/>
+      <c r="H40" s="30" t="inlineStr">
+        <is>
+          <t>S4 Planning</t>
+        </is>
+      </c>
       <c r="I40" s="39" t="n"/>
     </row>
     <row r="41" ht="44" customHeight="1">
       <c r="A41" s="40" t="inlineStr">
         <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="B41" s="45" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="C41" s="26" t="inlineStr">
-        <is>
-          <t>A·需求+架构+开发</t>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="B41" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="C41" s="48" t="inlineStr">
+        <is>
+          <t>E·架构+开发</t>
         </is>
       </c>
       <c r="D41" s="27" t="inlineStr">
         <is>
-          <t>① UAT 组织（5 场景 + 业务方验收）② UAT 反馈处理与优先级排序 ③ 安全评审提交 ④ 审批文档定稿</t>
+          <t>① 完成 Retention+审批界面并提测 ② 第二系统零代码接入验证 ③ 集成测试统筹</t>
         </is>
       </c>
       <c r="E41" s="28" t="inlineStr">
@@ -2942,17 +3008,17 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>UAT 签字；审批材料提交</t>
+          <t>第二系统接入 &lt;2h</t>
         </is>
       </c>
       <c r="G41" s="29" t="inlineStr">
         <is>
-          <t>业务方 UAT</t>
+          <t>第二系统账号</t>
         </is>
       </c>
       <c r="H41" s="30" t="inlineStr">
         <is>
-          <t>S4 Review（UAT）；S5 Planning</t>
+          <t>S3 Review；S4 Planning</t>
         </is>
       </c>
       <c r="I41" s="39" t="n"/>
@@ -2960,12 +3026,12 @@
     <row r="42" ht="44" customHeight="1">
       <c r="A42" s="40" t="inlineStr">
         <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="B42" s="45" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="B42" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="C42" s="31" t="inlineStr">
@@ -2975,23 +3041,23 @@
       </c>
       <c r="D42" s="27" t="inlineStr">
         <is>
-          <t>① UAT 支撑 ② 第二系统全量迁移准备 ③ 生产 Compaction 首次执行 ④ 销毁回路生产验证</t>
+          <t>① 第二系统 SeaTunnel+四层+SERVE ② 两系统联邦查询 ③ 性能调优</t>
         </is>
       </c>
       <c r="E42" s="28" t="inlineStr">
         <is>
-          <t>🟡</t>
+          <t>🔴 ★</t>
         </is>
       </c>
       <c r="F42" s="9" t="inlineStr">
         <is>
-          <t>UAT 数据问题全解决</t>
+          <t>第二系统端到端可查</t>
         </is>
       </c>
       <c r="G42" s="29" t="n"/>
       <c r="H42" s="30" t="inlineStr">
         <is>
-          <t>Sprint 4 Review</t>
+          <t>Sprint 3 Review</t>
         </is>
       </c>
       <c r="I42" s="39" t="n"/>
@@ -2999,12 +3065,12 @@
     <row r="43" ht="44" customHeight="1">
       <c r="A43" s="40" t="inlineStr">
         <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="B43" s="45" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="B43" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="C43" s="32" t="inlineStr">
@@ -3014,23 +3080,23 @@
       </c>
       <c r="D43" s="27" t="inlineStr">
         <is>
-          <t>① UAT Bug 修复 ② 生产监控 Dashboard ③ 性能微调 ④ 文档截图更新</t>
+          <t>① 第二系统前端配置（零代码）② 跨系统联邦查询测试 ③ 前端性能优化 ④ Bug 修复</t>
         </is>
       </c>
       <c r="E43" s="28" t="inlineStr">
         <is>
-          <t>🟡</t>
+          <t>🔴 ★</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>UAT Bug 全关闭；截图一致</t>
+          <t>第二系统查询页零代码上线</t>
         </is>
       </c>
       <c r="G43" s="29" t="n"/>
       <c r="H43" s="30" t="inlineStr">
         <is>
-          <t>Sprint 4 Review</t>
+          <t>Sprint 3 Review</t>
         </is>
       </c>
       <c r="I43" s="39" t="n"/>
@@ -3038,12 +3104,12 @@
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="40" t="inlineStr">
         <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="B44" s="45" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="B44" s="44" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
         </is>
       </c>
       <c r="C44" s="33" t="inlineStr">
@@ -3053,27 +3119,23 @@
       </c>
       <c r="D44" s="27" t="inlineStr">
         <is>
-          <t>① UAT 执行协调 + 结果记录 ② 文档终审（6 套 + 审批包 = 7 套）③ 上线 Checklist ④ 培训材料（业务用户 + 运维团队）</t>
+          <t>① 全量回归测试（S1+S2+S3）② 性能测试（20GB P95&lt;5s）③ 用户手册完善（80%）④ 运维手册初稿 ⑤ 数据字典初稿 ⑥ Sprint 3 测试报告 ⑦ UAT 场景脚本</t>
         </is>
       </c>
       <c r="E44" s="28" t="inlineStr">
         <is>
-          <t>🔴 ★</t>
+          <t>🟡</t>
         </is>
       </c>
       <c r="F44" s="9" t="inlineStr">
         <is>
-          <t>7 套文档终版；上线 Checklist 评审通过；培训 PPT + 演练脚本</t>
-        </is>
-      </c>
-      <c r="G44" s="29" t="inlineStr">
-        <is>
-          <t>审批方反馈</t>
-        </is>
-      </c>
+          <t>回归全通过；用户手册 80%；运维手册初稿；数据字典初稿</t>
+        </is>
+      </c>
+      <c r="G44" s="29" t="n"/>
       <c r="H44" s="30" t="inlineStr">
         <is>
-          <t>Sprint 4 Review</t>
+          <t>Sprint 3 Review</t>
         </is>
       </c>
       <c r="I44" s="39" t="n"/>
@@ -3081,38 +3143,42 @@
     <row r="45" ht="44" customHeight="1">
       <c r="A45" s="40" t="inlineStr">
         <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="B45" s="46" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="B45" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
         </is>
       </c>
       <c r="C45" s="26" t="inlineStr">
         <is>
-          <t>A·需求+架构+开发</t>
+          <t>A·需求(50%)</t>
         </is>
       </c>
       <c r="D45" s="27" t="inlineStr">
         <is>
-          <t>① Go/No-Go 决策 ② 上线指挥（回退方案就绪）③ 运维培训（架构+UC+权限+监控）④ 项目收尾文档启动</t>
+          <t>① UAT 组织协调（业务方排期+环境准备）② 需求冻结（Scope Freeze）宣布</t>
         </is>
       </c>
       <c r="E45" s="28" t="inlineStr">
         <is>
-          <t>🔴 ★</t>
+          <t>🔴</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>上线成功；运维培训完成</t>
-        </is>
-      </c>
-      <c r="G45" s="29" t="inlineStr"/>
+          <t>UAT 排期确认；冻结声明</t>
+        </is>
+      </c>
+      <c r="G45" s="29" t="inlineStr">
+        <is>
+          <t>业务方排期</t>
+        </is>
+      </c>
       <c r="H45" s="30" t="inlineStr">
         <is>
-          <t>Go-Live 决策会</t>
+          <t>Daily Standup</t>
         </is>
       </c>
       <c r="I45" s="39" t="n"/>
@@ -3120,38 +3186,42 @@
     <row r="46" ht="44" customHeight="1">
       <c r="A46" s="40" t="inlineStr">
         <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="B46" s="46" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="C46" s="31" t="inlineStr">
-        <is>
-          <t>B·数据工程</t>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="B46" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C46" s="48" t="inlineStr">
+        <is>
+          <t>E·架构+开发</t>
         </is>
       </c>
       <c r="D46" s="27" t="inlineStr">
         <is>
-          <t>① 生产运行监控（ETL/Compaction/销毁）② 异常处理 ③ 第二系统全量迁移 ④ 接入 SOP 初稿</t>
+          <t>① 生产环境部署（CLI 执行+验证）② 安全评审材料（等保/个保法对照）③ 生产域名/证书/迁移方案</t>
         </is>
       </c>
       <c r="E46" s="28" t="inlineStr">
         <is>
-          <t>🔴 ★</t>
+          <t>🔴</t>
         </is>
       </c>
       <c r="F46" s="9" t="inlineStr">
         <is>
-          <t>生产 Jobs 正常；第二系统入湖</t>
-        </is>
-      </c>
-      <c r="G46" s="29" t="n"/>
+          <t>生产就绪；安全材料初稿</t>
+        </is>
+      </c>
+      <c r="G46" s="29" t="inlineStr">
+        <is>
+          <t>生产订阅；证书</t>
+        </is>
+      </c>
       <c r="H46" s="30" t="inlineStr">
         <is>
-          <t>Go-Live</t>
+          <t>Daily Standup</t>
         </is>
       </c>
       <c r="I46" s="39" t="n"/>
@@ -3159,159 +3229,155 @@
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="40" t="inlineStr">
         <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="B47" s="46" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="C47" s="32" t="inlineStr">
-        <is>
-          <t>C·全栈+DevOps</t>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="B47" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C47" s="31" t="inlineStr">
+        <is>
+          <t>B·数据工程</t>
         </is>
       </c>
       <c r="D47" s="27" t="inlineStr">
         <is>
-          <t>① 生产运行监控（查询/前端/SSO）② 用户反馈响应 ③ 配置调优</t>
+          <t>① 首系统全量迁移执行（含对账）② 生产 Jobs 部署 ③ 生产 UC 权限配置</t>
         </is>
       </c>
       <c r="E47" s="28" t="inlineStr">
         <is>
-          <t>🔴 ★</t>
+          <t>🔴</t>
         </is>
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>生产查询正常</t>
-        </is>
-      </c>
-      <c r="G47" s="29" t="n"/>
-      <c r="H47" s="30" t="inlineStr">
-        <is>
-          <t>Go-Live</t>
-        </is>
-      </c>
+          <t>首系统全量入湖；对账通过</t>
+        </is>
+      </c>
+      <c r="G47" s="29" t="inlineStr">
+        <is>
+          <t>生产环境就绪</t>
+        </is>
+      </c>
+      <c r="H47" s="30" t="n"/>
       <c r="I47" s="39" t="n"/>
     </row>
     <row r="48" ht="44" customHeight="1">
       <c r="A48" s="40" t="inlineStr">
         <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="B48" s="46" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="C48" s="33" t="inlineStr">
-        <is>
-          <t>D·QA+SLC文档</t>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="B48" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C48" s="32" t="inlineStr">
+        <is>
+          <t>C·全栈+DevOps</t>
         </is>
       </c>
       <c r="D48" s="27" t="inlineStr">
         <is>
-          <t>① 上线执行（部署顺序/验证/回退点）② 48h 值守 ③ 告警验证 ④ 培训交付：业务用户培训（查询/导出/附件）+ 运维培训辅助</t>
+          <t>① 生产 AKS 部署（Helm Release）② 生产 SSO 配置 ③ 首系统查询页生产配置 ④ 性能监控接入</t>
         </is>
       </c>
       <c r="E48" s="28" t="inlineStr">
         <is>
-          <t>🔴 ★</t>
+          <t>🔴</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>上线 Checklist 全勾；培训完成；告警可达</t>
-        </is>
-      </c>
-      <c r="G48" s="29" t="n"/>
-      <c r="H48" s="30" t="inlineStr">
-        <is>
-          <t>Go-Live；培训</t>
-        </is>
-      </c>
+          <t>生产可访问；SSO 正常；查询可用</t>
+        </is>
+      </c>
+      <c r="G48" s="29" t="inlineStr">
+        <is>
+          <t>生产域名</t>
+        </is>
+      </c>
+      <c r="H48" s="30" t="n"/>
       <c r="I48" s="39" t="n"/>
     </row>
     <row r="49" ht="44" customHeight="1">
       <c r="A49" s="40" t="inlineStr">
         <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="B49" s="46" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="C49" s="26" t="inlineStr">
-        <is>
-          <t>A·需求+架构+开发</t>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="B49" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C49" s="33" t="inlineStr">
+        <is>
+          <t>D·QA+SLC文档</t>
         </is>
       </c>
       <c r="D49" s="27" t="inlineStr">
         <is>
-          <t>① 运维团队独立操作验证 ② 项目关闭报告 ③ 后续系统接入排期（与业务方）④ Retro</t>
+          <t>① 文档冲刺启动：用户手册终版 + 运维手册终版 + 数据字典终版 ② 架构图终版（4 张全更新到生产实际）③ 详细设计终版 ④ 接口文档终版 ⑤ 审批材料包准备（技术方案/安全评估/合规对照/验收报告）</t>
         </is>
       </c>
       <c r="E49" s="28" t="inlineStr">
         <is>
-          <t>⚪ ★</t>
+          <t>🔴</t>
         </is>
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>运维可独立日常操作；关闭报告签字</t>
-        </is>
-      </c>
-      <c r="G49" s="29" t="inlineStr">
-        <is>
-          <t>运维意愿</t>
-        </is>
-      </c>
-      <c r="H49" s="30" t="inlineStr">
-        <is>
-          <t>Retro；项目关闭会</t>
-        </is>
-      </c>
+          <t>6 套文档进入终审（用户/运维/架构×4/详细设计/接口/数据字典）；审批材料初稿</t>
+        </is>
+      </c>
+      <c r="G49" s="29" t="n"/>
+      <c r="H49" s="30" t="n"/>
       <c r="I49" s="39" t="n"/>
     </row>
     <row r="50" ht="44" customHeight="1">
       <c r="A50" s="40" t="inlineStr">
         <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="B50" s="46" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="C50" s="31" t="inlineStr">
-        <is>
-          <t>B·数据工程</t>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="B50" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>A·需求(50%)</t>
         </is>
       </c>
       <c r="D50" s="27" t="inlineStr">
         <is>
-          <t>① 运维知识转移（ETL/销毁）② 第三系统 PoC ③ 技术债清单 ④ Retro</t>
+          <t>① UAT 执行主持（5 场景走查+记录）② UAT 反馈分类（Bug/变更/澄清）</t>
         </is>
       </c>
       <c r="E50" s="28" t="inlineStr">
         <is>
-          <t>⚪ ★</t>
+          <t>🔴 ★</t>
         </is>
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>运维可独立跑 ETL+销毁</t>
-        </is>
-      </c>
-      <c r="G50" s="29" t="n"/>
+          <t>UAT 报告（含签字）</t>
+        </is>
+      </c>
+      <c r="G50" s="29" t="inlineStr">
+        <is>
+          <t>业务方参与</t>
+        </is>
+      </c>
       <c r="H50" s="30" t="inlineStr">
         <is>
-          <t>Retro</t>
+          <t>S4 Review（UAT）</t>
         </is>
       </c>
       <c r="I50" s="39" t="n"/>
@@ -3319,38 +3385,38 @@
     <row r="51" ht="44" customHeight="1">
       <c r="A51" s="40" t="inlineStr">
         <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="B51" s="46" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="C51" s="32" t="inlineStr">
-        <is>
-          <t>C·全栈+DevOps</t>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="B51" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C51" s="48" t="inlineStr">
+        <is>
+          <t>E·架构+开发</t>
         </is>
       </c>
       <c r="D51" s="27" t="inlineStr">
         <is>
-          <t>① 运维知识转移（部署/前端）② 第三系统配置 ③ 代码整理 ④ Retro</t>
+          <t>① UAT 技术支撑（环境/数据/缺陷定位）② 安全评审提交 ③ 审批文档技术部分定稿</t>
         </is>
       </c>
       <c r="E51" s="28" t="inlineStr">
         <is>
-          <t>⚪ ★</t>
+          <t>🔴 ★</t>
         </is>
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>运维可改前端配置；代码整洁</t>
-        </is>
-      </c>
-      <c r="G51" s="29" t="n"/>
+          <t>审批材料提交</t>
+        </is>
+      </c>
+      <c r="G51" s="29" t="inlineStr"/>
       <c r="H51" s="30" t="inlineStr">
         <is>
-          <t>Retro</t>
+          <t>S4 Review；S5 Planning</t>
         </is>
       </c>
       <c r="I51" s="39" t="n"/>
@@ -3358,63 +3424,505 @@
     <row r="52" ht="44" customHeight="1">
       <c r="A52" s="40" t="inlineStr">
         <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="B52" s="46" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="C52" s="33" t="inlineStr">
-        <is>
-          <t>D·QA+SLC文档</t>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="B52" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C52" s="31" t="inlineStr">
+        <is>
+          <t>B·数据工程</t>
         </is>
       </c>
       <c r="D52" s="27" t="inlineStr">
         <is>
-          <t>① 文档包归档（7 套 + 培训视频 + 接入手册）② 培训视频录制 ③ 后续接入手册终版 ④ Retro + 行动项</t>
+          <t>① UAT 支撑 ② 第二系统全量迁移准备 ③ 生产 Compaction 首次执行 ④ 销毁回路生产验证</t>
         </is>
       </c>
       <c r="E52" s="28" t="inlineStr">
         <is>
-          <t>⚪ ★</t>
+          <t>🟡</t>
         </is>
       </c>
       <c r="F52" s="9" t="inlineStr">
         <is>
-          <t>全部文档归档；培训视频上传</t>
+          <t>UAT 数据问题全解决</t>
         </is>
       </c>
       <c r="G52" s="29" t="n"/>
       <c r="H52" s="30" t="inlineStr">
         <is>
+          <t>Sprint 4 Review</t>
+        </is>
+      </c>
+      <c r="I52" s="39" t="n"/>
+    </row>
+    <row r="53" ht="44" customHeight="1">
+      <c r="A53" s="40" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="B53" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C53" s="32" t="inlineStr">
+        <is>
+          <t>C·全栈+DevOps</t>
+        </is>
+      </c>
+      <c r="D53" s="27" t="inlineStr">
+        <is>
+          <t>① UAT Bug 修复 ② 生产监控 Dashboard ③ 性能微调 ④ 文档截图更新</t>
+        </is>
+      </c>
+      <c r="E53" s="28" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>UAT Bug 全关闭；截图一致</t>
+        </is>
+      </c>
+      <c r="G53" s="29" t="n"/>
+      <c r="H53" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 4 Review</t>
+        </is>
+      </c>
+      <c r="I53" s="39" t="n"/>
+    </row>
+    <row r="54" ht="44" customHeight="1">
+      <c r="A54" s="40" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="B54" s="45" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C54" s="33" t="inlineStr">
+        <is>
+          <t>D·QA+SLC文档</t>
+        </is>
+      </c>
+      <c r="D54" s="27" t="inlineStr">
+        <is>
+          <t>① UAT 执行协调 + 结果记录 ② 文档终审（6 套 + 审批包 = 7 套）③ 上线 Checklist ④ 培训材料（业务用户 + 运维团队）</t>
+        </is>
+      </c>
+      <c r="E54" s="28" t="inlineStr">
+        <is>
+          <t>🔴 ★</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>7 套文档终版；上线 Checklist 评审通过；培训 PPT + 演练脚本</t>
+        </is>
+      </c>
+      <c r="G54" s="29" t="inlineStr">
+        <is>
+          <t>审批方反馈</t>
+        </is>
+      </c>
+      <c r="H54" s="30" t="inlineStr">
+        <is>
+          <t>Sprint 4 Review</t>
+        </is>
+      </c>
+      <c r="I54" s="39" t="n"/>
+    </row>
+    <row r="55" ht="44" customHeight="1">
+      <c r="A55" s="40" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="B55" s="46" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C55" s="26" t="inlineStr">
+        <is>
+          <t>A·需求(50%)</t>
+        </is>
+      </c>
+      <c r="D55" s="27" t="inlineStr">
+        <is>
+          <t>① 上线后用户反馈收集与分诊 ② 培训内容审阅（业务视角）</t>
+        </is>
+      </c>
+      <c r="E55" s="28" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>反馈清单；培训内容确认</t>
+        </is>
+      </c>
+      <c r="G55" s="29" t="inlineStr"/>
+      <c r="H55" s="30" t="inlineStr">
+        <is>
+          <t>Go-Live</t>
+        </is>
+      </c>
+      <c r="I55" s="39" t="n"/>
+    </row>
+    <row r="56" ht="44" customHeight="1">
+      <c r="A56" s="40" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="B56" s="46" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C56" s="48" t="inlineStr">
+        <is>
+          <t>E·架构+开发</t>
+        </is>
+      </c>
+      <c r="D56" s="27" t="inlineStr">
+        <is>
+          <t>① Go/No-Go 技术评估 ② 上线指挥（回退方案就绪）③ 运维培训（架构/UC/权限/监控）</t>
+        </is>
+      </c>
+      <c r="E56" s="28" t="inlineStr">
+        <is>
+          <t>🔴 ★</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>上线成功；运维培训完成</t>
+        </is>
+      </c>
+      <c r="G56" s="29" t="inlineStr"/>
+      <c r="H56" s="30" t="inlineStr">
+        <is>
+          <t>Go-Live 决策会</t>
+        </is>
+      </c>
+      <c r="I56" s="39" t="n"/>
+    </row>
+    <row r="57" ht="44" customHeight="1">
+      <c r="A57" s="40" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="B57" s="46" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C57" s="31" t="inlineStr">
+        <is>
+          <t>B·数据工程</t>
+        </is>
+      </c>
+      <c r="D57" s="27" t="inlineStr">
+        <is>
+          <t>① 生产运行监控（ETL/Compaction/销毁）② 异常处理 ③ 第二系统全量迁移 ④ 接入 SOP 初稿</t>
+        </is>
+      </c>
+      <c r="E57" s="28" t="inlineStr">
+        <is>
+          <t>🔴 ★</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>生产 Jobs 正常；第二系统入湖</t>
+        </is>
+      </c>
+      <c r="G57" s="29" t="n"/>
+      <c r="H57" s="30" t="inlineStr">
+        <is>
+          <t>Go-Live</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="44" customHeight="1">
+      <c r="A58" s="40" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="B58" s="46" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C58" s="32" t="inlineStr">
+        <is>
+          <t>C·全栈+DevOps</t>
+        </is>
+      </c>
+      <c r="D58" s="27" t="inlineStr">
+        <is>
+          <t>① 生产运行监控（查询/前端/SSO）② 用户反馈响应 ③ 配置调优</t>
+        </is>
+      </c>
+      <c r="E58" s="28" t="inlineStr">
+        <is>
+          <t>🔴 ★</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>生产查询正常</t>
+        </is>
+      </c>
+      <c r="G58" s="29" t="n"/>
+      <c r="H58" s="30" t="inlineStr">
+        <is>
+          <t>Go-Live</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="44" customHeight="1">
+      <c r="A59" s="40" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="B59" s="46" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C59" s="33" t="inlineStr">
+        <is>
+          <t>D·QA+SLC文档</t>
+        </is>
+      </c>
+      <c r="D59" s="27" t="inlineStr">
+        <is>
+          <t>① 上线执行（部署顺序/验证/回退点）② 48h 值守 ③ 告警验证 ④ 培训交付：业务用户培训（查询/导出/附件）+ 运维培训辅助</t>
+        </is>
+      </c>
+      <c r="E59" s="28" t="inlineStr">
+        <is>
+          <t>🔴 ★</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>上线 Checklist 全勾；培训完成；告警可达</t>
+        </is>
+      </c>
+      <c r="G59" s="29" t="n"/>
+      <c r="H59" s="30" t="inlineStr">
+        <is>
+          <t>Go-Live；培训</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="44" customHeight="1">
+      <c r="A60" s="40" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="B60" s="46" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="inlineStr">
+        <is>
+          <t>A·需求(50%)</t>
+        </is>
+      </c>
+      <c r="D60" s="27" t="inlineStr">
+        <is>
+          <t>① 项目复盘（需求满足度回顾）② 后续系统需求排期 ③ Retro</t>
+        </is>
+      </c>
+      <c r="E60" s="28" t="inlineStr">
+        <is>
+          <t>⚪ ★</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>需求满足度报告；后续排期</t>
+        </is>
+      </c>
+      <c r="G60" s="29" t="inlineStr"/>
+      <c r="H60" s="30" t="inlineStr">
+        <is>
+          <t>Retro；关闭会</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="44" customHeight="1">
+      <c r="A61" s="40" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="B61" s="46" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C61" s="48" t="inlineStr">
+        <is>
+          <t>E·架构+开发</t>
+        </is>
+      </c>
+      <c r="D61" s="27" t="inlineStr">
+        <is>
+          <t>① 运维独立操作验证 ② 项目关闭报告（技术部分）③ 后续接入技术排期 ④ Retro</t>
+        </is>
+      </c>
+      <c r="E61" s="28" t="inlineStr">
+        <is>
+          <t>⚪ ★</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>运维可独立操作；技术关闭报告</t>
+        </is>
+      </c>
+      <c r="G61" s="29" t="inlineStr"/>
+      <c r="H61" s="30" t="inlineStr">
+        <is>
+          <t>Retro；关闭会</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="44" customHeight="1">
+      <c r="A62" s="40" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="B62" s="46" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C62" s="31" t="inlineStr">
+        <is>
+          <t>B·数据工程</t>
+        </is>
+      </c>
+      <c r="D62" s="27" t="inlineStr">
+        <is>
+          <t>① 运维知识转移（ETL/销毁）② 第三系统 PoC ③ 技术债清单 ④ Retro</t>
+        </is>
+      </c>
+      <c r="E62" s="28" t="inlineStr">
+        <is>
+          <t>⚪ ★</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>运维可独立跑 ETL+销毁</t>
+        </is>
+      </c>
+      <c r="G62" s="29" t="n"/>
+      <c r="H62" s="30" t="inlineStr">
+        <is>
+          <t>Retro</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="44" customHeight="1">
+      <c r="A63" s="40" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="B63" s="46" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C63" s="32" t="inlineStr">
+        <is>
+          <t>C·全栈+DevOps</t>
+        </is>
+      </c>
+      <c r="D63" s="27" t="inlineStr">
+        <is>
+          <t>① 运维知识转移（部署/前端）② 第三系统配置 ③ 代码整理 ④ Retro</t>
+        </is>
+      </c>
+      <c r="E63" s="28" t="inlineStr">
+        <is>
+          <t>⚪ ★</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>运维可改前端配置；代码整洁</t>
+        </is>
+      </c>
+      <c r="G63" s="29" t="n"/>
+      <c r="H63" s="30" t="inlineStr">
+        <is>
+          <t>Retro</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="44" customHeight="1">
+      <c r="A64" s="40" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="B64" s="46" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C64" s="33" t="inlineStr">
+        <is>
+          <t>D·QA+SLC文档</t>
+        </is>
+      </c>
+      <c r="D64" s="27" t="inlineStr">
+        <is>
+          <t>① 文档包归档（7 套 + 培训视频 + 接入手册）② 培训视频录制 ③ 后续接入手册终版 ④ Retro + 行动项</t>
+        </is>
+      </c>
+      <c r="E64" s="28" t="inlineStr">
+        <is>
+          <t>⚪ ★</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>全部文档归档；培训视频上传</t>
+        </is>
+      </c>
+      <c r="G64" s="29" t="n"/>
+      <c r="H64" s="30" t="inlineStr">
+        <is>
           <t>Retro；项目关闭会</t>
         </is>
       </c>
-      <c r="I52" s="39" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="39" t="n"/>
-      <c r="B53" s="39" t="n"/>
-      <c r="C53" s="39" t="n"/>
-      <c r="D53" s="39" t="n"/>
-      <c r="E53" s="39" t="n"/>
-      <c r="F53" s="39" t="n"/>
-      <c r="G53" s="39" t="n"/>
-      <c r="H53" s="39" t="n"/>
-      <c r="I53" s="39" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="39" t="n"/>
-      <c r="B54" s="39" t="n"/>
-      <c r="C54" s="39" t="n"/>
-      <c r="D54" s="39" t="n"/>
-      <c r="E54" s="39" t="n"/>
-      <c r="F54" s="39" t="n"/>
-      <c r="G54" s="39" t="n"/>
-      <c r="H54" s="39" t="n"/>
-      <c r="I54" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/report/项目执行计划.xlsx
+++ b/report/项目执行计划.xlsx
@@ -3763,7 +3763,7 @@
       <c r="C80" s="69" t="n"/>
       <c r="D80" s="64" t="inlineStr">
         <is>
-          <t>• 冷热存储方案②：生命周期管理规则（30 天降 Cool、90 天降 Cold、附件独立策略）+ Terraform 无关的 CLI 落地</t>
+          <t>• 冷热存储方案②：生命周期管理规则（30 天降 Cool、90 天降 Cold、附件独立策略）（Azure CLI 落地）</t>
         </is>
       </c>
       <c r="E80" s="68" t="n"/>

--- a/report/项目执行计划.xlsx
+++ b/report/项目执行计划.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;￥&quot;#,##0;&quot;￥&quot;\-#,##0"/>
   </numFmts>
-  <fonts count="56">
+  <fonts count="70">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -416,8 +416,87 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="0064748b"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.199999999999999"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00475569"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00B45309"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00DC2626"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="000284c7"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00d97706"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00dc2626"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007c3aed"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="45">
+  <fills count="52">
     <fill>
       <patternFill/>
     </fill>
@@ -682,8 +761,43 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0F2FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDE9FE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -804,6 +918,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -952,7 +1081,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1113,6 +1242,48 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="20" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="45" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="46" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="47" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="48" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="49" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="50" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="51" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1856,258 +2027,757 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col width="13.8461538461538" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="55.9615384615385" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="68" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>12 周 Sprint 计划</t>
-        </is>
-      </c>
+      <c r="A1" s="58" t="inlineStr">
+        <is>
+          <t>12 周 Sprint 计划总览（V8：按 8 大功能域重排 · CC 单系统接入验证 · 上线即收尾）</t>
+        </is>
+      </c>
+      <c r="B1" s="59" t="n"/>
+      <c r="C1" s="59" t="n"/>
+      <c r="D1" s="59" t="n"/>
+      <c r="E1" s="59" t="n"/>
+      <c r="F1" s="59" t="n"/>
+      <c r="G1" s="59" t="n"/>
+      <c r="H1" s="59" t="n"/>
+      <c r="I1" s="59" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="60" t="inlineStr">
+        <is>
+          <t>接入测试系统：Caring Center（CC，SQL Server，1253 表/24,620 字段）· 上线后无知识转移/项目关闭环节，W12 稳定运行一周即结束</t>
+        </is>
+      </c>
+      <c r="B2" s="59" t="n"/>
+      <c r="C2" s="59" t="n"/>
+      <c r="D2" s="59" t="n"/>
+      <c r="E2" s="59" t="n"/>
+      <c r="F2" s="59" t="n"/>
+      <c r="G2" s="59" t="n"/>
+      <c r="H2" s="59" t="n"/>
+      <c r="I2" s="59" t="n"/>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="61" t="n"/>
+      <c r="B3" s="61" t="n"/>
+      <c r="C3" s="61" t="n"/>
+      <c r="D3" s="61" t="n"/>
+      <c r="E3" s="61" t="n"/>
+      <c r="F3" s="61" t="n"/>
+      <c r="G3" s="59" t="n"/>
+      <c r="H3" s="59" t="n"/>
+      <c r="I3" s="59" t="n"/>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="62" t="inlineStr">
         <is>
           <t>Sprint</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="62" t="inlineStr">
         <is>
           <t>周次</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="62" t="inlineStr">
         <is>
           <t>主题 / 目标</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>核心交付物</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="D4" s="62" t="inlineStr">
+        <is>
+          <t>核心交付物（按功能域编号）</t>
+        </is>
+      </c>
+      <c r="E4" s="62" t="inlineStr">
         <is>
           <t>演示内容（Sprint Review）</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F4" s="62" t="inlineStr">
         <is>
           <t>主要风险</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="76" customHeight="1">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="G4" s="62" t="inlineStr">
+        <is>
+          <t>需确认/决策项</t>
+        </is>
+      </c>
+      <c r="H4" s="59" t="n"/>
+      <c r="I4" s="59" t="n"/>
+    </row>
+    <row r="5" ht="120" customHeight="1">
+      <c r="A5" s="63" t="inlineStr">
         <is>
           <t>Sprint 0
 需求+筹备</t>
         </is>
       </c>
-      <c r="B4" s="31" t="inlineStr">
+      <c r="B5" s="64" t="inlineStr">
         <is>
           <t>W1~W2</t>
         </is>
       </c>
-      <c r="C4" s="32" t="inlineStr">
-        <is>
-          <t>需求确认 + 技术选型落地 + 环境搭建（并行推进）</t>
-        </is>
-      </c>
-      <c r="D4" s="33" t="inlineStr">
-        <is>
-          <t>① A：BRD 初稿 + 用户故事地图 + 验收标准 + 首系统确认 ② A：Azure 环境搭建（VNet/AKS/ADLS/SQL DB/Key Vault/Databricks）③ B：Databricks 工作区 + UC 初始化 + 源库 PoC ④ C：项目骨架 + CI/CD 流水线 + Docker 本地开发环境 ⑤ D：测试计划 + 架构图初稿（系统上下文图 + 容器图）</t>
-        </is>
-      </c>
-      <c r="E4" s="33" t="inlineStr">
-        <is>
-          <t>PoC：SeaTunnel 从源库抽数 → Iceberg RAW → SQL Warehouse 可查 + BRD 评审通过</t>
-        </is>
-      </c>
-      <c r="F4" s="33" t="inlineStr">
-        <is>
-          <t>需求不明确导致后续返工；源库账号/网络延迟</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="76" customHeight="1">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="C5" s="65" t="inlineStr">
+        <is>
+          <t>需求定稿 + 环境就绪 + CC 连接打通</t>
+        </is>
+      </c>
+      <c r="D5" s="66" t="inlineStr">
+        <is>
+          <t>【全部功能域需求澄清】① A：BRD 定稿（8 大功能域 + 数据流图 + 保留期矩阵 + PII 分级 + 检索权限矩阵 + UAT 场景）② B：架构定稿 + 资源申请单（区域锁定=境内驻留）+ 平台交付资源验收 + UC 初始化 ③ C：SeaTunnel PoC——用 Caring Center 源库实测连通（1253 表全量扫描 information_schema，完成表分类：业务表/垃圾表/附件元数据表）④ D：前后端骨架 + CI/CD 就绪 + SSO（OIDC）走通 ⑤ E：测试计划（8 域全覆盖）+ 架构图×2 + 文档模板</t>
+        </is>
+      </c>
+      <c r="E5" s="66" t="inlineStr">
+        <is>
+          <t>① CC 源库连接打通：SeaTunnel 抽样 10 张表 → Iceberg RAW → SQL Warehouse 可查 ② BRD 评审通过 ③ 登录页可访问</t>
+        </is>
+      </c>
+      <c r="F5" s="67" t="inlineStr">
+        <is>
+          <t>CC 源库账号/白名单延迟；1253 表审表工作量大（A 需业务方配合勾选）；实时性指标（02 域）未定</t>
+        </is>
+      </c>
+      <c r="G5" s="68" t="inlineStr">
+        <is>
+          <t>① CC 只读账号 + NAT 白名单（W1 必须）② 垃圾表剔除标准业务确认 ③ 02 域"实时"指标：分钟级 or 小时级？④ 04 域境内驻留的区域要求 ⑤ Legal Hold 触发条件（法务）</t>
+        </is>
+      </c>
+      <c r="H5" s="59" t="n"/>
+      <c r="I5" s="59" t="n"/>
+    </row>
+    <row r="6" ht="120" customHeight="1">
+      <c r="A6" s="69" t="inlineStr">
         <is>
           <t>Sprint 1
-MVP</t>
-        </is>
-      </c>
-      <c r="B5" s="31" t="inlineStr">
+迁移+检索 MVP</t>
+        </is>
+      </c>
+      <c r="B6" s="64" t="inlineStr">
         <is>
           <t>W3~W4</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
-        <is>
-          <t>端到端最小闭环：1 张表从源库到查询页可查</t>
-        </is>
-      </c>
-      <c r="D5" s="33" t="inlineStr">
-        <is>
-          <t>① B：ETL 配置生成器 + RAW→LAKE 直达 ② C：查询代理 API + React 基础查询页 + SSO + Helm 部署到 AKS Dev ③ A：代码评审 + UC 权限落地 ④ D：集成测试 + 架构图完善（组件图 + 部署图）+ 接口文档初稿</t>
-        </is>
-      </c>
-      <c r="E5" s="33" t="inlineStr">
-        <is>
-          <t>演示：登录 → 系统列表 → 查询页 → 输入条件 → 看到 1 张表数据</t>
-        </is>
-      </c>
-      <c r="F5" s="33" t="inlineStr">
-        <is>
-          <t>前后端联调超预期；UC 权限首次落地</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="76" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="C6" s="65" t="inlineStr">
+        <is>
+          <t>01 存量迁移 + 05 检索 端到端（CC 首批 50 张表）</t>
+        </is>
+      </c>
+      <c r="D6" s="66" t="inlineStr">
+        <is>
+          <t>【01 域】① C：SeaTunnel 批量导入 CC 首批 50 张勾选表（分片/限速/断点）+ 迁移任务管理（生成器→调度→状态）+ 完整性校验（行数/校验和/SHA-256 台账）② A：迁移规则确认（垃圾表剔除、字段映射）③ D：迁移任务管理界面【05 域】④ D：基础检索页（配置化动态渲染）+ 结果预览（图片/附件 SAS）+ 导出 CSV【08 域】⑤ B：RBAC 五角色 + Entra ID 组映射 + UC GRANT（CC 的 catalog）+ SSO JWT Claims 贯通【06 域】⑥ D：操作审计埋点 v1【07 域】⑦ C：JDBC 连接器模板 v1（SQL Server 类型映射）</t>
+        </is>
+      </c>
+      <c r="E6" s="66" t="inlineStr">
+        <is>
+          <t>① CC 50 张表端到端：登录 → 选系统 → 检索 → 预览附件 → 导出，全程带权限与审计 ② 迁移对账报告（行数 100% 一致）</t>
+        </is>
+      </c>
+      <c r="F6" s="67" t="inlineStr">
+        <is>
+          <t>CC 全量 1253 表审表压力；前后端联调；掩码函数首次落地</t>
+        </is>
+      </c>
+      <c r="G6" s="68" t="inlineStr">
+        <is>
+          <t>① CC 首批勾选表清单（业务方 W2 末确认）② PII 字段标记（哪些列脱敏）③ 预览格式范围（图片/音频/视频）</t>
+        </is>
+      </c>
+      <c r="H6" s="59" t="n"/>
+      <c r="I6" s="59" t="n"/>
+    </row>
+    <row r="7" ht="120" customHeight="1">
+      <c r="A7" s="70" t="inlineStr">
         <is>
           <t>Sprint 2
-核心功能</t>
-        </is>
-      </c>
-      <c r="B6" s="31" t="inlineStr">
+治理+安全</t>
+        </is>
+      </c>
+      <c r="B7" s="64" t="inlineStr">
         <is>
           <t>W5~W6</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
-        <is>
-          <t>完整四层转换 + 附件链路 + 权限体系</t>
-        </is>
-      </c>
-      <c r="D6" s="33" t="inlineStr">
-        <is>
-          <t>① B：四层转换 + Z-Order + Compaction + 附件链路 ② C：配置化查询表单（元数据驱动）+ 附件预览 + 多表 JOIN + 下钻 ③ A：掩码函数 + 密钥体系+l冷热数据隔离 ④ D：功能测试全量 + 性能测试 + 详细设计文档（数据层+应用层+安全层 3 模块）</t>
-        </is>
-      </c>
-      <c r="E6" s="33" t="inlineStr">
-        <is>
-          <t>演示：① 掩码查询（有权限明文/无权限掩码）② 附件在线预览 ③ 多表 JOIN</t>
-        </is>
-      </c>
-      <c r="F6" s="33" t="inlineStr">
-        <is>
-          <t>掩码函数复杂度；Storage Mover 网络打通；D 的文档量大</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="76" customHeight="1">
-      <c r="A7" s="36" t="inlineStr">
+      <c r="C7" s="65" t="inlineStr">
+        <is>
+          <t>02 数据治理 + 03 归档生命周期 + 04 安全管控</t>
+        </is>
+      </c>
+      <c r="D7" s="66" t="inlineStr">
+        <is>
+          <t>【02 域】① C：增量/准实时接入方案落地（按 W1 确认的实时指标）+ 冷数据识别与自动转冷（按 A 的冷数据标准）② D：元数据标准管理界面【03 域】③ B：标准归档模型管理 + 到期处置引擎（扫描→DROP PARTITION→VACUUM）+ Legal Hold（Hold/Release + 留痕）④ C：归档转换校验（CURATED/LAKE 层 Spark SQL + Schema Evolution）⑤ D+B：到期处置与 Legal Hold 界面（含审批）【04 域】⑥ B：加密体系落地（CMK + aes_encrypt 字段级 + 密钥轮转）+ UC COLUMN MASK 动态脱敏 + 境内驻留核查（区域配置+出口流量）⑦ C：ADLS 冷热分层 + 生命周期规则 + Compaction 调度</t>
+        </is>
+      </c>
+      <c r="E7" s="66" t="inlineStr">
+        <is>
+          <t>① 增量数据自动入湖（准实时时效达标）② 设 1 天保留期 → 到期自动处置 → Legal Hold 拦截 → 审计留痕全链路 ③ 无权限见掩码/有权限见明文 ④ 存储分层生效（Cool 层成本可见）</t>
+        </is>
+      </c>
+      <c r="F7" s="67" t="inlineStr">
+        <is>
+          <t>实时方案技术风险（CDC vs 轮询）；处置不可逆需沙箱充分验证；掩码函数与前端联动</t>
+        </is>
+      </c>
+      <c r="G7" s="68" t="inlineStr">
+        <is>
+          <t>① 02 域实时指标验收标准 ② Legal Hold 审批人 ③ 保留期合规底线（法务）④ 性能验收标准（首屏 P95&lt;5s）</t>
+        </is>
+      </c>
+      <c r="H7" s="59" t="n"/>
+      <c r="I7" s="59" t="n"/>
+    </row>
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="71" t="inlineStr">
         <is>
           <t>Sprint 3
-销毁+第二系统</t>
-        </is>
-      </c>
-      <c r="B7" s="31" t="inlineStr">
+CC 全量+连接器</t>
+        </is>
+      </c>
+      <c r="B8" s="64" t="inlineStr">
         <is>
           <t>W7~W8</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
-        <is>
-          <t>保留策略 + 销毁回路 + 第二系统接入 + 全量测试</t>
-        </is>
-      </c>
-      <c r="D7" s="33" t="inlineStr">
-        <is>
-          <t>① B：到期扫描 + DROP PARTITION + VACUUM + 销毁作业 ② C：Retention 策略界面 + 审批界面 + 通知 + Dashboard ③ A：第二系统零代码接入验证 ④ D：全量回归测试 + 用户手册初稿 + 数据字典 + 运维手册初稿</t>
-        </is>
-      </c>
-      <c r="E7" s="33" t="inlineStr">
-        <is>
-          <t>演示：① 保留期→到期自动销毁→审计留痕 ② 第二系统纯配置接入 ③ 监控大盘</t>
-        </is>
-      </c>
-      <c r="F7" s="33" t="inlineStr">
-        <is>
-          <t>销毁不可逆需严格测试；UAT 场景可能不完整</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="76" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="C8" s="65" t="inlineStr">
+        <is>
+          <t>CC 1253 表全量迁移 + 07 连接器完善 + 06 合规报表</t>
+        </is>
+      </c>
+      <c r="D8" s="66" t="inlineStr">
+        <is>
+          <t>【01+02 域】① C：CC 全量 1253 表分批迁移（垃圾表按规则剔除后约 600~800 张）+ 增量常态化运行 ② A：迁移范围最终确认 + 范围变更裁决【07 域】③ C：连接器模板库扩展（MySQL 类型映射 + 文件源模板）+ 连接器运行监控与审计上报 ④ D：多源连接管理界面（配置/测试/模板选择/状态）【06 域】⑤ D：合规报表 v1（操作审计查询 + 导出 + 等保/个保法对照视图）⑥ E：合规口径验证（报表可举证）【08 域】⑦ B：行级隔离验证（跨系统越权测试全过）</t>
+        </is>
+      </c>
+      <c r="E8" s="66" t="inlineStr">
+        <is>
+          <t>① CC 全量数据入湖（对账 100%）+ 增量自动运行 ② 新数据源 30 分钟完成配置接入（连接器模板演示）③ 合规报表一键导出 ④ 越权测试全部拦截</t>
+        </is>
+      </c>
+      <c r="F8" s="67" t="inlineStr">
+        <is>
+          <t>CC 全量迁移时长不可控（数据量未知）；1253 表逐批对账耗时；报表合规口径与法务理解偏差</t>
+        </is>
+      </c>
+      <c r="G8" s="68" t="inlineStr">
+        <is>
+          <t>① CC 全量数据量确认（sp_spaceused）② 全量迁移窗口（周末？）③ 合规报表口径签字人</t>
+        </is>
+      </c>
+      <c r="H8" s="59" t="n"/>
+      <c r="I8" s="59" t="n"/>
+    </row>
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="72" t="inlineStr">
         <is>
           <t>Sprint 4
-上线准备</t>
-        </is>
-      </c>
-      <c r="B8" s="31" t="inlineStr">
+UAT+生产部署</t>
+        </is>
+      </c>
+      <c r="B9" s="64" t="inlineStr">
         <is>
           <t>W9~W10</t>
         </is>
       </c>
-      <c r="C8" s="32" t="inlineStr">
-        <is>
-          <t>生产部署 + 全量文档 + UAT + 审批材料</t>
-        </is>
-      </c>
-      <c r="D8" s="33" t="inlineStr">
-        <is>
-          <t>① A：生产环境部署（CLI/Bicep）+ 安全评审材料 ② B：首系统全量迁移 + 生产 Jobs 部署 ③ C：生产 AKS 部署 + SSO + 监控接入 ④ D：文档冲刺（用户手册终版 + 运维手册终版 + 架构图终版 + 详细设计终版 + 接口文档终版 + 审批材料包）+ UAT 执行</t>
-        </is>
-      </c>
-      <c r="E8" s="33" t="inlineStr">
-        <is>
-          <t>演示：① 生产环境端到端 ② UAT 报告 ③ 文档包 ④ 审批材料提交状态</t>
-        </is>
-      </c>
-      <c r="F8" s="33" t="inlineStr">
-        <is>
-          <t>UAT 业务方配合度；安全评审整改；D 的文档冲刺压力最大</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="76" customHeight="1">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="C9" s="65" t="inlineStr">
+        <is>
+          <t>生产部署 + UAT + 安全评审 + 文档审批</t>
+        </is>
+      </c>
+      <c r="D9" s="66" t="inlineStr">
+        <is>
+          <t>① B：生产发布（服务 Helm + UC 权限/掩码/生命周期/驻留核查生产版）+ 安全评审材料 ② C：CC 生产全量迁移执行 + 生产 Jobs（增量/Compaction/处置）③ D：生产部署验证 + 监控接入 + 安全四门禁生产终检（SAST/依赖/密钥/镜像全过 + 渗透配合）④ A：UAT 主持（8 域核心场景：迁移对账/检索/预览导出/脱敏/处置/Legal Hold/审计报表/SSO）+ 需求冻结 ⑤ E：7 套文档终版（用户/运维/架构/详细设计×3/接口/数据字典）+ 审批材料包提交</t>
+        </is>
+      </c>
+      <c r="E9" s="66" t="inlineStr">
+        <is>
+          <t>① 生产环境 8 域功能全通 ② UAT 报告（业务方签字）③ 安全评审通过 ④ 审批材料提交受理</t>
+        </is>
+      </c>
+      <c r="F9" s="67" t="inlineStr">
+        <is>
+          <t>UAT 业务方配合度；CC 生产迁移时长（TB 级可能跨周末）；安全评审整改返工</t>
+        </is>
+      </c>
+      <c r="G9" s="68" t="inlineStr">
+        <is>
+          <t>① UAT 签字人 ② 生产域名/证书 ③ 审批流程周期 ④ CC 生产迁移停机窗口</t>
+        </is>
+      </c>
+      <c r="H9" s="59" t="n"/>
+      <c r="I9" s="59" t="n"/>
+    </row>
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="73" t="inlineStr">
         <is>
           <t>Sprint 5
-上线+移交</t>
-        </is>
-      </c>
-      <c r="B9" s="31" t="inlineStr">
+上线</t>
+        </is>
+      </c>
+      <c r="B10" s="64" t="inlineStr">
         <is>
           <t>W11~W12</t>
         </is>
       </c>
-      <c r="C9" s="32" t="inlineStr">
-        <is>
-          <t>正式上线 + 培训 + 知识转移 + 项目关闭</t>
-        </is>
-      </c>
-      <c r="D9" s="33" t="inlineStr">
-        <is>
-          <t>① 全员：上线值守 ② A：运维培训 + 项目关闭报告 ③ B：运维知识转移（ETL/销毁）④ C：运维知识转移（部署/前端配置）⑤ D：培训交付（业务用户+运维）+ 培训视频 + 接入手册 + 文档归档 + Retro</t>
-        </is>
-      </c>
-      <c r="E9" s="33" t="inlineStr">
-        <is>
-          <t>演示：① 生产运行报告 ② 运维团队独立操作 ③ 后续接入 SOP</t>
-        </is>
-      </c>
-      <c r="F9" s="33" t="inlineStr">
-        <is>
-          <t>上线后首周异常；运维团队接手意愿</t>
-        </is>
-      </c>
+      <c r="C10" s="65" t="inlineStr">
+        <is>
+          <t>Go-Live + 上线保障 + 收尾（无知识转移/项目关闭）</t>
+        </is>
+      </c>
+      <c r="D10" s="66" t="inlineStr">
+        <is>
+          <t>① W11：Go/No-Go 决策 → 上线执行（发布编排/验证点/回退预案）→ 48h 值守（增量作业/查询性能/审计正常）② W11：A：用户反馈分诊；B/C/D：生产问题快速修复；E：上线验证报告 ③ W12：上线后稳定运行（增量/处置/检索/审计全正常）+ 遗留问题清零 + 交付物最终归档（文档包 + 培训视频 + 版本 tag）④ W12 末：项目结束</t>
+        </is>
+      </c>
+      <c r="E10" s="66" t="inlineStr">
+        <is>
+          <t>① 上线成功 + 稳定运行 7 天无 P1 事故 ② 交付物清单全部归档 ③ 项目收尾确认</t>
+        </is>
+      </c>
+      <c r="F10" s="67" t="inlineStr">
+        <is>
+          <t>上线首周 P1 事故；CC 增量链路稳定性；遗留 Bug 上线后暴露</t>
+        </is>
+      </c>
+      <c r="G10" s="68" t="inlineStr">
+        <is>
+          <t>① Go-Live 窗口（建议 W11 周二）② P1 事故响应 SLA ③ 上线后支持期多久（建议含在 W12 内）</t>
+        </is>
+      </c>
+      <c r="H10" s="59" t="n"/>
+      <c r="I10" s="59" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="59" t="n"/>
+      <c r="B11" s="59" t="n"/>
+      <c r="C11" s="59" t="n"/>
+      <c r="D11" s="59" t="n"/>
+      <c r="E11" s="59" t="n"/>
+      <c r="F11" s="59" t="n"/>
+      <c r="G11" s="59" t="n"/>
+      <c r="H11" s="59" t="n"/>
+      <c r="I11" s="59" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="59" t="n"/>
+      <c r="B12" s="59" t="n"/>
+      <c r="C12" s="59" t="n"/>
+      <c r="D12" s="59" t="n"/>
+      <c r="E12" s="59" t="n"/>
+      <c r="F12" s="59" t="n"/>
+      <c r="G12" s="59" t="n"/>
+      <c r="H12" s="59" t="n"/>
+      <c r="I12" s="59" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="59" t="n"/>
+      <c r="B13" s="59" t="n"/>
+      <c r="C13" s="59" t="n"/>
+      <c r="D13" s="59" t="n"/>
+      <c r="E13" s="59" t="n"/>
+      <c r="F13" s="59" t="n"/>
+      <c r="G13" s="59" t="n"/>
+      <c r="H13" s="59" t="n"/>
+      <c r="I13" s="59" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="59" t="n"/>
+      <c r="B14" s="59" t="n"/>
+      <c r="C14" s="59" t="n"/>
+      <c r="D14" s="59" t="n"/>
+      <c r="E14" s="59" t="n"/>
+      <c r="F14" s="59" t="n"/>
+      <c r="G14" s="59" t="n"/>
+      <c r="H14" s="59" t="n"/>
+      <c r="I14" s="59" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="59" t="n"/>
+      <c r="B15" s="59" t="n"/>
+      <c r="C15" s="59" t="n"/>
+      <c r="D15" s="59" t="n"/>
+      <c r="E15" s="59" t="n"/>
+      <c r="F15" s="59" t="n"/>
+      <c r="G15" s="59" t="n"/>
+      <c r="H15" s="59" t="n"/>
+      <c r="I15" s="59" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="59" t="n"/>
+      <c r="B16" s="59" t="n"/>
+      <c r="C16" s="59" t="n"/>
+      <c r="D16" s="59" t="n"/>
+      <c r="E16" s="59" t="n"/>
+      <c r="F16" s="59" t="n"/>
+      <c r="G16" s="59" t="n"/>
+      <c r="H16" s="59" t="n"/>
+      <c r="I16" s="59" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="59" t="n"/>
+      <c r="B17" s="59" t="n"/>
+      <c r="C17" s="59" t="n"/>
+      <c r="D17" s="59" t="n"/>
+      <c r="E17" s="59" t="n"/>
+      <c r="F17" s="59" t="n"/>
+      <c r="G17" s="59" t="n"/>
+      <c r="H17" s="59" t="n"/>
+      <c r="I17" s="59" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="59" t="n"/>
+      <c r="B18" s="59" t="n"/>
+      <c r="C18" s="59" t="n"/>
+      <c r="D18" s="59" t="n"/>
+      <c r="E18" s="59" t="n"/>
+      <c r="F18" s="59" t="n"/>
+      <c r="G18" s="59" t="n"/>
+      <c r="H18" s="59" t="n"/>
+      <c r="I18" s="59" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="59" t="n"/>
+      <c r="B19" s="59" t="n"/>
+      <c r="C19" s="59" t="n"/>
+      <c r="D19" s="59" t="n"/>
+      <c r="E19" s="59" t="n"/>
+      <c r="F19" s="59" t="n"/>
+      <c r="G19" s="59" t="n"/>
+      <c r="H19" s="59" t="n"/>
+      <c r="I19" s="59" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="59" t="n"/>
+      <c r="B20" s="59" t="n"/>
+      <c r="C20" s="59" t="n"/>
+      <c r="D20" s="59" t="n"/>
+      <c r="E20" s="59" t="n"/>
+      <c r="F20" s="59" t="n"/>
+      <c r="G20" s="59" t="n"/>
+      <c r="H20" s="59" t="n"/>
+      <c r="I20" s="59" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="59" t="n"/>
+      <c r="B21" s="59" t="n"/>
+      <c r="C21" s="59" t="n"/>
+      <c r="D21" s="59" t="n"/>
+      <c r="E21" s="59" t="n"/>
+      <c r="F21" s="59" t="n"/>
+      <c r="G21" s="59" t="n"/>
+      <c r="H21" s="59" t="n"/>
+      <c r="I21" s="59" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="59" t="n"/>
+      <c r="B22" s="59" t="n"/>
+      <c r="C22" s="59" t="n"/>
+      <c r="D22" s="59" t="n"/>
+      <c r="E22" s="59" t="n"/>
+      <c r="F22" s="59" t="n"/>
+      <c r="G22" s="59" t="n"/>
+      <c r="H22" s="59" t="n"/>
+      <c r="I22" s="59" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="59" t="n"/>
+      <c r="B23" s="59" t="n"/>
+      <c r="C23" s="59" t="n"/>
+      <c r="D23" s="59" t="n"/>
+      <c r="E23" s="59" t="n"/>
+      <c r="F23" s="59" t="n"/>
+      <c r="G23" s="59" t="n"/>
+      <c r="H23" s="59" t="n"/>
+      <c r="I23" s="59" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="59" t="n"/>
+      <c r="B24" s="59" t="n"/>
+      <c r="C24" s="59" t="n"/>
+      <c r="D24" s="59" t="n"/>
+      <c r="E24" s="59" t="n"/>
+      <c r="F24" s="59" t="n"/>
+      <c r="G24" s="59" t="n"/>
+      <c r="H24" s="59" t="n"/>
+      <c r="I24" s="59" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="59" t="n"/>
+      <c r="B25" s="59" t="n"/>
+      <c r="C25" s="59" t="n"/>
+      <c r="D25" s="59" t="n"/>
+      <c r="E25" s="59" t="n"/>
+      <c r="F25" s="59" t="n"/>
+      <c r="G25" s="59" t="n"/>
+      <c r="H25" s="59" t="n"/>
+      <c r="I25" s="59" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="59" t="n"/>
+      <c r="B26" s="59" t="n"/>
+      <c r="C26" s="59" t="n"/>
+      <c r="D26" s="59" t="n"/>
+      <c r="E26" s="59" t="n"/>
+      <c r="F26" s="59" t="n"/>
+      <c r="G26" s="59" t="n"/>
+      <c r="H26" s="59" t="n"/>
+      <c r="I26" s="59" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="59" t="n"/>
+      <c r="B27" s="59" t="n"/>
+      <c r="C27" s="59" t="n"/>
+      <c r="D27" s="59" t="n"/>
+      <c r="E27" s="59" t="n"/>
+      <c r="F27" s="59" t="n"/>
+      <c r="G27" s="59" t="n"/>
+      <c r="H27" s="59" t="n"/>
+      <c r="I27" s="59" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="59" t="n"/>
+      <c r="B28" s="59" t="n"/>
+      <c r="C28" s="59" t="n"/>
+      <c r="D28" s="59" t="n"/>
+      <c r="E28" s="59" t="n"/>
+      <c r="F28" s="59" t="n"/>
+      <c r="G28" s="59" t="n"/>
+      <c r="H28" s="59" t="n"/>
+      <c r="I28" s="59" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="59" t="n"/>
+      <c r="B29" s="59" t="n"/>
+      <c r="C29" s="59" t="n"/>
+      <c r="D29" s="59" t="n"/>
+      <c r="E29" s="59" t="n"/>
+      <c r="F29" s="59" t="n"/>
+      <c r="G29" s="59" t="n"/>
+      <c r="H29" s="59" t="n"/>
+      <c r="I29" s="59" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="59" t="n"/>
+      <c r="B30" s="59" t="n"/>
+      <c r="C30" s="59" t="n"/>
+      <c r="D30" s="59" t="n"/>
+      <c r="E30" s="59" t="n"/>
+      <c r="F30" s="59" t="n"/>
+      <c r="G30" s="59" t="n"/>
+      <c r="H30" s="59" t="n"/>
+      <c r="I30" s="59" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="59" t="n"/>
+      <c r="B31" s="59" t="n"/>
+      <c r="C31" s="59" t="n"/>
+      <c r="D31" s="59" t="n"/>
+      <c r="E31" s="59" t="n"/>
+      <c r="F31" s="59" t="n"/>
+      <c r="G31" s="59" t="n"/>
+      <c r="H31" s="59" t="n"/>
+      <c r="I31" s="59" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="59" t="n"/>
+      <c r="B32" s="59" t="n"/>
+      <c r="C32" s="59" t="n"/>
+      <c r="D32" s="59" t="n"/>
+      <c r="E32" s="59" t="n"/>
+      <c r="F32" s="59" t="n"/>
+      <c r="G32" s="59" t="n"/>
+      <c r="H32" s="59" t="n"/>
+      <c r="I32" s="59" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="59" t="n"/>
+      <c r="B33" s="59" t="n"/>
+      <c r="C33" s="59" t="n"/>
+      <c r="D33" s="59" t="n"/>
+      <c r="E33" s="59" t="n"/>
+      <c r="F33" s="59" t="n"/>
+      <c r="G33" s="59" t="n"/>
+      <c r="H33" s="59" t="n"/>
+      <c r="I33" s="59" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="59" t="n"/>
+      <c r="B34" s="59" t="n"/>
+      <c r="C34" s="59" t="n"/>
+      <c r="D34" s="59" t="n"/>
+      <c r="E34" s="59" t="n"/>
+      <c r="F34" s="59" t="n"/>
+      <c r="G34" s="59" t="n"/>
+      <c r="H34" s="59" t="n"/>
+      <c r="I34" s="59" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="59" t="n"/>
+      <c r="B35" s="59" t="n"/>
+      <c r="C35" s="59" t="n"/>
+      <c r="D35" s="59" t="n"/>
+      <c r="E35" s="59" t="n"/>
+      <c r="F35" s="59" t="n"/>
+      <c r="G35" s="59" t="n"/>
+      <c r="H35" s="59" t="n"/>
+      <c r="I35" s="59" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="59" t="n"/>
+      <c r="B36" s="59" t="n"/>
+      <c r="C36" s="59" t="n"/>
+      <c r="D36" s="59" t="n"/>
+      <c r="E36" s="59" t="n"/>
+      <c r="F36" s="59" t="n"/>
+      <c r="G36" s="59" t="n"/>
+      <c r="H36" s="59" t="n"/>
+      <c r="I36" s="59" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="59" t="n"/>
+      <c r="B37" s="59" t="n"/>
+      <c r="C37" s="59" t="n"/>
+      <c r="D37" s="59" t="n"/>
+      <c r="E37" s="59" t="n"/>
+      <c r="F37" s="59" t="n"/>
+      <c r="G37" s="59" t="n"/>
+      <c r="H37" s="59" t="n"/>
+      <c r="I37" s="59" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="59" t="n"/>
+      <c r="B38" s="59" t="n"/>
+      <c r="C38" s="59" t="n"/>
+      <c r="D38" s="59" t="n"/>
+      <c r="E38" s="59" t="n"/>
+      <c r="F38" s="59" t="n"/>
+      <c r="G38" s="59" t="n"/>
+      <c r="H38" s="59" t="n"/>
+      <c r="I38" s="59" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="59" t="n"/>
+      <c r="B39" s="59" t="n"/>
+      <c r="C39" s="59" t="n"/>
+      <c r="D39" s="59" t="n"/>
+      <c r="E39" s="59" t="n"/>
+      <c r="F39" s="59" t="n"/>
+      <c r="G39" s="59" t="n"/>
+      <c r="H39" s="59" t="n"/>
+      <c r="I39" s="59" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="59" t="n"/>
+      <c r="B40" s="59" t="n"/>
+      <c r="C40" s="59" t="n"/>
+      <c r="D40" s="59" t="n"/>
+      <c r="E40" s="59" t="n"/>
+      <c r="F40" s="59" t="n"/>
+      <c r="G40" s="59" t="n"/>
+      <c r="H40" s="59" t="n"/>
+      <c r="I40" s="59" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="59" t="n"/>
+      <c r="B41" s="59" t="n"/>
+      <c r="C41" s="59" t="n"/>
+      <c r="D41" s="59" t="n"/>
+      <c r="E41" s="59" t="n"/>
+      <c r="F41" s="59" t="n"/>
+      <c r="G41" s="59" t="n"/>
+      <c r="H41" s="59" t="n"/>
+      <c r="I41" s="59" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="59" t="n"/>
+      <c r="B42" s="59" t="n"/>
+      <c r="C42" s="59" t="n"/>
+      <c r="D42" s="59" t="n"/>
+      <c r="E42" s="59" t="n"/>
+      <c r="F42" s="59" t="n"/>
+      <c r="G42" s="59" t="n"/>
+      <c r="H42" s="59" t="n"/>
+      <c r="I42" s="59" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="59" t="n"/>
+      <c r="B43" s="59" t="n"/>
+      <c r="C43" s="59" t="n"/>
+      <c r="D43" s="59" t="n"/>
+      <c r="E43" s="59" t="n"/>
+      <c r="F43" s="59" t="n"/>
+      <c r="G43" s="59" t="n"/>
+      <c r="H43" s="59" t="n"/>
+      <c r="I43" s="59" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="59" t="n"/>
+      <c r="B44" s="59" t="n"/>
+      <c r="C44" s="59" t="n"/>
+      <c r="D44" s="59" t="n"/>
+      <c r="E44" s="59" t="n"/>
+      <c r="F44" s="59" t="n"/>
+      <c r="G44" s="59" t="n"/>
+      <c r="H44" s="59" t="n"/>
+      <c r="I44" s="59" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="59" t="n"/>
+      <c r="B45" s="59" t="n"/>
+      <c r="C45" s="59" t="n"/>
+      <c r="D45" s="59" t="n"/>
+      <c r="E45" s="59" t="n"/>
+      <c r="F45" s="59" t="n"/>
+      <c r="G45" s="59" t="n"/>
+      <c r="H45" s="59" t="n"/>
+      <c r="I45" s="59" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="59" t="n"/>
+      <c r="B46" s="59" t="n"/>
+      <c r="C46" s="59" t="n"/>
+      <c r="D46" s="59" t="n"/>
+      <c r="E46" s="59" t="n"/>
+      <c r="F46" s="59" t="n"/>
+      <c r="G46" s="59" t="n"/>
+      <c r="H46" s="59" t="n"/>
+      <c r="I46" s="59" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="59" t="n"/>
+      <c r="B47" s="59" t="n"/>
+      <c r="C47" s="59" t="n"/>
+      <c r="D47" s="59" t="n"/>
+      <c r="E47" s="59" t="n"/>
+      <c r="F47" s="59" t="n"/>
+      <c r="G47" s="59" t="n"/>
+      <c r="H47" s="59" t="n"/>
+      <c r="I47" s="59" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="59" t="n"/>
+      <c r="B48" s="59" t="n"/>
+      <c r="C48" s="59" t="n"/>
+      <c r="D48" s="59" t="n"/>
+      <c r="E48" s="59" t="n"/>
+      <c r="F48" s="59" t="n"/>
+      <c r="G48" s="59" t="n"/>
+      <c r="H48" s="59" t="n"/>
+      <c r="I48" s="59" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/report/项目执行计划.xlsx
+++ b/report/项目执行计划.xlsx
@@ -2983,7 +2983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I512"/>
+  <dimension ref="A1:I174"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6656,3724 +6656,38 @@
       <c r="H174" s="59" t="n"/>
       <c r="I174" s="59" t="n"/>
     </row>
-    <row r="175" ht="22" customHeight="1">
-      <c r="A175" s="96" t="n"/>
-      <c r="B175" s="96" t="n"/>
-      <c r="C175" s="96" t="n"/>
-      <c r="D175" s="97" t="n"/>
-      <c r="E175" s="96" t="n"/>
-      <c r="F175" s="98" t="n"/>
-      <c r="G175" s="59" t="n"/>
-      <c r="H175" s="59" t="n"/>
-      <c r="I175" s="59" t="n"/>
-    </row>
-    <row r="176" ht="22" customHeight="1">
-      <c r="A176" s="96" t="n"/>
-      <c r="B176" s="96" t="n"/>
-      <c r="C176" s="96" t="n"/>
-      <c r="D176" s="97" t="n"/>
-      <c r="E176" s="96" t="n"/>
-      <c r="F176" s="98" t="n"/>
-      <c r="G176" s="59" t="n"/>
-      <c r="H176" s="59" t="n"/>
-      <c r="I176" s="59" t="n"/>
-    </row>
-    <row r="177" ht="22" customHeight="1">
-      <c r="A177" s="99" t="n"/>
-      <c r="B177" s="100" t="n"/>
-      <c r="C177" s="101" t="n"/>
-      <c r="D177" s="97" t="n"/>
-      <c r="E177" s="98" t="n"/>
-      <c r="F177" s="98" t="n"/>
-      <c r="G177" s="59" t="n"/>
-      <c r="H177" s="59" t="n"/>
-      <c r="I177" s="59" t="n"/>
-    </row>
-    <row r="178" ht="22" customHeight="1">
-      <c r="A178" s="96" t="n"/>
-      <c r="B178" s="96" t="n"/>
-      <c r="C178" s="96" t="n"/>
-      <c r="D178" s="97" t="n"/>
-      <c r="E178" s="96" t="n"/>
-      <c r="F178" s="98" t="n"/>
-      <c r="G178" s="59" t="n"/>
-      <c r="H178" s="59" t="n"/>
-      <c r="I178" s="59" t="n"/>
-    </row>
-    <row r="179" ht="22" customHeight="1">
-      <c r="A179" s="99" t="n"/>
-      <c r="B179" s="100" t="n"/>
-      <c r="C179" s="102" t="n"/>
-      <c r="D179" s="97" t="n"/>
-      <c r="E179" s="98" t="n"/>
-      <c r="F179" s="98" t="n"/>
-      <c r="G179" s="59" t="n"/>
-      <c r="H179" s="59" t="n"/>
-      <c r="I179" s="59" t="n"/>
-    </row>
-    <row r="180" ht="22" customHeight="1">
-      <c r="A180" s="96" t="n"/>
-      <c r="B180" s="96" t="n"/>
-      <c r="C180" s="96" t="n"/>
-      <c r="D180" s="97" t="n"/>
-      <c r="E180" s="96" t="n"/>
-      <c r="F180" s="98" t="n"/>
-      <c r="G180" s="59" t="n"/>
-      <c r="H180" s="59" t="n"/>
-      <c r="I180" s="59" t="n"/>
-    </row>
-    <row r="181" ht="22" customHeight="1">
-      <c r="A181" s="96" t="n"/>
-      <c r="B181" s="96" t="n"/>
-      <c r="C181" s="96" t="n"/>
-      <c r="D181" s="97" t="n"/>
-      <c r="E181" s="96" t="n"/>
-      <c r="F181" s="98" t="n"/>
-      <c r="G181" s="59" t="n"/>
-      <c r="H181" s="59" t="n"/>
-      <c r="I181" s="59" t="n"/>
-    </row>
-    <row r="182" ht="22" customHeight="1">
-      <c r="A182" s="96" t="n"/>
-      <c r="B182" s="96" t="n"/>
-      <c r="C182" s="96" t="n"/>
-      <c r="D182" s="97" t="n"/>
-      <c r="E182" s="96" t="n"/>
-      <c r="F182" s="98" t="n"/>
-      <c r="G182" s="59" t="n"/>
-      <c r="H182" s="59" t="n"/>
-      <c r="I182" s="59" t="n"/>
-    </row>
-    <row r="183" ht="22" customHeight="1">
-      <c r="A183" s="99" t="n"/>
-      <c r="B183" s="100" t="n"/>
-      <c r="C183" s="103" t="n"/>
-      <c r="D183" s="97" t="n"/>
-      <c r="E183" s="98" t="n"/>
-      <c r="F183" s="98" t="n"/>
-      <c r="G183" s="59" t="n"/>
-      <c r="H183" s="59" t="n"/>
-      <c r="I183" s="59" t="n"/>
-    </row>
-    <row r="184" ht="22" customHeight="1">
-      <c r="A184" s="96" t="n"/>
-      <c r="B184" s="96" t="n"/>
-      <c r="C184" s="96" t="n"/>
-      <c r="D184" s="97" t="n"/>
-      <c r="E184" s="96" t="n"/>
-      <c r="F184" s="98" t="n"/>
-      <c r="G184" s="59" t="n"/>
-      <c r="H184" s="59" t="n"/>
-      <c r="I184" s="59" t="n"/>
-    </row>
-    <row r="185" ht="22" customHeight="1">
-      <c r="A185" s="96" t="n"/>
-      <c r="B185" s="96" t="n"/>
-      <c r="C185" s="96" t="n"/>
-      <c r="D185" s="97" t="n"/>
-      <c r="E185" s="96" t="n"/>
-      <c r="F185" s="98" t="n"/>
-      <c r="G185" s="59" t="n"/>
-      <c r="H185" s="59" t="n"/>
-      <c r="I185" s="59" t="n"/>
-    </row>
-    <row r="186" ht="22" customHeight="1">
-      <c r="A186" s="96" t="n"/>
-      <c r="B186" s="96" t="n"/>
-      <c r="C186" s="96" t="n"/>
-      <c r="D186" s="97" t="n"/>
-      <c r="E186" s="96" t="n"/>
-      <c r="F186" s="98" t="n"/>
-      <c r="G186" s="59" t="n"/>
-      <c r="H186" s="59" t="n"/>
-      <c r="I186" s="59" t="n"/>
-    </row>
-    <row r="187" ht="22" customHeight="1">
-      <c r="A187" s="99" t="n"/>
-      <c r="B187" s="100" t="n"/>
-      <c r="C187" s="99" t="n"/>
-      <c r="D187" s="97" t="n"/>
-      <c r="E187" s="98" t="n"/>
-      <c r="F187" s="98" t="n"/>
-      <c r="G187" s="59" t="n"/>
-      <c r="H187" s="59" t="n"/>
-      <c r="I187" s="59" t="n"/>
-    </row>
-    <row r="188" ht="22" customHeight="1">
-      <c r="A188" s="96" t="n"/>
-      <c r="B188" s="96" t="n"/>
-      <c r="C188" s="96" t="n"/>
-      <c r="D188" s="97" t="n"/>
-      <c r="E188" s="96" t="n"/>
-      <c r="F188" s="98" t="n"/>
-      <c r="G188" s="59" t="n"/>
-      <c r="H188" s="59" t="n"/>
-      <c r="I188" s="59" t="n"/>
-    </row>
-    <row r="189" ht="22" customHeight="1">
-      <c r="A189" s="96" t="n"/>
-      <c r="B189" s="96" t="n"/>
-      <c r="C189" s="96" t="n"/>
-      <c r="D189" s="97" t="n"/>
-      <c r="E189" s="96" t="n"/>
-      <c r="F189" s="98" t="n"/>
-      <c r="G189" s="59" t="n"/>
-      <c r="H189" s="59" t="n"/>
-      <c r="I189" s="59" t="n"/>
-    </row>
-    <row r="190" ht="22" customHeight="1">
-      <c r="A190" s="96" t="n"/>
-      <c r="B190" s="96" t="n"/>
-      <c r="C190" s="96" t="n"/>
-      <c r="D190" s="97" t="n"/>
-      <c r="E190" s="96" t="n"/>
-      <c r="F190" s="98" t="n"/>
-      <c r="G190" s="59" t="n"/>
-      <c r="H190" s="59" t="n"/>
-      <c r="I190" s="59" t="n"/>
-    </row>
-    <row r="191" ht="22" customHeight="1">
-      <c r="A191" s="99" t="n"/>
-      <c r="B191" s="100" t="n"/>
-      <c r="C191" s="104" t="n"/>
-      <c r="D191" s="97" t="n"/>
-      <c r="E191" s="98" t="n"/>
-      <c r="F191" s="98" t="n"/>
-      <c r="G191" s="59" t="n"/>
-      <c r="H191" s="59" t="n"/>
-      <c r="I191" s="59" t="n"/>
-    </row>
-    <row r="192" ht="22" customHeight="1">
-      <c r="A192" s="96" t="n"/>
-      <c r="B192" s="96" t="n"/>
-      <c r="C192" s="96" t="n"/>
-      <c r="D192" s="97" t="n"/>
-      <c r="E192" s="96" t="n"/>
-      <c r="F192" s="98" t="n"/>
-      <c r="G192" s="59" t="n"/>
-      <c r="H192" s="59" t="n"/>
-      <c r="I192" s="59" t="n"/>
-    </row>
-    <row r="193" ht="22" customHeight="1">
-      <c r="A193" s="96" t="n"/>
-      <c r="B193" s="96" t="n"/>
-      <c r="C193" s="96" t="n"/>
-      <c r="D193" s="97" t="n"/>
-      <c r="E193" s="96" t="n"/>
-      <c r="F193" s="98" t="n"/>
-      <c r="G193" s="59" t="n"/>
-      <c r="H193" s="59" t="n"/>
-      <c r="I193" s="59" t="n"/>
-    </row>
-    <row r="194" ht="22" customHeight="1">
-      <c r="A194" s="99" t="n"/>
-      <c r="B194" s="100" t="n"/>
-      <c r="C194" s="101" t="n"/>
-      <c r="D194" s="97" t="n"/>
-      <c r="E194" s="98" t="n"/>
-      <c r="F194" s="98" t="n"/>
-      <c r="G194" s="59" t="n"/>
-      <c r="H194" s="59" t="n"/>
-      <c r="I194" s="59" t="n"/>
-    </row>
-    <row r="195" ht="22" customHeight="1">
-      <c r="A195" s="96" t="n"/>
-      <c r="B195" s="96" t="n"/>
-      <c r="C195" s="96" t="n"/>
-      <c r="D195" s="97" t="n"/>
-      <c r="E195" s="96" t="n"/>
-      <c r="F195" s="98" t="n"/>
-      <c r="G195" s="59" t="n"/>
-      <c r="H195" s="59" t="n"/>
-      <c r="I195" s="59" t="n"/>
-    </row>
-    <row r="196" ht="22" customHeight="1">
-      <c r="A196" s="99" t="n"/>
-      <c r="B196" s="100" t="n"/>
-      <c r="C196" s="102" t="n"/>
-      <c r="D196" s="97" t="n"/>
-      <c r="E196" s="98" t="n"/>
-      <c r="F196" s="98" t="n"/>
-      <c r="G196" s="59" t="n"/>
-      <c r="H196" s="59" t="n"/>
-      <c r="I196" s="59" t="n"/>
-    </row>
-    <row r="197" ht="22" customHeight="1">
-      <c r="A197" s="96" t="n"/>
-      <c r="B197" s="96" t="n"/>
-      <c r="C197" s="96" t="n"/>
-      <c r="D197" s="97" t="n"/>
-      <c r="E197" s="96" t="n"/>
-      <c r="F197" s="98" t="n"/>
-      <c r="G197" s="59" t="n"/>
-      <c r="H197" s="59" t="n"/>
-      <c r="I197" s="59" t="n"/>
-    </row>
-    <row r="198" ht="22" customHeight="1">
-      <c r="A198" s="96" t="n"/>
-      <c r="B198" s="96" t="n"/>
-      <c r="C198" s="96" t="n"/>
-      <c r="D198" s="97" t="n"/>
-      <c r="E198" s="96" t="n"/>
-      <c r="F198" s="98" t="n"/>
-      <c r="G198" s="59" t="n"/>
-      <c r="H198" s="59" t="n"/>
-      <c r="I198" s="59" t="n"/>
-    </row>
-    <row r="199" ht="22" customHeight="1">
-      <c r="A199" s="99" t="n"/>
-      <c r="B199" s="100" t="n"/>
-      <c r="C199" s="103" t="n"/>
-      <c r="D199" s="97" t="n"/>
-      <c r="E199" s="98" t="n"/>
-      <c r="F199" s="98" t="n"/>
-      <c r="G199" s="59" t="n"/>
-      <c r="H199" s="59" t="n"/>
-      <c r="I199" s="59" t="n"/>
-    </row>
-    <row r="200" ht="22" customHeight="1">
-      <c r="A200" s="96" t="n"/>
-      <c r="B200" s="96" t="n"/>
-      <c r="C200" s="96" t="n"/>
-      <c r="D200" s="97" t="n"/>
-      <c r="E200" s="96" t="n"/>
-      <c r="F200" s="98" t="n"/>
-      <c r="G200" s="59" t="n"/>
-      <c r="H200" s="59" t="n"/>
-      <c r="I200" s="59" t="n"/>
-    </row>
-    <row r="201" ht="22" customHeight="1">
-      <c r="A201" s="99" t="n"/>
-      <c r="B201" s="100" t="n"/>
-      <c r="C201" s="99" t="n"/>
-      <c r="D201" s="97" t="n"/>
-      <c r="E201" s="98" t="n"/>
-      <c r="F201" s="98" t="n"/>
-      <c r="G201" s="59" t="n"/>
-      <c r="H201" s="59" t="n"/>
-      <c r="I201" s="59" t="n"/>
-    </row>
-    <row r="202" ht="22" customHeight="1">
-      <c r="A202" s="96" t="n"/>
-      <c r="B202" s="96" t="n"/>
-      <c r="C202" s="96" t="n"/>
-      <c r="D202" s="97" t="n"/>
-      <c r="E202" s="96" t="n"/>
-      <c r="F202" s="98" t="n"/>
-      <c r="G202" s="59" t="n"/>
-      <c r="H202" s="59" t="n"/>
-      <c r="I202" s="59" t="n"/>
-    </row>
-    <row r="203" ht="22" customHeight="1">
-      <c r="A203" s="96" t="n"/>
-      <c r="B203" s="96" t="n"/>
-      <c r="C203" s="96" t="n"/>
-      <c r="D203" s="97" t="n"/>
-      <c r="E203" s="96" t="n"/>
-      <c r="F203" s="98" t="n"/>
-      <c r="G203" s="59" t="n"/>
-      <c r="H203" s="59" t="n"/>
-      <c r="I203" s="59" t="n"/>
-    </row>
-    <row r="204" ht="22" customHeight="1">
-      <c r="A204" s="99" t="n"/>
-      <c r="B204" s="100" t="n"/>
-      <c r="C204" s="104" t="n"/>
-      <c r="D204" s="97" t="n"/>
-      <c r="E204" s="98" t="n"/>
-      <c r="F204" s="98" t="n"/>
-      <c r="G204" s="59" t="n"/>
-      <c r="H204" s="59" t="n"/>
-      <c r="I204" s="59" t="n"/>
-    </row>
-    <row r="205" ht="22" customHeight="1">
-      <c r="A205" s="96" t="n"/>
-      <c r="B205" s="96" t="n"/>
-      <c r="C205" s="96" t="n"/>
-      <c r="D205" s="97" t="n"/>
-      <c r="E205" s="96" t="n"/>
-      <c r="F205" s="98" t="n"/>
-      <c r="G205" s="59" t="n"/>
-      <c r="H205" s="59" t="n"/>
-      <c r="I205" s="59" t="n"/>
-    </row>
-    <row r="206" ht="22" customHeight="1">
-      <c r="A206" s="96" t="n"/>
-      <c r="B206" s="96" t="n"/>
-      <c r="C206" s="96" t="n"/>
-      <c r="D206" s="97" t="n"/>
-      <c r="E206" s="96" t="n"/>
-      <c r="F206" s="98" t="n"/>
-      <c r="G206" s="59" t="n"/>
-      <c r="H206" s="59" t="n"/>
-      <c r="I206" s="59" t="n"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="99" t="n"/>
-      <c r="B207" s="100" t="n"/>
-      <c r="C207" s="105" t="n"/>
-      <c r="D207" s="97" t="n"/>
-      <c r="E207" s="105" t="n"/>
-      <c r="F207" s="98" t="n"/>
-      <c r="G207" s="59" t="n"/>
-      <c r="H207" s="59" t="n"/>
-      <c r="I207" s="59" t="n"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="99" t="n"/>
-      <c r="B208" s="100" t="n"/>
-      <c r="C208" s="99" t="n"/>
-      <c r="D208" s="97" t="n"/>
-      <c r="E208" s="98" t="n"/>
-      <c r="F208" s="98" t="n"/>
-      <c r="G208" s="59" t="n"/>
-      <c r="H208" s="59" t="n"/>
-      <c r="I208" s="59" t="n"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="99" t="n"/>
-      <c r="B209" s="100" t="n"/>
-      <c r="C209" s="105" t="n"/>
-      <c r="D209" s="97" t="n"/>
-      <c r="E209" s="105" t="n"/>
-      <c r="F209" s="98" t="n"/>
-      <c r="G209" s="59" t="n"/>
-      <c r="H209" s="59" t="n"/>
-      <c r="I209" s="59" t="n"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="99" t="n"/>
-      <c r="B210" s="100" t="n"/>
-      <c r="C210" s="105" t="n"/>
-      <c r="D210" s="97" t="n"/>
-      <c r="E210" s="105" t="n"/>
-      <c r="F210" s="98" t="n"/>
-      <c r="G210" s="59" t="n"/>
-      <c r="H210" s="59" t="n"/>
-      <c r="I210" s="59" t="n"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="99" t="n"/>
-      <c r="B211" s="100" t="n"/>
-      <c r="C211" s="104" t="n"/>
-      <c r="D211" s="97" t="n"/>
-      <c r="E211" s="98" t="n"/>
-      <c r="F211" s="98" t="n"/>
-      <c r="G211" s="59" t="n"/>
-      <c r="H211" s="59" t="n"/>
-      <c r="I211" s="59" t="n"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="99" t="n"/>
-      <c r="B212" s="100" t="n"/>
-      <c r="C212" s="105" t="n"/>
-      <c r="D212" s="97" t="n"/>
-      <c r="E212" s="105" t="n"/>
-      <c r="F212" s="98" t="n"/>
-      <c r="G212" s="59" t="n"/>
-      <c r="H212" s="59" t="n"/>
-      <c r="I212" s="59" t="n"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="99" t="n"/>
-      <c r="B213" s="100" t="n"/>
-      <c r="C213" s="105" t="n"/>
-      <c r="D213" s="97" t="n"/>
-      <c r="E213" s="105" t="n"/>
-      <c r="F213" s="98" t="n"/>
-      <c r="G213" s="59" t="n"/>
-      <c r="H213" s="59" t="n"/>
-      <c r="I213" s="59" t="n"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="59" t="n"/>
-      <c r="B214" s="59" t="n"/>
-      <c r="C214" s="59" t="n"/>
-      <c r="D214" s="59" t="n"/>
-      <c r="E214" s="59" t="n"/>
-      <c r="F214" s="59" t="n"/>
-      <c r="G214" s="59" t="n"/>
-      <c r="H214" s="59" t="n"/>
-      <c r="I214" s="59" t="n"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="59" t="n"/>
-      <c r="B215" s="59" t="n"/>
-      <c r="C215" s="59" t="n"/>
-      <c r="D215" s="59" t="n"/>
-      <c r="E215" s="59" t="n"/>
-      <c r="F215" s="59" t="n"/>
-      <c r="G215" s="59" t="n"/>
-      <c r="H215" s="59" t="n"/>
-      <c r="I215" s="59" t="n"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="59" t="n"/>
-      <c r="B216" s="59" t="n"/>
-      <c r="C216" s="59" t="n"/>
-      <c r="D216" s="59" t="n"/>
-      <c r="E216" s="59" t="n"/>
-      <c r="F216" s="59" t="n"/>
-      <c r="G216" s="59" t="n"/>
-      <c r="H216" s="59" t="n"/>
-      <c r="I216" s="59" t="n"/>
-    </row>
-    <row r="217">
-      <c r="A217" s="59" t="n"/>
-      <c r="B217" s="59" t="n"/>
-      <c r="C217" s="59" t="n"/>
-      <c r="D217" s="59" t="n"/>
-      <c r="E217" s="59" t="n"/>
-      <c r="F217" s="59" t="n"/>
-      <c r="G217" s="59" t="n"/>
-      <c r="H217" s="59" t="n"/>
-      <c r="I217" s="59" t="n"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="59" t="n"/>
-      <c r="B218" s="59" t="n"/>
-      <c r="C218" s="59" t="n"/>
-      <c r="D218" s="59" t="n"/>
-      <c r="E218" s="59" t="n"/>
-      <c r="F218" s="59" t="n"/>
-      <c r="G218" s="59" t="n"/>
-      <c r="H218" s="59" t="n"/>
-      <c r="I218" s="59" t="n"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="59" t="n"/>
-      <c r="B219" s="59" t="n"/>
-      <c r="C219" s="59" t="n"/>
-      <c r="D219" s="59" t="n"/>
-      <c r="E219" s="59" t="n"/>
-      <c r="F219" s="59" t="n"/>
-      <c r="G219" s="59" t="n"/>
-      <c r="H219" s="59" t="n"/>
-      <c r="I219" s="59" t="n"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="59" t="n"/>
-      <c r="B220" s="59" t="n"/>
-      <c r="C220" s="59" t="n"/>
-      <c r="D220" s="59" t="n"/>
-      <c r="E220" s="59" t="n"/>
-      <c r="F220" s="59" t="n"/>
-      <c r="G220" s="59" t="n"/>
-      <c r="H220" s="59" t="n"/>
-      <c r="I220" s="59" t="n"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="59" t="n"/>
-      <c r="B221" s="59" t="n"/>
-      <c r="C221" s="59" t="n"/>
-      <c r="D221" s="59" t="n"/>
-      <c r="E221" s="59" t="n"/>
-      <c r="F221" s="59" t="n"/>
-      <c r="G221" s="59" t="n"/>
-      <c r="H221" s="59" t="n"/>
-      <c r="I221" s="59" t="n"/>
-    </row>
-    <row r="222">
-      <c r="A222" s="59" t="n"/>
-      <c r="B222" s="59" t="n"/>
-      <c r="C222" s="59" t="n"/>
-      <c r="D222" s="59" t="n"/>
-      <c r="E222" s="59" t="n"/>
-      <c r="F222" s="59" t="n"/>
-      <c r="G222" s="59" t="n"/>
-      <c r="H222" s="59" t="n"/>
-      <c r="I222" s="59" t="n"/>
-    </row>
-    <row r="223">
-      <c r="A223" s="59" t="n"/>
-      <c r="B223" s="59" t="n"/>
-      <c r="C223" s="59" t="n"/>
-      <c r="D223" s="59" t="n"/>
-      <c r="E223" s="59" t="n"/>
-      <c r="F223" s="59" t="n"/>
-      <c r="G223" s="59" t="n"/>
-      <c r="H223" s="59" t="n"/>
-      <c r="I223" s="59" t="n"/>
-    </row>
-    <row r="224">
-      <c r="A224" s="59" t="n"/>
-      <c r="B224" s="59" t="n"/>
-      <c r="C224" s="59" t="n"/>
-      <c r="D224" s="59" t="n"/>
-      <c r="E224" s="59" t="n"/>
-      <c r="F224" s="59" t="n"/>
-      <c r="G224" s="59" t="n"/>
-      <c r="H224" s="59" t="n"/>
-      <c r="I224" s="59" t="n"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="59" t="n"/>
-      <c r="B225" s="59" t="n"/>
-      <c r="C225" s="59" t="n"/>
-      <c r="D225" s="59" t="n"/>
-      <c r="E225" s="59" t="n"/>
-      <c r="F225" s="59" t="n"/>
-      <c r="G225" s="59" t="n"/>
-      <c r="H225" s="59" t="n"/>
-      <c r="I225" s="59" t="n"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="59" t="n"/>
-      <c r="B226" s="59" t="n"/>
-      <c r="C226" s="59" t="n"/>
-      <c r="D226" s="59" t="n"/>
-      <c r="E226" s="59" t="n"/>
-      <c r="F226" s="59" t="n"/>
-      <c r="G226" s="59" t="n"/>
-      <c r="H226" s="59" t="n"/>
-      <c r="I226" s="59" t="n"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="59" t="n"/>
-      <c r="B227" s="59" t="n"/>
-      <c r="C227" s="59" t="n"/>
-      <c r="D227" s="59" t="n"/>
-      <c r="E227" s="59" t="n"/>
-      <c r="F227" s="59" t="n"/>
-      <c r="G227" s="59" t="n"/>
-      <c r="H227" s="59" t="n"/>
-      <c r="I227" s="59" t="n"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="59" t="n"/>
-      <c r="B228" s="59" t="n"/>
-      <c r="C228" s="59" t="n"/>
-      <c r="D228" s="59" t="n"/>
-      <c r="E228" s="59" t="n"/>
-      <c r="F228" s="59" t="n"/>
-      <c r="G228" s="59" t="n"/>
-      <c r="H228" s="59" t="n"/>
-      <c r="I228" s="59" t="n"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="59" t="n"/>
-      <c r="B229" s="59" t="n"/>
-      <c r="C229" s="59" t="n"/>
-      <c r="D229" s="59" t="n"/>
-      <c r="E229" s="59" t="n"/>
-      <c r="F229" s="59" t="n"/>
-      <c r="G229" s="59" t="n"/>
-      <c r="H229" s="59" t="n"/>
-      <c r="I229" s="59" t="n"/>
-    </row>
-    <row r="230">
-      <c r="A230" s="59" t="n"/>
-      <c r="B230" s="59" t="n"/>
-      <c r="C230" s="59" t="n"/>
-      <c r="D230" s="59" t="n"/>
-      <c r="E230" s="59" t="n"/>
-      <c r="F230" s="59" t="n"/>
-      <c r="G230" s="59" t="n"/>
-      <c r="H230" s="59" t="n"/>
-      <c r="I230" s="59" t="n"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="59" t="n"/>
-      <c r="B231" s="59" t="n"/>
-      <c r="C231" s="59" t="n"/>
-      <c r="D231" s="59" t="n"/>
-      <c r="E231" s="59" t="n"/>
-      <c r="F231" s="59" t="n"/>
-      <c r="G231" s="59" t="n"/>
-      <c r="H231" s="59" t="n"/>
-      <c r="I231" s="59" t="n"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="59" t="n"/>
-      <c r="B232" s="59" t="n"/>
-      <c r="C232" s="59" t="n"/>
-      <c r="D232" s="59" t="n"/>
-      <c r="E232" s="59" t="n"/>
-      <c r="F232" s="59" t="n"/>
-      <c r="G232" s="59" t="n"/>
-      <c r="H232" s="59" t="n"/>
-      <c r="I232" s="59" t="n"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="59" t="n"/>
-      <c r="B233" s="59" t="n"/>
-      <c r="C233" s="59" t="n"/>
-      <c r="D233" s="59" t="n"/>
-      <c r="E233" s="59" t="n"/>
-      <c r="F233" s="59" t="n"/>
-      <c r="G233" s="59" t="n"/>
-      <c r="H233" s="59" t="n"/>
-      <c r="I233" s="59" t="n"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="59" t="n"/>
-      <c r="B234" s="59" t="n"/>
-      <c r="C234" s="59" t="n"/>
-      <c r="D234" s="59" t="n"/>
-      <c r="E234" s="59" t="n"/>
-      <c r="F234" s="59" t="n"/>
-      <c r="G234" s="59" t="n"/>
-      <c r="H234" s="59" t="n"/>
-      <c r="I234" s="59" t="n"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="59" t="n"/>
-      <c r="B235" s="59" t="n"/>
-      <c r="C235" s="59" t="n"/>
-      <c r="D235" s="59" t="n"/>
-      <c r="E235" s="59" t="n"/>
-      <c r="F235" s="59" t="n"/>
-      <c r="G235" s="59" t="n"/>
-      <c r="H235" s="59" t="n"/>
-      <c r="I235" s="59" t="n"/>
-    </row>
-    <row r="236">
-      <c r="A236" s="59" t="n"/>
-      <c r="B236" s="59" t="n"/>
-      <c r="C236" s="59" t="n"/>
-      <c r="D236" s="59" t="n"/>
-      <c r="E236" s="59" t="n"/>
-      <c r="F236" s="59" t="n"/>
-      <c r="G236" s="59" t="n"/>
-      <c r="H236" s="59" t="n"/>
-      <c r="I236" s="59" t="n"/>
-    </row>
-    <row r="237">
-      <c r="A237" s="59" t="n"/>
-      <c r="B237" s="59" t="n"/>
-      <c r="C237" s="59" t="n"/>
-      <c r="D237" s="59" t="n"/>
-      <c r="E237" s="59" t="n"/>
-      <c r="F237" s="59" t="n"/>
-      <c r="G237" s="59" t="n"/>
-      <c r="H237" s="59" t="n"/>
-      <c r="I237" s="59" t="n"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="59" t="n"/>
-      <c r="B238" s="59" t="n"/>
-      <c r="C238" s="59" t="n"/>
-      <c r="D238" s="59" t="n"/>
-      <c r="E238" s="59" t="n"/>
-      <c r="F238" s="59" t="n"/>
-      <c r="G238" s="59" t="n"/>
-      <c r="H238" s="59" t="n"/>
-      <c r="I238" s="59" t="n"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="59" t="n"/>
-      <c r="B239" s="59" t="n"/>
-      <c r="C239" s="59" t="n"/>
-      <c r="D239" s="59" t="n"/>
-      <c r="E239" s="59" t="n"/>
-      <c r="F239" s="59" t="n"/>
-      <c r="G239" s="59" t="n"/>
-      <c r="H239" s="59" t="n"/>
-      <c r="I239" s="59" t="n"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="59" t="n"/>
-      <c r="B240" s="59" t="n"/>
-      <c r="C240" s="59" t="n"/>
-      <c r="D240" s="59" t="n"/>
-      <c r="E240" s="59" t="n"/>
-      <c r="F240" s="59" t="n"/>
-      <c r="G240" s="59" t="n"/>
-      <c r="H240" s="59" t="n"/>
-      <c r="I240" s="59" t="n"/>
-    </row>
-    <row r="241">
-      <c r="A241" s="59" t="n"/>
-      <c r="B241" s="59" t="n"/>
-      <c r="C241" s="59" t="n"/>
-      <c r="D241" s="59" t="n"/>
-      <c r="E241" s="59" t="n"/>
-      <c r="F241" s="59" t="n"/>
-      <c r="G241" s="59" t="n"/>
-      <c r="H241" s="59" t="n"/>
-      <c r="I241" s="59" t="n"/>
-    </row>
-    <row r="242">
-      <c r="A242" s="59" t="n"/>
-      <c r="B242" s="59" t="n"/>
-      <c r="C242" s="59" t="n"/>
-      <c r="D242" s="59" t="n"/>
-      <c r="E242" s="59" t="n"/>
-      <c r="F242" s="59" t="n"/>
-      <c r="G242" s="59" t="n"/>
-      <c r="H242" s="59" t="n"/>
-      <c r="I242" s="59" t="n"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="59" t="n"/>
-      <c r="B243" s="59" t="n"/>
-      <c r="C243" s="59" t="n"/>
-      <c r="D243" s="59" t="n"/>
-      <c r="E243" s="59" t="n"/>
-      <c r="F243" s="59" t="n"/>
-      <c r="G243" s="59" t="n"/>
-      <c r="H243" s="59" t="n"/>
-      <c r="I243" s="59" t="n"/>
-    </row>
-    <row r="244">
-      <c r="A244" s="59" t="n"/>
-      <c r="B244" s="59" t="n"/>
-      <c r="C244" s="59" t="n"/>
-      <c r="D244" s="59" t="n"/>
-      <c r="E244" s="59" t="n"/>
-      <c r="F244" s="59" t="n"/>
-      <c r="G244" s="59" t="n"/>
-      <c r="H244" s="59" t="n"/>
-      <c r="I244" s="59" t="n"/>
-    </row>
-    <row r="245">
-      <c r="A245" s="59" t="n"/>
-      <c r="B245" s="59" t="n"/>
-      <c r="C245" s="59" t="n"/>
-      <c r="D245" s="59" t="n"/>
-      <c r="E245" s="59" t="n"/>
-      <c r="F245" s="59" t="n"/>
-      <c r="G245" s="59" t="n"/>
-      <c r="H245" s="59" t="n"/>
-      <c r="I245" s="59" t="n"/>
-    </row>
-    <row r="246">
-      <c r="A246" s="59" t="n"/>
-      <c r="B246" s="59" t="n"/>
-      <c r="C246" s="59" t="n"/>
-      <c r="D246" s="59" t="n"/>
-      <c r="E246" s="59" t="n"/>
-      <c r="F246" s="59" t="n"/>
-      <c r="G246" s="59" t="n"/>
-      <c r="H246" s="59" t="n"/>
-      <c r="I246" s="59" t="n"/>
-    </row>
-    <row r="247">
-      <c r="A247" s="59" t="n"/>
-      <c r="B247" s="59" t="n"/>
-      <c r="C247" s="59" t="n"/>
-      <c r="D247" s="59" t="n"/>
-      <c r="E247" s="59" t="n"/>
-      <c r="F247" s="59" t="n"/>
-      <c r="G247" s="59" t="n"/>
-      <c r="H247" s="59" t="n"/>
-      <c r="I247" s="59" t="n"/>
-    </row>
-    <row r="248">
-      <c r="A248" s="59" t="n"/>
-      <c r="B248" s="59" t="n"/>
-      <c r="C248" s="59" t="n"/>
-      <c r="D248" s="59" t="n"/>
-      <c r="E248" s="59" t="n"/>
-      <c r="F248" s="59" t="n"/>
-      <c r="G248" s="59" t="n"/>
-      <c r="H248" s="59" t="n"/>
-      <c r="I248" s="59" t="n"/>
-    </row>
-    <row r="249">
-      <c r="A249" s="59" t="n"/>
-      <c r="B249" s="59" t="n"/>
-      <c r="C249" s="59" t="n"/>
-      <c r="D249" s="59" t="n"/>
-      <c r="E249" s="59" t="n"/>
-      <c r="F249" s="59" t="n"/>
-      <c r="G249" s="59" t="n"/>
-      <c r="H249" s="59" t="n"/>
-      <c r="I249" s="59" t="n"/>
-    </row>
-    <row r="250">
-      <c r="A250" s="59" t="n"/>
-      <c r="B250" s="59" t="n"/>
-      <c r="C250" s="59" t="n"/>
-      <c r="D250" s="59" t="n"/>
-      <c r="E250" s="59" t="n"/>
-      <c r="F250" s="59" t="n"/>
-      <c r="G250" s="59" t="n"/>
-      <c r="H250" s="59" t="n"/>
-      <c r="I250" s="59" t="n"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="59" t="n"/>
-      <c r="B251" s="59" t="n"/>
-      <c r="C251" s="59" t="n"/>
-      <c r="D251" s="59" t="n"/>
-      <c r="E251" s="59" t="n"/>
-      <c r="F251" s="59" t="n"/>
-      <c r="G251" s="59" t="n"/>
-      <c r="H251" s="59" t="n"/>
-      <c r="I251" s="59" t="n"/>
-    </row>
-    <row r="252">
-      <c r="A252" s="59" t="n"/>
-      <c r="B252" s="59" t="n"/>
-      <c r="C252" s="59" t="n"/>
-      <c r="D252" s="59" t="n"/>
-      <c r="E252" s="59" t="n"/>
-      <c r="F252" s="59" t="n"/>
-      <c r="G252" s="59" t="n"/>
-      <c r="H252" s="59" t="n"/>
-      <c r="I252" s="59" t="n"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="59" t="n"/>
-      <c r="B253" s="59" t="n"/>
-      <c r="C253" s="59" t="n"/>
-      <c r="D253" s="59" t="n"/>
-      <c r="E253" s="59" t="n"/>
-      <c r="F253" s="59" t="n"/>
-      <c r="G253" s="59" t="n"/>
-      <c r="H253" s="59" t="n"/>
-      <c r="I253" s="59" t="n"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="59" t="n"/>
-      <c r="B254" s="59" t="n"/>
-      <c r="C254" s="59" t="n"/>
-      <c r="D254" s="59" t="n"/>
-      <c r="E254" s="59" t="n"/>
-      <c r="F254" s="59" t="n"/>
-      <c r="G254" s="59" t="n"/>
-      <c r="H254" s="59" t="n"/>
-      <c r="I254" s="59" t="n"/>
-    </row>
-    <row r="255">
-      <c r="A255" s="59" t="n"/>
-      <c r="B255" s="59" t="n"/>
-      <c r="C255" s="59" t="n"/>
-      <c r="D255" s="59" t="n"/>
-      <c r="E255" s="59" t="n"/>
-      <c r="F255" s="59" t="n"/>
-      <c r="G255" s="59" t="n"/>
-      <c r="H255" s="59" t="n"/>
-      <c r="I255" s="59" t="n"/>
-    </row>
-    <row r="256">
-      <c r="A256" s="59" t="n"/>
-      <c r="B256" s="59" t="n"/>
-      <c r="C256" s="59" t="n"/>
-      <c r="D256" s="59" t="n"/>
-      <c r="E256" s="59" t="n"/>
-      <c r="F256" s="59" t="n"/>
-      <c r="G256" s="59" t="n"/>
-      <c r="H256" s="59" t="n"/>
-      <c r="I256" s="59" t="n"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="59" t="n"/>
-      <c r="B257" s="59" t="n"/>
-      <c r="C257" s="59" t="n"/>
-      <c r="D257" s="59" t="n"/>
-      <c r="E257" s="59" t="n"/>
-      <c r="F257" s="59" t="n"/>
-      <c r="G257" s="59" t="n"/>
-      <c r="H257" s="59" t="n"/>
-      <c r="I257" s="59" t="n"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="59" t="n"/>
-      <c r="B258" s="59" t="n"/>
-      <c r="C258" s="59" t="n"/>
-      <c r="D258" s="59" t="n"/>
-      <c r="E258" s="59" t="n"/>
-      <c r="F258" s="59" t="n"/>
-      <c r="G258" s="59" t="n"/>
-      <c r="H258" s="59" t="n"/>
-      <c r="I258" s="59" t="n"/>
-    </row>
-    <row r="259">
-      <c r="A259" s="59" t="n"/>
-      <c r="B259" s="59" t="n"/>
-      <c r="C259" s="59" t="n"/>
-      <c r="D259" s="59" t="n"/>
-      <c r="E259" s="59" t="n"/>
-      <c r="F259" s="59" t="n"/>
-      <c r="G259" s="59" t="n"/>
-      <c r="H259" s="59" t="n"/>
-      <c r="I259" s="59" t="n"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="59" t="n"/>
-      <c r="B260" s="59" t="n"/>
-      <c r="C260" s="59" t="n"/>
-      <c r="D260" s="59" t="n"/>
-      <c r="E260" s="59" t="n"/>
-      <c r="F260" s="59" t="n"/>
-      <c r="G260" s="59" t="n"/>
-      <c r="H260" s="59" t="n"/>
-      <c r="I260" s="59" t="n"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="59" t="n"/>
-      <c r="B261" s="59" t="n"/>
-      <c r="C261" s="59" t="n"/>
-      <c r="D261" s="59" t="n"/>
-      <c r="E261" s="59" t="n"/>
-      <c r="F261" s="59" t="n"/>
-      <c r="G261" s="59" t="n"/>
-      <c r="H261" s="59" t="n"/>
-      <c r="I261" s="59" t="n"/>
-    </row>
-    <row r="262">
-      <c r="A262" s="59" t="n"/>
-      <c r="B262" s="59" t="n"/>
-      <c r="C262" s="59" t="n"/>
-      <c r="D262" s="59" t="n"/>
-      <c r="E262" s="59" t="n"/>
-      <c r="F262" s="59" t="n"/>
-      <c r="G262" s="59" t="n"/>
-      <c r="H262" s="59" t="n"/>
-      <c r="I262" s="59" t="n"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="59" t="n"/>
-      <c r="B263" s="59" t="n"/>
-      <c r="C263" s="59" t="n"/>
-      <c r="D263" s="59" t="n"/>
-      <c r="E263" s="59" t="n"/>
-      <c r="F263" s="59" t="n"/>
-      <c r="G263" s="59" t="n"/>
-      <c r="H263" s="59" t="n"/>
-      <c r="I263" s="59" t="n"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="59" t="n"/>
-      <c r="B264" s="59" t="n"/>
-      <c r="C264" s="59" t="n"/>
-      <c r="D264" s="59" t="n"/>
-      <c r="E264" s="59" t="n"/>
-      <c r="F264" s="59" t="n"/>
-      <c r="G264" s="59" t="n"/>
-      <c r="H264" s="59" t="n"/>
-      <c r="I264" s="59" t="n"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="59" t="n"/>
-      <c r="B265" s="59" t="n"/>
-      <c r="C265" s="59" t="n"/>
-      <c r="D265" s="59" t="n"/>
-      <c r="E265" s="59" t="n"/>
-      <c r="F265" s="59" t="n"/>
-      <c r="G265" s="59" t="n"/>
-      <c r="H265" s="59" t="n"/>
-      <c r="I265" s="59" t="n"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="59" t="n"/>
-      <c r="B266" s="59" t="n"/>
-      <c r="C266" s="59" t="n"/>
-      <c r="D266" s="59" t="n"/>
-      <c r="E266" s="59" t="n"/>
-      <c r="F266" s="59" t="n"/>
-      <c r="G266" s="59" t="n"/>
-      <c r="H266" s="59" t="n"/>
-      <c r="I266" s="59" t="n"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="59" t="n"/>
-      <c r="B267" s="59" t="n"/>
-      <c r="C267" s="59" t="n"/>
-      <c r="D267" s="59" t="n"/>
-      <c r="E267" s="59" t="n"/>
-      <c r="F267" s="59" t="n"/>
-      <c r="G267" s="59" t="n"/>
-      <c r="H267" s="59" t="n"/>
-      <c r="I267" s="59" t="n"/>
-    </row>
-    <row r="268">
-      <c r="A268" s="59" t="n"/>
-      <c r="B268" s="59" t="n"/>
-      <c r="C268" s="59" t="n"/>
-      <c r="D268" s="59" t="n"/>
-      <c r="E268" s="59" t="n"/>
-      <c r="F268" s="59" t="n"/>
-      <c r="G268" s="59" t="n"/>
-      <c r="H268" s="59" t="n"/>
-      <c r="I268" s="59" t="n"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="59" t="n"/>
-      <c r="B269" s="59" t="n"/>
-      <c r="C269" s="59" t="n"/>
-      <c r="D269" s="59" t="n"/>
-      <c r="E269" s="59" t="n"/>
-      <c r="F269" s="59" t="n"/>
-      <c r="G269" s="59" t="n"/>
-      <c r="H269" s="59" t="n"/>
-      <c r="I269" s="59" t="n"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="59" t="n"/>
-      <c r="B270" s="59" t="n"/>
-      <c r="C270" s="59" t="n"/>
-      <c r="D270" s="59" t="n"/>
-      <c r="E270" s="59" t="n"/>
-      <c r="F270" s="59" t="n"/>
-      <c r="G270" s="59" t="n"/>
-      <c r="H270" s="59" t="n"/>
-      <c r="I270" s="59" t="n"/>
-    </row>
-    <row r="271">
-      <c r="A271" s="59" t="n"/>
-      <c r="B271" s="59" t="n"/>
-      <c r="C271" s="59" t="n"/>
-      <c r="D271" s="59" t="n"/>
-      <c r="E271" s="59" t="n"/>
-      <c r="F271" s="59" t="n"/>
-      <c r="G271" s="59" t="n"/>
-      <c r="H271" s="59" t="n"/>
-      <c r="I271" s="59" t="n"/>
-    </row>
-    <row r="272">
-      <c r="A272" s="59" t="n"/>
-      <c r="B272" s="59" t="n"/>
-      <c r="C272" s="59" t="n"/>
-      <c r="D272" s="59" t="n"/>
-      <c r="E272" s="59" t="n"/>
-      <c r="F272" s="59" t="n"/>
-      <c r="G272" s="59" t="n"/>
-      <c r="H272" s="59" t="n"/>
-      <c r="I272" s="59" t="n"/>
-    </row>
-    <row r="273">
-      <c r="A273" s="59" t="n"/>
-      <c r="B273" s="59" t="n"/>
-      <c r="C273" s="59" t="n"/>
-      <c r="D273" s="59" t="n"/>
-      <c r="E273" s="59" t="n"/>
-      <c r="F273" s="59" t="n"/>
-      <c r="G273" s="59" t="n"/>
-      <c r="H273" s="59" t="n"/>
-      <c r="I273" s="59" t="n"/>
-    </row>
-    <row r="274">
-      <c r="A274" s="59" t="n"/>
-      <c r="B274" s="59" t="n"/>
-      <c r="C274" s="59" t="n"/>
-      <c r="D274" s="59" t="n"/>
-      <c r="E274" s="59" t="n"/>
-      <c r="F274" s="59" t="n"/>
-      <c r="G274" s="59" t="n"/>
-      <c r="H274" s="59" t="n"/>
-      <c r="I274" s="59" t="n"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="59" t="n"/>
-      <c r="B275" s="59" t="n"/>
-      <c r="C275" s="59" t="n"/>
-      <c r="D275" s="59" t="n"/>
-      <c r="E275" s="59" t="n"/>
-      <c r="F275" s="59" t="n"/>
-      <c r="G275" s="59" t="n"/>
-      <c r="H275" s="59" t="n"/>
-      <c r="I275" s="59" t="n"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="59" t="n"/>
-      <c r="B276" s="59" t="n"/>
-      <c r="C276" s="59" t="n"/>
-      <c r="D276" s="59" t="n"/>
-      <c r="E276" s="59" t="n"/>
-      <c r="F276" s="59" t="n"/>
-      <c r="G276" s="59" t="n"/>
-      <c r="H276" s="59" t="n"/>
-      <c r="I276" s="59" t="n"/>
-    </row>
-    <row r="277">
-      <c r="A277" s="59" t="n"/>
-      <c r="B277" s="59" t="n"/>
-      <c r="C277" s="59" t="n"/>
-      <c r="D277" s="59" t="n"/>
-      <c r="E277" s="59" t="n"/>
-      <c r="F277" s="59" t="n"/>
-      <c r="G277" s="59" t="n"/>
-      <c r="H277" s="59" t="n"/>
-      <c r="I277" s="59" t="n"/>
-    </row>
-    <row r="278">
-      <c r="A278" s="59" t="n"/>
-      <c r="B278" s="59" t="n"/>
-      <c r="C278" s="59" t="n"/>
-      <c r="D278" s="59" t="n"/>
-      <c r="E278" s="59" t="n"/>
-      <c r="F278" s="59" t="n"/>
-      <c r="G278" s="59" t="n"/>
-      <c r="H278" s="59" t="n"/>
-      <c r="I278" s="59" t="n"/>
-    </row>
-    <row r="279">
-      <c r="A279" s="59" t="n"/>
-      <c r="B279" s="59" t="n"/>
-      <c r="C279" s="59" t="n"/>
-      <c r="D279" s="59" t="n"/>
-      <c r="E279" s="59" t="n"/>
-      <c r="F279" s="59" t="n"/>
-      <c r="G279" s="59" t="n"/>
-      <c r="H279" s="59" t="n"/>
-      <c r="I279" s="59" t="n"/>
-    </row>
-    <row r="280">
-      <c r="A280" s="59" t="n"/>
-      <c r="B280" s="59" t="n"/>
-      <c r="C280" s="59" t="n"/>
-      <c r="D280" s="59" t="n"/>
-      <c r="E280" s="59" t="n"/>
-      <c r="F280" s="59" t="n"/>
-      <c r="G280" s="59" t="n"/>
-      <c r="H280" s="59" t="n"/>
-      <c r="I280" s="59" t="n"/>
-    </row>
-    <row r="281">
-      <c r="A281" s="59" t="n"/>
-      <c r="B281" s="59" t="n"/>
-      <c r="C281" s="59" t="n"/>
-      <c r="D281" s="59" t="n"/>
-      <c r="E281" s="59" t="n"/>
-      <c r="F281" s="59" t="n"/>
-      <c r="G281" s="59" t="n"/>
-      <c r="H281" s="59" t="n"/>
-      <c r="I281" s="59" t="n"/>
-    </row>
-    <row r="282">
-      <c r="A282" s="59" t="n"/>
-      <c r="B282" s="59" t="n"/>
-      <c r="C282" s="59" t="n"/>
-      <c r="D282" s="59" t="n"/>
-      <c r="E282" s="59" t="n"/>
-      <c r="F282" s="59" t="n"/>
-      <c r="G282" s="59" t="n"/>
-      <c r="H282" s="59" t="n"/>
-      <c r="I282" s="59" t="n"/>
-    </row>
-    <row r="283">
-      <c r="A283" s="59" t="n"/>
-      <c r="B283" s="59" t="n"/>
-      <c r="C283" s="59" t="n"/>
-      <c r="D283" s="59" t="n"/>
-      <c r="E283" s="59" t="n"/>
-      <c r="F283" s="59" t="n"/>
-      <c r="G283" s="59" t="n"/>
-      <c r="H283" s="59" t="n"/>
-      <c r="I283" s="59" t="n"/>
-    </row>
-    <row r="284">
-      <c r="A284" s="59" t="n"/>
-      <c r="B284" s="59" t="n"/>
-      <c r="C284" s="59" t="n"/>
-      <c r="D284" s="59" t="n"/>
-      <c r="E284" s="59" t="n"/>
-      <c r="F284" s="59" t="n"/>
-      <c r="G284" s="59" t="n"/>
-      <c r="H284" s="59" t="n"/>
-      <c r="I284" s="59" t="n"/>
-    </row>
-    <row r="285">
-      <c r="A285" s="59" t="n"/>
-      <c r="B285" s="59" t="n"/>
-      <c r="C285" s="59" t="n"/>
-      <c r="D285" s="59" t="n"/>
-      <c r="E285" s="59" t="n"/>
-      <c r="F285" s="59" t="n"/>
-      <c r="G285" s="59" t="n"/>
-      <c r="H285" s="59" t="n"/>
-      <c r="I285" s="59" t="n"/>
-    </row>
-    <row r="286">
-      <c r="A286" s="59" t="n"/>
-      <c r="B286" s="59" t="n"/>
-      <c r="C286" s="59" t="n"/>
-      <c r="D286" s="59" t="n"/>
-      <c r="E286" s="59" t="n"/>
-      <c r="F286" s="59" t="n"/>
-      <c r="G286" s="59" t="n"/>
-      <c r="H286" s="59" t="n"/>
-      <c r="I286" s="59" t="n"/>
-    </row>
-    <row r="287">
-      <c r="A287" s="59" t="n"/>
-      <c r="B287" s="59" t="n"/>
-      <c r="C287" s="59" t="n"/>
-      <c r="D287" s="59" t="n"/>
-      <c r="E287" s="59" t="n"/>
-      <c r="F287" s="59" t="n"/>
-      <c r="G287" s="59" t="n"/>
-      <c r="H287" s="59" t="n"/>
-      <c r="I287" s="59" t="n"/>
-    </row>
-    <row r="288">
-      <c r="A288" s="59" t="n"/>
-      <c r="B288" s="59" t="n"/>
-      <c r="C288" s="59" t="n"/>
-      <c r="D288" s="59" t="n"/>
-      <c r="E288" s="59" t="n"/>
-      <c r="F288" s="59" t="n"/>
-      <c r="G288" s="59" t="n"/>
-      <c r="H288" s="59" t="n"/>
-      <c r="I288" s="59" t="n"/>
-    </row>
-    <row r="289">
-      <c r="A289" s="59" t="n"/>
-      <c r="B289" s="59" t="n"/>
-      <c r="C289" s="59" t="n"/>
-      <c r="D289" s="59" t="n"/>
-      <c r="E289" s="59" t="n"/>
-      <c r="F289" s="59" t="n"/>
-      <c r="G289" s="59" t="n"/>
-      <c r="H289" s="59" t="n"/>
-      <c r="I289" s="59" t="n"/>
-    </row>
-    <row r="290">
-      <c r="A290" s="59" t="n"/>
-      <c r="B290" s="59" t="n"/>
-      <c r="C290" s="59" t="n"/>
-      <c r="D290" s="59" t="n"/>
-      <c r="E290" s="59" t="n"/>
-      <c r="F290" s="59" t="n"/>
-      <c r="G290" s="59" t="n"/>
-      <c r="H290" s="59" t="n"/>
-      <c r="I290" s="59" t="n"/>
-    </row>
-    <row r="291">
-      <c r="A291" s="59" t="n"/>
-      <c r="B291" s="59" t="n"/>
-      <c r="C291" s="59" t="n"/>
-      <c r="D291" s="59" t="n"/>
-      <c r="E291" s="59" t="n"/>
-      <c r="F291" s="59" t="n"/>
-      <c r="G291" s="59" t="n"/>
-      <c r="H291" s="59" t="n"/>
-      <c r="I291" s="59" t="n"/>
-    </row>
-    <row r="292">
-      <c r="A292" s="59" t="n"/>
-      <c r="B292" s="59" t="n"/>
-      <c r="C292" s="59" t="n"/>
-      <c r="D292" s="59" t="n"/>
-      <c r="E292" s="59" t="n"/>
-      <c r="F292" s="59" t="n"/>
-      <c r="G292" s="59" t="n"/>
-      <c r="H292" s="59" t="n"/>
-      <c r="I292" s="59" t="n"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="59" t="n"/>
-      <c r="B293" s="59" t="n"/>
-      <c r="C293" s="59" t="n"/>
-      <c r="D293" s="59" t="n"/>
-      <c r="E293" s="59" t="n"/>
-      <c r="F293" s="59" t="n"/>
-      <c r="G293" s="59" t="n"/>
-      <c r="H293" s="59" t="n"/>
-      <c r="I293" s="59" t="n"/>
-    </row>
-    <row r="294">
-      <c r="A294" s="59" t="n"/>
-      <c r="B294" s="59" t="n"/>
-      <c r="C294" s="59" t="n"/>
-      <c r="D294" s="59" t="n"/>
-      <c r="E294" s="59" t="n"/>
-      <c r="F294" s="59" t="n"/>
-      <c r="G294" s="59" t="n"/>
-      <c r="H294" s="59" t="n"/>
-      <c r="I294" s="59" t="n"/>
-    </row>
-    <row r="295">
-      <c r="A295" s="59" t="n"/>
-      <c r="B295" s="59" t="n"/>
-      <c r="C295" s="59" t="n"/>
-      <c r="D295" s="59" t="n"/>
-      <c r="E295" s="59" t="n"/>
-      <c r="F295" s="59" t="n"/>
-      <c r="G295" s="59" t="n"/>
-      <c r="H295" s="59" t="n"/>
-      <c r="I295" s="59" t="n"/>
-    </row>
-    <row r="296">
-      <c r="A296" s="59" t="n"/>
-      <c r="B296" s="59" t="n"/>
-      <c r="C296" s="59" t="n"/>
-      <c r="D296" s="59" t="n"/>
-      <c r="E296" s="59" t="n"/>
-      <c r="F296" s="59" t="n"/>
-      <c r="G296" s="59" t="n"/>
-      <c r="H296" s="59" t="n"/>
-      <c r="I296" s="59" t="n"/>
-    </row>
-    <row r="297">
-      <c r="A297" s="59" t="n"/>
-      <c r="B297" s="59" t="n"/>
-      <c r="C297" s="59" t="n"/>
-      <c r="D297" s="59" t="n"/>
-      <c r="E297" s="59" t="n"/>
-      <c r="F297" s="59" t="n"/>
-      <c r="G297" s="59" t="n"/>
-      <c r="H297" s="59" t="n"/>
-      <c r="I297" s="59" t="n"/>
-    </row>
-    <row r="298">
-      <c r="A298" s="59" t="n"/>
-      <c r="B298" s="59" t="n"/>
-      <c r="C298" s="59" t="n"/>
-      <c r="D298" s="59" t="n"/>
-      <c r="E298" s="59" t="n"/>
-      <c r="F298" s="59" t="n"/>
-      <c r="G298" s="59" t="n"/>
-      <c r="H298" s="59" t="n"/>
-      <c r="I298" s="59" t="n"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="59" t="n"/>
-      <c r="B299" s="59" t="n"/>
-      <c r="C299" s="59" t="n"/>
-      <c r="D299" s="59" t="n"/>
-      <c r="E299" s="59" t="n"/>
-      <c r="F299" s="59" t="n"/>
-      <c r="G299" s="59" t="n"/>
-      <c r="H299" s="59" t="n"/>
-      <c r="I299" s="59" t="n"/>
-    </row>
-    <row r="300">
-      <c r="A300" s="59" t="n"/>
-      <c r="B300" s="59" t="n"/>
-      <c r="C300" s="59" t="n"/>
-      <c r="D300" s="59" t="n"/>
-      <c r="E300" s="59" t="n"/>
-      <c r="F300" s="59" t="n"/>
-      <c r="G300" s="59" t="n"/>
-      <c r="H300" s="59" t="n"/>
-      <c r="I300" s="59" t="n"/>
-    </row>
-    <row r="301">
-      <c r="A301" s="59" t="n"/>
-      <c r="B301" s="59" t="n"/>
-      <c r="C301" s="59" t="n"/>
-      <c r="D301" s="59" t="n"/>
-      <c r="E301" s="59" t="n"/>
-      <c r="F301" s="59" t="n"/>
-      <c r="G301" s="59" t="n"/>
-      <c r="H301" s="59" t="n"/>
-      <c r="I301" s="59" t="n"/>
-    </row>
-    <row r="302">
-      <c r="A302" s="59" t="n"/>
-      <c r="B302" s="59" t="n"/>
-      <c r="C302" s="59" t="n"/>
-      <c r="D302" s="59" t="n"/>
-      <c r="E302" s="59" t="n"/>
-      <c r="F302" s="59" t="n"/>
-      <c r="G302" s="59" t="n"/>
-      <c r="H302" s="59" t="n"/>
-      <c r="I302" s="59" t="n"/>
-    </row>
-    <row r="303">
-      <c r="A303" s="59" t="n"/>
-      <c r="B303" s="59" t="n"/>
-      <c r="C303" s="59" t="n"/>
-      <c r="D303" s="59" t="n"/>
-      <c r="E303" s="59" t="n"/>
-      <c r="F303" s="59" t="n"/>
-      <c r="G303" s="59" t="n"/>
-      <c r="H303" s="59" t="n"/>
-      <c r="I303" s="59" t="n"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="59" t="n"/>
-      <c r="B304" s="59" t="n"/>
-      <c r="C304" s="59" t="n"/>
-      <c r="D304" s="59" t="n"/>
-      <c r="E304" s="59" t="n"/>
-      <c r="F304" s="59" t="n"/>
-      <c r="G304" s="59" t="n"/>
-      <c r="H304" s="59" t="n"/>
-      <c r="I304" s="59" t="n"/>
-    </row>
-    <row r="305">
-      <c r="A305" s="59" t="n"/>
-      <c r="B305" s="59" t="n"/>
-      <c r="C305" s="59" t="n"/>
-      <c r="D305" s="59" t="n"/>
-      <c r="E305" s="59" t="n"/>
-      <c r="F305" s="59" t="n"/>
-      <c r="G305" s="59" t="n"/>
-      <c r="H305" s="59" t="n"/>
-      <c r="I305" s="59" t="n"/>
-    </row>
-    <row r="306">
-      <c r="A306" s="59" t="n"/>
-      <c r="B306" s="59" t="n"/>
-      <c r="C306" s="59" t="n"/>
-      <c r="D306" s="59" t="n"/>
-      <c r="E306" s="59" t="n"/>
-      <c r="F306" s="59" t="n"/>
-      <c r="G306" s="59" t="n"/>
-      <c r="H306" s="59" t="n"/>
-      <c r="I306" s="59" t="n"/>
-    </row>
-    <row r="307">
-      <c r="A307" s="59" t="n"/>
-      <c r="B307" s="59" t="n"/>
-      <c r="C307" s="59" t="n"/>
-      <c r="D307" s="59" t="n"/>
-      <c r="E307" s="59" t="n"/>
-      <c r="F307" s="59" t="n"/>
-      <c r="G307" s="59" t="n"/>
-      <c r="H307" s="59" t="n"/>
-      <c r="I307" s="59" t="n"/>
-    </row>
-    <row r="308">
-      <c r="A308" s="59" t="n"/>
-      <c r="B308" s="59" t="n"/>
-      <c r="C308" s="59" t="n"/>
-      <c r="D308" s="59" t="n"/>
-      <c r="E308" s="59" t="n"/>
-      <c r="F308" s="59" t="n"/>
-      <c r="G308" s="59" t="n"/>
-      <c r="H308" s="59" t="n"/>
-      <c r="I308" s="59" t="n"/>
-    </row>
-    <row r="309">
-      <c r="A309" s="59" t="n"/>
-      <c r="B309" s="59" t="n"/>
-      <c r="C309" s="59" t="n"/>
-      <c r="D309" s="59" t="n"/>
-      <c r="E309" s="59" t="n"/>
-      <c r="F309" s="59" t="n"/>
-      <c r="G309" s="59" t="n"/>
-      <c r="H309" s="59" t="n"/>
-      <c r="I309" s="59" t="n"/>
-    </row>
-    <row r="310">
-      <c r="A310" s="59" t="n"/>
-      <c r="B310" s="59" t="n"/>
-      <c r="C310" s="59" t="n"/>
-      <c r="D310" s="59" t="n"/>
-      <c r="E310" s="59" t="n"/>
-      <c r="F310" s="59" t="n"/>
-      <c r="G310" s="59" t="n"/>
-      <c r="H310" s="59" t="n"/>
-      <c r="I310" s="59" t="n"/>
-    </row>
-    <row r="311">
-      <c r="A311" s="59" t="n"/>
-      <c r="B311" s="59" t="n"/>
-      <c r="C311" s="59" t="n"/>
-      <c r="D311" s="59" t="n"/>
-      <c r="E311" s="59" t="n"/>
-      <c r="F311" s="59" t="n"/>
-      <c r="G311" s="59" t="n"/>
-      <c r="H311" s="59" t="n"/>
-      <c r="I311" s="59" t="n"/>
-    </row>
-    <row r="312">
-      <c r="A312" s="59" t="n"/>
-      <c r="B312" s="59" t="n"/>
-      <c r="C312" s="59" t="n"/>
-      <c r="D312" s="59" t="n"/>
-      <c r="E312" s="59" t="n"/>
-      <c r="F312" s="59" t="n"/>
-      <c r="G312" s="59" t="n"/>
-      <c r="H312" s="59" t="n"/>
-      <c r="I312" s="59" t="n"/>
-    </row>
-    <row r="313">
-      <c r="A313" s="59" t="n"/>
-      <c r="B313" s="59" t="n"/>
-      <c r="C313" s="59" t="n"/>
-      <c r="D313" s="59" t="n"/>
-      <c r="E313" s="59" t="n"/>
-      <c r="F313" s="59" t="n"/>
-      <c r="G313" s="59" t="n"/>
-      <c r="H313" s="59" t="n"/>
-      <c r="I313" s="59" t="n"/>
-    </row>
-    <row r="314">
-      <c r="A314" s="59" t="n"/>
-      <c r="B314" s="59" t="n"/>
-      <c r="C314" s="59" t="n"/>
-      <c r="D314" s="59" t="n"/>
-      <c r="E314" s="59" t="n"/>
-      <c r="F314" s="59" t="n"/>
-      <c r="G314" s="59" t="n"/>
-      <c r="H314" s="59" t="n"/>
-      <c r="I314" s="59" t="n"/>
-    </row>
-    <row r="315">
-      <c r="A315" s="59" t="n"/>
-      <c r="B315" s="59" t="n"/>
-      <c r="C315" s="59" t="n"/>
-      <c r="D315" s="59" t="n"/>
-      <c r="E315" s="59" t="n"/>
-      <c r="F315" s="59" t="n"/>
-      <c r="G315" s="59" t="n"/>
-      <c r="H315" s="59" t="n"/>
-      <c r="I315" s="59" t="n"/>
-    </row>
-    <row r="316">
-      <c r="A316" s="59" t="n"/>
-      <c r="B316" s="59" t="n"/>
-      <c r="C316" s="59" t="n"/>
-      <c r="D316" s="59" t="n"/>
-      <c r="E316" s="59" t="n"/>
-      <c r="F316" s="59" t="n"/>
-      <c r="G316" s="59" t="n"/>
-      <c r="H316" s="59" t="n"/>
-      <c r="I316" s="59" t="n"/>
-    </row>
-    <row r="317">
-      <c r="A317" s="59" t="n"/>
-      <c r="B317" s="59" t="n"/>
-      <c r="C317" s="59" t="n"/>
-      <c r="D317" s="59" t="n"/>
-      <c r="E317" s="59" t="n"/>
-      <c r="F317" s="59" t="n"/>
-      <c r="G317" s="59" t="n"/>
-      <c r="H317" s="59" t="n"/>
-      <c r="I317" s="59" t="n"/>
-    </row>
-    <row r="318">
-      <c r="A318" s="59" t="n"/>
-      <c r="B318" s="59" t="n"/>
-      <c r="C318" s="59" t="n"/>
-      <c r="D318" s="59" t="n"/>
-      <c r="E318" s="59" t="n"/>
-      <c r="F318" s="59" t="n"/>
-      <c r="G318" s="59" t="n"/>
-      <c r="H318" s="59" t="n"/>
-      <c r="I318" s="59" t="n"/>
-    </row>
-    <row r="319">
-      <c r="A319" s="59" t="n"/>
-      <c r="B319" s="59" t="n"/>
-      <c r="C319" s="59" t="n"/>
-      <c r="D319" s="59" t="n"/>
-      <c r="E319" s="59" t="n"/>
-      <c r="F319" s="59" t="n"/>
-      <c r="G319" s="59" t="n"/>
-      <c r="H319" s="59" t="n"/>
-      <c r="I319" s="59" t="n"/>
-    </row>
-    <row r="320">
-      <c r="A320" s="59" t="n"/>
-      <c r="B320" s="59" t="n"/>
-      <c r="C320" s="59" t="n"/>
-      <c r="D320" s="59" t="n"/>
-      <c r="E320" s="59" t="n"/>
-      <c r="F320" s="59" t="n"/>
-      <c r="G320" s="59" t="n"/>
-      <c r="H320" s="59" t="n"/>
-      <c r="I320" s="59" t="n"/>
-    </row>
-    <row r="321">
-      <c r="A321" s="59" t="n"/>
-      <c r="B321" s="59" t="n"/>
-      <c r="C321" s="59" t="n"/>
-      <c r="D321" s="59" t="n"/>
-      <c r="E321" s="59" t="n"/>
-      <c r="F321" s="59" t="n"/>
-      <c r="G321" s="59" t="n"/>
-      <c r="H321" s="59" t="n"/>
-      <c r="I321" s="59" t="n"/>
-    </row>
-    <row r="322">
-      <c r="A322" s="59" t="n"/>
-      <c r="B322" s="59" t="n"/>
-      <c r="C322" s="59" t="n"/>
-      <c r="D322" s="59" t="n"/>
-      <c r="E322" s="59" t="n"/>
-      <c r="F322" s="59" t="n"/>
-      <c r="G322" s="59" t="n"/>
-      <c r="H322" s="59" t="n"/>
-      <c r="I322" s="59" t="n"/>
-    </row>
-    <row r="323">
-      <c r="A323" s="59" t="n"/>
-      <c r="B323" s="59" t="n"/>
-      <c r="C323" s="59" t="n"/>
-      <c r="D323" s="59" t="n"/>
-      <c r="E323" s="59" t="n"/>
-      <c r="F323" s="59" t="n"/>
-      <c r="G323" s="59" t="n"/>
-      <c r="H323" s="59" t="n"/>
-      <c r="I323" s="59" t="n"/>
-    </row>
-    <row r="324">
-      <c r="A324" s="59" t="n"/>
-      <c r="B324" s="59" t="n"/>
-      <c r="C324" s="59" t="n"/>
-      <c r="D324" s="59" t="n"/>
-      <c r="E324" s="59" t="n"/>
-      <c r="F324" s="59" t="n"/>
-      <c r="G324" s="59" t="n"/>
-      <c r="H324" s="59" t="n"/>
-      <c r="I324" s="59" t="n"/>
-    </row>
-    <row r="325">
-      <c r="A325" s="59" t="n"/>
-      <c r="B325" s="59" t="n"/>
-      <c r="C325" s="59" t="n"/>
-      <c r="D325" s="59" t="n"/>
-      <c r="E325" s="59" t="n"/>
-      <c r="F325" s="59" t="n"/>
-      <c r="G325" s="59" t="n"/>
-      <c r="H325" s="59" t="n"/>
-      <c r="I325" s="59" t="n"/>
-    </row>
-    <row r="326">
-      <c r="A326" s="59" t="n"/>
-      <c r="B326" s="59" t="n"/>
-      <c r="C326" s="59" t="n"/>
-      <c r="D326" s="59" t="n"/>
-      <c r="E326" s="59" t="n"/>
-      <c r="F326" s="59" t="n"/>
-      <c r="G326" s="59" t="n"/>
-      <c r="H326" s="59" t="n"/>
-      <c r="I326" s="59" t="n"/>
-    </row>
-    <row r="327">
-      <c r="A327" s="59" t="n"/>
-      <c r="B327" s="59" t="n"/>
-      <c r="C327" s="59" t="n"/>
-      <c r="D327" s="59" t="n"/>
-      <c r="E327" s="59" t="n"/>
-      <c r="F327" s="59" t="n"/>
-      <c r="G327" s="59" t="n"/>
-      <c r="H327" s="59" t="n"/>
-      <c r="I327" s="59" t="n"/>
-    </row>
-    <row r="328">
-      <c r="A328" s="59" t="n"/>
-      <c r="B328" s="59" t="n"/>
-      <c r="C328" s="59" t="n"/>
-      <c r="D328" s="59" t="n"/>
-      <c r="E328" s="59" t="n"/>
-      <c r="F328" s="59" t="n"/>
-      <c r="G328" s="59" t="n"/>
-      <c r="H328" s="59" t="n"/>
-      <c r="I328" s="59" t="n"/>
-    </row>
-    <row r="329">
-      <c r="A329" s="59" t="n"/>
-      <c r="B329" s="59" t="n"/>
-      <c r="C329" s="59" t="n"/>
-      <c r="D329" s="59" t="n"/>
-      <c r="E329" s="59" t="n"/>
-      <c r="F329" s="59" t="n"/>
-      <c r="G329" s="59" t="n"/>
-      <c r="H329" s="59" t="n"/>
-      <c r="I329" s="59" t="n"/>
-    </row>
-    <row r="330">
-      <c r="A330" s="59" t="n"/>
-      <c r="B330" s="59" t="n"/>
-      <c r="C330" s="59" t="n"/>
-      <c r="D330" s="59" t="n"/>
-      <c r="E330" s="59" t="n"/>
-      <c r="F330" s="59" t="n"/>
-      <c r="G330" s="59" t="n"/>
-      <c r="H330" s="59" t="n"/>
-      <c r="I330" s="59" t="n"/>
-    </row>
-    <row r="331">
-      <c r="A331" s="59" t="n"/>
-      <c r="B331" s="59" t="n"/>
-      <c r="C331" s="59" t="n"/>
-      <c r="D331" s="59" t="n"/>
-      <c r="E331" s="59" t="n"/>
-      <c r="F331" s="59" t="n"/>
-      <c r="G331" s="59" t="n"/>
-      <c r="H331" s="59" t="n"/>
-      <c r="I331" s="59" t="n"/>
-    </row>
-    <row r="332">
-      <c r="A332" s="59" t="n"/>
-      <c r="B332" s="59" t="n"/>
-      <c r="C332" s="59" t="n"/>
-      <c r="D332" s="59" t="n"/>
-      <c r="E332" s="59" t="n"/>
-      <c r="F332" s="59" t="n"/>
-      <c r="G332" s="59" t="n"/>
-      <c r="H332" s="59" t="n"/>
-      <c r="I332" s="59" t="n"/>
-    </row>
-    <row r="333">
-      <c r="A333" s="59" t="n"/>
-      <c r="B333" s="59" t="n"/>
-      <c r="C333" s="59" t="n"/>
-      <c r="D333" s="59" t="n"/>
-      <c r="E333" s="59" t="n"/>
-      <c r="F333" s="59" t="n"/>
-      <c r="G333" s="59" t="n"/>
-      <c r="H333" s="59" t="n"/>
-      <c r="I333" s="59" t="n"/>
-    </row>
-    <row r="334">
-      <c r="A334" s="59" t="n"/>
-      <c r="B334" s="59" t="n"/>
-      <c r="C334" s="59" t="n"/>
-      <c r="D334" s="59" t="n"/>
-      <c r="E334" s="59" t="n"/>
-      <c r="F334" s="59" t="n"/>
-      <c r="G334" s="59" t="n"/>
-      <c r="H334" s="59" t="n"/>
-      <c r="I334" s="59" t="n"/>
-    </row>
-    <row r="335">
-      <c r="A335" s="59" t="n"/>
-      <c r="B335" s="59" t="n"/>
-      <c r="C335" s="59" t="n"/>
-      <c r="D335" s="59" t="n"/>
-      <c r="E335" s="59" t="n"/>
-      <c r="F335" s="59" t="n"/>
-      <c r="G335" s="59" t="n"/>
-      <c r="H335" s="59" t="n"/>
-      <c r="I335" s="59" t="n"/>
-    </row>
-    <row r="336">
-      <c r="A336" s="59" t="n"/>
-      <c r="B336" s="59" t="n"/>
-      <c r="C336" s="59" t="n"/>
-      <c r="D336" s="59" t="n"/>
-      <c r="E336" s="59" t="n"/>
-      <c r="F336" s="59" t="n"/>
-      <c r="G336" s="59" t="n"/>
-      <c r="H336" s="59" t="n"/>
-      <c r="I336" s="59" t="n"/>
-    </row>
-    <row r="337">
-      <c r="A337" s="59" t="n"/>
-      <c r="B337" s="59" t="n"/>
-      <c r="C337" s="59" t="n"/>
-      <c r="D337" s="59" t="n"/>
-      <c r="E337" s="59" t="n"/>
-      <c r="F337" s="59" t="n"/>
-      <c r="G337" s="59" t="n"/>
-      <c r="H337" s="59" t="n"/>
-      <c r="I337" s="59" t="n"/>
-    </row>
-    <row r="338">
-      <c r="A338" s="59" t="n"/>
-      <c r="B338" s="59" t="n"/>
-      <c r="C338" s="59" t="n"/>
-      <c r="D338" s="59" t="n"/>
-      <c r="E338" s="59" t="n"/>
-      <c r="F338" s="59" t="n"/>
-      <c r="G338" s="59" t="n"/>
-      <c r="H338" s="59" t="n"/>
-      <c r="I338" s="59" t="n"/>
-    </row>
-    <row r="339">
-      <c r="A339" s="59" t="n"/>
-      <c r="B339" s="59" t="n"/>
-      <c r="C339" s="59" t="n"/>
-      <c r="D339" s="59" t="n"/>
-      <c r="E339" s="59" t="n"/>
-      <c r="F339" s="59" t="n"/>
-      <c r="G339" s="59" t="n"/>
-      <c r="H339" s="59" t="n"/>
-      <c r="I339" s="59" t="n"/>
-    </row>
-    <row r="340">
-      <c r="A340" s="59" t="n"/>
-      <c r="B340" s="59" t="n"/>
-      <c r="C340" s="59" t="n"/>
-      <c r="D340" s="59" t="n"/>
-      <c r="E340" s="59" t="n"/>
-      <c r="F340" s="59" t="n"/>
-      <c r="G340" s="59" t="n"/>
-      <c r="H340" s="59" t="n"/>
-      <c r="I340" s="59" t="n"/>
-    </row>
-    <row r="341">
-      <c r="A341" s="59" t="n"/>
-      <c r="B341" s="59" t="n"/>
-      <c r="C341" s="59" t="n"/>
-      <c r="D341" s="59" t="n"/>
-      <c r="E341" s="59" t="n"/>
-      <c r="F341" s="59" t="n"/>
-      <c r="G341" s="59" t="n"/>
-      <c r="H341" s="59" t="n"/>
-      <c r="I341" s="59" t="n"/>
-    </row>
-    <row r="342">
-      <c r="A342" s="59" t="n"/>
-      <c r="B342" s="59" t="n"/>
-      <c r="C342" s="59" t="n"/>
-      <c r="D342" s="59" t="n"/>
-      <c r="E342" s="59" t="n"/>
-      <c r="F342" s="59" t="n"/>
-      <c r="G342" s="59" t="n"/>
-      <c r="H342" s="59" t="n"/>
-      <c r="I342" s="59" t="n"/>
-    </row>
-    <row r="343">
-      <c r="A343" s="59" t="n"/>
-      <c r="B343" s="59" t="n"/>
-      <c r="C343" s="59" t="n"/>
-      <c r="D343" s="59" t="n"/>
-      <c r="E343" s="59" t="n"/>
-      <c r="F343" s="59" t="n"/>
-      <c r="G343" s="59" t="n"/>
-      <c r="H343" s="59" t="n"/>
-      <c r="I343" s="59" t="n"/>
-    </row>
-    <row r="344">
-      <c r="A344" s="59" t="n"/>
-      <c r="B344" s="59" t="n"/>
-      <c r="C344" s="59" t="n"/>
-      <c r="D344" s="59" t="n"/>
-      <c r="E344" s="59" t="n"/>
-      <c r="F344" s="59" t="n"/>
-      <c r="G344" s="59" t="n"/>
-      <c r="H344" s="59" t="n"/>
-      <c r="I344" s="59" t="n"/>
-    </row>
-    <row r="345">
-      <c r="A345" s="59" t="n"/>
-      <c r="B345" s="59" t="n"/>
-      <c r="C345" s="59" t="n"/>
-      <c r="D345" s="59" t="n"/>
-      <c r="E345" s="59" t="n"/>
-      <c r="F345" s="59" t="n"/>
-      <c r="G345" s="59" t="n"/>
-      <c r="H345" s="59" t="n"/>
-      <c r="I345" s="59" t="n"/>
-    </row>
-    <row r="346">
-      <c r="A346" s="59" t="n"/>
-      <c r="B346" s="59" t="n"/>
-      <c r="C346" s="59" t="n"/>
-      <c r="D346" s="59" t="n"/>
-      <c r="E346" s="59" t="n"/>
-      <c r="F346" s="59" t="n"/>
-      <c r="G346" s="59" t="n"/>
-      <c r="H346" s="59" t="n"/>
-      <c r="I346" s="59" t="n"/>
-    </row>
-    <row r="347">
-      <c r="A347" s="59" t="n"/>
-      <c r="B347" s="59" t="n"/>
-      <c r="C347" s="59" t="n"/>
-      <c r="D347" s="59" t="n"/>
-      <c r="E347" s="59" t="n"/>
-      <c r="F347" s="59" t="n"/>
-      <c r="G347" s="59" t="n"/>
-      <c r="H347" s="59" t="n"/>
-      <c r="I347" s="59" t="n"/>
-    </row>
-    <row r="348">
-      <c r="A348" s="59" t="n"/>
-      <c r="B348" s="59" t="n"/>
-      <c r="C348" s="59" t="n"/>
-      <c r="D348" s="59" t="n"/>
-      <c r="E348" s="59" t="n"/>
-      <c r="F348" s="59" t="n"/>
-      <c r="G348" s="59" t="n"/>
-      <c r="H348" s="59" t="n"/>
-      <c r="I348" s="59" t="n"/>
-    </row>
-    <row r="349">
-      <c r="A349" s="59" t="n"/>
-      <c r="B349" s="59" t="n"/>
-      <c r="C349" s="59" t="n"/>
-      <c r="D349" s="59" t="n"/>
-      <c r="E349" s="59" t="n"/>
-      <c r="F349" s="59" t="n"/>
-      <c r="G349" s="59" t="n"/>
-      <c r="H349" s="59" t="n"/>
-      <c r="I349" s="59" t="n"/>
-    </row>
-    <row r="350">
-      <c r="A350" s="59" t="n"/>
-      <c r="B350" s="59" t="n"/>
-      <c r="C350" s="59" t="n"/>
-      <c r="D350" s="59" t="n"/>
-      <c r="E350" s="59" t="n"/>
-      <c r="F350" s="59" t="n"/>
-      <c r="G350" s="59" t="n"/>
-      <c r="H350" s="59" t="n"/>
-      <c r="I350" s="59" t="n"/>
-    </row>
-    <row r="351">
-      <c r="A351" s="59" t="n"/>
-      <c r="B351" s="59" t="n"/>
-      <c r="C351" s="59" t="n"/>
-      <c r="D351" s="59" t="n"/>
-      <c r="E351" s="59" t="n"/>
-      <c r="F351" s="59" t="n"/>
-      <c r="G351" s="59" t="n"/>
-      <c r="H351" s="59" t="n"/>
-      <c r="I351" s="59" t="n"/>
-    </row>
-    <row r="352">
-      <c r="A352" s="59" t="n"/>
-      <c r="B352" s="59" t="n"/>
-      <c r="C352" s="59" t="n"/>
-      <c r="D352" s="59" t="n"/>
-      <c r="E352" s="59" t="n"/>
-      <c r="F352" s="59" t="n"/>
-      <c r="G352" s="59" t="n"/>
-      <c r="H352" s="59" t="n"/>
-      <c r="I352" s="59" t="n"/>
-    </row>
-    <row r="353">
-      <c r="A353" s="59" t="n"/>
-      <c r="B353" s="59" t="n"/>
-      <c r="C353" s="59" t="n"/>
-      <c r="D353" s="59" t="n"/>
-      <c r="E353" s="59" t="n"/>
-      <c r="F353" s="59" t="n"/>
-      <c r="G353" s="59" t="n"/>
-      <c r="H353" s="59" t="n"/>
-      <c r="I353" s="59" t="n"/>
-    </row>
-    <row r="354">
-      <c r="A354" s="59" t="n"/>
-      <c r="B354" s="59" t="n"/>
-      <c r="C354" s="59" t="n"/>
-      <c r="D354" s="59" t="n"/>
-      <c r="E354" s="59" t="n"/>
-      <c r="F354" s="59" t="n"/>
-      <c r="G354" s="59" t="n"/>
-      <c r="H354" s="59" t="n"/>
-      <c r="I354" s="59" t="n"/>
-    </row>
-    <row r="355">
-      <c r="A355" s="59" t="n"/>
-      <c r="B355" s="59" t="n"/>
-      <c r="C355" s="59" t="n"/>
-      <c r="D355" s="59" t="n"/>
-      <c r="E355" s="59" t="n"/>
-      <c r="F355" s="59" t="n"/>
-      <c r="G355" s="59" t="n"/>
-      <c r="H355" s="59" t="n"/>
-      <c r="I355" s="59" t="n"/>
-    </row>
-    <row r="356">
-      <c r="A356" s="59" t="n"/>
-      <c r="B356" s="59" t="n"/>
-      <c r="C356" s="59" t="n"/>
-      <c r="D356" s="59" t="n"/>
-      <c r="E356" s="59" t="n"/>
-      <c r="F356" s="59" t="n"/>
-      <c r="G356" s="59" t="n"/>
-      <c r="H356" s="59" t="n"/>
-      <c r="I356" s="59" t="n"/>
-    </row>
-    <row r="357">
-      <c r="A357" s="59" t="n"/>
-      <c r="B357" s="59" t="n"/>
-      <c r="C357" s="59" t="n"/>
-      <c r="D357" s="59" t="n"/>
-      <c r="E357" s="59" t="n"/>
-      <c r="F357" s="59" t="n"/>
-      <c r="G357" s="59" t="n"/>
-      <c r="H357" s="59" t="n"/>
-      <c r="I357" s="59" t="n"/>
-    </row>
-    <row r="358">
-      <c r="A358" s="59" t="n"/>
-      <c r="B358" s="59" t="n"/>
-      <c r="C358" s="59" t="n"/>
-      <c r="D358" s="59" t="n"/>
-      <c r="E358" s="59" t="n"/>
-      <c r="F358" s="59" t="n"/>
-      <c r="G358" s="59" t="n"/>
-      <c r="H358" s="59" t="n"/>
-      <c r="I358" s="59" t="n"/>
-    </row>
-    <row r="359">
-      <c r="A359" s="59" t="n"/>
-      <c r="B359" s="59" t="n"/>
-      <c r="C359" s="59" t="n"/>
-      <c r="D359" s="59" t="n"/>
-      <c r="E359" s="59" t="n"/>
-      <c r="F359" s="59" t="n"/>
-      <c r="G359" s="59" t="n"/>
-      <c r="H359" s="59" t="n"/>
-      <c r="I359" s="59" t="n"/>
-    </row>
-    <row r="360">
-      <c r="A360" s="59" t="n"/>
-      <c r="B360" s="59" t="n"/>
-      <c r="C360" s="59" t="n"/>
-      <c r="D360" s="59" t="n"/>
-      <c r="E360" s="59" t="n"/>
-      <c r="F360" s="59" t="n"/>
-      <c r="G360" s="59" t="n"/>
-      <c r="H360" s="59" t="n"/>
-      <c r="I360" s="59" t="n"/>
-    </row>
-    <row r="361">
-      <c r="A361" s="59" t="n"/>
-      <c r="B361" s="59" t="n"/>
-      <c r="C361" s="59" t="n"/>
-      <c r="D361" s="59" t="n"/>
-      <c r="E361" s="59" t="n"/>
-      <c r="F361" s="59" t="n"/>
-      <c r="G361" s="59" t="n"/>
-      <c r="H361" s="59" t="n"/>
-      <c r="I361" s="59" t="n"/>
-    </row>
-    <row r="362">
-      <c r="A362" s="59" t="n"/>
-      <c r="B362" s="59" t="n"/>
-      <c r="C362" s="59" t="n"/>
-      <c r="D362" s="59" t="n"/>
-      <c r="E362" s="59" t="n"/>
-      <c r="F362" s="59" t="n"/>
-      <c r="G362" s="59" t="n"/>
-      <c r="H362" s="59" t="n"/>
-      <c r="I362" s="59" t="n"/>
-    </row>
-    <row r="363">
-      <c r="A363" s="59" t="n"/>
-      <c r="B363" s="59" t="n"/>
-      <c r="C363" s="59" t="n"/>
-      <c r="D363" s="59" t="n"/>
-      <c r="E363" s="59" t="n"/>
-      <c r="F363" s="59" t="n"/>
-      <c r="G363" s="59" t="n"/>
-      <c r="H363" s="59" t="n"/>
-      <c r="I363" s="59" t="n"/>
-    </row>
-    <row r="364">
-      <c r="A364" s="59" t="n"/>
-      <c r="B364" s="59" t="n"/>
-      <c r="C364" s="59" t="n"/>
-      <c r="D364" s="59" t="n"/>
-      <c r="E364" s="59" t="n"/>
-      <c r="F364" s="59" t="n"/>
-      <c r="G364" s="59" t="n"/>
-      <c r="H364" s="59" t="n"/>
-      <c r="I364" s="59" t="n"/>
-    </row>
-    <row r="365">
-      <c r="A365" s="59" t="n"/>
-      <c r="B365" s="59" t="n"/>
-      <c r="C365" s="59" t="n"/>
-      <c r="D365" s="59" t="n"/>
-      <c r="E365" s="59" t="n"/>
-      <c r="F365" s="59" t="n"/>
-      <c r="G365" s="59" t="n"/>
-      <c r="H365" s="59" t="n"/>
-      <c r="I365" s="59" t="n"/>
-    </row>
-    <row r="366">
-      <c r="A366" s="59" t="n"/>
-      <c r="B366" s="59" t="n"/>
-      <c r="C366" s="59" t="n"/>
-      <c r="D366" s="59" t="n"/>
-      <c r="E366" s="59" t="n"/>
-      <c r="F366" s="59" t="n"/>
-      <c r="G366" s="59" t="n"/>
-      <c r="H366" s="59" t="n"/>
-      <c r="I366" s="59" t="n"/>
-    </row>
-    <row r="367">
-      <c r="A367" s="59" t="n"/>
-      <c r="B367" s="59" t="n"/>
-      <c r="C367" s="59" t="n"/>
-      <c r="D367" s="59" t="n"/>
-      <c r="E367" s="59" t="n"/>
-      <c r="F367" s="59" t="n"/>
-      <c r="G367" s="59" t="n"/>
-      <c r="H367" s="59" t="n"/>
-      <c r="I367" s="59" t="n"/>
-    </row>
-    <row r="368">
-      <c r="A368" s="59" t="n"/>
-      <c r="B368" s="59" t="n"/>
-      <c r="C368" s="59" t="n"/>
-      <c r="D368" s="59" t="n"/>
-      <c r="E368" s="59" t="n"/>
-      <c r="F368" s="59" t="n"/>
-      <c r="G368" s="59" t="n"/>
-      <c r="H368" s="59" t="n"/>
-      <c r="I368" s="59" t="n"/>
-    </row>
-    <row r="369">
-      <c r="A369" s="59" t="n"/>
-      <c r="B369" s="59" t="n"/>
-      <c r="C369" s="59" t="n"/>
-      <c r="D369" s="59" t="n"/>
-      <c r="E369" s="59" t="n"/>
-      <c r="F369" s="59" t="n"/>
-      <c r="G369" s="59" t="n"/>
-      <c r="H369" s="59" t="n"/>
-      <c r="I369" s="59" t="n"/>
-    </row>
-    <row r="370">
-      <c r="A370" s="59" t="n"/>
-      <c r="B370" s="59" t="n"/>
-      <c r="C370" s="59" t="n"/>
-      <c r="D370" s="59" t="n"/>
-      <c r="E370" s="59" t="n"/>
-      <c r="F370" s="59" t="n"/>
-      <c r="G370" s="59" t="n"/>
-      <c r="H370" s="59" t="n"/>
-      <c r="I370" s="59" t="n"/>
-    </row>
-    <row r="371">
-      <c r="A371" s="59" t="n"/>
-      <c r="B371" s="59" t="n"/>
-      <c r="C371" s="59" t="n"/>
-      <c r="D371" s="59" t="n"/>
-      <c r="E371" s="59" t="n"/>
-      <c r="F371" s="59" t="n"/>
-      <c r="G371" s="59" t="n"/>
-      <c r="H371" s="59" t="n"/>
-      <c r="I371" s="59" t="n"/>
-    </row>
-    <row r="372">
-      <c r="A372" s="59" t="n"/>
-      <c r="B372" s="59" t="n"/>
-      <c r="C372" s="59" t="n"/>
-      <c r="D372" s="59" t="n"/>
-      <c r="E372" s="59" t="n"/>
-      <c r="F372" s="59" t="n"/>
-      <c r="G372" s="59" t="n"/>
-      <c r="H372" s="59" t="n"/>
-      <c r="I372" s="59" t="n"/>
-    </row>
-    <row r="373">
-      <c r="A373" s="59" t="n"/>
-      <c r="B373" s="59" t="n"/>
-      <c r="C373" s="59" t="n"/>
-      <c r="D373" s="59" t="n"/>
-      <c r="E373" s="59" t="n"/>
-      <c r="F373" s="59" t="n"/>
-      <c r="G373" s="59" t="n"/>
-      <c r="H373" s="59" t="n"/>
-      <c r="I373" s="59" t="n"/>
-    </row>
-    <row r="374">
-      <c r="A374" s="59" t="n"/>
-      <c r="B374" s="59" t="n"/>
-      <c r="C374" s="59" t="n"/>
-      <c r="D374" s="59" t="n"/>
-      <c r="E374" s="59" t="n"/>
-      <c r="F374" s="59" t="n"/>
-      <c r="G374" s="59" t="n"/>
-      <c r="H374" s="59" t="n"/>
-      <c r="I374" s="59" t="n"/>
-    </row>
-    <row r="375">
-      <c r="A375" s="59" t="n"/>
-      <c r="B375" s="59" t="n"/>
-      <c r="C375" s="59" t="n"/>
-      <c r="D375" s="59" t="n"/>
-      <c r="E375" s="59" t="n"/>
-      <c r="F375" s="59" t="n"/>
-      <c r="G375" s="59" t="n"/>
-      <c r="H375" s="59" t="n"/>
-      <c r="I375" s="59" t="n"/>
-    </row>
-    <row r="376">
-      <c r="A376" s="59" t="n"/>
-      <c r="B376" s="59" t="n"/>
-      <c r="C376" s="59" t="n"/>
-      <c r="D376" s="59" t="n"/>
-      <c r="E376" s="59" t="n"/>
-      <c r="F376" s="59" t="n"/>
-      <c r="G376" s="59" t="n"/>
-      <c r="H376" s="59" t="n"/>
-      <c r="I376" s="59" t="n"/>
-    </row>
-    <row r="377">
-      <c r="A377" s="59" t="n"/>
-      <c r="B377" s="59" t="n"/>
-      <c r="C377" s="59" t="n"/>
-      <c r="D377" s="59" t="n"/>
-      <c r="E377" s="59" t="n"/>
-      <c r="F377" s="59" t="n"/>
-      <c r="G377" s="59" t="n"/>
-      <c r="H377" s="59" t="n"/>
-      <c r="I377" s="59" t="n"/>
-    </row>
-    <row r="378">
-      <c r="A378" s="59" t="n"/>
-      <c r="B378" s="59" t="n"/>
-      <c r="C378" s="59" t="n"/>
-      <c r="D378" s="59" t="n"/>
-      <c r="E378" s="59" t="n"/>
-      <c r="F378" s="59" t="n"/>
-      <c r="G378" s="59" t="n"/>
-      <c r="H378" s="59" t="n"/>
-      <c r="I378" s="59" t="n"/>
-    </row>
-    <row r="379">
-      <c r="A379" s="59" t="n"/>
-      <c r="B379" s="59" t="n"/>
-      <c r="C379" s="59" t="n"/>
-      <c r="D379" s="59" t="n"/>
-      <c r="E379" s="59" t="n"/>
-      <c r="F379" s="59" t="n"/>
-      <c r="G379" s="59" t="n"/>
-      <c r="H379" s="59" t="n"/>
-      <c r="I379" s="59" t="n"/>
-    </row>
-    <row r="380">
-      <c r="A380" s="59" t="n"/>
-      <c r="B380" s="59" t="n"/>
-      <c r="C380" s="59" t="n"/>
-      <c r="D380" s="59" t="n"/>
-      <c r="E380" s="59" t="n"/>
-      <c r="F380" s="59" t="n"/>
-      <c r="G380" s="59" t="n"/>
-      <c r="H380" s="59" t="n"/>
-      <c r="I380" s="59" t="n"/>
-    </row>
-    <row r="381">
-      <c r="A381" s="59" t="n"/>
-      <c r="B381" s="59" t="n"/>
-      <c r="C381" s="59" t="n"/>
-      <c r="D381" s="59" t="n"/>
-      <c r="E381" s="59" t="n"/>
-      <c r="F381" s="59" t="n"/>
-      <c r="G381" s="59" t="n"/>
-      <c r="H381" s="59" t="n"/>
-      <c r="I381" s="59" t="n"/>
-    </row>
-    <row r="382">
-      <c r="A382" s="59" t="n"/>
-      <c r="B382" s="59" t="n"/>
-      <c r="C382" s="59" t="n"/>
-      <c r="D382" s="59" t="n"/>
-      <c r="E382" s="59" t="n"/>
-      <c r="F382" s="59" t="n"/>
-      <c r="G382" s="59" t="n"/>
-      <c r="H382" s="59" t="n"/>
-      <c r="I382" s="59" t="n"/>
-    </row>
-    <row r="383">
-      <c r="A383" s="59" t="n"/>
-      <c r="B383" s="59" t="n"/>
-      <c r="C383" s="59" t="n"/>
-      <c r="D383" s="59" t="n"/>
-      <c r="E383" s="59" t="n"/>
-      <c r="F383" s="59" t="n"/>
-      <c r="G383" s="59" t="n"/>
-      <c r="H383" s="59" t="n"/>
-      <c r="I383" s="59" t="n"/>
-    </row>
-    <row r="384">
-      <c r="A384" s="59" t="n"/>
-      <c r="B384" s="59" t="n"/>
-      <c r="C384" s="59" t="n"/>
-      <c r="D384" s="59" t="n"/>
-      <c r="E384" s="59" t="n"/>
-      <c r="F384" s="59" t="n"/>
-      <c r="G384" s="59" t="n"/>
-      <c r="H384" s="59" t="n"/>
-      <c r="I384" s="59" t="n"/>
-    </row>
-    <row r="385">
-      <c r="A385" s="59" t="n"/>
-      <c r="B385" s="59" t="n"/>
-      <c r="C385" s="59" t="n"/>
-      <c r="D385" s="59" t="n"/>
-      <c r="E385" s="59" t="n"/>
-      <c r="F385" s="59" t="n"/>
-      <c r="G385" s="59" t="n"/>
-      <c r="H385" s="59" t="n"/>
-      <c r="I385" s="59" t="n"/>
-    </row>
-    <row r="386">
-      <c r="A386" s="59" t="n"/>
-      <c r="B386" s="59" t="n"/>
-      <c r="C386" s="59" t="n"/>
-      <c r="D386" s="59" t="n"/>
-      <c r="E386" s="59" t="n"/>
-      <c r="F386" s="59" t="n"/>
-      <c r="G386" s="59" t="n"/>
-      <c r="H386" s="59" t="n"/>
-      <c r="I386" s="59" t="n"/>
-    </row>
-    <row r="387">
-      <c r="A387" s="59" t="n"/>
-      <c r="B387" s="59" t="n"/>
-      <c r="C387" s="59" t="n"/>
-      <c r="D387" s="59" t="n"/>
-      <c r="E387" s="59" t="n"/>
-      <c r="F387" s="59" t="n"/>
-      <c r="G387" s="59" t="n"/>
-      <c r="H387" s="59" t="n"/>
-      <c r="I387" s="59" t="n"/>
-    </row>
-    <row r="388">
-      <c r="A388" s="59" t="n"/>
-      <c r="B388" s="59" t="n"/>
-      <c r="C388" s="59" t="n"/>
-      <c r="D388" s="59" t="n"/>
-      <c r="E388" s="59" t="n"/>
-      <c r="F388" s="59" t="n"/>
-      <c r="G388" s="59" t="n"/>
-      <c r="H388" s="59" t="n"/>
-      <c r="I388" s="59" t="n"/>
-    </row>
-    <row r="389">
-      <c r="A389" s="59" t="n"/>
-      <c r="B389" s="59" t="n"/>
-      <c r="C389" s="59" t="n"/>
-      <c r="D389" s="59" t="n"/>
-      <c r="E389" s="59" t="n"/>
-      <c r="F389" s="59" t="n"/>
-      <c r="G389" s="59" t="n"/>
-      <c r="H389" s="59" t="n"/>
-      <c r="I389" s="59" t="n"/>
-    </row>
-    <row r="390">
-      <c r="A390" s="59" t="n"/>
-      <c r="B390" s="59" t="n"/>
-      <c r="C390" s="59" t="n"/>
-      <c r="D390" s="59" t="n"/>
-      <c r="E390" s="59" t="n"/>
-      <c r="F390" s="59" t="n"/>
-      <c r="G390" s="59" t="n"/>
-      <c r="H390" s="59" t="n"/>
-      <c r="I390" s="59" t="n"/>
-    </row>
-    <row r="391">
-      <c r="A391" s="59" t="n"/>
-      <c r="B391" s="59" t="n"/>
-      <c r="C391" s="59" t="n"/>
-      <c r="D391" s="59" t="n"/>
-      <c r="E391" s="59" t="n"/>
-      <c r="F391" s="59" t="n"/>
-      <c r="G391" s="59" t="n"/>
-      <c r="H391" s="59" t="n"/>
-      <c r="I391" s="59" t="n"/>
-    </row>
-    <row r="392">
-      <c r="A392" s="59" t="n"/>
-      <c r="B392" s="59" t="n"/>
-      <c r="C392" s="59" t="n"/>
-      <c r="D392" s="59" t="n"/>
-      <c r="E392" s="59" t="n"/>
-      <c r="F392" s="59" t="n"/>
-      <c r="G392" s="59" t="n"/>
-      <c r="H392" s="59" t="n"/>
-      <c r="I392" s="59" t="n"/>
-    </row>
-    <row r="393">
-      <c r="A393" s="59" t="n"/>
-      <c r="B393" s="59" t="n"/>
-      <c r="C393" s="59" t="n"/>
-      <c r="D393" s="59" t="n"/>
-      <c r="E393" s="59" t="n"/>
-      <c r="F393" s="59" t="n"/>
-      <c r="G393" s="59" t="n"/>
-      <c r="H393" s="59" t="n"/>
-      <c r="I393" s="59" t="n"/>
-    </row>
-    <row r="394">
-      <c r="A394" s="59" t="n"/>
-      <c r="B394" s="59" t="n"/>
-      <c r="C394" s="59" t="n"/>
-      <c r="D394" s="59" t="n"/>
-      <c r="E394" s="59" t="n"/>
-      <c r="F394" s="59" t="n"/>
-      <c r="G394" s="59" t="n"/>
-      <c r="H394" s="59" t="n"/>
-      <c r="I394" s="59" t="n"/>
-    </row>
-    <row r="395">
-      <c r="A395" s="59" t="n"/>
-      <c r="B395" s="59" t="n"/>
-      <c r="C395" s="59" t="n"/>
-      <c r="D395" s="59" t="n"/>
-      <c r="E395" s="59" t="n"/>
-      <c r="F395" s="59" t="n"/>
-      <c r="G395" s="59" t="n"/>
-      <c r="H395" s="59" t="n"/>
-      <c r="I395" s="59" t="n"/>
-    </row>
-    <row r="396">
-      <c r="A396" s="59" t="n"/>
-      <c r="B396" s="59" t="n"/>
-      <c r="C396" s="59" t="n"/>
-      <c r="D396" s="59" t="n"/>
-      <c r="E396" s="59" t="n"/>
-      <c r="F396" s="59" t="n"/>
-      <c r="G396" s="59" t="n"/>
-      <c r="H396" s="59" t="n"/>
-      <c r="I396" s="59" t="n"/>
-    </row>
-    <row r="397">
-      <c r="A397" s="59" t="n"/>
-      <c r="B397" s="59" t="n"/>
-      <c r="C397" s="59" t="n"/>
-      <c r="D397" s="59" t="n"/>
-      <c r="E397" s="59" t="n"/>
-      <c r="F397" s="59" t="n"/>
-      <c r="G397" s="59" t="n"/>
-      <c r="H397" s="59" t="n"/>
-      <c r="I397" s="59" t="n"/>
-    </row>
-    <row r="398">
-      <c r="A398" s="59" t="n"/>
-      <c r="B398" s="59" t="n"/>
-      <c r="C398" s="59" t="n"/>
-      <c r="D398" s="59" t="n"/>
-      <c r="E398" s="59" t="n"/>
-      <c r="F398" s="59" t="n"/>
-      <c r="G398" s="59" t="n"/>
-      <c r="H398" s="59" t="n"/>
-      <c r="I398" s="59" t="n"/>
-    </row>
-    <row r="399">
-      <c r="A399" s="59" t="n"/>
-      <c r="B399" s="59" t="n"/>
-      <c r="C399" s="59" t="n"/>
-      <c r="D399" s="59" t="n"/>
-      <c r="E399" s="59" t="n"/>
-      <c r="F399" s="59" t="n"/>
-      <c r="G399" s="59" t="n"/>
-      <c r="H399" s="59" t="n"/>
-      <c r="I399" s="59" t="n"/>
-    </row>
-    <row r="400">
-      <c r="A400" s="59" t="n"/>
-      <c r="B400" s="59" t="n"/>
-      <c r="C400" s="59" t="n"/>
-      <c r="D400" s="59" t="n"/>
-      <c r="E400" s="59" t="n"/>
-      <c r="F400" s="59" t="n"/>
-      <c r="G400" s="59" t="n"/>
-      <c r="H400" s="59" t="n"/>
-      <c r="I400" s="59" t="n"/>
-    </row>
-    <row r="401">
-      <c r="A401" s="59" t="n"/>
-      <c r="B401" s="59" t="n"/>
-      <c r="C401" s="59" t="n"/>
-      <c r="D401" s="59" t="n"/>
-      <c r="E401" s="59" t="n"/>
-      <c r="F401" s="59" t="n"/>
-      <c r="G401" s="59" t="n"/>
-      <c r="H401" s="59" t="n"/>
-      <c r="I401" s="59" t="n"/>
-    </row>
-    <row r="402">
-      <c r="A402" s="59" t="n"/>
-      <c r="B402" s="59" t="n"/>
-      <c r="C402" s="59" t="n"/>
-      <c r="D402" s="59" t="n"/>
-      <c r="E402" s="59" t="n"/>
-      <c r="F402" s="59" t="n"/>
-      <c r="G402" s="59" t="n"/>
-      <c r="H402" s="59" t="n"/>
-      <c r="I402" s="59" t="n"/>
-    </row>
-    <row r="403">
-      <c r="A403" s="59" t="n"/>
-      <c r="B403" s="59" t="n"/>
-      <c r="C403" s="59" t="n"/>
-      <c r="D403" s="59" t="n"/>
-      <c r="E403" s="59" t="n"/>
-      <c r="F403" s="59" t="n"/>
-      <c r="G403" s="59" t="n"/>
-      <c r="H403" s="59" t="n"/>
-      <c r="I403" s="59" t="n"/>
-    </row>
-    <row r="404">
-      <c r="A404" s="59" t="n"/>
-      <c r="B404" s="59" t="n"/>
-      <c r="C404" s="59" t="n"/>
-      <c r="D404" s="59" t="n"/>
-      <c r="E404" s="59" t="n"/>
-      <c r="F404" s="59" t="n"/>
-      <c r="G404" s="59" t="n"/>
-      <c r="H404" s="59" t="n"/>
-      <c r="I404" s="59" t="n"/>
-    </row>
-    <row r="405">
-      <c r="A405" s="59" t="n"/>
-      <c r="B405" s="59" t="n"/>
-      <c r="C405" s="59" t="n"/>
-      <c r="D405" s="59" t="n"/>
-      <c r="E405" s="59" t="n"/>
-      <c r="F405" s="59" t="n"/>
-      <c r="G405" s="59" t="n"/>
-      <c r="H405" s="59" t="n"/>
-      <c r="I405" s="59" t="n"/>
-    </row>
-    <row r="406">
-      <c r="A406" s="59" t="n"/>
-      <c r="B406" s="59" t="n"/>
-      <c r="C406" s="59" t="n"/>
-      <c r="D406" s="59" t="n"/>
-      <c r="E406" s="59" t="n"/>
-      <c r="F406" s="59" t="n"/>
-      <c r="G406" s="59" t="n"/>
-      <c r="H406" s="59" t="n"/>
-      <c r="I406" s="59" t="n"/>
-    </row>
-    <row r="407">
-      <c r="A407" s="59" t="n"/>
-      <c r="B407" s="59" t="n"/>
-      <c r="C407" s="59" t="n"/>
-      <c r="D407" s="59" t="n"/>
-      <c r="E407" s="59" t="n"/>
-      <c r="F407" s="59" t="n"/>
-      <c r="G407" s="59" t="n"/>
-      <c r="H407" s="59" t="n"/>
-      <c r="I407" s="59" t="n"/>
-    </row>
-    <row r="408">
-      <c r="A408" s="59" t="n"/>
-      <c r="B408" s="59" t="n"/>
-      <c r="C408" s="59" t="n"/>
-      <c r="D408" s="59" t="n"/>
-      <c r="E408" s="59" t="n"/>
-      <c r="F408" s="59" t="n"/>
-      <c r="G408" s="59" t="n"/>
-      <c r="H408" s="59" t="n"/>
-      <c r="I408" s="59" t="n"/>
-    </row>
-    <row r="409">
-      <c r="A409" s="59" t="n"/>
-      <c r="B409" s="59" t="n"/>
-      <c r="C409" s="59" t="n"/>
-      <c r="D409" s="59" t="n"/>
-      <c r="E409" s="59" t="n"/>
-      <c r="F409" s="59" t="n"/>
-      <c r="G409" s="59" t="n"/>
-      <c r="H409" s="59" t="n"/>
-      <c r="I409" s="59" t="n"/>
-    </row>
-    <row r="410">
-      <c r="A410" s="59" t="n"/>
-      <c r="B410" s="59" t="n"/>
-      <c r="C410" s="59" t="n"/>
-      <c r="D410" s="59" t="n"/>
-      <c r="E410" s="59" t="n"/>
-      <c r="F410" s="59" t="n"/>
-      <c r="G410" s="59" t="n"/>
-      <c r="H410" s="59" t="n"/>
-      <c r="I410" s="59" t="n"/>
-    </row>
-    <row r="411">
-      <c r="A411" s="59" t="n"/>
-      <c r="B411" s="59" t="n"/>
-      <c r="C411" s="59" t="n"/>
-      <c r="D411" s="59" t="n"/>
-      <c r="E411" s="59" t="n"/>
-      <c r="F411" s="59" t="n"/>
-      <c r="G411" s="59" t="n"/>
-      <c r="H411" s="59" t="n"/>
-      <c r="I411" s="59" t="n"/>
-    </row>
-    <row r="412">
-      <c r="A412" s="59" t="n"/>
-      <c r="B412" s="59" t="n"/>
-      <c r="C412" s="59" t="n"/>
-      <c r="D412" s="59" t="n"/>
-      <c r="E412" s="59" t="n"/>
-      <c r="F412" s="59" t="n"/>
-      <c r="G412" s="59" t="n"/>
-      <c r="H412" s="59" t="n"/>
-      <c r="I412" s="59" t="n"/>
-    </row>
-    <row r="413">
-      <c r="A413" s="59" t="n"/>
-      <c r="B413" s="59" t="n"/>
-      <c r="C413" s="59" t="n"/>
-      <c r="D413" s="59" t="n"/>
-      <c r="E413" s="59" t="n"/>
-      <c r="F413" s="59" t="n"/>
-      <c r="G413" s="59" t="n"/>
-      <c r="H413" s="59" t="n"/>
-      <c r="I413" s="59" t="n"/>
-    </row>
-    <row r="414">
-      <c r="A414" s="59" t="n"/>
-      <c r="B414" s="59" t="n"/>
-      <c r="C414" s="59" t="n"/>
-      <c r="D414" s="59" t="n"/>
-      <c r="E414" s="59" t="n"/>
-      <c r="F414" s="59" t="n"/>
-      <c r="G414" s="59" t="n"/>
-      <c r="H414" s="59" t="n"/>
-      <c r="I414" s="59" t="n"/>
-    </row>
-    <row r="415">
-      <c r="A415" s="59" t="n"/>
-      <c r="B415" s="59" t="n"/>
-      <c r="C415" s="59" t="n"/>
-      <c r="D415" s="59" t="n"/>
-      <c r="E415" s="59" t="n"/>
-      <c r="F415" s="59" t="n"/>
-      <c r="G415" s="59" t="n"/>
-      <c r="H415" s="59" t="n"/>
-      <c r="I415" s="59" t="n"/>
-    </row>
-    <row r="416">
-      <c r="A416" s="59" t="n"/>
-      <c r="B416" s="59" t="n"/>
-      <c r="C416" s="59" t="n"/>
-      <c r="D416" s="59" t="n"/>
-      <c r="E416" s="59" t="n"/>
-      <c r="F416" s="59" t="n"/>
-      <c r="G416" s="59" t="n"/>
-      <c r="H416" s="59" t="n"/>
-      <c r="I416" s="59" t="n"/>
-    </row>
-    <row r="417">
-      <c r="A417" s="59" t="n"/>
-      <c r="B417" s="59" t="n"/>
-      <c r="C417" s="59" t="n"/>
-      <c r="D417" s="59" t="n"/>
-      <c r="E417" s="59" t="n"/>
-      <c r="F417" s="59" t="n"/>
-      <c r="G417" s="59" t="n"/>
-      <c r="H417" s="59" t="n"/>
-      <c r="I417" s="59" t="n"/>
-    </row>
-    <row r="418">
-      <c r="A418" s="59" t="n"/>
-      <c r="B418" s="59" t="n"/>
-      <c r="C418" s="59" t="n"/>
-      <c r="D418" s="59" t="n"/>
-      <c r="E418" s="59" t="n"/>
-      <c r="F418" s="59" t="n"/>
-      <c r="G418" s="59" t="n"/>
-      <c r="H418" s="59" t="n"/>
-      <c r="I418" s="59" t="n"/>
-    </row>
-    <row r="419">
-      <c r="A419" s="59" t="n"/>
-      <c r="B419" s="59" t="n"/>
-      <c r="C419" s="59" t="n"/>
-      <c r="D419" s="59" t="n"/>
-      <c r="E419" s="59" t="n"/>
-      <c r="F419" s="59" t="n"/>
-      <c r="G419" s="59" t="n"/>
-      <c r="H419" s="59" t="n"/>
-      <c r="I419" s="59" t="n"/>
-    </row>
-    <row r="420">
-      <c r="A420" s="59" t="n"/>
-      <c r="B420" s="59" t="n"/>
-      <c r="C420" s="59" t="n"/>
-      <c r="D420" s="59" t="n"/>
-      <c r="E420" s="59" t="n"/>
-      <c r="F420" s="59" t="n"/>
-      <c r="G420" s="59" t="n"/>
-      <c r="H420" s="59" t="n"/>
-      <c r="I420" s="59" t="n"/>
-    </row>
-    <row r="421">
-      <c r="A421" s="59" t="n"/>
-      <c r="B421" s="59" t="n"/>
-      <c r="C421" s="59" t="n"/>
-      <c r="D421" s="59" t="n"/>
-      <c r="E421" s="59" t="n"/>
-      <c r="F421" s="59" t="n"/>
-      <c r="G421" s="59" t="n"/>
-      <c r="H421" s="59" t="n"/>
-      <c r="I421" s="59" t="n"/>
-    </row>
-    <row r="422">
-      <c r="A422" s="59" t="n"/>
-      <c r="B422" s="59" t="n"/>
-      <c r="C422" s="59" t="n"/>
-      <c r="D422" s="59" t="n"/>
-      <c r="E422" s="59" t="n"/>
-      <c r="F422" s="59" t="n"/>
-      <c r="G422" s="59" t="n"/>
-      <c r="H422" s="59" t="n"/>
-      <c r="I422" s="59" t="n"/>
-    </row>
-    <row r="423">
-      <c r="A423" s="59" t="n"/>
-      <c r="B423" s="59" t="n"/>
-      <c r="C423" s="59" t="n"/>
-      <c r="D423" s="59" t="n"/>
-      <c r="E423" s="59" t="n"/>
-      <c r="F423" s="59" t="n"/>
-      <c r="G423" s="59" t="n"/>
-      <c r="H423" s="59" t="n"/>
-      <c r="I423" s="59" t="n"/>
-    </row>
-    <row r="424">
-      <c r="A424" s="59" t="n"/>
-      <c r="B424" s="59" t="n"/>
-      <c r="C424" s="59" t="n"/>
-      <c r="D424" s="59" t="n"/>
-      <c r="E424" s="59" t="n"/>
-      <c r="F424" s="59" t="n"/>
-      <c r="G424" s="59" t="n"/>
-      <c r="H424" s="59" t="n"/>
-      <c r="I424" s="59" t="n"/>
-    </row>
-    <row r="425">
-      <c r="A425" s="59" t="n"/>
-      <c r="B425" s="59" t="n"/>
-      <c r="C425" s="59" t="n"/>
-      <c r="D425" s="59" t="n"/>
-      <c r="E425" s="59" t="n"/>
-      <c r="F425" s="59" t="n"/>
-      <c r="G425" s="59" t="n"/>
-      <c r="H425" s="59" t="n"/>
-      <c r="I425" s="59" t="n"/>
-    </row>
-    <row r="426">
-      <c r="A426" s="59" t="n"/>
-      <c r="B426" s="59" t="n"/>
-      <c r="C426" s="59" t="n"/>
-      <c r="D426" s="59" t="n"/>
-      <c r="E426" s="59" t="n"/>
-      <c r="F426" s="59" t="n"/>
-      <c r="G426" s="59" t="n"/>
-      <c r="H426" s="59" t="n"/>
-      <c r="I426" s="59" t="n"/>
-    </row>
-    <row r="427">
-      <c r="A427" s="59" t="n"/>
-      <c r="B427" s="59" t="n"/>
-      <c r="C427" s="59" t="n"/>
-      <c r="D427" s="59" t="n"/>
-      <c r="E427" s="59" t="n"/>
-      <c r="F427" s="59" t="n"/>
-      <c r="G427" s="59" t="n"/>
-      <c r="H427" s="59" t="n"/>
-      <c r="I427" s="59" t="n"/>
-    </row>
-    <row r="428">
-      <c r="A428" s="59" t="n"/>
-      <c r="B428" s="59" t="n"/>
-      <c r="C428" s="59" t="n"/>
-      <c r="D428" s="59" t="n"/>
-      <c r="E428" s="59" t="n"/>
-      <c r="F428" s="59" t="n"/>
-      <c r="G428" s="59" t="n"/>
-      <c r="H428" s="59" t="n"/>
-      <c r="I428" s="59" t="n"/>
-    </row>
-    <row r="429">
-      <c r="A429" s="59" t="n"/>
-      <c r="B429" s="59" t="n"/>
-      <c r="C429" s="59" t="n"/>
-      <c r="D429" s="59" t="n"/>
-      <c r="E429" s="59" t="n"/>
-      <c r="F429" s="59" t="n"/>
-      <c r="G429" s="59" t="n"/>
-      <c r="H429" s="59" t="n"/>
-      <c r="I429" s="59" t="n"/>
-    </row>
-    <row r="430">
-      <c r="A430" s="59" t="n"/>
-      <c r="B430" s="59" t="n"/>
-      <c r="C430" s="59" t="n"/>
-      <c r="D430" s="59" t="n"/>
-      <c r="E430" s="59" t="n"/>
-      <c r="F430" s="59" t="n"/>
-      <c r="G430" s="59" t="n"/>
-      <c r="H430" s="59" t="n"/>
-      <c r="I430" s="59" t="n"/>
-    </row>
-    <row r="431">
-      <c r="A431" s="59" t="n"/>
-      <c r="B431" s="59" t="n"/>
-      <c r="C431" s="59" t="n"/>
-      <c r="D431" s="59" t="n"/>
-      <c r="E431" s="59" t="n"/>
-      <c r="F431" s="59" t="n"/>
-      <c r="G431" s="59" t="n"/>
-      <c r="H431" s="59" t="n"/>
-      <c r="I431" s="59" t="n"/>
-    </row>
-    <row r="432">
-      <c r="A432" s="59" t="n"/>
-      <c r="B432" s="59" t="n"/>
-      <c r="C432" s="59" t="n"/>
-      <c r="D432" s="59" t="n"/>
-      <c r="E432" s="59" t="n"/>
-      <c r="F432" s="59" t="n"/>
-      <c r="G432" s="59" t="n"/>
-      <c r="H432" s="59" t="n"/>
-      <c r="I432" s="59" t="n"/>
-    </row>
-    <row r="433">
-      <c r="A433" s="59" t="n"/>
-      <c r="B433" s="59" t="n"/>
-      <c r="C433" s="59" t="n"/>
-      <c r="D433" s="59" t="n"/>
-      <c r="E433" s="59" t="n"/>
-      <c r="F433" s="59" t="n"/>
-      <c r="G433" s="59" t="n"/>
-      <c r="H433" s="59" t="n"/>
-      <c r="I433" s="59" t="n"/>
-    </row>
-    <row r="434">
-      <c r="A434" s="59" t="n"/>
-      <c r="B434" s="59" t="n"/>
-      <c r="C434" s="59" t="n"/>
-      <c r="D434" s="59" t="n"/>
-      <c r="E434" s="59" t="n"/>
-      <c r="F434" s="59" t="n"/>
-      <c r="G434" s="59" t="n"/>
-      <c r="H434" s="59" t="n"/>
-      <c r="I434" s="59" t="n"/>
-    </row>
-    <row r="435">
-      <c r="A435" s="59" t="n"/>
-      <c r="B435" s="59" t="n"/>
-      <c r="C435" s="59" t="n"/>
-      <c r="D435" s="59" t="n"/>
-      <c r="E435" s="59" t="n"/>
-      <c r="F435" s="59" t="n"/>
-      <c r="G435" s="59" t="n"/>
-      <c r="H435" s="59" t="n"/>
-      <c r="I435" s="59" t="n"/>
-    </row>
-    <row r="436">
-      <c r="A436" s="59" t="n"/>
-      <c r="B436" s="59" t="n"/>
-      <c r="C436" s="59" t="n"/>
-      <c r="D436" s="59" t="n"/>
-      <c r="E436" s="59" t="n"/>
-      <c r="F436" s="59" t="n"/>
-      <c r="G436" s="59" t="n"/>
-      <c r="H436" s="59" t="n"/>
-      <c r="I436" s="59" t="n"/>
-    </row>
-    <row r="437">
-      <c r="A437" s="59" t="n"/>
-      <c r="B437" s="59" t="n"/>
-      <c r="C437" s="59" t="n"/>
-      <c r="D437" s="59" t="n"/>
-      <c r="E437" s="59" t="n"/>
-      <c r="F437" s="59" t="n"/>
-      <c r="G437" s="59" t="n"/>
-      <c r="H437" s="59" t="n"/>
-      <c r="I437" s="59" t="n"/>
-    </row>
-    <row r="438">
-      <c r="A438" s="59" t="n"/>
-      <c r="B438" s="59" t="n"/>
-      <c r="C438" s="59" t="n"/>
-      <c r="D438" s="59" t="n"/>
-      <c r="E438" s="59" t="n"/>
-      <c r="F438" s="59" t="n"/>
-      <c r="G438" s="59" t="n"/>
-      <c r="H438" s="59" t="n"/>
-      <c r="I438" s="59" t="n"/>
-    </row>
-    <row r="439">
-      <c r="A439" s="59" t="n"/>
-      <c r="B439" s="59" t="n"/>
-      <c r="C439" s="59" t="n"/>
-      <c r="D439" s="59" t="n"/>
-      <c r="E439" s="59" t="n"/>
-      <c r="F439" s="59" t="n"/>
-      <c r="G439" s="59" t="n"/>
-      <c r="H439" s="59" t="n"/>
-      <c r="I439" s="59" t="n"/>
-    </row>
-    <row r="440">
-      <c r="A440" s="59" t="n"/>
-      <c r="B440" s="59" t="n"/>
-      <c r="C440" s="59" t="n"/>
-      <c r="D440" s="59" t="n"/>
-      <c r="E440" s="59" t="n"/>
-      <c r="F440" s="59" t="n"/>
-      <c r="G440" s="59" t="n"/>
-      <c r="H440" s="59" t="n"/>
-      <c r="I440" s="59" t="n"/>
-    </row>
-    <row r="441">
-      <c r="A441" s="59" t="n"/>
-      <c r="B441" s="59" t="n"/>
-      <c r="C441" s="59" t="n"/>
-      <c r="D441" s="59" t="n"/>
-      <c r="E441" s="59" t="n"/>
-      <c r="F441" s="59" t="n"/>
-      <c r="G441" s="59" t="n"/>
-      <c r="H441" s="59" t="n"/>
-      <c r="I441" s="59" t="n"/>
-    </row>
-    <row r="442">
-      <c r="A442" s="59" t="n"/>
-      <c r="B442" s="59" t="n"/>
-      <c r="C442" s="59" t="n"/>
-      <c r="D442" s="59" t="n"/>
-      <c r="E442" s="59" t="n"/>
-      <c r="F442" s="59" t="n"/>
-      <c r="G442" s="59" t="n"/>
-      <c r="H442" s="59" t="n"/>
-      <c r="I442" s="59" t="n"/>
-    </row>
-    <row r="443">
-      <c r="A443" s="59" t="n"/>
-      <c r="B443" s="59" t="n"/>
-      <c r="C443" s="59" t="n"/>
-      <c r="D443" s="59" t="n"/>
-      <c r="E443" s="59" t="n"/>
-      <c r="F443" s="59" t="n"/>
-      <c r="G443" s="59" t="n"/>
-      <c r="H443" s="59" t="n"/>
-      <c r="I443" s="59" t="n"/>
-    </row>
-    <row r="444">
-      <c r="A444" s="59" t="n"/>
-      <c r="B444" s="59" t="n"/>
-      <c r="C444" s="59" t="n"/>
-      <c r="D444" s="59" t="n"/>
-      <c r="E444" s="59" t="n"/>
-      <c r="F444" s="59" t="n"/>
-      <c r="G444" s="59" t="n"/>
-      <c r="H444" s="59" t="n"/>
-      <c r="I444" s="59" t="n"/>
-    </row>
-    <row r="445">
-      <c r="A445" s="59" t="n"/>
-      <c r="B445" s="59" t="n"/>
-      <c r="C445" s="59" t="n"/>
-      <c r="D445" s="59" t="n"/>
-      <c r="E445" s="59" t="n"/>
-      <c r="F445" s="59" t="n"/>
-      <c r="G445" s="59" t="n"/>
-      <c r="H445" s="59" t="n"/>
-      <c r="I445" s="59" t="n"/>
-    </row>
-    <row r="446">
-      <c r="A446" s="59" t="n"/>
-      <c r="B446" s="59" t="n"/>
-      <c r="C446" s="59" t="n"/>
-      <c r="D446" s="59" t="n"/>
-      <c r="E446" s="59" t="n"/>
-      <c r="F446" s="59" t="n"/>
-      <c r="G446" s="59" t="n"/>
-      <c r="H446" s="59" t="n"/>
-      <c r="I446" s="59" t="n"/>
-    </row>
-    <row r="447">
-      <c r="A447" s="59" t="n"/>
-      <c r="B447" s="59" t="n"/>
-      <c r="C447" s="59" t="n"/>
-      <c r="D447" s="59" t="n"/>
-      <c r="E447" s="59" t="n"/>
-      <c r="F447" s="59" t="n"/>
-      <c r="G447" s="59" t="n"/>
-      <c r="H447" s="59" t="n"/>
-      <c r="I447" s="59" t="n"/>
-    </row>
-    <row r="448">
-      <c r="A448" s="59" t="n"/>
-      <c r="B448" s="59" t="n"/>
-      <c r="C448" s="59" t="n"/>
-      <c r="D448" s="59" t="n"/>
-      <c r="E448" s="59" t="n"/>
-      <c r="F448" s="59" t="n"/>
-      <c r="G448" s="59" t="n"/>
-      <c r="H448" s="59" t="n"/>
-      <c r="I448" s="59" t="n"/>
-    </row>
-    <row r="449">
-      <c r="A449" s="59" t="n"/>
-      <c r="B449" s="59" t="n"/>
-      <c r="C449" s="59" t="n"/>
-      <c r="D449" s="59" t="n"/>
-      <c r="E449" s="59" t="n"/>
-      <c r="F449" s="59" t="n"/>
-      <c r="G449" s="59" t="n"/>
-      <c r="H449" s="59" t="n"/>
-      <c r="I449" s="59" t="n"/>
-    </row>
-    <row r="450">
-      <c r="A450" s="59" t="n"/>
-      <c r="B450" s="59" t="n"/>
-      <c r="C450" s="59" t="n"/>
-      <c r="D450" s="59" t="n"/>
-      <c r="E450" s="59" t="n"/>
-      <c r="F450" s="59" t="n"/>
-      <c r="G450" s="59" t="n"/>
-      <c r="H450" s="59" t="n"/>
-      <c r="I450" s="59" t="n"/>
-    </row>
-    <row r="451">
-      <c r="A451" s="59" t="n"/>
-      <c r="B451" s="59" t="n"/>
-      <c r="C451" s="59" t="n"/>
-      <c r="D451" s="59" t="n"/>
-      <c r="E451" s="59" t="n"/>
-      <c r="F451" s="59" t="n"/>
-      <c r="G451" s="59" t="n"/>
-      <c r="H451" s="59" t="n"/>
-      <c r="I451" s="59" t="n"/>
-    </row>
-    <row r="452">
-      <c r="A452" s="59" t="n"/>
-      <c r="B452" s="59" t="n"/>
-      <c r="C452" s="59" t="n"/>
-      <c r="D452" s="59" t="n"/>
-      <c r="E452" s="59" t="n"/>
-      <c r="F452" s="59" t="n"/>
-      <c r="G452" s="59" t="n"/>
-      <c r="H452" s="59" t="n"/>
-      <c r="I452" s="59" t="n"/>
-    </row>
-    <row r="453">
-      <c r="A453" s="59" t="n"/>
-      <c r="B453" s="59" t="n"/>
-      <c r="C453" s="59" t="n"/>
-      <c r="D453" s="59" t="n"/>
-      <c r="E453" s="59" t="n"/>
-      <c r="F453" s="59" t="n"/>
-      <c r="G453" s="59" t="n"/>
-      <c r="H453" s="59" t="n"/>
-      <c r="I453" s="59" t="n"/>
-    </row>
-    <row r="454">
-      <c r="A454" s="59" t="n"/>
-      <c r="B454" s="59" t="n"/>
-      <c r="C454" s="59" t="n"/>
-      <c r="D454" s="59" t="n"/>
-      <c r="E454" s="59" t="n"/>
-      <c r="F454" s="59" t="n"/>
-      <c r="G454" s="59" t="n"/>
-      <c r="H454" s="59" t="n"/>
-      <c r="I454" s="59" t="n"/>
-    </row>
-    <row r="455">
-      <c r="A455" s="59" t="n"/>
-      <c r="B455" s="59" t="n"/>
-      <c r="C455" s="59" t="n"/>
-      <c r="D455" s="59" t="n"/>
-      <c r="E455" s="59" t="n"/>
-      <c r="F455" s="59" t="n"/>
-      <c r="G455" s="59" t="n"/>
-      <c r="H455" s="59" t="n"/>
-      <c r="I455" s="59" t="n"/>
-    </row>
-    <row r="456">
-      <c r="A456" s="59" t="n"/>
-      <c r="B456" s="59" t="n"/>
-      <c r="C456" s="59" t="n"/>
-      <c r="D456" s="59" t="n"/>
-      <c r="E456" s="59" t="n"/>
-      <c r="F456" s="59" t="n"/>
-      <c r="G456" s="59" t="n"/>
-      <c r="H456" s="59" t="n"/>
-      <c r="I456" s="59" t="n"/>
-    </row>
-    <row r="457">
-      <c r="A457" s="59" t="n"/>
-      <c r="B457" s="59" t="n"/>
-      <c r="C457" s="59" t="n"/>
-      <c r="D457" s="59" t="n"/>
-      <c r="E457" s="59" t="n"/>
-      <c r="F457" s="59" t="n"/>
-      <c r="G457" s="59" t="n"/>
-      <c r="H457" s="59" t="n"/>
-      <c r="I457" s="59" t="n"/>
-    </row>
-    <row r="458">
-      <c r="A458" s="59" t="n"/>
-      <c r="B458" s="59" t="n"/>
-      <c r="C458" s="59" t="n"/>
-      <c r="D458" s="59" t="n"/>
-      <c r="E458" s="59" t="n"/>
-      <c r="F458" s="59" t="n"/>
-      <c r="G458" s="59" t="n"/>
-      <c r="H458" s="59" t="n"/>
-      <c r="I458" s="59" t="n"/>
-    </row>
-    <row r="459">
-      <c r="A459" s="59" t="n"/>
-      <c r="B459" s="59" t="n"/>
-      <c r="C459" s="59" t="n"/>
-      <c r="D459" s="59" t="n"/>
-      <c r="E459" s="59" t="n"/>
-      <c r="F459" s="59" t="n"/>
-      <c r="G459" s="59" t="n"/>
-      <c r="H459" s="59" t="n"/>
-      <c r="I459" s="59" t="n"/>
-    </row>
-    <row r="460">
-      <c r="A460" s="59" t="n"/>
-      <c r="B460" s="59" t="n"/>
-      <c r="C460" s="59" t="n"/>
-      <c r="D460" s="59" t="n"/>
-      <c r="E460" s="59" t="n"/>
-      <c r="F460" s="59" t="n"/>
-      <c r="G460" s="59" t="n"/>
-      <c r="H460" s="59" t="n"/>
-      <c r="I460" s="59" t="n"/>
-    </row>
-    <row r="461">
-      <c r="A461" s="59" t="n"/>
-      <c r="B461" s="59" t="n"/>
-      <c r="C461" s="59" t="n"/>
-      <c r="D461" s="59" t="n"/>
-      <c r="E461" s="59" t="n"/>
-      <c r="F461" s="59" t="n"/>
-      <c r="G461" s="59" t="n"/>
-      <c r="H461" s="59" t="n"/>
-      <c r="I461" s="59" t="n"/>
-    </row>
-    <row r="462">
-      <c r="A462" s="59" t="n"/>
-      <c r="B462" s="59" t="n"/>
-      <c r="C462" s="59" t="n"/>
-      <c r="D462" s="59" t="n"/>
-      <c r="E462" s="59" t="n"/>
-      <c r="F462" s="59" t="n"/>
-      <c r="G462" s="59" t="n"/>
-      <c r="H462" s="59" t="n"/>
-      <c r="I462" s="59" t="n"/>
-    </row>
-    <row r="463">
-      <c r="A463" s="59" t="n"/>
-      <c r="B463" s="59" t="n"/>
-      <c r="C463" s="59" t="n"/>
-      <c r="D463" s="59" t="n"/>
-      <c r="E463" s="59" t="n"/>
-      <c r="F463" s="59" t="n"/>
-      <c r="G463" s="59" t="n"/>
-      <c r="H463" s="59" t="n"/>
-      <c r="I463" s="59" t="n"/>
-    </row>
-    <row r="464">
-      <c r="A464" s="59" t="n"/>
-      <c r="B464" s="59" t="n"/>
-      <c r="C464" s="59" t="n"/>
-      <c r="D464" s="59" t="n"/>
-      <c r="E464" s="59" t="n"/>
-      <c r="F464" s="59" t="n"/>
-      <c r="G464" s="59" t="n"/>
-      <c r="H464" s="59" t="n"/>
-      <c r="I464" s="59" t="n"/>
-    </row>
-    <row r="465">
-      <c r="A465" s="59" t="n"/>
-      <c r="B465" s="59" t="n"/>
-      <c r="C465" s="59" t="n"/>
-      <c r="D465" s="59" t="n"/>
-      <c r="E465" s="59" t="n"/>
-      <c r="F465" s="59" t="n"/>
-      <c r="G465" s="59" t="n"/>
-      <c r="H465" s="59" t="n"/>
-      <c r="I465" s="59" t="n"/>
-    </row>
-    <row r="466">
-      <c r="A466" s="59" t="n"/>
-      <c r="B466" s="59" t="n"/>
-      <c r="C466" s="59" t="n"/>
-      <c r="D466" s="59" t="n"/>
-      <c r="E466" s="59" t="n"/>
-      <c r="F466" s="59" t="n"/>
-      <c r="G466" s="59" t="n"/>
-      <c r="H466" s="59" t="n"/>
-      <c r="I466" s="59" t="n"/>
-    </row>
-    <row r="467">
-      <c r="A467" s="59" t="n"/>
-      <c r="B467" s="59" t="n"/>
-      <c r="C467" s="59" t="n"/>
-      <c r="D467" s="59" t="n"/>
-      <c r="E467" s="59" t="n"/>
-      <c r="F467" s="59" t="n"/>
-      <c r="G467" s="59" t="n"/>
-      <c r="H467" s="59" t="n"/>
-      <c r="I467" s="59" t="n"/>
-    </row>
-    <row r="468">
-      <c r="A468" s="59" t="n"/>
-      <c r="B468" s="59" t="n"/>
-      <c r="C468" s="59" t="n"/>
-      <c r="D468" s="59" t="n"/>
-      <c r="E468" s="59" t="n"/>
-      <c r="F468" s="59" t="n"/>
-      <c r="G468" s="59" t="n"/>
-      <c r="H468" s="59" t="n"/>
-      <c r="I468" s="59" t="n"/>
-    </row>
-    <row r="469">
-      <c r="A469" s="59" t="n"/>
-      <c r="B469" s="59" t="n"/>
-      <c r="C469" s="59" t="n"/>
-      <c r="D469" s="59" t="n"/>
-      <c r="E469" s="59" t="n"/>
-      <c r="F469" s="59" t="n"/>
-      <c r="G469" s="59" t="n"/>
-      <c r="H469" s="59" t="n"/>
-      <c r="I469" s="59" t="n"/>
-    </row>
-    <row r="470">
-      <c r="A470" s="59" t="n"/>
-      <c r="B470" s="59" t="n"/>
-      <c r="C470" s="59" t="n"/>
-      <c r="D470" s="59" t="n"/>
-      <c r="E470" s="59" t="n"/>
-      <c r="F470" s="59" t="n"/>
-      <c r="G470" s="59" t="n"/>
-      <c r="H470" s="59" t="n"/>
-      <c r="I470" s="59" t="n"/>
-    </row>
-    <row r="471">
-      <c r="A471" s="59" t="n"/>
-      <c r="B471" s="59" t="n"/>
-      <c r="C471" s="59" t="n"/>
-      <c r="D471" s="59" t="n"/>
-      <c r="E471" s="59" t="n"/>
-      <c r="F471" s="59" t="n"/>
-      <c r="G471" s="59" t="n"/>
-      <c r="H471" s="59" t="n"/>
-      <c r="I471" s="59" t="n"/>
-    </row>
-    <row r="472">
-      <c r="A472" s="59" t="n"/>
-      <c r="B472" s="59" t="n"/>
-      <c r="C472" s="59" t="n"/>
-      <c r="D472" s="59" t="n"/>
-      <c r="E472" s="59" t="n"/>
-      <c r="F472" s="59" t="n"/>
-      <c r="G472" s="59" t="n"/>
-      <c r="H472" s="59" t="n"/>
-      <c r="I472" s="59" t="n"/>
-    </row>
-    <row r="473">
-      <c r="A473" s="59" t="n"/>
-      <c r="B473" s="59" t="n"/>
-      <c r="C473" s="59" t="n"/>
-      <c r="D473" s="59" t="n"/>
-      <c r="E473" s="59" t="n"/>
-      <c r="F473" s="59" t="n"/>
-      <c r="G473" s="59" t="n"/>
-      <c r="H473" s="59" t="n"/>
-      <c r="I473" s="59" t="n"/>
-    </row>
-    <row r="474">
-      <c r="A474" s="59" t="n"/>
-      <c r="B474" s="59" t="n"/>
-      <c r="C474" s="59" t="n"/>
-      <c r="D474" s="59" t="n"/>
-      <c r="E474" s="59" t="n"/>
-      <c r="F474" s="59" t="n"/>
-      <c r="G474" s="59" t="n"/>
-      <c r="H474" s="59" t="n"/>
-      <c r="I474" s="59" t="n"/>
-    </row>
-    <row r="475">
-      <c r="A475" s="59" t="n"/>
-      <c r="B475" s="59" t="n"/>
-      <c r="C475" s="59" t="n"/>
-      <c r="D475" s="59" t="n"/>
-      <c r="E475" s="59" t="n"/>
-      <c r="F475" s="59" t="n"/>
-      <c r="G475" s="59" t="n"/>
-      <c r="H475" s="59" t="n"/>
-      <c r="I475" s="59" t="n"/>
-    </row>
-    <row r="476">
-      <c r="A476" s="59" t="n"/>
-      <c r="B476" s="59" t="n"/>
-      <c r="C476" s="59" t="n"/>
-      <c r="D476" s="59" t="n"/>
-      <c r="E476" s="59" t="n"/>
-      <c r="F476" s="59" t="n"/>
-      <c r="G476" s="59" t="n"/>
-      <c r="H476" s="59" t="n"/>
-      <c r="I476" s="59" t="n"/>
-    </row>
-    <row r="477">
-      <c r="A477" s="59" t="n"/>
-      <c r="B477" s="59" t="n"/>
-      <c r="C477" s="59" t="n"/>
-      <c r="D477" s="59" t="n"/>
-      <c r="E477" s="59" t="n"/>
-      <c r="F477" s="59" t="n"/>
-      <c r="G477" s="59" t="n"/>
-      <c r="H477" s="59" t="n"/>
-      <c r="I477" s="59" t="n"/>
-    </row>
-    <row r="478">
-      <c r="A478" s="59" t="n"/>
-      <c r="B478" s="59" t="n"/>
-      <c r="C478" s="59" t="n"/>
-      <c r="D478" s="59" t="n"/>
-      <c r="E478" s="59" t="n"/>
-      <c r="F478" s="59" t="n"/>
-      <c r="G478" s="59" t="n"/>
-      <c r="H478" s="59" t="n"/>
-      <c r="I478" s="59" t="n"/>
-    </row>
-    <row r="479">
-      <c r="A479" s="59" t="n"/>
-      <c r="B479" s="59" t="n"/>
-      <c r="C479" s="59" t="n"/>
-      <c r="D479" s="59" t="n"/>
-      <c r="E479" s="59" t="n"/>
-      <c r="F479" s="59" t="n"/>
-      <c r="G479" s="59" t="n"/>
-      <c r="H479" s="59" t="n"/>
-      <c r="I479" s="59" t="n"/>
-    </row>
-    <row r="480">
-      <c r="A480" s="59" t="n"/>
-      <c r="B480" s="59" t="n"/>
-      <c r="C480" s="59" t="n"/>
-      <c r="D480" s="59" t="n"/>
-      <c r="E480" s="59" t="n"/>
-      <c r="F480" s="59" t="n"/>
-      <c r="G480" s="59" t="n"/>
-      <c r="H480" s="59" t="n"/>
-      <c r="I480" s="59" t="n"/>
-    </row>
-    <row r="481">
-      <c r="A481" s="59" t="n"/>
-      <c r="B481" s="59" t="n"/>
-      <c r="C481" s="59" t="n"/>
-      <c r="D481" s="59" t="n"/>
-      <c r="E481" s="59" t="n"/>
-      <c r="F481" s="59" t="n"/>
-      <c r="G481" s="59" t="n"/>
-      <c r="H481" s="59" t="n"/>
-      <c r="I481" s="59" t="n"/>
-    </row>
-    <row r="482">
-      <c r="A482" s="59" t="n"/>
-      <c r="B482" s="59" t="n"/>
-      <c r="C482" s="59" t="n"/>
-      <c r="D482" s="59" t="n"/>
-      <c r="E482" s="59" t="n"/>
-      <c r="F482" s="59" t="n"/>
-      <c r="G482" s="59" t="n"/>
-      <c r="H482" s="59" t="n"/>
-      <c r="I482" s="59" t="n"/>
-    </row>
-    <row r="483">
-      <c r="A483" s="59" t="n"/>
-      <c r="B483" s="59" t="n"/>
-      <c r="C483" s="59" t="n"/>
-      <c r="D483" s="59" t="n"/>
-      <c r="E483" s="59" t="n"/>
-      <c r="F483" s="59" t="n"/>
-      <c r="G483" s="59" t="n"/>
-      <c r="H483" s="59" t="n"/>
-      <c r="I483" s="59" t="n"/>
-    </row>
-    <row r="484">
-      <c r="A484" s="59" t="n"/>
-      <c r="B484" s="59" t="n"/>
-      <c r="C484" s="59" t="n"/>
-      <c r="D484" s="59" t="n"/>
-      <c r="E484" s="59" t="n"/>
-      <c r="F484" s="59" t="n"/>
-      <c r="G484" s="59" t="n"/>
-      <c r="H484" s="59" t="n"/>
-      <c r="I484" s="59" t="n"/>
-    </row>
-    <row r="485">
-      <c r="A485" s="59" t="n"/>
-      <c r="B485" s="59" t="n"/>
-      <c r="C485" s="59" t="n"/>
-      <c r="D485" s="59" t="n"/>
-      <c r="E485" s="59" t="n"/>
-      <c r="F485" s="59" t="n"/>
-      <c r="G485" s="59" t="n"/>
-      <c r="H485" s="59" t="n"/>
-      <c r="I485" s="59" t="n"/>
-    </row>
-    <row r="486">
-      <c r="A486" s="59" t="n"/>
-      <c r="B486" s="59" t="n"/>
-      <c r="C486" s="59" t="n"/>
-      <c r="D486" s="59" t="n"/>
-      <c r="E486" s="59" t="n"/>
-      <c r="F486" s="59" t="n"/>
-      <c r="G486" s="59" t="n"/>
-      <c r="H486" s="59" t="n"/>
-      <c r="I486" s="59" t="n"/>
-    </row>
-    <row r="487">
-      <c r="A487" s="59" t="n"/>
-      <c r="B487" s="59" t="n"/>
-      <c r="C487" s="59" t="n"/>
-      <c r="D487" s="59" t="n"/>
-      <c r="E487" s="59" t="n"/>
-      <c r="F487" s="59" t="n"/>
-      <c r="G487" s="59" t="n"/>
-      <c r="H487" s="59" t="n"/>
-      <c r="I487" s="59" t="n"/>
-    </row>
-    <row r="488">
-      <c r="A488" s="59" t="n"/>
-      <c r="B488" s="59" t="n"/>
-      <c r="C488" s="59" t="n"/>
-      <c r="D488" s="59" t="n"/>
-      <c r="E488" s="59" t="n"/>
-      <c r="F488" s="59" t="n"/>
-      <c r="G488" s="59" t="n"/>
-      <c r="H488" s="59" t="n"/>
-      <c r="I488" s="59" t="n"/>
-    </row>
-    <row r="489">
-      <c r="A489" s="59" t="n"/>
-      <c r="B489" s="59" t="n"/>
-      <c r="C489" s="59" t="n"/>
-      <c r="D489" s="59" t="n"/>
-      <c r="E489" s="59" t="n"/>
-      <c r="F489" s="59" t="n"/>
-      <c r="G489" s="59" t="n"/>
-      <c r="H489" s="59" t="n"/>
-      <c r="I489" s="59" t="n"/>
-    </row>
-    <row r="490">
-      <c r="A490" s="59" t="n"/>
-      <c r="B490" s="59" t="n"/>
-      <c r="C490" s="59" t="n"/>
-      <c r="D490" s="59" t="n"/>
-      <c r="E490" s="59" t="n"/>
-      <c r="F490" s="59" t="n"/>
-      <c r="G490" s="59" t="n"/>
-      <c r="H490" s="59" t="n"/>
-      <c r="I490" s="59" t="n"/>
-    </row>
-    <row r="491">
-      <c r="A491" s="59" t="n"/>
-      <c r="B491" s="59" t="n"/>
-      <c r="C491" s="59" t="n"/>
-      <c r="D491" s="59" t="n"/>
-      <c r="E491" s="59" t="n"/>
-      <c r="F491" s="59" t="n"/>
-      <c r="G491" s="59" t="n"/>
-      <c r="H491" s="59" t="n"/>
-      <c r="I491" s="59" t="n"/>
-    </row>
-    <row r="492">
-      <c r="A492" s="59" t="n"/>
-      <c r="B492" s="59" t="n"/>
-      <c r="C492" s="59" t="n"/>
-      <c r="D492" s="59" t="n"/>
-      <c r="E492" s="59" t="n"/>
-      <c r="F492" s="59" t="n"/>
-      <c r="G492" s="59" t="n"/>
-      <c r="H492" s="59" t="n"/>
-      <c r="I492" s="59" t="n"/>
-    </row>
-    <row r="493">
-      <c r="A493" s="59" t="n"/>
-      <c r="B493" s="59" t="n"/>
-      <c r="C493" s="59" t="n"/>
-      <c r="D493" s="59" t="n"/>
-      <c r="E493" s="59" t="n"/>
-      <c r="F493" s="59" t="n"/>
-      <c r="G493" s="59" t="n"/>
-      <c r="H493" s="59" t="n"/>
-      <c r="I493" s="59" t="n"/>
-    </row>
-    <row r="494">
-      <c r="A494" s="59" t="n"/>
-      <c r="B494" s="59" t="n"/>
-      <c r="C494" s="59" t="n"/>
-      <c r="D494" s="59" t="n"/>
-      <c r="E494" s="59" t="n"/>
-      <c r="F494" s="59" t="n"/>
-      <c r="G494" s="59" t="n"/>
-      <c r="H494" s="59" t="n"/>
-      <c r="I494" s="59" t="n"/>
-    </row>
-    <row r="495">
-      <c r="A495" s="59" t="n"/>
-      <c r="B495" s="59" t="n"/>
-      <c r="C495" s="59" t="n"/>
-      <c r="D495" s="59" t="n"/>
-      <c r="E495" s="59" t="n"/>
-      <c r="F495" s="59" t="n"/>
-      <c r="G495" s="59" t="n"/>
-      <c r="H495" s="59" t="n"/>
-      <c r="I495" s="59" t="n"/>
-    </row>
-    <row r="496">
-      <c r="A496" s="59" t="n"/>
-      <c r="B496" s="59" t="n"/>
-      <c r="C496" s="59" t="n"/>
-      <c r="D496" s="59" t="n"/>
-      <c r="E496" s="59" t="n"/>
-      <c r="F496" s="59" t="n"/>
-      <c r="G496" s="59" t="n"/>
-      <c r="H496" s="59" t="n"/>
-      <c r="I496" s="59" t="n"/>
-    </row>
-    <row r="497">
-      <c r="A497" s="59" t="n"/>
-      <c r="B497" s="59" t="n"/>
-      <c r="C497" s="59" t="n"/>
-      <c r="D497" s="59" t="n"/>
-      <c r="E497" s="59" t="n"/>
-      <c r="F497" s="59" t="n"/>
-      <c r="G497" s="59" t="n"/>
-      <c r="H497" s="59" t="n"/>
-      <c r="I497" s="59" t="n"/>
-    </row>
-    <row r="498">
-      <c r="A498" s="59" t="n"/>
-      <c r="B498" s="59" t="n"/>
-      <c r="C498" s="59" t="n"/>
-      <c r="D498" s="59" t="n"/>
-      <c r="E498" s="59" t="n"/>
-      <c r="F498" s="59" t="n"/>
-      <c r="G498" s="59" t="n"/>
-      <c r="H498" s="59" t="n"/>
-      <c r="I498" s="59" t="n"/>
-    </row>
-    <row r="499">
-      <c r="A499" s="59" t="n"/>
-      <c r="B499" s="59" t="n"/>
-      <c r="C499" s="59" t="n"/>
-      <c r="D499" s="59" t="n"/>
-      <c r="E499" s="59" t="n"/>
-      <c r="F499" s="59" t="n"/>
-      <c r="G499" s="59" t="n"/>
-      <c r="H499" s="59" t="n"/>
-      <c r="I499" s="59" t="n"/>
-    </row>
-    <row r="500">
-      <c r="A500" s="59" t="n"/>
-      <c r="B500" s="59" t="n"/>
-      <c r="C500" s="59" t="n"/>
-      <c r="D500" s="59" t="n"/>
-      <c r="E500" s="59" t="n"/>
-      <c r="F500" s="59" t="n"/>
-      <c r="G500" s="59" t="n"/>
-      <c r="H500" s="59" t="n"/>
-      <c r="I500" s="59" t="n"/>
-    </row>
-    <row r="501">
-      <c r="A501" s="59" t="n"/>
-      <c r="B501" s="59" t="n"/>
-      <c r="C501" s="59" t="n"/>
-      <c r="D501" s="59" t="n"/>
-      <c r="E501" s="59" t="n"/>
-      <c r="F501" s="59" t="n"/>
-      <c r="G501" s="59" t="n"/>
-      <c r="H501" s="59" t="n"/>
-      <c r="I501" s="59" t="n"/>
-    </row>
-    <row r="502">
-      <c r="A502" s="59" t="n"/>
-      <c r="B502" s="59" t="n"/>
-      <c r="C502" s="59" t="n"/>
-      <c r="D502" s="59" t="n"/>
-      <c r="E502" s="59" t="n"/>
-      <c r="F502" s="59" t="n"/>
-      <c r="G502" s="59" t="n"/>
-      <c r="H502" s="59" t="n"/>
-      <c r="I502" s="59" t="n"/>
-    </row>
-    <row r="503">
-      <c r="A503" s="59" t="n"/>
-      <c r="B503" s="59" t="n"/>
-      <c r="C503" s="59" t="n"/>
-      <c r="D503" s="59" t="n"/>
-      <c r="E503" s="59" t="n"/>
-      <c r="F503" s="59" t="n"/>
-      <c r="G503" s="59" t="n"/>
-      <c r="H503" s="59" t="n"/>
-      <c r="I503" s="59" t="n"/>
-    </row>
-    <row r="504">
-      <c r="A504" s="59" t="n"/>
-      <c r="B504" s="59" t="n"/>
-      <c r="C504" s="59" t="n"/>
-      <c r="D504" s="59" t="n"/>
-      <c r="E504" s="59" t="n"/>
-      <c r="F504" s="59" t="n"/>
-      <c r="G504" s="59" t="n"/>
-      <c r="H504" s="59" t="n"/>
-      <c r="I504" s="59" t="n"/>
-    </row>
-    <row r="505">
-      <c r="A505" s="59" t="n"/>
-      <c r="B505" s="59" t="n"/>
-      <c r="C505" s="59" t="n"/>
-      <c r="D505" s="59" t="n"/>
-      <c r="E505" s="59" t="n"/>
-      <c r="F505" s="59" t="n"/>
-      <c r="G505" s="59" t="n"/>
-      <c r="H505" s="59" t="n"/>
-      <c r="I505" s="59" t="n"/>
-    </row>
-    <row r="506">
-      <c r="A506" s="59" t="n"/>
-      <c r="B506" s="59" t="n"/>
-      <c r="C506" s="59" t="n"/>
-      <c r="D506" s="59" t="n"/>
-      <c r="E506" s="59" t="n"/>
-      <c r="F506" s="59" t="n"/>
-      <c r="G506" s="59" t="n"/>
-      <c r="H506" s="59" t="n"/>
-      <c r="I506" s="59" t="n"/>
-    </row>
-    <row r="507">
-      <c r="A507" s="59" t="n"/>
-      <c r="B507" s="59" t="n"/>
-      <c r="C507" s="59" t="n"/>
-      <c r="D507" s="59" t="n"/>
-      <c r="E507" s="59" t="n"/>
-      <c r="F507" s="59" t="n"/>
-      <c r="G507" s="59" t="n"/>
-      <c r="H507" s="59" t="n"/>
-      <c r="I507" s="59" t="n"/>
-    </row>
-    <row r="508">
-      <c r="A508" s="59" t="n"/>
-      <c r="B508" s="59" t="n"/>
-      <c r="C508" s="59" t="n"/>
-      <c r="D508" s="59" t="n"/>
-      <c r="E508" s="59" t="n"/>
-      <c r="F508" s="59" t="n"/>
-      <c r="G508" s="59" t="n"/>
-      <c r="H508" s="59" t="n"/>
-      <c r="I508" s="59" t="n"/>
-    </row>
-    <row r="509">
-      <c r="A509" s="59" t="n"/>
-      <c r="B509" s="59" t="n"/>
-      <c r="C509" s="59" t="n"/>
-      <c r="D509" s="59" t="n"/>
-      <c r="E509" s="59" t="n"/>
-      <c r="F509" s="59" t="n"/>
-      <c r="G509" s="59" t="n"/>
-      <c r="H509" s="59" t="n"/>
-      <c r="I509" s="59" t="n"/>
-    </row>
-    <row r="510">
-      <c r="A510" s="59" t="n"/>
-      <c r="B510" s="59" t="n"/>
-      <c r="C510" s="59" t="n"/>
-      <c r="D510" s="59" t="n"/>
-      <c r="E510" s="59" t="n"/>
-      <c r="F510" s="59" t="n"/>
-      <c r="G510" s="59" t="n"/>
-      <c r="H510" s="59" t="n"/>
-      <c r="I510" s="59" t="n"/>
-    </row>
-    <row r="511">
-      <c r="A511" s="59" t="n"/>
-      <c r="B511" s="59" t="n"/>
-      <c r="C511" s="59" t="n"/>
-      <c r="D511" s="59" t="n"/>
-      <c r="E511" s="59" t="n"/>
-      <c r="F511" s="59" t="n"/>
-      <c r="G511" s="59" t="n"/>
-      <c r="H511" s="59" t="n"/>
-      <c r="I511" s="59" t="n"/>
-    </row>
-    <row r="512">
-      <c r="A512" s="59" t="n"/>
-      <c r="B512" s="59" t="n"/>
-      <c r="C512" s="59" t="n"/>
-      <c r="D512" s="59" t="n"/>
-      <c r="E512" s="59" t="n"/>
-      <c r="F512" s="59" t="n"/>
-      <c r="G512" s="59" t="n"/>
-      <c r="H512" s="59" t="n"/>
-      <c r="I512" s="59" t="n"/>
-    </row>
+    <row r="175" ht="22" customHeight="1"/>
+    <row r="176" ht="22" customHeight="1"/>
+    <row r="177" ht="22" customHeight="1"/>
+    <row r="178" ht="22" customHeight="1"/>
+    <row r="179" ht="22" customHeight="1"/>
+    <row r="180" ht="22" customHeight="1"/>
+    <row r="181" ht="22" customHeight="1"/>
+    <row r="182" ht="22" customHeight="1"/>
+    <row r="183" ht="22" customHeight="1"/>
+    <row r="184" ht="22" customHeight="1"/>
+    <row r="185" ht="22" customHeight="1"/>
+    <row r="186" ht="22" customHeight="1"/>
+    <row r="187" ht="22" customHeight="1"/>
+    <row r="188" ht="22" customHeight="1"/>
+    <row r="189" ht="22" customHeight="1"/>
+    <row r="190" ht="22" customHeight="1"/>
+    <row r="191" ht="22" customHeight="1"/>
+    <row r="192" ht="22" customHeight="1"/>
+    <row r="193" ht="22" customHeight="1"/>
+    <row r="194" ht="22" customHeight="1"/>
+    <row r="195" ht="22" customHeight="1"/>
+    <row r="196" ht="22" customHeight="1"/>
+    <row r="197" ht="22" customHeight="1"/>
+    <row r="198" ht="22" customHeight="1"/>
+    <row r="199" ht="22" customHeight="1"/>
+    <row r="200" ht="22" customHeight="1"/>
+    <row r="201" ht="22" customHeight="1"/>
+    <row r="202" ht="22" customHeight="1"/>
+    <row r="203" ht="22" customHeight="1"/>
+    <row r="204" ht="22" customHeight="1"/>
+    <row r="205" ht="22" customHeight="1"/>
+    <row r="206" ht="22" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report/项目执行计划.xlsx
+++ b/report/项目执行计划.xlsx
@@ -1920,6 +1920,7 @@
         <v>3300</v>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2109,12 +2110,12 @@
       </c>
       <c r="C8" s="43" t="inlineStr">
         <is>
-          <t>① .NET 10 后端：元数据服务 + 查询代理（SQL 拼装与白名单校验）+ 附件服务（SAS 签发）+ 调度服务 ② React 前端：配置化查询平台（JSON Schema 动态渲染）③ CI/CD：GitHub Actions → ACR → Helm 部署到平台提供的 AKS 命名空间（多环境 values）④ 代码安全四道门禁：SAST（CodeQL/Semgrep）、依赖漏洞扫描（Dependabot/audit）、密钥泄漏扫描（gitleaks）、镜像 CVE 扫描（Trivy）—— CI 强制卡点 + 高中危清零 ⑤ SSO 集成（Entra ID OIDC + JWT 角色 Claims）</t>
+          <t>① .NET 10 后端：元数据服务 + 查询代理（SQL 拼装与白名单校验）+ 附件服务（SAS 签发）+ 调度服务 ② React 前端：配置化查询平台（JSON Schema 动态渲染）③ CI/CD：Azure DevOps Pipelines → ACR → Helm 部署到平台提供的 AKS 命名空间（多环境 values）④ 代码安全四道门禁：SAST（CodeQL/Semgrep）、依赖漏洞扫描（Dependabot/audit）、密钥泄漏扫描（gitleaks）、镜像 CVE 扫描（Trivy）—— CI 强制卡点 + 高中危清零 ⑤ SSO 集成（Entra ID OIDC + JWT 角色 Claims）</t>
         </is>
       </c>
       <c r="D8" s="33" t="inlineStr">
         <is>
-          <t>.NET 10 / React / Docker / Helm / GitHub Actions / AKS / OIDC</t>
+          <t>.NET 10 / React / Docker / Helm / Azure DevOps Pipelines / AKS / OIDC</t>
         </is>
       </c>
       <c r="E8" s="44">
@@ -2203,6 +2204,7 @@
       <c r="H10" s="53" t="n"/>
       <c r="I10" s="53" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="2" t="inlineStr"/>
     </row>
@@ -3332,7 +3334,7 @@
       <c r="C17" s="88" t="n"/>
       <c r="D17" s="78" t="inlineStr">
         <is>
-          <t>• CI 骨架：GitHub Actions build + 单测 + 推镜像（平台 ACR）</t>
+          <t>• CI 骨架：Azure DevOps Pipelines build + 单测 + 推镜像（平台 ACR）</t>
         </is>
       </c>
       <c r="E17" s="81" t="n"/>
@@ -3604,7 +3606,7 @@
       </c>
       <c r="D29" s="78" t="inlineStr">
         <is>
-          <t>• CD 流水线：Helm 部署到平台 AKS 的 Dev 命名空间</t>
+          <t>• CD 流水线：Azure DevOps Environments（Dev）+ Helm 部署到平台 AKS 命名空间（服务连接走托管标识）</t>
         </is>
       </c>
       <c r="E29" s="79" t="inlineStr">

--- a/report/项目执行计划.xlsx
+++ b/report/项目执行计划.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;￥&quot;#,##0;&quot;￥&quot;\-#,##0"/>
   </numFmts>
-  <fonts count="84">
+  <fonts count="98">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -575,6 +575,85 @@
       <b val="1"/>
       <color rgb="00dc2626"/>
       <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="001d4ed8"/>
+      <sz val="8.800000000000001"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="0064748b"/>
+      <sz val="9.199999999999999"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="001E3A8A"/>
+      <sz val="8.300000000000001"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00DC2626"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00059669"/>
+      <sz val="9.199999999999999"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="000284c7"/>
+      <sz val="9.199999999999999"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00d97706"/>
+      <sz val="9.199999999999999"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00dc2626"/>
+      <sz val="9.199999999999999"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007c3aed"/>
+      <sz val="9.199999999999999"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007c3aed"/>
+      <sz val="8.800000000000001"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="0064748B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="001E3A8A"/>
+      <sz val="8.199999999999999"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="001d4ed8"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="56">
@@ -1182,7 +1261,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1480,6 +1559,66 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="52" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="46" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="47" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="48" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="49" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="50" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="51" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="55" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="52" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="52" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="53" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="54" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="55" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="49" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1920,7 +2059,6 @@
         <v>3300</v>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2204,7 +2342,6 @@
       <c r="H10" s="53" t="n"/>
       <c r="I10" s="53" t="n"/>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="2" t="inlineStr"/>
     </row>
@@ -2224,22 +2361,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="68" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
       <c r="A1" s="58" t="inlineStr">
         <is>
-          <t>12 周 Sprint 计划总览（V8：按 8 大功能域重排 · CC 单系统接入验证 · 上线即收尾）</t>
+          <t>12 周 Sprint 计划总览（V9：双 Release · 上线压缩至 W11 一周 · CC 单系统验证）</t>
         </is>
       </c>
       <c r="B1" s="59" t="n"/>
@@ -2251,19 +2389,12 @@
       <c r="H1" s="59" t="n"/>
       <c r="I1" s="59" t="n"/>
     </row>
-    <row r="2">
-      <c r="A2" s="60" t="inlineStr">
-        <is>
-          <t>接入测试系统：Caring Center（CC，SQL Server，1253 表/24,620 字段）· 上线后无知识转移/项目关闭环节，W12 稳定运行一周即结束</t>
-        </is>
-      </c>
-      <c r="B2" s="59" t="n"/>
-      <c r="C2" s="59" t="n"/>
-      <c r="D2" s="59" t="n"/>
-      <c r="E2" s="59" t="n"/>
-      <c r="F2" s="59" t="n"/>
-      <c r="G2" s="59" t="n"/>
-      <c r="H2" s="59" t="n"/>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="106" t="inlineStr">
+        <is>
+          <t>R1 系统上线（W1~W11）：W1~W10 全部功能与上线就绪，W11 一周集中上线（发布→UAT→Go-Live）· R2 文档交付与收尾（W12）：文档终版 + 稳定确认 + 归档 → 项目结束（无知识转移/项目关闭）</t>
+        </is>
+      </c>
       <c r="I2" s="59" t="n"/>
     </row>
     <row r="3" ht="28" customHeight="1">
@@ -2280,291 +2411,359 @@
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="62" t="inlineStr">
         <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="B4" s="62" t="inlineStr">
+        <is>
           <t>Sprint</t>
         </is>
       </c>
-      <c r="B4" s="62" t="inlineStr">
+      <c r="C4" s="62" t="inlineStr">
         <is>
           <t>周次</t>
         </is>
       </c>
-      <c r="C4" s="62" t="inlineStr">
+      <c r="D4" s="62" t="inlineStr">
         <is>
           <t>主题 / 目标</t>
         </is>
       </c>
-      <c r="D4" s="62" t="inlineStr">
+      <c r="E4" s="62" t="inlineStr">
         <is>
           <t>核心交付物（按功能域编号）</t>
         </is>
       </c>
-      <c r="E4" s="62" t="inlineStr">
-        <is>
-          <t>演示内容（Sprint Review）</t>
-        </is>
-      </c>
       <c r="F4" s="62" t="inlineStr">
         <is>
+          <t>演示 / 里程碑</t>
+        </is>
+      </c>
+      <c r="G4" s="62" t="inlineStr">
+        <is>
           <t>主要风险</t>
         </is>
       </c>
-      <c r="G4" s="62" t="inlineStr">
+      <c r="H4" s="62" t="inlineStr">
         <is>
           <t>需确认/决策项</t>
         </is>
       </c>
-      <c r="H4" s="59" t="n"/>
       <c r="I4" s="59" t="n"/>
     </row>
-    <row r="5" ht="120" customHeight="1">
-      <c r="A5" s="63" t="inlineStr">
+    <row r="5" ht="122" customHeight="1">
+      <c r="A5" s="107" t="inlineStr">
+        <is>
+          <t>Release 1
+系统上线</t>
+        </is>
+      </c>
+      <c r="B5" s="108" t="inlineStr">
         <is>
           <t>Sprint 0
 需求+筹备</t>
         </is>
       </c>
-      <c r="B5" s="64" t="inlineStr">
+      <c r="C5" s="64" t="inlineStr">
         <is>
           <t>W1~W2</t>
         </is>
       </c>
-      <c r="C5" s="65" t="inlineStr">
+      <c r="D5" s="76" t="inlineStr">
         <is>
           <t>需求定稿 + 环境就绪 + CC 连接打通</t>
         </is>
       </c>
-      <c r="D5" s="66" t="inlineStr">
-        <is>
-          <t>【全部功能域需求澄清】① A：BRD 定稿（8 大功能域 + 数据流图 + 保留期矩阵 + PII 分级 + 检索权限矩阵 + UAT 场景）② B：架构定稿 + 资源申请单（区域锁定=境内驻留）+ 平台交付资源验收 + UC 初始化 ③ C：SeaTunnel PoC——用 Caring Center 源库实测连通（1253 表全量扫描 information_schema，完成表分类：业务表/垃圾表/附件元数据表）④ D：前后端骨架 + CI/CD 就绪 + SSO（OIDC）走通 ⑤ E：测试计划（8 域全覆盖）+ 架构图×2 + 文档模板</t>
-        </is>
-      </c>
-      <c r="E5" s="66" t="inlineStr">
-        <is>
-          <t>① CC 源库连接打通：SeaTunnel 抽样 10 张表 → Iceberg RAW → SQL Warehouse 可查 ② BRD 评审通过 ③ 登录页可访问</t>
-        </is>
-      </c>
-      <c r="F5" s="67" t="inlineStr">
-        <is>
-          <t>CC 源库账号/白名单延迟；1253 表审表工作量大（A 需业务方配合勾选）；实时性指标（02 域）未定</t>
-        </is>
-      </c>
-      <c r="G5" s="68" t="inlineStr">
-        <is>
-          <t>① CC 只读账号 + NAT 白名单（W1 必须）② 垃圾表剔除标准业务确认 ③ 02 域"实时"指标：分钟级 or 小时级？④ 04 域境内驻留的区域要求 ⑤ Legal Hold 触发条件（法务）</t>
-        </is>
-      </c>
-      <c r="H5" s="59" t="n"/>
+      <c r="E5" s="79" t="inlineStr">
+        <is>
+          <t>【8 域需求】① A：BRD 定稿（8 域 + 数据流图 + 保留期矩阵 + PII 分级 + 检索权限矩阵）② B：架构定稿 + 资源申请单（区域=境内）+ 资源验收 + UC 初始化 ③ C：SeaTunnel PoC（CC 抽样 10 表端到端）+ 1253 表扫描分类 ④ D：前后端骨架 + Azure DevOps Pipelines CI + SSO 走通 ⑤ E：测试计划（8 域）+ 架构图×2 + 文档模板</t>
+        </is>
+      </c>
+      <c r="F5" s="109" t="inlineStr">
+        <is>
+          <t>★ CC PoC 端到端；BRD 评审通过；登录页可访问</t>
+        </is>
+      </c>
+      <c r="G5" s="80" t="inlineStr">
+        <is>
+          <t>CC 账号/白名单周期；1253 表审表量；02 域实时指标未定</t>
+        </is>
+      </c>
+      <c r="H5" s="110" t="inlineStr">
+        <is>
+          <t>① CC 只读账号（W1 必须）② 垃圾表剔除标准 ③ 实时指标 ④ 境内驻留区域 ⑤ Legal Hold 条件</t>
+        </is>
+      </c>
       <c r="I5" s="59" t="n"/>
     </row>
-    <row r="6" ht="120" customHeight="1">
-      <c r="A6" s="69" t="inlineStr">
+    <row r="6" ht="122" customHeight="1">
+      <c r="A6" s="107" t="inlineStr">
+        <is>
+          <t>Release 1
+系统上线</t>
+        </is>
+      </c>
+      <c r="B6" s="111" t="inlineStr">
         <is>
           <t>Sprint 1
 迁移+检索 MVP</t>
         </is>
       </c>
-      <c r="B6" s="64" t="inlineStr">
+      <c r="C6" s="64" t="inlineStr">
         <is>
           <t>W3~W4</t>
         </is>
       </c>
-      <c r="C6" s="65" t="inlineStr">
-        <is>
-          <t>01 存量迁移 + 05 检索 端到端（CC 首批 50 张表）</t>
-        </is>
-      </c>
-      <c r="D6" s="66" t="inlineStr">
-        <is>
-          <t>【01 域】① C：SeaTunnel 批量导入 CC 首批 50 张勾选表（分片/限速/断点）+ 迁移任务管理（生成器→调度→状态）+ 完整性校验（行数/校验和/SHA-256 台账）② A：迁移规则确认（垃圾表剔除、字段映射）③ D：迁移任务管理界面【05 域】④ D：基础检索页（配置化动态渲染）+ 结果预览（图片/附件 SAS）+ 导出 CSV【08 域】⑤ B：RBAC 五角色 + Entra ID 组映射 + UC GRANT（CC 的 catalog）+ SSO JWT Claims 贯通【06 域】⑥ D：操作审计埋点 v1【07 域】⑦ C：JDBC 连接器模板 v1（SQL Server 类型映射）</t>
-        </is>
-      </c>
-      <c r="E6" s="66" t="inlineStr">
-        <is>
-          <t>① CC 50 张表端到端：登录 → 选系统 → 检索 → 预览附件 → 导出，全程带权限与审计 ② 迁移对账报告（行数 100% 一致）</t>
-        </is>
-      </c>
-      <c r="F6" s="67" t="inlineStr">
-        <is>
-          <t>CC 全量 1253 表审表压力；前后端联调；掩码函数首次落地</t>
-        </is>
-      </c>
-      <c r="G6" s="68" t="inlineStr">
-        <is>
-          <t>① CC 首批勾选表清单（业务方 W2 末确认）② PII 字段标记（哪些列脱敏）③ 预览格式范围（图片/音频/视频）</t>
-        </is>
-      </c>
-      <c r="H6" s="59" t="n"/>
+      <c r="D6" s="76" t="inlineStr">
+        <is>
+          <t>01 存量迁移 + 05 检索 端到端（CC 首批 50 表）</t>
+        </is>
+      </c>
+      <c r="E6" s="79" t="inlineStr">
+        <is>
+          <t>【01】① C：批量导入 50 表（分片/限速/断点）+ 任务管理（生成器+状态+对账 SHA-256）② D：迁移任务管理界面【05】③ D：检索页（配置化渲染）+ 预览（SAS）+ 导出【08】④ B：RBAC 五角色 + Entra ID 组映射 + UC GRANT + SSO Claims【06】⑤ D：审计埋点 v1【07】⑥ C：连接器模板 v1</t>
+        </is>
+      </c>
+      <c r="F6" s="109" t="inlineStr">
+        <is>
+          <t>★ CC 50 表端到端：登录→检索→预览→导出（带权限与审计）+ 对账 100%</t>
+        </is>
+      </c>
+      <c r="G6" s="80" t="inlineStr">
+        <is>
+          <t>审表与联调压力；掩码函数首次落地</t>
+        </is>
+      </c>
+      <c r="H6" s="110" t="inlineStr">
+        <is>
+          <t>① CC 首批表清单（W2 末）② PII 字段标记 ③ 预览格式范围</t>
+        </is>
+      </c>
       <c r="I6" s="59" t="n"/>
     </row>
-    <row r="7" ht="120" customHeight="1">
-      <c r="A7" s="70" t="inlineStr">
+    <row r="7" ht="122" customHeight="1">
+      <c r="A7" s="107" t="inlineStr">
+        <is>
+          <t>Release 1
+系统上线</t>
+        </is>
+      </c>
+      <c r="B7" s="112" t="inlineStr">
         <is>
           <t>Sprint 2
 治理+安全</t>
         </is>
       </c>
-      <c r="B7" s="64" t="inlineStr">
+      <c r="C7" s="64" t="inlineStr">
         <is>
           <t>W5~W6</t>
         </is>
       </c>
-      <c r="C7" s="65" t="inlineStr">
+      <c r="D7" s="76" t="inlineStr">
         <is>
           <t>02 数据治理 + 03 归档生命周期 + 04 安全管控</t>
         </is>
       </c>
-      <c r="D7" s="66" t="inlineStr">
-        <is>
-          <t>【02 域】① C：增量/准实时接入方案落地（按 W1 确认的实时指标）+ 冷数据识别与自动转冷（按 A 的冷数据标准）② D：元数据标准管理界面【03 域】③ B：标准归档模型管理 + 到期处置引擎（扫描→DROP PARTITION→VACUUM）+ Legal Hold（Hold/Release + 留痕）④ C：归档转换校验（CURATED/LAKE 层 Spark SQL + Schema Evolution）⑤ D+B：到期处置与 Legal Hold 界面（含审批）【04 域】⑥ B：加密体系落地（CMK + aes_encrypt 字段级 + 密钥轮转）+ UC COLUMN MASK 动态脱敏 + 境内驻留核查（区域配置+出口流量）⑦ C：ADLS 冷热分层 + 生命周期规则 + Compaction 调度</t>
-        </is>
-      </c>
-      <c r="E7" s="66" t="inlineStr">
-        <is>
-          <t>① 增量数据自动入湖（准实时时效达标）② 设 1 天保留期 → 到期自动处置 → Legal Hold 拦截 → 审计留痕全链路 ③ 无权限见掩码/有权限见明文 ④ 存储分层生效（Cool 层成本可见）</t>
-        </is>
-      </c>
-      <c r="F7" s="67" t="inlineStr">
-        <is>
-          <t>实时方案技术风险（CDC vs 轮询）；处置不可逆需沙箱充分验证；掩码函数与前端联动</t>
-        </is>
-      </c>
-      <c r="G7" s="68" t="inlineStr">
-        <is>
-          <t>① 02 域实时指标验收标准 ② Legal Hold 审批人 ③ 保留期合规底线（法务）④ 性能验收标准（首屏 P95&lt;5s）</t>
-        </is>
-      </c>
-      <c r="H7" s="59" t="n"/>
+      <c r="E7" s="79" t="inlineStr">
+        <is>
+          <t>【02】① C：增量接入（watermark）+ 冷数据识别自动转冷 ② D：元数据标准界面【03】③ B：处置引擎（扫描→DROP PARTITION→VACUUM）+ Legal Hold（Hold/Release+豁免+留痕）④ C：CURATED/LAKE 转换 + Schema Evolution【04】⑤ B：加密（CMK+字段级+轮转）+ 脱敏 + 境内驻留核查 ⑥ C：ADLS 分层 + 生命周期 + Compaction</t>
+        </is>
+      </c>
+      <c r="F7" s="109" t="inlineStr">
+        <is>
+          <t>★ 处置全链路（到期→Hold 拦截→处置→审计）+ 脱敏三态 + 分层生效</t>
+        </is>
+      </c>
+      <c r="G7" s="80" t="inlineStr">
+        <is>
+          <t>实时方案风险；处置不可逆需沙箱验证；掩码与前端联动</t>
+        </is>
+      </c>
+      <c r="H7" s="110" t="inlineStr">
+        <is>
+          <t>① 实时指标验收标准 ② Legal Hold 审批人 ③ 保留期底线 ④ 性能标准（P95&lt;5s）</t>
+        </is>
+      </c>
       <c r="I7" s="59" t="n"/>
     </row>
-    <row r="8" ht="120" customHeight="1">
-      <c r="A8" s="71" t="inlineStr">
+    <row r="8" ht="122" customHeight="1">
+      <c r="A8" s="107" t="inlineStr">
+        <is>
+          <t>Release 1
+系统上线</t>
+        </is>
+      </c>
+      <c r="B8" s="113" t="inlineStr">
         <is>
           <t>Sprint 3
 CC 全量+连接器</t>
         </is>
       </c>
-      <c r="B8" s="64" t="inlineStr">
+      <c r="C8" s="64" t="inlineStr">
         <is>
           <t>W7~W8</t>
         </is>
       </c>
-      <c r="C8" s="65" t="inlineStr">
-        <is>
-          <t>CC 1253 表全量迁移 + 07 连接器完善 + 06 合规报表</t>
-        </is>
-      </c>
-      <c r="D8" s="66" t="inlineStr">
-        <is>
-          <t>【01+02 域】① C：CC 全量 1253 表分批迁移（垃圾表按规则剔除后约 600~800 张）+ 增量常态化运行 ② A：迁移范围最终确认 + 范围变更裁决【07 域】③ C：连接器模板库扩展（MySQL 类型映射 + 文件源模板）+ 连接器运行监控与审计上报 ④ D：多源连接管理界面（配置/测试/模板选择/状态）【06 域】⑤ D：合规报表 v1（操作审计查询 + 导出 + 等保/个保法对照视图）⑥ E：合规口径验证（报表可举证）【08 域】⑦ B：行级隔离验证（跨系统越权测试全过）</t>
-        </is>
-      </c>
-      <c r="E8" s="66" t="inlineStr">
-        <is>
-          <t>① CC 全量数据入湖（对账 100%）+ 增量自动运行 ② 新数据源 30 分钟完成配置接入（连接器模板演示）③ 合规报表一键导出 ④ 越权测试全部拦截</t>
-        </is>
-      </c>
-      <c r="F8" s="67" t="inlineStr">
-        <is>
-          <t>CC 全量迁移时长不可控（数据量未知）；1253 表逐批对账耗时；报表合规口径与法务理解偏差</t>
-        </is>
-      </c>
-      <c r="G8" s="68" t="inlineStr">
-        <is>
-          <t>① CC 全量数据量确认（sp_spaceused）② 全量迁移窗口（周末？）③ 合规报表口径签字人</t>
-        </is>
-      </c>
-      <c r="H8" s="59" t="n"/>
+      <c r="D8" s="76" t="inlineStr">
+        <is>
+          <t>CC 1253 表全量迁移 + 07 连接器库 + 06 合规报表</t>
+        </is>
+      </c>
+      <c r="E8" s="79" t="inlineStr">
+        <is>
+          <t>【01+02】① C：CC 全量分批迁移（600~800 有效表）+ 增量常态化 ② A：范围最终确认【07】③ C：模板库（MySQL+文件源）+ 运行监控审计 ④ D：连接管理界面【06】⑤ D：合规报表（等保/个保法对照）⑥ E：合规口径验证【08】⑦ B：行级隔离验证</t>
+        </is>
+      </c>
+      <c r="F8" s="109" t="inlineStr">
+        <is>
+          <t>★ CC 全量对账 100% + 新数据源 30 分钟接入 + 越权全拦截</t>
+        </is>
+      </c>
+      <c r="G8" s="80" t="inlineStr">
+        <is>
+          <t>全量迁移时长不可控；逐批对账耗时；报表口径偏差</t>
+        </is>
+      </c>
+      <c r="H8" s="110" t="inlineStr">
+        <is>
+          <t>① CC 数据量实测 ② 迁移窗口 ③ 合规报表口径签字人</t>
+        </is>
+      </c>
       <c r="I8" s="59" t="n"/>
     </row>
-    <row r="9" ht="120" customHeight="1">
-      <c r="A9" s="72" t="inlineStr">
+    <row r="9" ht="122" customHeight="1">
+      <c r="A9" s="107" t="inlineStr">
+        <is>
+          <t>Release 1
+系统上线</t>
+        </is>
+      </c>
+      <c r="B9" s="114" t="inlineStr">
         <is>
           <t>Sprint 4
-UAT+生产部署</t>
-        </is>
-      </c>
-      <c r="B9" s="64" t="inlineStr">
+功能收口+就绪</t>
+        </is>
+      </c>
+      <c r="C9" s="64" t="inlineStr">
         <is>
           <t>W9~W10</t>
         </is>
       </c>
-      <c r="C9" s="65" t="inlineStr">
-        <is>
-          <t>生产部署 + UAT + 安全评审 + 文档审批</t>
-        </is>
-      </c>
-      <c r="D9" s="66" t="inlineStr">
-        <is>
-          <t>① B：生产发布（服务 Helm + UC 权限/掩码/生命周期/驻留核查生产版）+ 安全评审材料 ② C：CC 生产全量迁移执行 + 生产 Jobs（增量/Compaction/处置）③ D：生产部署验证 + 监控接入 + 安全四门禁生产终检（SAST/依赖/密钥/镜像全过 + 渗透配合）④ A：UAT 主持（8 域核心场景：迁移对账/检索/预览导出/脱敏/处置/Legal Hold/审计报表/SSO）+ 需求冻结 ⑤ E：7 套文档终版（用户/运维/架构/详细设计×3/接口/数据字典）+ 审批材料包提交</t>
-        </is>
-      </c>
-      <c r="E9" s="66" t="inlineStr">
-        <is>
-          <t>① 生产环境 8 域功能全通 ② UAT 报告（业务方签字）③ 安全评审通过 ④ 审批材料提交受理</t>
-        </is>
-      </c>
-      <c r="F9" s="67" t="inlineStr">
-        <is>
-          <t>UAT 业务方配合度；CC 生产迁移时长（TB 级可能跨周末）；安全评审整改返工</t>
-        </is>
-      </c>
-      <c r="G9" s="68" t="inlineStr">
-        <is>
-          <t>① UAT 签字人 ② 生产域名/证书 ③ 审批流程周期 ④ CC 生产迁移停机窗口</t>
-        </is>
-      </c>
-      <c r="H9" s="59" t="n"/>
+      <c r="D9" s="76" t="inlineStr">
+        <is>
+          <t>功能收口 + 上线就绪（准备全部前移，不含上线动作）</t>
+        </is>
+      </c>
+      <c r="E9" s="79" t="inlineStr">
+        <is>
+          <t>【功能收口 W9】① 全员：功能打磨/性能优化/遗留 Bug 清零 + 全量回归（S1~S4 全功能）【上线就绪 W9~10】② B：🤖生产发布包（Helm 生产 values + UC 权限/掩码/生命周期/驻留 生产脚本，一键发布就绪）③ E：文档 80%（用户/运维/字典/架构图更新）+ 🤖审批材料起稿 ④ W10：UAT 预演（Staging 8 域走查，业务方提前介入）+ UAT 脚本定稿 ⑤ D：安全终检（四门禁生产版+渗透配合）+ 监控告警就绪 ⑥ C：生产迁移预跑 + 窗口预约 ⑦ W10 末：上线就绪检查（发布包/材料/预演/回退预案 全绿）</t>
+        </is>
+      </c>
+      <c r="F9" s="109" t="inlineStr">
+        <is>
+          <t>★ W10 末：上线就绪检查 100% 通过（W11 上线的前置条件）</t>
+        </is>
+      </c>
+      <c r="G9" s="80" t="inlineStr">
+        <is>
+          <t>就绪检查不过则 W11 顺延；UAT 预演需业务方排期；渗透测试排期</t>
+        </is>
+      </c>
+      <c r="H9" s="110" t="inlineStr">
+        <is>
+          <t>① UAT 预演排期 ② 渗透窗口 ③ 生产迁移窗口（W10 晚预约）④ 就绪检查 Checklist 签字人</t>
+        </is>
+      </c>
       <c r="I9" s="59" t="n"/>
     </row>
-    <row r="10" ht="120" customHeight="1">
-      <c r="A10" s="73" t="inlineStr">
+    <row r="10" ht="122" customHeight="1">
+      <c r="A10" s="107" t="inlineStr">
+        <is>
+          <t>Release 1
+系统上线</t>
+        </is>
+      </c>
+      <c r="B10" s="115" t="inlineStr">
         <is>
           <t>Sprint 5
-上线</t>
-        </is>
-      </c>
-      <c r="B10" s="64" t="inlineStr">
-        <is>
-          <t>W11~W12</t>
-        </is>
-      </c>
-      <c r="C10" s="65" t="inlineStr">
-        <is>
-          <t>Go-Live + 上线保障 + 收尾（无知识转移/项目关闭）</t>
-        </is>
-      </c>
-      <c r="D10" s="66" t="inlineStr">
-        <is>
-          <t>① W11：Go/No-Go 决策 → 上线执行（发布编排/验证点/回退预案）→ 48h 值守（增量作业/查询性能/审计正常）② W11：A：用户反馈分诊；B/C/D：生产问题快速修复；E：上线验证报告 ③ W12：上线后稳定运行（增量/处置/检索/审计全正常）+ 遗留问题清零 + 交付物最终归档（文档包 + 培训视频 + 版本 tag）④ W12 末：项目结束</t>
-        </is>
-      </c>
-      <c r="E10" s="66" t="inlineStr">
-        <is>
-          <t>① 上线成功 + 稳定运行 7 天无 P1 事故 ② 交付物清单全部归档 ③ 项目收尾确认</t>
-        </is>
-      </c>
-      <c r="F10" s="67" t="inlineStr">
-        <is>
-          <t>上线首周 P1 事故；CC 增量链路稳定性；遗留 Bug 上线后暴露</t>
-        </is>
-      </c>
-      <c r="G10" s="68" t="inlineStr">
-        <is>
-          <t>① Go-Live 窗口（建议 W11 周二）② P1 事故响应 SLA ③ 上线后支持期多久（建议含在 W12 内）</t>
-        </is>
-      </c>
-      <c r="H10" s="59" t="n"/>
+上线+收尾</t>
+        </is>
+      </c>
+      <c r="C10" s="64" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="D10" s="76" t="inlineStr">
+        <is>
+          <t>上线周：发布 → UAT → Go-Live（集中一周，仅执行）</t>
+        </is>
+      </c>
+      <c r="E10" s="79" t="inlineStr">
+        <is>
+          <t>① 生产发布执行（DevOps Environments 审批，就绪包一键发布）② CC 生产全量迁移收尾（预跑后增量补齐 + 对账）③ UAT 正式执行（8 域场景，业务方签字）④ P1 问题当日清 ⑤ 审批材料提交 ⑥ Go-Live 决策 + 上线 + 48h 值守（全员）</t>
+        </is>
+      </c>
+      <c r="F10" s="109" t="inlineStr">
+        <is>
+          <t>★ W11：Go-Live + UAT 签字 + 审批受理 → Release 1 交付</t>
+        </is>
+      </c>
+      <c r="G10" s="80" t="inlineStr">
+        <is>
+          <t>一周内完成发布+UAT+上线节奏紧：强依赖 W10 就绪检查通过；生产迁移建议 W10 晚启动</t>
+        </is>
+      </c>
+      <c r="H10" s="110" t="inlineStr">
+        <is>
+          <t>① Go-Live 窗口（建议 W11 周二）② P1 响应 SLA ③ 审批受理时长</t>
+        </is>
+      </c>
       <c r="I10" s="59" t="n"/>
     </row>
-    <row r="11">
-      <c r="A11" s="59" t="n"/>
-      <c r="B11" s="59" t="n"/>
-      <c r="C11" s="59" t="n"/>
-      <c r="D11" s="59" t="n"/>
-      <c r="E11" s="59" t="n"/>
-      <c r="F11" s="59" t="n"/>
-      <c r="G11" s="59" t="n"/>
-      <c r="H11" s="59" t="n"/>
+    <row r="11" ht="122" customHeight="1">
+      <c r="A11" s="116" t="inlineStr">
+        <is>
+          <t>Release 2
+文档交付与收尾</t>
+        </is>
+      </c>
+      <c r="B11" s="115" t="inlineStr">
+        <is>
+          <t>Sprint 5
+上线+收尾</t>
+        </is>
+      </c>
+      <c r="C11" s="64" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="D11" s="76" t="inlineStr">
+        <is>
+          <t>文档终版 + 稳定确认 + 收尾（Release 2）</t>
+        </is>
+      </c>
+      <c r="E11" s="79" t="inlineStr">
+        <is>
+          <t>① E：文档终审（7 套：用户/运维/架构×4/详细设计×3/接口/数据字典 + 审批包）② 全员：上线后一周稳定性观察（增量/处置/检索/审计全正常）③ 遗留问题清零 + 交付物版本 tag（代码/脚本/文档）④ E：上线验证与稳定性报告 ⑤ 项目结束（无知识转移/项目关闭环节）</t>
+        </is>
+      </c>
+      <c r="F11" s="109" t="inlineStr">
+        <is>
+          <t>★ W12：稳定运行确认 + 交付物归档 → 项目结束</t>
+        </is>
+      </c>
+      <c r="G11" s="80" t="inlineStr">
+        <is>
+          <t>上线首周 P1；文档确认排期；若 W11 顺延则本周压缩</t>
+        </is>
+      </c>
+      <c r="H11" s="110" t="inlineStr">
+        <is>
+          <t>① 文档确认签字人 ② 上线后支持期（含在 W12 内）</t>
+        </is>
+      </c>
       <c r="I11" s="59" t="n"/>
     </row>
     <row r="12">
@@ -2578,48 +2777,36 @@
       <c r="H12" s="59" t="n"/>
       <c r="I12" s="59" t="n"/>
     </row>
-    <row r="13">
-      <c r="A13" s="59" t="n"/>
-      <c r="B13" s="59" t="n"/>
-      <c r="C13" s="59" t="n"/>
-      <c r="D13" s="59" t="n"/>
-      <c r="E13" s="59" t="n"/>
-      <c r="F13" s="59" t="n"/>
-      <c r="G13" s="59" t="n"/>
-      <c r="H13" s="59" t="n"/>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="117" t="inlineStr">
+        <is>
+          <t>双 Release：R1（W1~W11）交付可上线的系统——W1~W10 功能与就绪、W11 一周集中上线；R2（W12）文档终版+稳定确认+归档即项目结束</t>
+        </is>
+      </c>
       <c r="I13" s="59" t="n"/>
     </row>
-    <row r="14">
-      <c r="A14" s="59" t="n"/>
-      <c r="B14" s="59" t="n"/>
-      <c r="C14" s="59" t="n"/>
-      <c r="D14" s="59" t="n"/>
-      <c r="E14" s="59" t="n"/>
-      <c r="F14" s="59" t="n"/>
-      <c r="G14" s="59" t="n"/>
-      <c r="H14" s="59" t="n"/>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="117" t="inlineStr">
+        <is>
+          <t>上线压缩依据：原 W9~W10 的生产部署/UAT/文档冲刺全部改为"准备"（发布包/材料/预演/预跑在 W9~10 完成），W11 仅执行，消除重叠</t>
+        </is>
+      </c>
       <c r="I14" s="59" t="n"/>
     </row>
-    <row r="15">
-      <c r="A15" s="59" t="n"/>
-      <c r="B15" s="59" t="n"/>
-      <c r="C15" s="59" t="n"/>
-      <c r="D15" s="59" t="n"/>
-      <c r="E15" s="59" t="n"/>
-      <c r="F15" s="59" t="n"/>
-      <c r="G15" s="59" t="n"/>
-      <c r="H15" s="59" t="n"/>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="117" t="inlineStr">
+        <is>
+          <t>W10 末就绪检查是 W11 上线的硬前置：发布包/审批材料/UAT 预演/回退预案全绿才上线；不过则顺延（压缩 R2）</t>
+        </is>
+      </c>
       <c r="I15" s="59" t="n"/>
     </row>
-    <row r="16">
-      <c r="A16" s="59" t="n"/>
-      <c r="B16" s="59" t="n"/>
-      <c r="C16" s="59" t="n"/>
-      <c r="D16" s="59" t="n"/>
-      <c r="E16" s="59" t="n"/>
-      <c r="F16" s="59" t="n"/>
-      <c r="G16" s="59" t="n"/>
-      <c r="H16" s="59" t="n"/>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="117" t="inlineStr">
+        <is>
+          <t>团队与口径不变：4.5 人（A 需求 50% + B/C/D/E 全职）· CC 单系统验证 · Azure DevOps CI/CD · 上线即结束</t>
+        </is>
+      </c>
       <c r="I16" s="59" t="n"/>
     </row>
     <row r="17">
@@ -2974,7 +3161,443 @@
       <c r="H48" s="59" t="n"/>
       <c r="I48" s="59" t="n"/>
     </row>
+    <row r="49">
+      <c r="A49" s="59" t="n"/>
+      <c r="B49" s="59" t="n"/>
+      <c r="C49" s="59" t="n"/>
+      <c r="D49" s="59" t="n"/>
+      <c r="E49" s="59" t="n"/>
+      <c r="F49" s="59" t="n"/>
+      <c r="G49" s="59" t="n"/>
+      <c r="H49" s="59" t="n"/>
+      <c r="I49" s="59" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="59" t="n"/>
+      <c r="B50" s="59" t="n"/>
+      <c r="C50" s="59" t="n"/>
+      <c r="D50" s="59" t="n"/>
+      <c r="E50" s="59" t="n"/>
+      <c r="F50" s="59" t="n"/>
+      <c r="G50" s="59" t="n"/>
+      <c r="H50" s="59" t="n"/>
+      <c r="I50" s="59" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="59" t="n"/>
+      <c r="B51" s="59" t="n"/>
+      <c r="C51" s="59" t="n"/>
+      <c r="D51" s="59" t="n"/>
+      <c r="E51" s="59" t="n"/>
+      <c r="F51" s="59" t="n"/>
+      <c r="G51" s="59" t="n"/>
+      <c r="H51" s="59" t="n"/>
+      <c r="I51" s="59" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="59" t="n"/>
+      <c r="B52" s="59" t="n"/>
+      <c r="C52" s="59" t="n"/>
+      <c r="D52" s="59" t="n"/>
+      <c r="E52" s="59" t="n"/>
+      <c r="F52" s="59" t="n"/>
+      <c r="G52" s="59" t="n"/>
+      <c r="H52" s="59" t="n"/>
+      <c r="I52" s="59" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="59" t="n"/>
+      <c r="B53" s="59" t="n"/>
+      <c r="C53" s="59" t="n"/>
+      <c r="D53" s="59" t="n"/>
+      <c r="E53" s="59" t="n"/>
+      <c r="F53" s="59" t="n"/>
+      <c r="G53" s="59" t="n"/>
+      <c r="H53" s="59" t="n"/>
+      <c r="I53" s="59" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="59" t="n"/>
+      <c r="B54" s="59" t="n"/>
+      <c r="C54" s="59" t="n"/>
+      <c r="D54" s="59" t="n"/>
+      <c r="E54" s="59" t="n"/>
+      <c r="F54" s="59" t="n"/>
+      <c r="G54" s="59" t="n"/>
+      <c r="H54" s="59" t="n"/>
+      <c r="I54" s="59" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="59" t="n"/>
+      <c r="B55" s="59" t="n"/>
+      <c r="C55" s="59" t="n"/>
+      <c r="D55" s="59" t="n"/>
+      <c r="E55" s="59" t="n"/>
+      <c r="F55" s="59" t="n"/>
+      <c r="G55" s="59" t="n"/>
+      <c r="H55" s="59" t="n"/>
+      <c r="I55" s="59" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="59" t="n"/>
+      <c r="B56" s="59" t="n"/>
+      <c r="C56" s="59" t="n"/>
+      <c r="D56" s="59" t="n"/>
+      <c r="E56" s="59" t="n"/>
+      <c r="F56" s="59" t="n"/>
+      <c r="G56" s="59" t="n"/>
+      <c r="H56" s="59" t="n"/>
+      <c r="I56" s="59" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="59" t="n"/>
+      <c r="B57" s="59" t="n"/>
+      <c r="C57" s="59" t="n"/>
+      <c r="D57" s="59" t="n"/>
+      <c r="E57" s="59" t="n"/>
+      <c r="F57" s="59" t="n"/>
+      <c r="G57" s="59" t="n"/>
+      <c r="H57" s="59" t="n"/>
+      <c r="I57" s="59" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="59" t="n"/>
+      <c r="B58" s="59" t="n"/>
+      <c r="C58" s="59" t="n"/>
+      <c r="D58" s="59" t="n"/>
+      <c r="E58" s="59" t="n"/>
+      <c r="F58" s="59" t="n"/>
+      <c r="G58" s="59" t="n"/>
+      <c r="H58" s="59" t="n"/>
+      <c r="I58" s="59" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="59" t="n"/>
+      <c r="B59" s="59" t="n"/>
+      <c r="C59" s="59" t="n"/>
+      <c r="D59" s="59" t="n"/>
+      <c r="E59" s="59" t="n"/>
+      <c r="F59" s="59" t="n"/>
+      <c r="G59" s="59" t="n"/>
+      <c r="H59" s="59" t="n"/>
+      <c r="I59" s="59" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="59" t="n"/>
+      <c r="B60" s="59" t="n"/>
+      <c r="C60" s="59" t="n"/>
+      <c r="D60" s="59" t="n"/>
+      <c r="E60" s="59" t="n"/>
+      <c r="F60" s="59" t="n"/>
+      <c r="G60" s="59" t="n"/>
+      <c r="H60" s="59" t="n"/>
+      <c r="I60" s="59" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="59" t="n"/>
+      <c r="B61" s="59" t="n"/>
+      <c r="C61" s="59" t="n"/>
+      <c r="D61" s="59" t="n"/>
+      <c r="E61" s="59" t="n"/>
+      <c r="F61" s="59" t="n"/>
+      <c r="G61" s="59" t="n"/>
+      <c r="H61" s="59" t="n"/>
+      <c r="I61" s="59" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="59" t="n"/>
+      <c r="B62" s="59" t="n"/>
+      <c r="C62" s="59" t="n"/>
+      <c r="D62" s="59" t="n"/>
+      <c r="E62" s="59" t="n"/>
+      <c r="F62" s="59" t="n"/>
+      <c r="G62" s="59" t="n"/>
+      <c r="H62" s="59" t="n"/>
+      <c r="I62" s="59" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="59" t="n"/>
+      <c r="B63" s="59" t="n"/>
+      <c r="C63" s="59" t="n"/>
+      <c r="D63" s="59" t="n"/>
+      <c r="E63" s="59" t="n"/>
+      <c r="F63" s="59" t="n"/>
+      <c r="G63" s="59" t="n"/>
+      <c r="H63" s="59" t="n"/>
+      <c r="I63" s="59" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="59" t="n"/>
+      <c r="B64" s="59" t="n"/>
+      <c r="C64" s="59" t="n"/>
+      <c r="D64" s="59" t="n"/>
+      <c r="E64" s="59" t="n"/>
+      <c r="F64" s="59" t="n"/>
+      <c r="G64" s="59" t="n"/>
+      <c r="H64" s="59" t="n"/>
+      <c r="I64" s="59" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="59" t="n"/>
+      <c r="B65" s="59" t="n"/>
+      <c r="C65" s="59" t="n"/>
+      <c r="D65" s="59" t="n"/>
+      <c r="E65" s="59" t="n"/>
+      <c r="F65" s="59" t="n"/>
+      <c r="G65" s="59" t="n"/>
+      <c r="H65" s="59" t="n"/>
+      <c r="I65" s="59" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="59" t="n"/>
+      <c r="B66" s="59" t="n"/>
+      <c r="C66" s="59" t="n"/>
+      <c r="D66" s="59" t="n"/>
+      <c r="E66" s="59" t="n"/>
+      <c r="F66" s="59" t="n"/>
+      <c r="G66" s="59" t="n"/>
+      <c r="H66" s="59" t="n"/>
+      <c r="I66" s="59" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="59" t="n"/>
+      <c r="B67" s="59" t="n"/>
+      <c r="C67" s="59" t="n"/>
+      <c r="D67" s="59" t="n"/>
+      <c r="E67" s="59" t="n"/>
+      <c r="F67" s="59" t="n"/>
+      <c r="G67" s="59" t="n"/>
+      <c r="H67" s="59" t="n"/>
+      <c r="I67" s="59" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="59" t="n"/>
+      <c r="B68" s="59" t="n"/>
+      <c r="C68" s="59" t="n"/>
+      <c r="D68" s="59" t="n"/>
+      <c r="E68" s="59" t="n"/>
+      <c r="F68" s="59" t="n"/>
+      <c r="G68" s="59" t="n"/>
+      <c r="H68" s="59" t="n"/>
+      <c r="I68" s="59" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="59" t="n"/>
+      <c r="B69" s="59" t="n"/>
+      <c r="C69" s="59" t="n"/>
+      <c r="D69" s="59" t="n"/>
+      <c r="E69" s="59" t="n"/>
+      <c r="F69" s="59" t="n"/>
+      <c r="G69" s="59" t="n"/>
+      <c r="H69" s="59" t="n"/>
+      <c r="I69" s="59" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="59" t="n"/>
+      <c r="B70" s="59" t="n"/>
+      <c r="C70" s="59" t="n"/>
+      <c r="D70" s="59" t="n"/>
+      <c r="E70" s="59" t="n"/>
+      <c r="F70" s="59" t="n"/>
+      <c r="G70" s="59" t="n"/>
+      <c r="H70" s="59" t="n"/>
+      <c r="I70" s="59" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="59" t="n"/>
+      <c r="B71" s="59" t="n"/>
+      <c r="C71" s="59" t="n"/>
+      <c r="D71" s="59" t="n"/>
+      <c r="E71" s="59" t="n"/>
+      <c r="F71" s="59" t="n"/>
+      <c r="G71" s="59" t="n"/>
+      <c r="H71" s="59" t="n"/>
+      <c r="I71" s="59" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="59" t="n"/>
+      <c r="B72" s="59" t="n"/>
+      <c r="C72" s="59" t="n"/>
+      <c r="D72" s="59" t="n"/>
+      <c r="E72" s="59" t="n"/>
+      <c r="F72" s="59" t="n"/>
+      <c r="G72" s="59" t="n"/>
+      <c r="H72" s="59" t="n"/>
+      <c r="I72" s="59" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="59" t="n"/>
+      <c r="B73" s="59" t="n"/>
+      <c r="C73" s="59" t="n"/>
+      <c r="D73" s="59" t="n"/>
+      <c r="E73" s="59" t="n"/>
+      <c r="F73" s="59" t="n"/>
+      <c r="G73" s="59" t="n"/>
+      <c r="H73" s="59" t="n"/>
+      <c r="I73" s="59" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="59" t="n"/>
+      <c r="B74" s="59" t="n"/>
+      <c r="C74" s="59" t="n"/>
+      <c r="D74" s="59" t="n"/>
+      <c r="E74" s="59" t="n"/>
+      <c r="F74" s="59" t="n"/>
+      <c r="G74" s="59" t="n"/>
+      <c r="H74" s="59" t="n"/>
+      <c r="I74" s="59" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="59" t="n"/>
+      <c r="B75" s="59" t="n"/>
+      <c r="C75" s="59" t="n"/>
+      <c r="D75" s="59" t="n"/>
+      <c r="E75" s="59" t="n"/>
+      <c r="F75" s="59" t="n"/>
+      <c r="G75" s="59" t="n"/>
+      <c r="H75" s="59" t="n"/>
+      <c r="I75" s="59" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="59" t="n"/>
+      <c r="B76" s="59" t="n"/>
+      <c r="C76" s="59" t="n"/>
+      <c r="D76" s="59" t="n"/>
+      <c r="E76" s="59" t="n"/>
+      <c r="F76" s="59" t="n"/>
+      <c r="G76" s="59" t="n"/>
+      <c r="H76" s="59" t="n"/>
+      <c r="I76" s="59" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="59" t="n"/>
+      <c r="B77" s="59" t="n"/>
+      <c r="C77" s="59" t="n"/>
+      <c r="D77" s="59" t="n"/>
+      <c r="E77" s="59" t="n"/>
+      <c r="F77" s="59" t="n"/>
+      <c r="G77" s="59" t="n"/>
+      <c r="H77" s="59" t="n"/>
+      <c r="I77" s="59" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="59" t="n"/>
+      <c r="B78" s="59" t="n"/>
+      <c r="C78" s="59" t="n"/>
+      <c r="D78" s="59" t="n"/>
+      <c r="E78" s="59" t="n"/>
+      <c r="F78" s="59" t="n"/>
+      <c r="G78" s="59" t="n"/>
+      <c r="H78" s="59" t="n"/>
+      <c r="I78" s="59" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="59" t="n"/>
+      <c r="B79" s="59" t="n"/>
+      <c r="C79" s="59" t="n"/>
+      <c r="D79" s="59" t="n"/>
+      <c r="E79" s="59" t="n"/>
+      <c r="F79" s="59" t="n"/>
+      <c r="G79" s="59" t="n"/>
+      <c r="H79" s="59" t="n"/>
+      <c r="I79" s="59" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="59" t="n"/>
+      <c r="B80" s="59" t="n"/>
+      <c r="C80" s="59" t="n"/>
+      <c r="D80" s="59" t="n"/>
+      <c r="E80" s="59" t="n"/>
+      <c r="F80" s="59" t="n"/>
+      <c r="G80" s="59" t="n"/>
+      <c r="H80" s="59" t="n"/>
+      <c r="I80" s="59" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="59" t="n"/>
+      <c r="B81" s="59" t="n"/>
+      <c r="C81" s="59" t="n"/>
+      <c r="D81" s="59" t="n"/>
+      <c r="E81" s="59" t="n"/>
+      <c r="F81" s="59" t="n"/>
+      <c r="G81" s="59" t="n"/>
+      <c r="H81" s="59" t="n"/>
+      <c r="I81" s="59" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="59" t="n"/>
+      <c r="B82" s="59" t="n"/>
+      <c r="C82" s="59" t="n"/>
+      <c r="D82" s="59" t="n"/>
+      <c r="E82" s="59" t="n"/>
+      <c r="F82" s="59" t="n"/>
+      <c r="G82" s="59" t="n"/>
+      <c r="H82" s="59" t="n"/>
+      <c r="I82" s="59" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="59" t="n"/>
+      <c r="B83" s="59" t="n"/>
+      <c r="C83" s="59" t="n"/>
+      <c r="D83" s="59" t="n"/>
+      <c r="E83" s="59" t="n"/>
+      <c r="F83" s="59" t="n"/>
+      <c r="G83" s="59" t="n"/>
+      <c r="H83" s="59" t="n"/>
+      <c r="I83" s="59" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="59" t="n"/>
+      <c r="B84" s="59" t="n"/>
+      <c r="C84" s="59" t="n"/>
+      <c r="D84" s="59" t="n"/>
+      <c r="E84" s="59" t="n"/>
+      <c r="F84" s="59" t="n"/>
+      <c r="G84" s="59" t="n"/>
+      <c r="H84" s="59" t="n"/>
+      <c r="I84" s="59" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="59" t="n"/>
+      <c r="B85" s="59" t="n"/>
+      <c r="C85" s="59" t="n"/>
+      <c r="D85" s="59" t="n"/>
+      <c r="E85" s="59" t="n"/>
+      <c r="F85" s="59" t="n"/>
+      <c r="G85" s="59" t="n"/>
+      <c r="H85" s="59" t="n"/>
+      <c r="I85" s="59" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="59" t="n"/>
+      <c r="B86" s="59" t="n"/>
+      <c r="C86" s="59" t="n"/>
+      <c r="D86" s="59" t="n"/>
+      <c r="E86" s="59" t="n"/>
+      <c r="F86" s="59" t="n"/>
+      <c r="G86" s="59" t="n"/>
+      <c r="H86" s="59" t="n"/>
+      <c r="I86" s="59" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="59" t="n"/>
+      <c r="B87" s="59" t="n"/>
+      <c r="C87" s="59" t="n"/>
+      <c r="D87" s="59" t="n"/>
+      <c r="E87" s="59" t="n"/>
+      <c r="F87" s="59" t="n"/>
+      <c r="G87" s="59" t="n"/>
+      <c r="H87" s="59" t="n"/>
+      <c r="I87" s="59" t="n"/>
+    </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A14:H14"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2985,10 +3608,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I174"/>
+  <dimension ref="A1:J234"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
@@ -2997,12 +3620,16 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.4" customHeight="1">
-      <c r="A1" s="58" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>周计划明细（V9：双 Release · R1 功能期 W1~W10 → W11 上线周 → R2 W12 收尾）</t>
+        </is>
+      </c>
+      <c r="B1" s="58" t="inlineStr">
         <is>
           <t>周计划明细（V8：按 8 大功能域编号 · CC 单系统贯穿 · 上线即结束）</t>
         </is>
       </c>
-      <c r="B1" s="59" t="n"/>
       <c r="C1" s="59" t="n"/>
       <c r="D1" s="59" t="n"/>
       <c r="E1" s="59" t="n"/>
@@ -3010,10 +3637,10 @@
       <c r="G1" s="59" t="n"/>
       <c r="H1" s="59" t="n"/>
       <c r="I1" s="59" t="n"/>
+      <c r="J1" s="59" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="74" t="n"/>
-      <c r="B2" s="59" t="n"/>
+      <c r="B2" s="74" t="n"/>
       <c r="C2" s="59" t="n"/>
       <c r="D2" s="59" t="n"/>
       <c r="E2" s="59" t="n"/>
@@ -3021,9 +3648,9 @@
       <c r="G2" s="59" t="n"/>
       <c r="H2" s="59" t="n"/>
       <c r="I2" s="59" t="n"/>
+      <c r="J2" s="59" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="59" t="n"/>
       <c r="B3" s="59" t="n"/>
       <c r="C3" s="59" t="n"/>
       <c r="D3" s="59" t="n"/>
@@ -3032,3664 +3659,4602 @@
       <c r="G3" s="59" t="n"/>
       <c r="H3" s="59" t="n"/>
       <c r="I3" s="59" t="n"/>
+      <c r="J3" s="59" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="62" t="inlineStr">
         <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="B4" s="62" t="inlineStr">
+        <is>
           <t>Sprint</t>
         </is>
       </c>
-      <c r="B4" s="62" t="inlineStr">
+      <c r="C4" s="62" t="inlineStr">
         <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="C4" s="62" t="inlineStr">
+      <c r="D4" s="62" t="inlineStr">
         <is>
           <t>角色</t>
         </is>
       </c>
-      <c r="D4" s="62" t="inlineStr">
+      <c r="E4" s="62" t="inlineStr">
         <is>
           <t>任务</t>
         </is>
       </c>
-      <c r="E4" s="62" t="inlineStr">
+      <c r="F4" s="62" t="inlineStr">
         <is>
           <t>产出物 / 验收标准</t>
         </is>
       </c>
-      <c r="F4" s="62" t="inlineStr">
+      <c r="G4" s="62" t="inlineStr">
         <is>
           <t>依赖/阻塞</t>
         </is>
       </c>
-      <c r="G4" s="59" t="n"/>
       <c r="H4" s="59" t="n"/>
       <c r="I4" s="59" t="n"/>
+      <c r="J4" s="59" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="75" t="inlineStr">
+      <c r="A5" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B5" s="75" t="inlineStr">
         <is>
           <t>Sprint 0</t>
         </is>
       </c>
-      <c r="B5" s="76" t="inlineStr">
+      <c r="C5" s="76" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="C5" s="77" t="inlineStr">
+      <c r="D5" s="77" t="inlineStr">
         <is>
           <t>A·需求(50%)</t>
         </is>
       </c>
-      <c r="D5" s="78" t="inlineStr">
+      <c r="E5" s="78" t="inlineStr">
         <is>
           <t>• 【8 域需求访谈】业务方×2 场（检索/导出/审计场景）+ 合规法务×1 场（保留期/PII/Legal Hold）</t>
         </is>
       </c>
-      <c r="E5" s="79" t="inlineStr">
+      <c r="F5" s="79" t="inlineStr">
         <is>
           <t>BRD 初稿可评审；CC 剔除规则确认</t>
         </is>
       </c>
-      <c r="F5" s="80" t="inlineStr">
+      <c r="G5" s="80" t="inlineStr">
         <is>
           <t>业务方访谈排期</t>
         </is>
       </c>
-      <c r="G5" s="59" t="n"/>
       <c r="H5" s="59" t="n"/>
       <c r="I5" s="59" t="n"/>
+      <c r="J5" s="59" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="81" t="n"/>
       <c r="B6" s="81" t="n"/>
-      <c r="C6" s="82" t="n"/>
-      <c r="D6" s="78" t="inlineStr">
+      <c r="C6" s="81" t="n"/>
+      <c r="D6" s="82" t="n"/>
+      <c r="E6" s="78" t="inlineStr">
         <is>
           <t>• 【BRD】数据流图（源系统→湖仓→查询/处置）+ 归档范围矩阵 + PII 字段分级清单</t>
         </is>
       </c>
-      <c r="E6" s="81" t="n"/>
       <c r="F6" s="81" t="n"/>
-      <c r="G6" s="59" t="n"/>
+      <c r="G6" s="81" t="n"/>
       <c r="H6" s="59" t="n"/>
       <c r="I6" s="59" t="n"/>
+      <c r="J6" s="59" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="81" t="n"/>
       <c r="B7" s="81" t="n"/>
-      <c r="C7" s="82" t="n"/>
-      <c r="D7" s="78" t="inlineStr">
+      <c r="C7" s="81" t="n"/>
+      <c r="D7" s="82" t="n"/>
+      <c r="E7" s="78" t="inlineStr">
         <is>
           <t>• 【02】"实时"指标确认（分钟级 or 小时级，直接影响技术方案）</t>
         </is>
       </c>
-      <c r="E7" s="81" t="n"/>
       <c r="F7" s="81" t="n"/>
-      <c r="G7" s="59" t="n"/>
+      <c r="G7" s="81" t="n"/>
       <c r="H7" s="59" t="n"/>
       <c r="I7" s="59" t="n"/>
+      <c r="J7" s="59" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="81" t="n"/>
       <c r="B8" s="81" t="n"/>
-      <c r="C8" s="82" t="n"/>
-      <c r="D8" s="78" t="inlineStr">
+      <c r="C8" s="81" t="n"/>
+      <c r="D8" s="82" t="n"/>
+      <c r="E8" s="78" t="inlineStr">
         <is>
           <t>• CC 接入范围初定：1253 表垃圾表剔除标准（bak/temp/_Old 规则）与业务方对齐</t>
         </is>
       </c>
-      <c r="E8" s="81" t="n"/>
       <c r="F8" s="81" t="n"/>
-      <c r="G8" s="59" t="n"/>
+      <c r="G8" s="81" t="n"/>
       <c r="H8" s="59" t="n"/>
       <c r="I8" s="59" t="n"/>
+      <c r="J8" s="59" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="75" t="inlineStr">
+      <c r="A9" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B9" s="75" t="inlineStr">
         <is>
           <t>Sprint 0</t>
         </is>
       </c>
-      <c r="B9" s="76" t="inlineStr">
+      <c r="C9" s="76" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="C9" s="83" t="inlineStr">
+      <c r="D9" s="83" t="inlineStr">
         <is>
           <t>B·架构+开发</t>
         </is>
       </c>
-      <c r="D9" s="78" t="inlineStr">
+      <c r="E9" s="78" t="inlineStr">
         <is>
           <t>• 架构设计文档定稿（湖仓分层 + 数据流 + UC 授权模型 + 存储分层）</t>
         </is>
       </c>
-      <c r="E9" s="79" t="inlineStr">
+      <c r="F9" s="79" t="inlineStr">
         <is>
           <t>架构文档 V1；资源申请单已交</t>
         </is>
       </c>
-      <c r="F9" s="80" t="inlineStr">
+      <c r="G9" s="80" t="inlineStr">
         <is>
           <t>平台团队受理周期；CC 账号</t>
         </is>
       </c>
-      <c r="G9" s="59" t="n"/>
       <c r="H9" s="59" t="n"/>
       <c r="I9" s="59" t="n"/>
+      <c r="J9" s="59" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="81" t="n"/>
       <c r="B10" s="81" t="n"/>
-      <c r="C10" s="84" t="n"/>
-      <c r="D10" s="78" t="inlineStr">
+      <c r="C10" s="81" t="n"/>
+      <c r="D10" s="84" t="n"/>
+      <c r="E10" s="78" t="inlineStr">
         <is>
           <t>• 资源申请单提交平台团队（AKS 命名空间/ADLS/SQL DB/Databricks/Key Vault/AGW，区域=境内）</t>
         </is>
       </c>
-      <c r="E10" s="81" t="n"/>
       <c r="F10" s="81" t="n"/>
-      <c r="G10" s="59" t="n"/>
+      <c r="G10" s="81" t="n"/>
       <c r="H10" s="59" t="n"/>
       <c r="I10" s="59" t="n"/>
+      <c r="J10" s="59" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="81" t="n"/>
       <c r="B11" s="81" t="n"/>
-      <c r="C11" s="84" t="n"/>
-      <c r="D11" s="78" t="inlineStr">
+      <c r="C11" s="81" t="n"/>
+      <c r="D11" s="84" t="n"/>
+      <c r="E11" s="78" t="inlineStr">
         <is>
           <t>• 源库对接：CC 只读账号 + NAT 白名单申请（流程最长，W1 必须启动）</t>
         </is>
       </c>
-      <c r="E11" s="81" t="n"/>
       <c r="F11" s="81" t="n"/>
-      <c r="G11" s="59" t="n"/>
+      <c r="G11" s="81" t="n"/>
       <c r="H11" s="59" t="n"/>
       <c r="I11" s="59" t="n"/>
+      <c r="J11" s="59" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="75" t="inlineStr">
+      <c r="A12" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B12" s="75" t="inlineStr">
         <is>
           <t>Sprint 0</t>
         </is>
       </c>
-      <c r="B12" s="76" t="inlineStr">
+      <c r="C12" s="76" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="C12" s="85" t="inlineStr">
+      <c r="D12" s="85" t="inlineStr">
         <is>
           <t>C·数据工程</t>
         </is>
       </c>
-      <c r="D12" s="78" t="inlineStr">
+      <c r="E12" s="78" t="inlineStr">
         <is>
           <t>• CC 源库结构预研：1253 表 information_schema 全量扫描 + 表分类（业务表/垃圾表/附件元数据表）</t>
         </is>
       </c>
-      <c r="E12" s="79" t="inlineStr">
+      <c r="F12" s="79" t="inlineStr">
         <is>
           <t>CC 表分类清单；四层设计文档</t>
         </is>
       </c>
-      <c r="F12" s="80" t="inlineStr">
+      <c r="G12" s="80" t="inlineStr">
         <is>
           <t>CC 只读账号（B 申请中）</t>
         </is>
       </c>
-      <c r="G12" s="59" t="n"/>
       <c r="H12" s="59" t="n"/>
       <c r="I12" s="59" t="n"/>
+      <c r="J12" s="59" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="81" t="n"/>
       <c r="B13" s="81" t="n"/>
-      <c r="C13" s="86" t="n"/>
-      <c r="D13" s="78" t="inlineStr">
+      <c r="C13" s="81" t="n"/>
+      <c r="D13" s="86" t="n"/>
+      <c r="E13" s="78" t="inlineStr">
         <is>
           <t>• 四层建模设计细化（RAW→CURATED→LAKE→SERVE 转换规则与分区策略）</t>
         </is>
       </c>
-      <c r="E13" s="81" t="n"/>
       <c r="F13" s="81" t="n"/>
-      <c r="G13" s="59" t="n"/>
+      <c r="G13" s="81" t="n"/>
       <c r="H13" s="59" t="n"/>
       <c r="I13" s="59" t="n"/>
+      <c r="J13" s="59" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="81" t="n"/>
       <c r="B14" s="81" t="n"/>
-      <c r="C14" s="86" t="n"/>
-      <c r="D14" s="78" t="inlineStr">
+      <c r="C14" s="81" t="n"/>
+      <c r="D14" s="86" t="n"/>
+      <c r="E14" s="78" t="inlineStr">
         <is>
           <t>• SeaTunnel 任务模板设计（元数据驱动 .conf 生成器架构）</t>
         </is>
       </c>
-      <c r="E14" s="81" t="n"/>
       <c r="F14" s="81" t="n"/>
-      <c r="G14" s="59" t="n"/>
+      <c r="G14" s="81" t="n"/>
       <c r="H14" s="59" t="n"/>
       <c r="I14" s="59" t="n"/>
+      <c r="J14" s="59" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="75" t="inlineStr">
+      <c r="A15" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B15" s="75" t="inlineStr">
         <is>
           <t>Sprint 0</t>
         </is>
       </c>
-      <c r="B15" s="76" t="inlineStr">
+      <c r="C15" s="76" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="C15" s="87" t="inlineStr">
+      <c r="D15" s="87" t="inlineStr">
         <is>
           <t>D·全栈+DevOps</t>
         </is>
       </c>
-      <c r="D15" s="78" t="inlineStr">
+      <c r="E15" s="78" t="inlineStr">
         <is>
           <t>• .NET 10 后端骨架（Clean Architecture + EF Core）+ React 前端骨架</t>
         </is>
       </c>
-      <c r="E15" s="79" t="inlineStr">
+      <c r="F15" s="79" t="inlineStr">
         <is>
           <t>本地可开发；CI 推镜像成功</t>
         </is>
       </c>
-      <c r="F15" s="80" t="inlineStr">
+      <c r="G15" s="80" t="inlineStr">
         <is>
           <t>平台 ACR</t>
         </is>
       </c>
-      <c r="G15" s="59" t="n"/>
       <c r="H15" s="59" t="n"/>
       <c r="I15" s="59" t="n"/>
+      <c r="J15" s="59" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="81" t="n"/>
       <c r="B16" s="81" t="n"/>
-      <c r="C16" s="88" t="n"/>
-      <c r="D16" s="78" t="inlineStr">
+      <c r="C16" s="81" t="n"/>
+      <c r="D16" s="88" t="n"/>
+      <c r="E16" s="78" t="inlineStr">
         <is>
           <t>• Docker Compose 本地开发环境（SQL Server + Azurite 模拟 ADLS）</t>
         </is>
       </c>
-      <c r="E16" s="81" t="n"/>
       <c r="F16" s="81" t="n"/>
-      <c r="G16" s="59" t="n"/>
+      <c r="G16" s="81" t="n"/>
       <c r="H16" s="59" t="n"/>
       <c r="I16" s="59" t="n"/>
+      <c r="J16" s="59" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="81" t="n"/>
       <c r="B17" s="81" t="n"/>
-      <c r="C17" s="88" t="n"/>
-      <c r="D17" s="78" t="inlineStr">
+      <c r="C17" s="81" t="n"/>
+      <c r="D17" s="88" t="n"/>
+      <c r="E17" s="78" t="inlineStr">
         <is>
           <t>• CI 骨架：Azure DevOps Pipelines build + 单测 + 推镜像（平台 ACR）</t>
         </is>
       </c>
-      <c r="E17" s="81" t="n"/>
       <c r="F17" s="81" t="n"/>
-      <c r="G17" s="59" t="n"/>
+      <c r="G17" s="81" t="n"/>
       <c r="H17" s="59" t="n"/>
       <c r="I17" s="59" t="n"/>
+      <c r="J17" s="59" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="75" t="inlineStr">
+      <c r="A18" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B18" s="75" t="inlineStr">
         <is>
           <t>Sprint 0</t>
         </is>
       </c>
-      <c r="B18" s="76" t="inlineStr">
+      <c r="C18" s="76" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="C18" s="89" t="inlineStr">
+      <c r="D18" s="89" t="inlineStr">
         <is>
           <t>E·QA+SLC文档</t>
         </is>
       </c>
-      <c r="D18" s="78" t="inlineStr">
+      <c r="E18" s="78" t="inlineStr">
         <is>
           <t>• 测试计划初稿（按 8 大功能域组织：迁移/治理/生命周期/安全/检索/合规/连接器/权限）</t>
         </is>
       </c>
-      <c r="E18" s="79" t="inlineStr">
+      <c r="F18" s="79" t="inlineStr">
         <is>
           <t>测试计划初稿；架构图×2 初稿</t>
         </is>
       </c>
-      <c r="F18" s="80" t="inlineStr">
+      <c r="G18" s="80" t="inlineStr">
         <is>
           <t>A 的 BRD 范围</t>
         </is>
       </c>
-      <c r="G18" s="59" t="n"/>
       <c r="H18" s="59" t="n"/>
       <c r="I18" s="59" t="n"/>
+      <c r="J18" s="59" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="81" t="n"/>
       <c r="B19" s="81" t="n"/>
-      <c r="C19" s="90" t="n"/>
-      <c r="D19" s="78" t="inlineStr">
+      <c r="C19" s="81" t="n"/>
+      <c r="D19" s="90" t="n"/>
+      <c r="E19" s="78" t="inlineStr">
         <is>
           <t>• 架构图初稿：系统上下文图 + 容器图</t>
         </is>
       </c>
-      <c r="E19" s="81" t="n"/>
       <c r="F19" s="81" t="n"/>
-      <c r="G19" s="59" t="n"/>
+      <c r="G19" s="81" t="n"/>
       <c r="H19" s="59" t="n"/>
       <c r="I19" s="59" t="n"/>
+      <c r="J19" s="59" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="81" t="n"/>
       <c r="B20" s="81" t="n"/>
-      <c r="C20" s="90" t="n"/>
-      <c r="D20" s="78" t="inlineStr">
+      <c r="C20" s="81" t="n"/>
+      <c r="D20" s="90" t="n"/>
+      <c r="E20" s="78" t="inlineStr">
         <is>
           <t>• 文档模板 4 套定稿（详细设计/接口/用户手册/运维手册）</t>
         </is>
       </c>
-      <c r="E20" s="81" t="n"/>
       <c r="F20" s="81" t="n"/>
-      <c r="G20" s="59" t="n"/>
+      <c r="G20" s="81" t="n"/>
       <c r="H20" s="59" t="n"/>
       <c r="I20" s="59" t="n"/>
+      <c r="J20" s="59" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="75" t="inlineStr">
+      <c r="A21" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B21" s="75" t="inlineStr">
         <is>
           <t>Sprint 0</t>
         </is>
       </c>
-      <c r="B21" s="76" t="inlineStr">
+      <c r="C21" s="76" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="C21" s="77" t="inlineStr">
+      <c r="D21" s="77" t="inlineStr">
         <is>
           <t>A·需求(50%)</t>
         </is>
       </c>
-      <c r="D21" s="78" t="inlineStr">
+      <c r="E21" s="78" t="inlineStr">
         <is>
           <t>• BRD 评审会 → 定稿签字（8 域功能清单 + 数据流图 + 保留期矩阵）</t>
         </is>
       </c>
-      <c r="E21" s="79" t="inlineStr">
+      <c r="F21" s="79" t="inlineStr">
         <is>
           <t>BRD 签字；CC 首批表清单</t>
         </is>
       </c>
-      <c r="F21" s="80" t="inlineStr">
+      <c r="G21" s="80" t="inlineStr">
         <is>
           <t>业务方到场</t>
         </is>
       </c>
-      <c r="G21" s="59" t="n"/>
       <c r="H21" s="59" t="n"/>
       <c r="I21" s="59" t="n"/>
+      <c r="J21" s="59" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="81" t="n"/>
       <c r="B22" s="81" t="n"/>
-      <c r="C22" s="82" t="n"/>
-      <c r="D22" s="78" t="inlineStr">
+      <c r="C22" s="81" t="n"/>
+      <c r="D22" s="82" t="n"/>
+      <c r="E22" s="78" t="inlineStr">
         <is>
           <t>• 用户故事地图 + Sprint 1~5 验收标准</t>
         </is>
       </c>
-      <c r="E22" s="81" t="n"/>
       <c r="F22" s="81" t="n"/>
-      <c r="G22" s="59" t="n"/>
+      <c r="G22" s="81" t="n"/>
       <c r="H22" s="59" t="n"/>
       <c r="I22" s="59" t="n"/>
+      <c r="J22" s="59" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="81" t="n"/>
       <c r="B23" s="81" t="n"/>
-      <c r="C23" s="82" t="n"/>
-      <c r="D23" s="78" t="inlineStr">
+      <c r="C23" s="81" t="n"/>
+      <c r="D23" s="82" t="n"/>
+      <c r="E23" s="78" t="inlineStr">
         <is>
           <t>• CC 首批 50 张热表清单确认（业务方勾选：高频查询表）</t>
         </is>
       </c>
-      <c r="E23" s="81" t="n"/>
       <c r="F23" s="81" t="n"/>
-      <c r="G23" s="59" t="n"/>
+      <c r="G23" s="81" t="n"/>
       <c r="H23" s="59" t="n"/>
       <c r="I23" s="59" t="n"/>
+      <c r="J23" s="59" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="75" t="inlineStr">
+      <c r="A24" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B24" s="75" t="inlineStr">
         <is>
           <t>Sprint 0</t>
         </is>
       </c>
-      <c r="B24" s="76" t="inlineStr">
+      <c r="C24" s="76" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="C24" s="83" t="inlineStr">
+      <c r="D24" s="83" t="inlineStr">
         <is>
           <t>B·架构+开发</t>
         </is>
       </c>
-      <c r="D24" s="78" t="inlineStr">
+      <c r="E24" s="78" t="inlineStr">
         <is>
           <t>• 平台交付资源验收（ADLS 读写/SQL DB/Databricks 登录/Key Vault 取密钥 逐项连通）</t>
         </is>
       </c>
-      <c r="E24" s="79" t="inlineStr">
+      <c r="F24" s="79" t="inlineStr">
         <is>
           <t>资源验收通过；UC 就绪</t>
         </is>
       </c>
-      <c r="F24" s="80" t="inlineStr">
+      <c r="G24" s="80" t="inlineStr">
         <is>
           <t>平台交付时间</t>
         </is>
       </c>
-      <c r="G24" s="59" t="n"/>
       <c r="H24" s="59" t="n"/>
       <c r="I24" s="59" t="n"/>
+      <c r="J24" s="59" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="81" t="n"/>
       <c r="B25" s="81" t="n"/>
-      <c r="C25" s="84" t="n"/>
-      <c r="D25" s="78" t="inlineStr">
+      <c r="C25" s="81" t="n"/>
+      <c r="D25" s="84" t="n"/>
+      <c r="E25" s="78" t="inlineStr">
         <is>
           <t>• UC 初始化：arch_cc catalog + GRANT 模板 + SP-query/SP-audit 服务主体</t>
         </is>
       </c>
-      <c r="E25" s="81" t="n"/>
       <c r="F25" s="81" t="n"/>
-      <c r="G25" s="59" t="n"/>
+      <c r="G25" s="81" t="n"/>
       <c r="H25" s="59" t="n"/>
       <c r="I25" s="59" t="n"/>
+      <c r="J25" s="59" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="81" t="n"/>
       <c r="B26" s="81" t="n"/>
-      <c r="C26" s="84" t="n"/>
-      <c r="D26" s="78" t="inlineStr">
+      <c r="C26" s="81" t="n"/>
+      <c r="D26" s="84" t="n"/>
+      <c r="E26" s="78" t="inlineStr">
         <is>
           <t>• 境内驻留核查 v1：全部资源区域配置确认</t>
         </is>
       </c>
-      <c r="E26" s="81" t="n"/>
       <c r="F26" s="81" t="n"/>
-      <c r="G26" s="59" t="n"/>
+      <c r="G26" s="81" t="n"/>
       <c r="H26" s="59" t="n"/>
       <c r="I26" s="59" t="n"/>
+      <c r="J26" s="59" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="75" t="inlineStr">
+      <c r="A27" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B27" s="75" t="inlineStr">
         <is>
           <t>Sprint 0</t>
         </is>
       </c>
-      <c r="B27" s="76" t="inlineStr">
+      <c r="C27" s="76" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="C27" s="85" t="inlineStr">
+      <c r="D27" s="85" t="inlineStr">
         <is>
           <t>C·数据工程</t>
         </is>
       </c>
-      <c r="D27" s="78" t="inlineStr">
+      <c r="E27" s="78" t="inlineStr">
         <is>
           <t>• SeaTunnel PoC：CC 源库抽样 10 张表 → Iceberg RAW → SQL Warehouse 可查</t>
         </is>
       </c>
-      <c r="E27" s="79" t="inlineStr">
+      <c r="F27" s="79" t="inlineStr">
         <is>
           <t>PoC 端到端成功</t>
         </is>
       </c>
-      <c r="F27" s="80" t="inlineStr">
+      <c r="G27" s="80" t="inlineStr">
         <is>
           <t>CC 账号 + 资源交付</t>
         </is>
       </c>
-      <c r="G27" s="59" t="n"/>
       <c r="H27" s="59" t="n"/>
       <c r="I27" s="59" t="n"/>
+      <c r="J27" s="59" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="81" t="n"/>
       <c r="B28" s="81" t="n"/>
-      <c r="C28" s="86" t="n"/>
-      <c r="D28" s="78" t="inlineStr">
+      <c r="C28" s="81" t="n"/>
+      <c r="D28" s="86" t="n"/>
+      <c r="E28" s="78" t="inlineStr">
         <is>
           <t>• PoC 风险记录（连接器兼容/类型映射问题清单）</t>
         </is>
       </c>
-      <c r="E28" s="81" t="n"/>
       <c r="F28" s="81" t="n"/>
-      <c r="G28" s="59" t="n"/>
+      <c r="G28" s="81" t="n"/>
       <c r="H28" s="59" t="n"/>
       <c r="I28" s="59" t="n"/>
+      <c r="J28" s="59" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="75" t="inlineStr">
+      <c r="A29" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B29" s="75" t="inlineStr">
         <is>
           <t>Sprint 0</t>
         </is>
       </c>
-      <c r="B29" s="76" t="inlineStr">
+      <c r="C29" s="76" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="C29" s="87" t="inlineStr">
+      <c r="D29" s="87" t="inlineStr">
         <is>
           <t>D·全栈+DevOps</t>
         </is>
       </c>
-      <c r="D29" s="78" t="inlineStr">
+      <c r="E29" s="78" t="inlineStr">
         <is>
           <t>• CD 流水线：Azure DevOps Environments（Dev）+ Helm 部署到平台 AKS 命名空间（服务连接走托管标识）</t>
         </is>
       </c>
-      <c r="E29" s="79" t="inlineStr">
+      <c r="F29" s="79" t="inlineStr">
         <is>
           <t>端到端自动部署；登录可走通</t>
         </is>
       </c>
-      <c r="F29" s="80" t="inlineStr">
+      <c r="G29" s="80" t="inlineStr">
         <is>
           <t>Entra ID 配置</t>
         </is>
       </c>
-      <c r="G29" s="59" t="n"/>
       <c r="H29" s="59" t="n"/>
       <c r="I29" s="59" t="n"/>
+      <c r="J29" s="59" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="81" t="n"/>
       <c r="B30" s="81" t="n"/>
-      <c r="C30" s="88" t="n"/>
-      <c r="D30" s="78" t="inlineStr">
+      <c r="C30" s="81" t="n"/>
+      <c r="D30" s="88" t="n"/>
+      <c r="E30" s="78" t="inlineStr">
         <is>
           <t>• 元数据库 35 张表 Migration + 种子数据</t>
         </is>
       </c>
-      <c r="E30" s="81" t="n"/>
       <c r="F30" s="81" t="n"/>
-      <c r="G30" s="59" t="n"/>
+      <c r="G30" s="81" t="n"/>
       <c r="H30" s="59" t="n"/>
       <c r="I30" s="59" t="n"/>
+      <c r="J30" s="59" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="81" t="n"/>
       <c r="B31" s="81" t="n"/>
-      <c r="C31" s="88" t="n"/>
-      <c r="D31" s="78" t="inlineStr">
+      <c r="C31" s="81" t="n"/>
+      <c r="D31" s="88" t="n"/>
+      <c r="E31" s="78" t="inlineStr">
         <is>
           <t>• SSO 走通：Entra ID OIDC 登录页 + 系统列表页</t>
         </is>
       </c>
-      <c r="E31" s="81" t="n"/>
       <c r="F31" s="81" t="n"/>
-      <c r="G31" s="59" t="n"/>
+      <c r="G31" s="81" t="n"/>
       <c r="H31" s="59" t="n"/>
       <c r="I31" s="59" t="n"/>
+      <c r="J31" s="59" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="75" t="inlineStr">
+      <c r="A32" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B32" s="75" t="inlineStr">
         <is>
           <t>Sprint 0</t>
         </is>
       </c>
-      <c r="B32" s="76" t="inlineStr">
+      <c r="C32" s="76" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="C32" s="89" t="inlineStr">
+      <c r="D32" s="89" t="inlineStr">
         <is>
           <t>E·QA+SLC文档</t>
         </is>
       </c>
-      <c r="D32" s="78" t="inlineStr">
+      <c r="E32" s="78" t="inlineStr">
         <is>
           <t>• 架构图完善：组件图 + 部署图（标注平台团队管理的资源边界）</t>
         </is>
       </c>
-      <c r="E32" s="79" t="inlineStr">
+      <c r="F32" s="79" t="inlineStr">
         <is>
           <t>架构图×4 初稿；UAT 清单</t>
         </is>
       </c>
-      <c r="F32" s="80" t="inlineStr"/>
-      <c r="G32" s="59" t="n"/>
+      <c r="G32" s="80" t="inlineStr"/>
       <c r="H32" s="59" t="n"/>
       <c r="I32" s="59" t="n"/>
+      <c r="J32" s="59" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="81" t="n"/>
       <c r="B33" s="81" t="n"/>
-      <c r="C33" s="90" t="n"/>
-      <c r="D33" s="78" t="inlineStr">
+      <c r="C33" s="81" t="n"/>
+      <c r="D33" s="90" t="n"/>
+      <c r="E33" s="78" t="inlineStr">
         <is>
           <t>• 接口文档初稿（API 清单 + 示例）</t>
         </is>
       </c>
-      <c r="E33" s="81" t="n"/>
       <c r="F33" s="81" t="n"/>
-      <c r="G33" s="59" t="n"/>
+      <c r="G33" s="81" t="n"/>
       <c r="H33" s="59" t="n"/>
       <c r="I33" s="59" t="n"/>
+      <c r="J33" s="59" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="81" t="n"/>
       <c r="B34" s="81" t="n"/>
-      <c r="C34" s="90" t="n"/>
-      <c r="D34" s="78" t="inlineStr">
+      <c r="C34" s="81" t="n"/>
+      <c r="D34" s="90" t="n"/>
+      <c r="E34" s="78" t="inlineStr">
         <is>
           <t>• UAT 场景清单（8 域各 1~2 场景初稿）</t>
         </is>
       </c>
-      <c r="E34" s="81" t="n"/>
       <c r="F34" s="81" t="n"/>
-      <c r="G34" s="59" t="n"/>
+      <c r="G34" s="81" t="n"/>
       <c r="H34" s="59" t="n"/>
       <c r="I34" s="59" t="n"/>
+      <c r="J34" s="59" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="91" t="inlineStr">
+      <c r="A35" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B35" s="91" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B35" s="76" t="inlineStr">
+      <c r="C35" s="76" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="C35" s="77" t="inlineStr">
+      <c r="D35" s="77" t="inlineStr">
         <is>
           <t>A·需求(50%)</t>
         </is>
       </c>
-      <c r="D35" s="78" t="inlineStr">
+      <c r="E35" s="78" t="inlineStr">
         <is>
           <t>• Sprint 2 需求澄清（增量频率/冷数据标准/Legal Hold 条件细化）</t>
         </is>
       </c>
-      <c r="E35" s="79" t="inlineStr">
+      <c r="F35" s="79" t="inlineStr">
         <is>
           <t>S2 需求就绪；PII 标记清单</t>
         </is>
       </c>
-      <c r="F35" s="80" t="inlineStr"/>
-      <c r="G35" s="59" t="n"/>
+      <c r="G35" s="80" t="inlineStr"/>
       <c r="H35" s="59" t="n"/>
       <c r="I35" s="59" t="n"/>
+      <c r="J35" s="59" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="81" t="n"/>
       <c r="B36" s="81" t="n"/>
-      <c r="C36" s="82" t="n"/>
-      <c r="D36" s="78" t="inlineStr">
+      <c r="C36" s="81" t="n"/>
+      <c r="D36" s="82" t="n"/>
+      <c r="E36" s="78" t="inlineStr">
         <is>
           <t>• CC 首批 50 表字段级确认（PII 列标记：身份证/手机号/录音索引）</t>
         </is>
       </c>
-      <c r="E36" s="81" t="n"/>
       <c r="F36" s="81" t="n"/>
-      <c r="G36" s="59" t="n"/>
+      <c r="G36" s="81" t="n"/>
       <c r="H36" s="59" t="n"/>
       <c r="I36" s="59" t="n"/>
+      <c r="J36" s="59" t="n"/>
     </row>
     <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="91" t="inlineStr">
+      <c r="A37" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B37" s="91" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B37" s="76" t="inlineStr">
+      <c r="C37" s="76" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="C37" s="83" t="inlineStr">
+      <c r="D37" s="83" t="inlineStr">
         <is>
           <t>B·架构+开发</t>
         </is>
       </c>
-      <c r="D37" s="78" t="inlineStr">
+      <c r="E37" s="78" t="inlineStr">
         <is>
           <t>• 【08】角色权限①：user/role/permission/page 四表 CRUD API + 关联表接口</t>
         </is>
       </c>
-      <c r="E37" s="79" t="inlineStr">
+      <c r="F37" s="79" t="inlineStr">
         <is>
           <t>RBAC API + 鉴权中间件提测</t>
         </is>
       </c>
-      <c r="F37" s="80" t="inlineStr"/>
-      <c r="G37" s="59" t="n"/>
+      <c r="G37" s="80" t="inlineStr"/>
       <c r="H37" s="59" t="n"/>
       <c r="I37" s="59" t="n"/>
+      <c r="J37" s="59" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="81" t="n"/>
       <c r="B38" s="81" t="n"/>
-      <c r="C38" s="84" t="n"/>
-      <c r="D38" s="78" t="inlineStr">
+      <c r="C38" s="81" t="n"/>
+      <c r="D38" s="84" t="n"/>
+      <c r="E38" s="78" t="inlineStr">
         <is>
           <t>• 【08】角色权限②：OIDC → JWT 角色 Claims → 后端鉴权中间件</t>
         </is>
       </c>
-      <c r="E38" s="81" t="n"/>
       <c r="F38" s="81" t="n"/>
-      <c r="G38" s="59" t="n"/>
+      <c r="G38" s="81" t="n"/>
       <c r="H38" s="59" t="n"/>
       <c r="I38" s="59" t="n"/>
+      <c r="J38" s="59" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="81" t="n"/>
       <c r="B39" s="81" t="n"/>
-      <c r="C39" s="84" t="n"/>
-      <c r="D39" s="78" t="inlineStr">
+      <c r="C39" s="81" t="n"/>
+      <c r="D39" s="84" t="n"/>
+      <c r="E39" s="78" t="inlineStr">
         <is>
           <t>• 【08】角色权限③：前端菜单/按钮级权限渲染指令</t>
         </is>
       </c>
-      <c r="E39" s="81" t="n"/>
       <c r="F39" s="81" t="n"/>
-      <c r="G39" s="59" t="n"/>
+      <c r="G39" s="81" t="n"/>
       <c r="H39" s="59" t="n"/>
       <c r="I39" s="59" t="n"/>
+      <c r="J39" s="59" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="81" t="n"/>
       <c r="B40" s="81" t="n"/>
-      <c r="C40" s="84" t="n"/>
-      <c r="D40" s="78" t="inlineStr">
+      <c r="C40" s="81" t="n"/>
+      <c r="D40" s="84" t="n"/>
+      <c r="E40" s="78" t="inlineStr">
         <is>
           <t>• 代码评审（C 数据链路 + D 骨架）</t>
         </is>
       </c>
-      <c r="E40" s="81" t="n"/>
       <c r="F40" s="81" t="n"/>
-      <c r="G40" s="59" t="n"/>
+      <c r="G40" s="81" t="n"/>
       <c r="H40" s="59" t="n"/>
       <c r="I40" s="59" t="n"/>
+      <c r="J40" s="59" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="91" t="inlineStr">
+      <c r="A41" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B41" s="91" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B41" s="76" t="inlineStr">
+      <c r="C41" s="76" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="C41" s="85" t="inlineStr">
+      <c r="D41" s="85" t="inlineStr">
         <is>
           <t>C·数据工程</t>
         </is>
       </c>
-      <c r="D41" s="78" t="inlineStr">
+      <c r="E41" s="78" t="inlineStr">
         <is>
           <t>• 【01】SeaTunnel 批量导入：CC 首批 50 表（分片并行/限速/断点续传）</t>
         </is>
       </c>
-      <c r="E41" s="79" t="inlineStr">
+      <c r="F41" s="79" t="inlineStr">
         <is>
           <t>CC 50 表批量入 RAW；任务可管理</t>
         </is>
       </c>
-      <c r="F41" s="80" t="inlineStr">
+      <c r="G41" s="80" t="inlineStr">
         <is>
           <t>CC 表清单（A 确认）</t>
         </is>
       </c>
-      <c r="G41" s="59" t="n"/>
       <c r="H41" s="59" t="n"/>
       <c r="I41" s="59" t="n"/>
+      <c r="J41" s="59" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="81" t="n"/>
       <c r="B42" s="81" t="n"/>
-      <c r="C42" s="86" t="n"/>
-      <c r="D42" s="78" t="inlineStr">
+      <c r="C42" s="81" t="n"/>
+      <c r="D42" s="86" t="n"/>
+      <c r="E42" s="78" t="inlineStr">
         <is>
           <t>• 【01】迁移任务管理：配置生成器（勾选→.conf→K8s Job）+ 状态跟踪</t>
         </is>
       </c>
-      <c r="E42" s="81" t="n"/>
       <c r="F42" s="81" t="n"/>
-      <c r="G42" s="59" t="n"/>
+      <c r="G42" s="81" t="n"/>
       <c r="H42" s="59" t="n"/>
       <c r="I42" s="59" t="n"/>
+      <c r="J42" s="59" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="81" t="n"/>
       <c r="B43" s="81" t="n"/>
-      <c r="C43" s="86" t="n"/>
-      <c r="D43" s="78" t="inlineStr">
+      <c r="C43" s="81" t="n"/>
+      <c r="D43" s="86" t="n"/>
+      <c r="E43" s="78" t="inlineStr">
         <is>
           <t>• 【07】JDBC 连接器模板 v1：SQL Server 类型映射表</t>
         </is>
       </c>
-      <c r="E43" s="81" t="n"/>
       <c r="F43" s="81" t="n"/>
-      <c r="G43" s="59" t="n"/>
+      <c r="G43" s="81" t="n"/>
       <c r="H43" s="59" t="n"/>
       <c r="I43" s="59" t="n"/>
+      <c r="J43" s="59" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="91" t="inlineStr">
+      <c r="A44" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B44" s="91" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B44" s="76" t="inlineStr">
+      <c r="C44" s="76" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="C44" s="87" t="inlineStr">
+      <c r="D44" s="87" t="inlineStr">
         <is>
           <t>D·全栈+DevOps</t>
         </is>
       </c>
-      <c r="D44" s="78" t="inlineStr">
+      <c r="E44" s="78" t="inlineStr">
         <is>
           <t>• 【01】迁移任务管理界面（任务列表/进度/对账结果查看）</t>
         </is>
       </c>
-      <c r="E44" s="79" t="inlineStr">
+      <c r="F44" s="79" t="inlineStr">
         <is>
           <t>任务管理界面；检索页可查</t>
         </is>
       </c>
-      <c r="F44" s="80" t="inlineStr"/>
-      <c r="G44" s="59" t="n"/>
+      <c r="G44" s="80" t="inlineStr"/>
       <c r="H44" s="59" t="n"/>
       <c r="I44" s="59" t="n"/>
+      <c r="J44" s="59" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="81" t="n"/>
       <c r="B45" s="81" t="n"/>
-      <c r="C45" s="88" t="n"/>
-      <c r="D45" s="78" t="inlineStr">
+      <c r="C45" s="81" t="n"/>
+      <c r="D45" s="88" t="n"/>
+      <c r="E45" s="78" t="inlineStr">
         <is>
           <t>• 【05】基础检索页：配置化动态渲染（筛选/表格/分页）</t>
         </is>
       </c>
-      <c r="E45" s="81" t="n"/>
       <c r="F45" s="81" t="n"/>
-      <c r="G45" s="59" t="n"/>
+      <c r="G45" s="81" t="n"/>
       <c r="H45" s="59" t="n"/>
       <c r="I45" s="59" t="n"/>
+      <c r="J45" s="59" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="81" t="n"/>
       <c r="B46" s="81" t="n"/>
-      <c r="C46" s="88" t="n"/>
-      <c r="D46" s="78" t="inlineStr">
+      <c r="C46" s="81" t="n"/>
+      <c r="D46" s="88" t="n"/>
+      <c r="E46" s="78" t="inlineStr">
         <is>
           <t>• 【06】操作审计埋点 v1（后端拦截 → 审计表）</t>
         </is>
       </c>
-      <c r="E46" s="81" t="n"/>
       <c r="F46" s="81" t="n"/>
-      <c r="G46" s="59" t="n"/>
+      <c r="G46" s="81" t="n"/>
       <c r="H46" s="59" t="n"/>
       <c r="I46" s="59" t="n"/>
+      <c r="J46" s="59" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="81" t="n"/>
       <c r="B47" s="81" t="n"/>
-      <c r="C47" s="88" t="n"/>
-      <c r="D47" s="78" t="inlineStr">
+      <c r="C47" s="81" t="n"/>
+      <c r="D47" s="88" t="n"/>
+      <c r="E47" s="78" t="inlineStr">
         <is>
           <t>• 代码安全①：依赖扫描进 CI（npm audit / dotnet audit）</t>
         </is>
       </c>
-      <c r="E47" s="81" t="n"/>
       <c r="F47" s="81" t="n"/>
-      <c r="G47" s="59" t="n"/>
+      <c r="G47" s="81" t="n"/>
       <c r="H47" s="59" t="n"/>
       <c r="I47" s="59" t="n"/>
+      <c r="J47" s="59" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="91" t="inlineStr">
+      <c r="A48" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B48" s="91" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B48" s="76" t="inlineStr">
+      <c r="C48" s="76" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="C48" s="89" t="inlineStr">
+      <c r="D48" s="89" t="inlineStr">
         <is>
           <t>E·QA+SLC文档</t>
         </is>
       </c>
-      <c r="D48" s="78" t="inlineStr">
+      <c r="E48" s="78" t="inlineStr">
         <is>
           <t>• 单元测试框架（xUnit + Mock）+ 覆盖率门禁 &gt;70% 进 CI</t>
         </is>
       </c>
-      <c r="E48" s="79" t="inlineStr">
+      <c r="F48" s="79" t="inlineStr">
         <is>
           <t>CI 门禁生效；用例 10 条</t>
         </is>
       </c>
-      <c r="F48" s="80" t="inlineStr">
+      <c r="G48" s="80" t="inlineStr">
         <is>
           <t>C/D API 稳定</t>
         </is>
       </c>
-      <c r="G48" s="59" t="n"/>
       <c r="H48" s="59" t="n"/>
       <c r="I48" s="59" t="n"/>
+      <c r="J48" s="59" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="81" t="n"/>
       <c r="B49" s="81" t="n"/>
-      <c r="C49" s="90" t="n"/>
-      <c r="D49" s="78" t="inlineStr">
+      <c r="C49" s="81" t="n"/>
+      <c r="D49" s="90" t="n"/>
+      <c r="E49" s="78" t="inlineStr">
         <is>
           <t>• 【01】迁移对账测试设计（行数/校验和双向比对用例）</t>
         </is>
       </c>
-      <c r="E49" s="81" t="n"/>
       <c r="F49" s="81" t="n"/>
-      <c r="G49" s="59" t="n"/>
+      <c r="G49" s="81" t="n"/>
       <c r="H49" s="59" t="n"/>
       <c r="I49" s="59" t="n"/>
+      <c r="J49" s="59" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="81" t="n"/>
       <c r="B50" s="81" t="n"/>
-      <c r="C50" s="90" t="n"/>
-      <c r="D50" s="78" t="inlineStr">
+      <c r="C50" s="81" t="n"/>
+      <c r="D50" s="90" t="n"/>
+      <c r="E50" s="78" t="inlineStr">
         <is>
           <t>• API 集成测试 10 核心场景</t>
         </is>
       </c>
-      <c r="E50" s="81" t="n"/>
       <c r="F50" s="81" t="n"/>
-      <c r="G50" s="59" t="n"/>
+      <c r="G50" s="81" t="n"/>
       <c r="H50" s="59" t="n"/>
       <c r="I50" s="59" t="n"/>
+      <c r="J50" s="59" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="81" t="n"/>
       <c r="B51" s="81" t="n"/>
-      <c r="C51" s="90" t="n"/>
-      <c r="D51" s="78" t="inlineStr">
+      <c r="C51" s="81" t="n"/>
+      <c r="D51" s="90" t="n"/>
+      <c r="E51" s="78" t="inlineStr">
         <is>
           <t>• 详细设计初稿：应用层</t>
         </is>
       </c>
-      <c r="E51" s="81" t="n"/>
       <c r="F51" s="81" t="n"/>
-      <c r="G51" s="59" t="n"/>
+      <c r="G51" s="81" t="n"/>
       <c r="H51" s="59" t="n"/>
       <c r="I51" s="59" t="n"/>
+      <c r="J51" s="59" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="91" t="inlineStr">
+      <c r="A52" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B52" s="91" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B52" s="76" t="inlineStr">
+      <c r="C52" s="76" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="C52" s="77" t="inlineStr">
+      <c r="D52" s="77" t="inlineStr">
         <is>
           <t>A·需求(50%)</t>
         </is>
       </c>
-      <c r="D52" s="78" t="inlineStr">
+      <c r="E52" s="78" t="inlineStr">
         <is>
           <t>• 验收 Sprint 1 交付（对照用户故事：迁移对账/检索/权限三态）</t>
         </is>
       </c>
-      <c r="E52" s="79" t="inlineStr">
+      <c r="F52" s="79" t="inlineStr">
         <is>
           <t>S1 验收记录；S3 需求就绪</t>
         </is>
       </c>
-      <c r="F52" s="80" t="inlineStr"/>
-      <c r="G52" s="59" t="n"/>
+      <c r="G52" s="80" t="inlineStr"/>
       <c r="H52" s="59" t="n"/>
       <c r="I52" s="59" t="n"/>
+      <c r="J52" s="59" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="81" t="n"/>
       <c r="B53" s="81" t="n"/>
-      <c r="C53" s="82" t="n"/>
-      <c r="D53" s="78" t="inlineStr">
+      <c r="C53" s="81" t="n"/>
+      <c r="D53" s="82" t="n"/>
+      <c r="E53" s="78" t="inlineStr">
         <is>
           <t>• Sprint 3 需求澄清（全量迁移范围最终确认 + 合规报表口径）</t>
         </is>
       </c>
-      <c r="E53" s="81" t="n"/>
       <c r="F53" s="81" t="n"/>
-      <c r="G53" s="59" t="n"/>
+      <c r="G53" s="81" t="n"/>
       <c r="H53" s="59" t="n"/>
       <c r="I53" s="59" t="n"/>
+      <c r="J53" s="59" t="n"/>
     </row>
     <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="91" t="inlineStr">
+      <c r="A54" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B54" s="91" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B54" s="76" t="inlineStr">
+      <c r="C54" s="76" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="C54" s="83" t="inlineStr">
+      <c r="D54" s="83" t="inlineStr">
         <is>
           <t>B·架构+开发</t>
         </is>
       </c>
-      <c r="D54" s="78" t="inlineStr">
+      <c r="E54" s="78" t="inlineStr">
         <is>
           <t>• 【08】角色权限④：UC GRANT 落地（arch_cc 的 SP-query/SP-audit）+ 掩码函数部署</t>
         </is>
       </c>
-      <c r="E54" s="79" t="inlineStr">
+      <c r="F54" s="79" t="inlineStr">
         <is>
           <t>权限三态演示通过</t>
         </is>
       </c>
-      <c r="F54" s="80" t="inlineStr">
+      <c r="G54" s="80" t="inlineStr">
         <is>
           <t>C 的 SERVE 数据</t>
         </is>
       </c>
-      <c r="G54" s="59" t="n"/>
       <c r="H54" s="59" t="n"/>
       <c r="I54" s="59" t="n"/>
+      <c r="J54" s="59" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="81" t="n"/>
       <c r="B55" s="81" t="n"/>
-      <c r="C55" s="84" t="n"/>
-      <c r="D55" s="78" t="inlineStr">
+      <c r="C55" s="81" t="n"/>
+      <c r="D55" s="84" t="n"/>
+      <c r="E55" s="78" t="inlineStr">
         <is>
           <t>• 【08】角色权限⑤：查询代理按角色路由连接池</t>
         </is>
       </c>
-      <c r="E55" s="81" t="n"/>
       <c r="F55" s="81" t="n"/>
-      <c r="G55" s="59" t="n"/>
+      <c r="G55" s="81" t="n"/>
       <c r="H55" s="59" t="n"/>
       <c r="I55" s="59" t="n"/>
+      <c r="J55" s="59" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="81" t="n"/>
       <c r="B56" s="81" t="n"/>
-      <c r="C56" s="84" t="n"/>
-      <c r="D56" s="78" t="inlineStr">
+      <c r="C56" s="81" t="n"/>
+      <c r="D56" s="84" t="n"/>
+      <c r="E56" s="78" t="inlineStr">
         <is>
           <t>• 端到端联调：登录 → 权限判定 → 明文/掩码/拒绝三态</t>
         </is>
       </c>
-      <c r="E56" s="81" t="n"/>
       <c r="F56" s="81" t="n"/>
-      <c r="G56" s="59" t="n"/>
+      <c r="G56" s="81" t="n"/>
       <c r="H56" s="59" t="n"/>
       <c r="I56" s="59" t="n"/>
+      <c r="J56" s="59" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="91" t="inlineStr">
+      <c r="A57" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B57" s="91" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B57" s="76" t="inlineStr">
+      <c r="C57" s="76" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="C57" s="85" t="inlineStr">
+      <c r="D57" s="85" t="inlineStr">
         <is>
           <t>C·数据工程</t>
         </is>
       </c>
-      <c r="D57" s="78" t="inlineStr">
+      <c r="E57" s="78" t="inlineStr">
         <is>
           <t>• 【01】完整性校验：行数/校验和双向对账 + SHA-256 台账</t>
         </is>
       </c>
-      <c r="E57" s="79" t="inlineStr">
+      <c r="F57" s="79" t="inlineStr">
         <is>
           <t>对账 100% 一致；SERVE 可查</t>
         </is>
       </c>
-      <c r="F57" s="80" t="inlineStr"/>
-      <c r="G57" s="59" t="n"/>
+      <c r="G57" s="80" t="inlineStr"/>
       <c r="H57" s="59" t="n"/>
       <c r="I57" s="59" t="n"/>
+      <c r="J57" s="59" t="n"/>
     </row>
     <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="81" t="n"/>
       <c r="B58" s="81" t="n"/>
-      <c r="C58" s="86" t="n"/>
-      <c r="D58" s="78" t="inlineStr">
+      <c r="C58" s="81" t="n"/>
+      <c r="D58" s="86" t="n"/>
+      <c r="E58" s="78" t="inlineStr">
         <is>
           <t>• 【01】首批 50 表 RAW→LAKE 直达转换</t>
         </is>
       </c>
-      <c r="E58" s="81" t="n"/>
       <c r="F58" s="81" t="n"/>
-      <c r="G58" s="59" t="n"/>
+      <c r="G58" s="81" t="n"/>
       <c r="H58" s="59" t="n"/>
       <c r="I58" s="59" t="n"/>
+      <c r="J58" s="59" t="n"/>
     </row>
     <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="81" t="n"/>
       <c r="B59" s="81" t="n"/>
-      <c r="C59" s="86" t="n"/>
-      <c r="D59" s="78" t="inlineStr">
+      <c r="C59" s="81" t="n"/>
+      <c r="D59" s="86" t="n"/>
+      <c r="E59" s="78" t="inlineStr">
         <is>
           <t>• 【05】SERVE 层首版（热表物化 + Z-Order）</t>
         </is>
       </c>
-      <c r="E59" s="81" t="n"/>
       <c r="F59" s="81" t="n"/>
-      <c r="G59" s="59" t="n"/>
+      <c r="G59" s="81" t="n"/>
       <c r="H59" s="59" t="n"/>
       <c r="I59" s="59" t="n"/>
+      <c r="J59" s="59" t="n"/>
     </row>
     <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="81" t="n"/>
       <c r="B60" s="81" t="n"/>
-      <c r="C60" s="86" t="n"/>
-      <c r="D60" s="78" t="inlineStr">
+      <c r="C60" s="81" t="n"/>
+      <c r="D60" s="86" t="n"/>
+      <c r="E60" s="78" t="inlineStr">
         <is>
           <t>• 代码安全：JDBC 连接串走 Key Vault（零硬编码）</t>
         </is>
       </c>
-      <c r="E60" s="81" t="n"/>
       <c r="F60" s="81" t="n"/>
-      <c r="G60" s="59" t="n"/>
+      <c r="G60" s="81" t="n"/>
       <c r="H60" s="59" t="n"/>
       <c r="I60" s="59" t="n"/>
+      <c r="J60" s="59" t="n"/>
     </row>
     <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="91" t="inlineStr">
+      <c r="A61" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B61" s="91" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B61" s="76" t="inlineStr">
+      <c r="C61" s="76" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="C61" s="87" t="inlineStr">
+      <c r="D61" s="87" t="inlineStr">
         <is>
           <t>D·全栈+DevOps</t>
         </is>
       </c>
-      <c r="D61" s="78" t="inlineStr">
+      <c r="E61" s="78" t="inlineStr">
         <is>
           <t>• 【05】结果预览：图片/附件 SAS 直连；导出 CSV</t>
         </is>
       </c>
-      <c r="E61" s="79" t="inlineStr">
+      <c r="F61" s="79" t="inlineStr">
         <is>
           <t>预览/导出可用；SAST 零 High</t>
         </is>
       </c>
-      <c r="F61" s="80" t="inlineStr"/>
-      <c r="G61" s="59" t="n"/>
+      <c r="G61" s="80" t="inlineStr"/>
       <c r="H61" s="59" t="n"/>
       <c r="I61" s="59" t="n"/>
+      <c r="J61" s="59" t="n"/>
     </row>
     <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="81" t="n"/>
       <c r="B62" s="81" t="n"/>
-      <c r="C62" s="88" t="n"/>
-      <c r="D62" s="78" t="inlineStr">
+      <c r="C62" s="81" t="n"/>
+      <c r="D62" s="88" t="n"/>
+      <c r="E62" s="78" t="inlineStr">
         <is>
           <t>• 代码安全②：SAST 进 CI（CodeQL/Semgrep）</t>
         </is>
       </c>
-      <c r="E62" s="81" t="n"/>
       <c r="F62" s="81" t="n"/>
-      <c r="G62" s="59" t="n"/>
+      <c r="G62" s="81" t="n"/>
       <c r="H62" s="59" t="n"/>
       <c r="I62" s="59" t="n"/>
+      <c r="J62" s="59" t="n"/>
     </row>
     <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="81" t="n"/>
       <c r="B63" s="81" t="n"/>
-      <c r="C63" s="88" t="n"/>
-      <c r="D63" s="78" t="inlineStr">
+      <c r="C63" s="81" t="n"/>
+      <c r="D63" s="88" t="n"/>
+      <c r="E63" s="78" t="inlineStr">
         <is>
           <t>• 安全修复：Sprint 1 扫描 High 级清零</t>
         </is>
       </c>
-      <c r="E63" s="81" t="n"/>
       <c r="F63" s="81" t="n"/>
-      <c r="G63" s="59" t="n"/>
+      <c r="G63" s="81" t="n"/>
       <c r="H63" s="59" t="n"/>
       <c r="I63" s="59" t="n"/>
+      <c r="J63" s="59" t="n"/>
     </row>
     <row r="64" ht="22" customHeight="1">
-      <c r="A64" s="91" t="inlineStr">
+      <c r="A64" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B64" s="91" t="inlineStr">
         <is>
           <t>Sprint 1</t>
         </is>
       </c>
-      <c r="B64" s="76" t="inlineStr">
+      <c r="C64" s="76" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="C64" s="89" t="inlineStr">
+      <c r="D64" s="89" t="inlineStr">
         <is>
           <t>E·QA+SLC文档</t>
         </is>
       </c>
-      <c r="D64" s="78" t="inlineStr">
+      <c r="E64" s="78" t="inlineStr">
         <is>
           <t>• 【01】迁移对账执行 + 报告</t>
         </is>
       </c>
-      <c r="E64" s="79" t="inlineStr">
+      <c r="F64" s="79" t="inlineStr">
         <is>
           <t>对账报告；测试报告</t>
         </is>
       </c>
-      <c r="F64" s="80" t="inlineStr"/>
-      <c r="G64" s="59" t="n"/>
+      <c r="G64" s="80" t="inlineStr"/>
       <c r="H64" s="59" t="n"/>
       <c r="I64" s="59" t="n"/>
+      <c r="J64" s="59" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="81" t="n"/>
       <c r="B65" s="81" t="n"/>
-      <c r="C65" s="90" t="n"/>
-      <c r="D65" s="78" t="inlineStr">
+      <c r="C65" s="81" t="n"/>
+      <c r="D65" s="90" t="n"/>
+      <c r="E65" s="78" t="inlineStr">
         <is>
           <t>• 安全测试①：注入/XSS/越权手工用例</t>
         </is>
       </c>
-      <c r="E65" s="81" t="n"/>
       <c r="F65" s="81" t="n"/>
-      <c r="G65" s="59" t="n"/>
+      <c r="G65" s="81" t="n"/>
       <c r="H65" s="59" t="n"/>
       <c r="I65" s="59" t="n"/>
+      <c r="J65" s="59" t="n"/>
     </row>
     <row r="66" ht="22" customHeight="1">
-      <c r="A66" s="81" t="n"/>
       <c r="B66" s="81" t="n"/>
-      <c r="C66" s="90" t="n"/>
-      <c r="D66" s="78" t="inlineStr">
+      <c r="C66" s="81" t="n"/>
+      <c r="D66" s="90" t="n"/>
+      <c r="E66" s="78" t="inlineStr">
         <is>
           <t>• 详细设计初稿：数据层（四层 + ER 图）</t>
         </is>
       </c>
-      <c r="E66" s="81" t="n"/>
       <c r="F66" s="81" t="n"/>
-      <c r="G66" s="59" t="n"/>
+      <c r="G66" s="81" t="n"/>
       <c r="H66" s="59" t="n"/>
       <c r="I66" s="59" t="n"/>
+      <c r="J66" s="59" t="n"/>
     </row>
     <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="81" t="n"/>
       <c r="B67" s="81" t="n"/>
-      <c r="C67" s="90" t="n"/>
-      <c r="D67" s="78" t="inlineStr">
+      <c r="C67" s="81" t="n"/>
+      <c r="D67" s="90" t="n"/>
+      <c r="E67" s="78" t="inlineStr">
         <is>
           <t>• Sprint 1 测试报告</t>
         </is>
       </c>
-      <c r="E67" s="81" t="n"/>
       <c r="F67" s="81" t="n"/>
-      <c r="G67" s="59" t="n"/>
+      <c r="G67" s="81" t="n"/>
       <c r="H67" s="59" t="n"/>
       <c r="I67" s="59" t="n"/>
+      <c r="J67" s="59" t="n"/>
     </row>
     <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="92" t="inlineStr">
+      <c r="A68" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B68" s="92" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B68" s="76" t="inlineStr">
+      <c r="C68" s="76" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="C68" s="77" t="inlineStr">
+      <c r="D68" s="77" t="inlineStr">
         <is>
           <t>A·需求(50%)</t>
         </is>
       </c>
-      <c r="D68" s="78" t="inlineStr">
+      <c r="E68" s="78" t="inlineStr">
         <is>
           <t>• Sprint 4 需求澄清（UAT 场景细化 + 生产迁移窗口）</t>
         </is>
       </c>
-      <c r="E68" s="79" t="inlineStr">
+      <c r="F68" s="79" t="inlineStr">
         <is>
           <t>S4 需求就绪；Legal Hold 条件</t>
         </is>
       </c>
-      <c r="F68" s="80" t="inlineStr">
+      <c r="G68" s="80" t="inlineStr">
         <is>
           <t>法务配合</t>
         </is>
       </c>
-      <c r="G68" s="59" t="n"/>
       <c r="H68" s="59" t="n"/>
       <c r="I68" s="59" t="n"/>
+      <c r="J68" s="59" t="n"/>
     </row>
     <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="81" t="n"/>
       <c r="B69" s="81" t="n"/>
-      <c r="C69" s="82" t="n"/>
-      <c r="D69" s="78" t="inlineStr">
+      <c r="C69" s="81" t="n"/>
+      <c r="D69" s="82" t="n"/>
+      <c r="E69" s="78" t="inlineStr">
         <is>
           <t>• 【03】Legal Hold 触发条件定稿（法务确认：哪些档案可 Hold/谁有权 Hold）</t>
         </is>
       </c>
-      <c r="E69" s="81" t="n"/>
       <c r="F69" s="81" t="n"/>
-      <c r="G69" s="59" t="n"/>
+      <c r="G69" s="81" t="n"/>
       <c r="H69" s="59" t="n"/>
       <c r="I69" s="59" t="n"/>
+      <c r="J69" s="59" t="n"/>
     </row>
     <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="92" t="inlineStr">
+      <c r="A70" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B70" s="92" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B70" s="76" t="inlineStr">
+      <c r="C70" s="76" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="C70" s="83" t="inlineStr">
+      <c r="D70" s="83" t="inlineStr">
         <is>
           <t>B·架构+开发</t>
         </is>
       </c>
-      <c r="D70" s="78" t="inlineStr">
+      <c r="E70" s="78" t="inlineStr">
         <is>
           <t>• 【03】到期处置引擎①：扫描（retention_assignment 到期计算）→ DROP PARTITION → VACUUM</t>
         </is>
       </c>
-      <c r="E70" s="79" t="inlineStr">
+      <c r="F70" s="79" t="inlineStr">
         <is>
           <t>处置引擎可跑；Hold 机制可用</t>
         </is>
       </c>
-      <c r="F70" s="80" t="inlineStr"/>
-      <c r="G70" s="59" t="n"/>
+      <c r="G70" s="80" t="inlineStr"/>
       <c r="H70" s="59" t="n"/>
       <c r="I70" s="59" t="n"/>
+      <c r="J70" s="59" t="n"/>
     </row>
     <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="81" t="n"/>
       <c r="B71" s="81" t="n"/>
-      <c r="C71" s="84" t="n"/>
-      <c r="D71" s="78" t="inlineStr">
+      <c r="C71" s="81" t="n"/>
+      <c r="D71" s="84" t="n"/>
+      <c r="E71" s="78" t="inlineStr">
         <is>
           <t>• 【03】Legal Hold②：Hold/Release 机制 + 处置豁免 + 留痕</t>
         </is>
       </c>
-      <c r="E71" s="81" t="n"/>
       <c r="F71" s="81" t="n"/>
-      <c r="G71" s="59" t="n"/>
+      <c r="G71" s="81" t="n"/>
       <c r="H71" s="59" t="n"/>
       <c r="I71" s="59" t="n"/>
+      <c r="J71" s="59" t="n"/>
     </row>
     <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="81" t="n"/>
       <c r="B72" s="81" t="n"/>
-      <c r="C72" s="84" t="n"/>
-      <c r="D72" s="78" t="inlineStr">
+      <c r="C72" s="81" t="n"/>
+      <c r="D72" s="84" t="n"/>
+      <c r="E72" s="78" t="inlineStr">
         <is>
           <t>• 【04】加密体系③：CMK + aes_encrypt 字段级 + 密钥轮转（Key Vault DEK/KEK）</t>
         </is>
       </c>
-      <c r="E72" s="81" t="n"/>
       <c r="F72" s="81" t="n"/>
-      <c r="G72" s="59" t="n"/>
+      <c r="G72" s="81" t="n"/>
       <c r="H72" s="59" t="n"/>
       <c r="I72" s="59" t="n"/>
+      <c r="J72" s="59" t="n"/>
     </row>
     <row r="73" ht="22" customHeight="1">
-      <c r="A73" s="92" t="inlineStr">
+      <c r="A73" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B73" s="92" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B73" s="76" t="inlineStr">
+      <c r="C73" s="76" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="C73" s="85" t="inlineStr">
+      <c r="D73" s="85" t="inlineStr">
         <is>
           <t>C·数据工程</t>
         </is>
       </c>
-      <c r="D73" s="78" t="inlineStr">
+      <c r="E73" s="78" t="inlineStr">
         <is>
           <t>• 【02】增量接入：watermark 列方案落地（按 W1 确认的实时指标）</t>
         </is>
       </c>
-      <c r="E73" s="79" t="inlineStr">
+      <c r="F73" s="79" t="inlineStr">
         <is>
           <t>增量自动入湖；分层生效</t>
         </is>
       </c>
-      <c r="F73" s="80" t="inlineStr"/>
-      <c r="G73" s="59" t="n"/>
+      <c r="G73" s="80" t="inlineStr"/>
       <c r="H73" s="59" t="n"/>
       <c r="I73" s="59" t="n"/>
+      <c r="J73" s="59" t="n"/>
     </row>
     <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="81" t="n"/>
       <c r="B74" s="81" t="n"/>
-      <c r="C74" s="86" t="n"/>
-      <c r="D74" s="78" t="inlineStr">
+      <c r="C74" s="81" t="n"/>
+      <c r="D74" s="86" t="n"/>
+      <c r="E74" s="78" t="inlineStr">
         <is>
           <t>• 【02】冷数据识别与自动转冷（按 A 的冷数据标准：访问频率→分层）</t>
         </is>
       </c>
-      <c r="E74" s="81" t="n"/>
       <c r="F74" s="81" t="n"/>
-      <c r="G74" s="59" t="n"/>
+      <c r="G74" s="81" t="n"/>
       <c r="H74" s="59" t="n"/>
       <c r="I74" s="59" t="n"/>
+      <c r="J74" s="59" t="n"/>
     </row>
     <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="81" t="n"/>
       <c r="B75" s="81" t="n"/>
-      <c r="C75" s="86" t="n"/>
-      <c r="D75" s="78" t="inlineStr">
+      <c r="C75" s="81" t="n"/>
+      <c r="D75" s="86" t="n"/>
+      <c r="E75" s="78" t="inlineStr">
         <is>
           <t>• 【04】ADLS 冷热分层：生命周期规则（30 天 Cool/90 天 Cold）+ Compaction 调度</t>
         </is>
       </c>
-      <c r="E75" s="81" t="n"/>
       <c r="F75" s="81" t="n"/>
-      <c r="G75" s="59" t="n"/>
+      <c r="G75" s="81" t="n"/>
       <c r="H75" s="59" t="n"/>
       <c r="I75" s="59" t="n"/>
+      <c r="J75" s="59" t="n"/>
     </row>
     <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="92" t="inlineStr">
+      <c r="A76" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B76" s="92" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B76" s="76" t="inlineStr">
+      <c r="C76" s="76" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="C76" s="87" t="inlineStr">
+      <c r="D76" s="87" t="inlineStr">
         <is>
           <t>D·全栈+DevOps</t>
         </is>
       </c>
-      <c r="D76" s="78" t="inlineStr">
+      <c r="E76" s="78" t="inlineStr">
         <is>
           <t>• 【02】元数据标准管理界面（数据 Owner/来源/命名规范 CRUD）</t>
         </is>
       </c>
-      <c r="E76" s="79" t="inlineStr">
+      <c r="F76" s="79" t="inlineStr">
         <is>
           <t>元数据界面；安全门禁四道全开</t>
         </is>
       </c>
-      <c r="F76" s="80" t="inlineStr"/>
-      <c r="G76" s="59" t="n"/>
+      <c r="G76" s="80" t="inlineStr"/>
       <c r="H76" s="59" t="n"/>
       <c r="I76" s="59" t="n"/>
+      <c r="J76" s="59" t="n"/>
     </row>
     <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="81" t="n"/>
       <c r="B77" s="81" t="n"/>
-      <c r="C77" s="88" t="n"/>
-      <c r="D77" s="78" t="inlineStr">
+      <c r="C77" s="81" t="n"/>
+      <c r="D77" s="88" t="n"/>
+      <c r="E77" s="78" t="inlineStr">
         <is>
           <t>• 【05】检索完善：动态列/排序/筛选联动 + 权限列隐藏</t>
         </is>
       </c>
-      <c r="E77" s="81" t="n"/>
       <c r="F77" s="81" t="n"/>
-      <c r="G77" s="59" t="n"/>
+      <c r="G77" s="81" t="n"/>
       <c r="H77" s="59" t="n"/>
       <c r="I77" s="59" t="n"/>
+      <c r="J77" s="59" t="n"/>
     </row>
     <row r="78" ht="22" customHeight="1">
-      <c r="A78" s="81" t="n"/>
       <c r="B78" s="81" t="n"/>
-      <c r="C78" s="88" t="n"/>
-      <c r="D78" s="78" t="inlineStr">
+      <c r="C78" s="81" t="n"/>
+      <c r="D78" s="88" t="n"/>
+      <c r="E78" s="78" t="inlineStr">
         <is>
           <t>• 代码安全③：gitleaks 密钥扫描 + Trivy 镜像扫描进 CI；中危清零</t>
         </is>
       </c>
-      <c r="E78" s="81" t="n"/>
       <c r="F78" s="81" t="n"/>
-      <c r="G78" s="59" t="n"/>
+      <c r="G78" s="81" t="n"/>
       <c r="H78" s="59" t="n"/>
       <c r="I78" s="59" t="n"/>
+      <c r="J78" s="59" t="n"/>
     </row>
     <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="92" t="inlineStr">
+      <c r="A79" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B79" s="92" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B79" s="76" t="inlineStr">
+      <c r="C79" s="76" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="C79" s="89" t="inlineStr">
+      <c r="D79" s="89" t="inlineStr">
         <is>
           <t>E·QA+SLC文档</t>
         </is>
       </c>
-      <c r="D79" s="78" t="inlineStr">
+      <c r="E79" s="78" t="inlineStr">
         <is>
           <t>• 功能用例扩充（50+：权限三态/增量/处置/Hold/脱敏）</t>
         </is>
       </c>
-      <c r="E79" s="79" t="inlineStr">
+      <c r="F79" s="79" t="inlineStr">
         <is>
           <t>用例 50+；越权全拦截</t>
         </is>
       </c>
-      <c r="F79" s="80" t="inlineStr"/>
-      <c r="G79" s="59" t="n"/>
+      <c r="G79" s="80" t="inlineStr"/>
       <c r="H79" s="59" t="n"/>
       <c r="I79" s="59" t="n"/>
+      <c r="J79" s="59" t="n"/>
     </row>
     <row r="80" ht="22" customHeight="1">
-      <c r="A80" s="81" t="n"/>
       <c r="B80" s="81" t="n"/>
-      <c r="C80" s="90" t="n"/>
-      <c r="D80" s="78" t="inlineStr">
+      <c r="C80" s="81" t="n"/>
+      <c r="D80" s="90" t="n"/>
+      <c r="E80" s="78" t="inlineStr">
         <is>
           <t>• 安全测试②：掩码旁路 + 越权（垂直/水平）用例 + 修复验证</t>
         </is>
       </c>
-      <c r="E80" s="81" t="n"/>
       <c r="F80" s="81" t="n"/>
-      <c r="G80" s="59" t="n"/>
+      <c r="G80" s="81" t="n"/>
       <c r="H80" s="59" t="n"/>
       <c r="I80" s="59" t="n"/>
+      <c r="J80" s="59" t="n"/>
     </row>
     <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="81" t="n"/>
       <c r="B81" s="81" t="n"/>
-      <c r="C81" s="90" t="n"/>
-      <c r="D81" s="78" t="inlineStr">
+      <c r="C81" s="81" t="n"/>
+      <c r="D81" s="90" t="n"/>
+      <c r="E81" s="78" t="inlineStr">
         <is>
           <t>• 详细设计初稿：安全层</t>
         </is>
       </c>
-      <c r="E81" s="81" t="n"/>
       <c r="F81" s="81" t="n"/>
-      <c r="G81" s="59" t="n"/>
+      <c r="G81" s="81" t="n"/>
       <c r="H81" s="59" t="n"/>
       <c r="I81" s="59" t="n"/>
+      <c r="J81" s="59" t="n"/>
     </row>
     <row r="82" ht="22" customHeight="1">
-      <c r="A82" s="92" t="inlineStr">
+      <c r="A82" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B82" s="92" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B82" s="76" t="inlineStr">
+      <c r="C82" s="76" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="C82" s="77" t="inlineStr">
+      <c r="D82" s="77" t="inlineStr">
         <is>
           <t>A·需求(50%)</t>
         </is>
       </c>
-      <c r="D82" s="78" t="inlineStr">
+      <c r="E82" s="78" t="inlineStr">
         <is>
           <t>• 验收 Sprint 2 交付（增量时效/处置链路/脱敏三态）</t>
         </is>
       </c>
-      <c r="E82" s="79" t="inlineStr">
+      <c r="F82" s="79" t="inlineStr">
         <is>
           <t>S2 验收；全量范围签字</t>
         </is>
       </c>
-      <c r="F82" s="80" t="inlineStr"/>
-      <c r="G82" s="59" t="n"/>
+      <c r="G82" s="80" t="inlineStr"/>
       <c r="H82" s="59" t="n"/>
       <c r="I82" s="59" t="n"/>
+      <c r="J82" s="59" t="n"/>
     </row>
     <row r="83" ht="22" customHeight="1">
-      <c r="A83" s="81" t="n"/>
       <c r="B83" s="81" t="n"/>
-      <c r="C83" s="82" t="n"/>
-      <c r="D83" s="78" t="inlineStr">
+      <c r="C83" s="81" t="n"/>
+      <c r="D83" s="82" t="n"/>
+      <c r="E83" s="78" t="inlineStr">
         <is>
           <t>• CC 全量迁移范围最终确认（600~800 张有效表清单签字）</t>
         </is>
       </c>
-      <c r="E83" s="81" t="n"/>
       <c r="F83" s="81" t="n"/>
-      <c r="G83" s="59" t="n"/>
+      <c r="G83" s="81" t="n"/>
       <c r="H83" s="59" t="n"/>
       <c r="I83" s="59" t="n"/>
+      <c r="J83" s="59" t="n"/>
     </row>
     <row r="84" ht="22" customHeight="1">
-      <c r="A84" s="92" t="inlineStr">
+      <c r="A84" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B84" s="92" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B84" s="76" t="inlineStr">
+      <c r="C84" s="76" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="C84" s="83" t="inlineStr">
+      <c r="D84" s="83" t="inlineStr">
         <is>
           <t>B·架构+开发</t>
         </is>
       </c>
-      <c r="D84" s="78" t="inlineStr">
+      <c r="E84" s="78" t="inlineStr">
         <is>
           <t>• 【03】标准归档模型管理界面（保管期限表 + 分类模型）</t>
         </is>
       </c>
-      <c r="E84" s="79" t="inlineStr">
+      <c r="F84" s="79" t="inlineStr">
         <is>
           <t>归档模型可配；驻留核查通过</t>
         </is>
       </c>
-      <c r="F84" s="80" t="inlineStr"/>
-      <c r="G84" s="59" t="n"/>
+      <c r="G84" s="80" t="inlineStr"/>
       <c r="H84" s="59" t="n"/>
       <c r="I84" s="59" t="n"/>
+      <c r="J84" s="59" t="n"/>
     </row>
     <row r="85" ht="22" customHeight="1">
-      <c r="A85" s="81" t="n"/>
       <c r="B85" s="81" t="n"/>
-      <c r="C85" s="84" t="n"/>
-      <c r="D85" s="78" t="inlineStr">
+      <c r="C85" s="81" t="n"/>
+      <c r="D85" s="84" t="n"/>
+      <c r="E85" s="78" t="inlineStr">
         <is>
           <t>• 【04】境内驻留核查②：出口流量管控 + 数据不出境验证用例</t>
         </is>
       </c>
-      <c r="E85" s="81" t="n"/>
       <c r="F85" s="81" t="n"/>
-      <c r="G85" s="59" t="n"/>
+      <c r="G85" s="81" t="n"/>
       <c r="H85" s="59" t="n"/>
       <c r="I85" s="59" t="n"/>
+      <c r="J85" s="59" t="n"/>
     </row>
     <row r="86" ht="22" customHeight="1">
-      <c r="A86" s="81" t="n"/>
       <c r="B86" s="81" t="n"/>
-      <c r="C86" s="84" t="n"/>
-      <c r="D86" s="78" t="inlineStr">
+      <c r="C86" s="81" t="n"/>
+      <c r="D86" s="84" t="n"/>
+      <c r="E86" s="78" t="inlineStr">
         <is>
           <t>• 前端功能：到期处置与 Legal Hold 审批界面</t>
         </is>
       </c>
-      <c r="E86" s="81" t="n"/>
       <c r="F86" s="81" t="n"/>
-      <c r="G86" s="59" t="n"/>
+      <c r="G86" s="81" t="n"/>
       <c r="H86" s="59" t="n"/>
       <c r="I86" s="59" t="n"/>
+      <c r="J86" s="59" t="n"/>
     </row>
     <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="92" t="inlineStr">
+      <c r="A87" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B87" s="92" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B87" s="76" t="inlineStr">
+      <c r="C87" s="76" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="C87" s="85" t="inlineStr">
+      <c r="D87" s="85" t="inlineStr">
         <is>
           <t>C·数据工程</t>
         </is>
       </c>
-      <c r="D87" s="78" t="inlineStr">
+      <c r="E87" s="78" t="inlineStr">
         <is>
           <t>• 【03】归档转换校验：CURATED/LAKE 层 Spark SQL + Schema Evolution</t>
         </is>
       </c>
-      <c r="E87" s="79" t="inlineStr">
+      <c r="F87" s="79" t="inlineStr">
         <is>
           <t>四层全通；增量稳定运行</t>
         </is>
       </c>
-      <c r="F87" s="80" t="inlineStr"/>
-      <c r="G87" s="59" t="n"/>
+      <c r="G87" s="80" t="inlineStr"/>
       <c r="H87" s="59" t="n"/>
       <c r="I87" s="59" t="n"/>
+      <c r="J87" s="59" t="n"/>
     </row>
     <row r="88" ht="22" customHeight="1">
-      <c r="A88" s="81" t="n"/>
       <c r="B88" s="81" t="n"/>
-      <c r="C88" s="86" t="n"/>
-      <c r="D88" s="78" t="inlineStr">
+      <c r="C88" s="81" t="n"/>
+      <c r="D88" s="86" t="n"/>
+      <c r="E88" s="78" t="inlineStr">
         <is>
           <t>• 【02】增量常态化运行（CC 每日增量）</t>
         </is>
       </c>
-      <c r="E88" s="81" t="n"/>
       <c r="F88" s="81" t="n"/>
-      <c r="G88" s="59" t="n"/>
+      <c r="G88" s="81" t="n"/>
       <c r="H88" s="59" t="n"/>
       <c r="I88" s="59" t="n"/>
+      <c r="J88" s="59" t="n"/>
     </row>
     <row r="89" ht="22" customHeight="1">
-      <c r="A89" s="81" t="n"/>
       <c r="B89" s="81" t="n"/>
-      <c r="C89" s="86" t="n"/>
-      <c r="D89" s="78" t="inlineStr">
+      <c r="C89" s="81" t="n"/>
+      <c r="D89" s="86" t="n"/>
+      <c r="E89" s="78" t="inlineStr">
         <is>
           <t>• 性能优化（文件大小/分区裁剪/查询计划）</t>
         </is>
       </c>
-      <c r="E89" s="81" t="n"/>
       <c r="F89" s="81" t="n"/>
-      <c r="G89" s="59" t="n"/>
+      <c r="G89" s="81" t="n"/>
       <c r="H89" s="59" t="n"/>
       <c r="I89" s="59" t="n"/>
+      <c r="J89" s="59" t="n"/>
     </row>
     <row r="90" ht="22" customHeight="1">
-      <c r="A90" s="92" t="inlineStr">
+      <c r="A90" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B90" s="92" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B90" s="76" t="inlineStr">
+      <c r="C90" s="76" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="C90" s="87" t="inlineStr">
+      <c r="D90" s="87" t="inlineStr">
         <is>
           <t>D·全栈+DevOps</t>
         </is>
       </c>
-      <c r="D90" s="78" t="inlineStr">
+      <c r="E90" s="78" t="inlineStr">
         <is>
           <t>• 【03】处置/Hold 界面联调</t>
         </is>
       </c>
-      <c r="E90" s="79" t="inlineStr">
+      <c r="F90" s="79" t="inlineStr">
         <is>
           <t>报表 v1 可用</t>
         </is>
       </c>
-      <c r="F90" s="80" t="inlineStr"/>
-      <c r="G90" s="59" t="n"/>
+      <c r="G90" s="80" t="inlineStr"/>
       <c r="H90" s="59" t="n"/>
       <c r="I90" s="59" t="n"/>
+      <c r="J90" s="59" t="n"/>
     </row>
     <row r="91" ht="22" customHeight="1">
-      <c r="A91" s="81" t="n"/>
       <c r="B91" s="81" t="n"/>
-      <c r="C91" s="88" t="n"/>
-      <c r="D91" s="78" t="inlineStr">
+      <c r="C91" s="81" t="n"/>
+      <c r="D91" s="88" t="n"/>
+      <c r="E91" s="78" t="inlineStr">
         <is>
           <t>• 【06】合规报表 v1 开发（审计查询 + 导出）</t>
         </is>
       </c>
-      <c r="E91" s="81" t="n"/>
       <c r="F91" s="81" t="n"/>
-      <c r="G91" s="59" t="n"/>
+      <c r="G91" s="81" t="n"/>
       <c r="H91" s="59" t="n"/>
       <c r="I91" s="59" t="n"/>
+      <c r="J91" s="59" t="n"/>
     </row>
     <row r="92" ht="22" customHeight="1">
-      <c r="A92" s="81" t="n"/>
       <c r="B92" s="81" t="n"/>
-      <c r="C92" s="88" t="n"/>
-      <c r="D92" s="78" t="inlineStr">
+      <c r="C92" s="81" t="n"/>
+      <c r="D92" s="88" t="n"/>
+      <c r="E92" s="78" t="inlineStr">
         <is>
           <t>• 性能优化：前端懒加载/虚拟滚动</t>
         </is>
       </c>
-      <c r="E92" s="81" t="n"/>
       <c r="F92" s="81" t="n"/>
-      <c r="G92" s="59" t="n"/>
+      <c r="G92" s="81" t="n"/>
       <c r="H92" s="59" t="n"/>
       <c r="I92" s="59" t="n"/>
+      <c r="J92" s="59" t="n"/>
     </row>
     <row r="93" ht="30" customHeight="1">
-      <c r="A93" s="92" t="inlineStr">
+      <c r="A93" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B93" s="92" t="inlineStr">
         <is>
           <t>Sprint 2</t>
         </is>
       </c>
-      <c r="B93" s="76" t="inlineStr">
+      <c r="C93" s="76" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="C93" s="89" t="inlineStr">
+      <c r="D93" s="89" t="inlineStr">
         <is>
           <t>E·QA+SLC文档</t>
         </is>
       </c>
-      <c r="D93" s="78" t="inlineStr">
+      <c r="E93" s="78" t="inlineStr">
         <is>
           <t>• 【03】处置全链路 E2E：设 1 天保留期 → 到期 → Hold 拦截 → Release → 处置 → 审计</t>
         </is>
       </c>
-      <c r="E93" s="79" t="inlineStr">
+      <c r="F93" s="79" t="inlineStr">
         <is>
           <t>处置 E2E 通过；合稿</t>
         </is>
       </c>
-      <c r="F93" s="80" t="inlineStr">
+      <c r="G93" s="80" t="inlineStr">
         <is>
           <t>性能数据由 C 备</t>
         </is>
       </c>
-      <c r="G93" s="59" t="n"/>
       <c r="H93" s="59" t="n"/>
       <c r="I93" s="59" t="n"/>
+      <c r="J93" s="59" t="n"/>
     </row>
     <row r="94" ht="22" customHeight="1">
-      <c r="A94" s="81" t="n"/>
       <c r="B94" s="81" t="n"/>
-      <c r="C94" s="90" t="n"/>
-      <c r="D94" s="78" t="inlineStr">
+      <c r="C94" s="81" t="n"/>
+      <c r="D94" s="90" t="n"/>
+      <c r="E94" s="78" t="inlineStr">
         <is>
           <t>• 性能测试（100 万行 P95&lt;5s）</t>
         </is>
       </c>
-      <c r="E94" s="81" t="n"/>
       <c r="F94" s="81" t="n"/>
-      <c r="G94" s="59" t="n"/>
+      <c r="G94" s="81" t="n"/>
       <c r="H94" s="59" t="n"/>
       <c r="I94" s="59" t="n"/>
+      <c r="J94" s="59" t="n"/>
     </row>
     <row r="95" ht="22" customHeight="1">
-      <c r="A95" s="81" t="n"/>
       <c r="B95" s="81" t="n"/>
-      <c r="C95" s="90" t="n"/>
-      <c r="D95" s="78" t="inlineStr">
+      <c r="C95" s="81" t="n"/>
+      <c r="D95" s="90" t="n"/>
+      <c r="E95" s="78" t="inlineStr">
         <is>
           <t>• 安全修复回归 + 详细设计三模块合稿</t>
         </is>
       </c>
-      <c r="E95" s="81" t="n"/>
       <c r="F95" s="81" t="n"/>
-      <c r="G95" s="59" t="n"/>
+      <c r="G95" s="81" t="n"/>
       <c r="H95" s="59" t="n"/>
       <c r="I95" s="59" t="n"/>
+      <c r="J95" s="59" t="n"/>
     </row>
     <row r="96" ht="22" customHeight="1">
-      <c r="A96" s="81" t="n"/>
       <c r="B96" s="81" t="n"/>
-      <c r="C96" s="90" t="n"/>
-      <c r="D96" s="78" t="inlineStr">
+      <c r="C96" s="81" t="n"/>
+      <c r="D96" s="90" t="n"/>
+      <c r="E96" s="78" t="inlineStr">
         <is>
           <t>• Sprint 2 测试报告</t>
         </is>
       </c>
-      <c r="E96" s="81" t="n"/>
       <c r="F96" s="81" t="n"/>
-      <c r="G96" s="59" t="n"/>
+      <c r="G96" s="81" t="n"/>
       <c r="H96" s="59" t="n"/>
       <c r="I96" s="59" t="n"/>
+      <c r="J96" s="59" t="n"/>
     </row>
     <row r="97" ht="22" customHeight="1">
-      <c r="A97" s="93" t="inlineStr">
+      <c r="A97" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B97" s="93" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B97" s="76" t="inlineStr">
+      <c r="C97" s="76" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="C97" s="77" t="inlineStr">
+      <c r="D97" s="77" t="inlineStr">
         <is>
           <t>A·需求(50%)</t>
         </is>
       </c>
-      <c r="D97" s="78" t="inlineStr">
+      <c r="E97" s="78" t="inlineStr">
         <is>
           <t>• CC 全量迁移进度跟踪 + 范围变更裁决</t>
         </is>
       </c>
-      <c r="E97" s="79" t="inlineStr">
+      <c r="F97" s="79" t="inlineStr">
         <is>
           <t>范围冻结；报表口径确认</t>
         </is>
       </c>
-      <c r="F97" s="80" t="inlineStr"/>
-      <c r="G97" s="59" t="n"/>
+      <c r="G97" s="80" t="inlineStr"/>
       <c r="H97" s="59" t="n"/>
       <c r="I97" s="59" t="n"/>
+      <c r="J97" s="59" t="n"/>
     </row>
     <row r="98" ht="22" customHeight="1">
-      <c r="A98" s="81" t="n"/>
       <c r="B98" s="81" t="n"/>
-      <c r="C98" s="82" t="n"/>
-      <c r="D98" s="78" t="inlineStr">
+      <c r="C98" s="81" t="n"/>
+      <c r="D98" s="82" t="n"/>
+      <c r="E98" s="78" t="inlineStr">
         <is>
           <t>• 合规报表口径与法务对齐（等保/个保法条目映射）</t>
         </is>
       </c>
-      <c r="E98" s="81" t="n"/>
       <c r="F98" s="81" t="n"/>
-      <c r="G98" s="59" t="n"/>
+      <c r="G98" s="81" t="n"/>
       <c r="H98" s="59" t="n"/>
       <c r="I98" s="59" t="n"/>
+      <c r="J98" s="59" t="n"/>
     </row>
     <row r="99" ht="22" customHeight="1">
-      <c r="A99" s="93" t="inlineStr">
+      <c r="A99" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B99" s="93" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B99" s="76" t="inlineStr">
+      <c r="C99" s="76" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="C99" s="83" t="inlineStr">
+      <c r="D99" s="83" t="inlineStr">
         <is>
           <t>B·架构+开发</t>
         </is>
       </c>
-      <c r="D99" s="78" t="inlineStr">
+      <c r="E99" s="78" t="inlineStr">
         <is>
           <t>• CC 全量迁移技术指挥（分批策略/失败重跑/优先级）</t>
         </is>
       </c>
-      <c r="E99" s="79" t="inlineStr">
+      <c r="F99" s="79" t="inlineStr">
         <is>
           <t>全量迁移启动；隔离验证通过</t>
         </is>
       </c>
-      <c r="F99" s="80" t="inlineStr"/>
-      <c r="G99" s="59" t="n"/>
+      <c r="G99" s="80" t="inlineStr"/>
       <c r="H99" s="59" t="n"/>
       <c r="I99" s="59" t="n"/>
+      <c r="J99" s="59" t="n"/>
     </row>
     <row r="100" ht="22" customHeight="1">
-      <c r="A100" s="81" t="n"/>
       <c r="B100" s="81" t="n"/>
-      <c r="C100" s="84" t="n"/>
-      <c r="D100" s="78" t="inlineStr">
+      <c r="C100" s="81" t="n"/>
+      <c r="D100" s="84" t="n"/>
+      <c r="E100" s="78" t="inlineStr">
         <is>
           <t>• 【07】连接器架构评审（模板化扩展性）</t>
         </is>
       </c>
-      <c r="E100" s="81" t="n"/>
       <c r="F100" s="81" t="n"/>
-      <c r="G100" s="59" t="n"/>
+      <c r="G100" s="81" t="n"/>
       <c r="H100" s="59" t="n"/>
       <c r="I100" s="59" t="n"/>
+      <c r="J100" s="59" t="n"/>
     </row>
     <row r="101" ht="22" customHeight="1">
-      <c r="A101" s="81" t="n"/>
       <c r="B101" s="81" t="n"/>
-      <c r="C101" s="84" t="n"/>
-      <c r="D101" s="78" t="inlineStr">
+      <c r="C101" s="81" t="n"/>
+      <c r="D101" s="84" t="n"/>
+      <c r="E101" s="78" t="inlineStr">
         <is>
           <t>• 【08】行级隔离验证（越权测试全过）</t>
         </is>
       </c>
-      <c r="E101" s="81" t="n"/>
       <c r="F101" s="81" t="n"/>
-      <c r="G101" s="59" t="n"/>
+      <c r="G101" s="81" t="n"/>
       <c r="H101" s="59" t="n"/>
       <c r="I101" s="59" t="n"/>
+      <c r="J101" s="59" t="n"/>
     </row>
     <row r="102" ht="30" customHeight="1">
-      <c r="A102" s="93" t="inlineStr">
+      <c r="A102" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B102" s="93" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B102" s="76" t="inlineStr">
+      <c r="C102" s="76" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="C102" s="85" t="inlineStr">
+      <c r="D102" s="85" t="inlineStr">
         <is>
           <t>C·数据工程</t>
         </is>
       </c>
-      <c r="D102" s="78" t="inlineStr">
+      <c r="E102" s="78" t="inlineStr">
         <is>
           <t>• 【01】CC 全量 1253 表分批迁移（剔除垃圾表后约 600~800 张，分 5~8 批）</t>
         </is>
       </c>
-      <c r="E102" s="79" t="inlineStr">
+      <c r="F102" s="79" t="inlineStr">
         <is>
           <t>全量迁移过半；模板库 v2</t>
         </is>
       </c>
-      <c r="F102" s="80" t="inlineStr">
+      <c r="G102" s="80" t="inlineStr">
         <is>
           <t>CC 数据量（sp_spaceused）</t>
         </is>
       </c>
-      <c r="G102" s="59" t="n"/>
       <c r="H102" s="59" t="n"/>
       <c r="I102" s="59" t="n"/>
+      <c r="J102" s="59" t="n"/>
     </row>
     <row r="103" ht="22" customHeight="1">
-      <c r="A103" s="81" t="n"/>
       <c r="B103" s="81" t="n"/>
-      <c r="C103" s="86" t="n"/>
-      <c r="D103" s="78" t="inlineStr">
+      <c r="C103" s="81" t="n"/>
+      <c r="D103" s="86" t="n"/>
+      <c r="E103" s="78" t="inlineStr">
         <is>
           <t>• 【07】连接器模板库扩展：MySQL 类型映射 + 文件源模板</t>
         </is>
       </c>
-      <c r="E103" s="81" t="n"/>
       <c r="F103" s="81" t="n"/>
-      <c r="G103" s="59" t="n"/>
+      <c r="G103" s="81" t="n"/>
       <c r="H103" s="59" t="n"/>
       <c r="I103" s="59" t="n"/>
+      <c r="J103" s="59" t="n"/>
     </row>
     <row r="104" ht="22" customHeight="1">
-      <c r="A104" s="81" t="n"/>
       <c r="B104" s="81" t="n"/>
-      <c r="C104" s="86" t="n"/>
-      <c r="D104" s="78" t="inlineStr">
+      <c r="C104" s="81" t="n"/>
+      <c r="D104" s="86" t="n"/>
+      <c r="E104" s="78" t="inlineStr">
         <is>
           <t>• 【07】连接器运行监控与审计上报</t>
         </is>
       </c>
-      <c r="E104" s="81" t="n"/>
       <c r="F104" s="81" t="n"/>
-      <c r="G104" s="59" t="n"/>
+      <c r="G104" s="81" t="n"/>
       <c r="H104" s="59" t="n"/>
       <c r="I104" s="59" t="n"/>
+      <c r="J104" s="59" t="n"/>
     </row>
     <row r="105" ht="22" customHeight="1">
-      <c r="A105" s="93" t="inlineStr">
+      <c r="A105" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B105" s="93" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B105" s="76" t="inlineStr">
+      <c r="C105" s="76" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="C105" s="87" t="inlineStr">
+      <c r="D105" s="87" t="inlineStr">
         <is>
           <t>D·全栈+DevOps</t>
         </is>
       </c>
-      <c r="D105" s="78" t="inlineStr">
+      <c r="E105" s="78" t="inlineStr">
         <is>
           <t>• 【07】多源连接管理界面（配置/测试连接/模板选择/状态监控）</t>
         </is>
       </c>
-      <c r="E105" s="79" t="inlineStr">
+      <c r="F105" s="79" t="inlineStr">
         <is>
           <t>连接管理可用；报表完善</t>
         </is>
       </c>
-      <c r="F105" s="80" t="inlineStr"/>
-      <c r="G105" s="59" t="n"/>
+      <c r="G105" s="80" t="inlineStr"/>
       <c r="H105" s="59" t="n"/>
       <c r="I105" s="59" t="n"/>
+      <c r="J105" s="59" t="n"/>
     </row>
     <row r="106" ht="22" customHeight="1">
-      <c r="A106" s="81" t="n"/>
       <c r="B106" s="81" t="n"/>
-      <c r="C106" s="88" t="n"/>
-      <c r="D106" s="78" t="inlineStr">
+      <c r="C106" s="81" t="n"/>
+      <c r="D106" s="88" t="n"/>
+      <c r="E106" s="78" t="inlineStr">
         <is>
           <t>• 【06】合规报表完善（等保/个保法对照视图 + 一键导出）</t>
         </is>
       </c>
-      <c r="E106" s="81" t="n"/>
       <c r="F106" s="81" t="n"/>
-      <c r="G106" s="59" t="n"/>
+      <c r="G106" s="81" t="n"/>
       <c r="H106" s="59" t="n"/>
       <c r="I106" s="59" t="n"/>
+      <c r="J106" s="59" t="n"/>
     </row>
     <row r="107" ht="22" customHeight="1">
-      <c r="A107" s="93" t="inlineStr">
+      <c r="A107" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B107" s="93" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B107" s="76" t="inlineStr">
+      <c r="C107" s="76" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="C107" s="89" t="inlineStr">
+      <c r="D107" s="89" t="inlineStr">
         <is>
           <t>E·QA+SLC文档</t>
         </is>
       </c>
-      <c r="D107" s="78" t="inlineStr">
+      <c r="E107" s="78" t="inlineStr">
         <is>
           <t>• 【07】连接器兼容性测试（SQL Server/MySQL 逐版本矩阵）</t>
         </is>
       </c>
-      <c r="E107" s="79" t="inlineStr">
+      <c r="F107" s="79" t="inlineStr">
         <is>
           <t>兼容矩阵；手册 50%</t>
         </is>
       </c>
-      <c r="F107" s="80" t="inlineStr"/>
-      <c r="G107" s="59" t="n"/>
+      <c r="G107" s="80" t="inlineStr"/>
       <c r="H107" s="59" t="n"/>
       <c r="I107" s="59" t="n"/>
+      <c r="J107" s="59" t="n"/>
     </row>
     <row r="108" ht="22" customHeight="1">
-      <c r="A108" s="81" t="n"/>
       <c r="B108" s="81" t="n"/>
-      <c r="C108" s="90" t="n"/>
-      <c r="D108" s="78" t="inlineStr">
+      <c r="C108" s="81" t="n"/>
+      <c r="D108" s="90" t="n"/>
+      <c r="E108" s="78" t="inlineStr">
         <is>
           <t>• 【06】合规报表口径验证（可举证性：谁在何时查了什么）</t>
         </is>
       </c>
-      <c r="E108" s="81" t="n"/>
       <c r="F108" s="81" t="n"/>
-      <c r="G108" s="59" t="n"/>
+      <c r="G108" s="81" t="n"/>
       <c r="H108" s="59" t="n"/>
       <c r="I108" s="59" t="n"/>
+      <c r="J108" s="59" t="n"/>
     </row>
     <row r="109" ht="22" customHeight="1">
-      <c r="A109" s="81" t="n"/>
       <c r="B109" s="81" t="n"/>
-      <c r="C109" s="90" t="n"/>
-      <c r="D109" s="78" t="inlineStr">
+      <c r="C109" s="81" t="n"/>
+      <c r="D109" s="90" t="n"/>
+      <c r="E109" s="78" t="inlineStr">
         <is>
           <t>• 用户手册初稿（50%，按 8 域组织）</t>
         </is>
       </c>
-      <c r="E109" s="81" t="n"/>
       <c r="F109" s="81" t="n"/>
-      <c r="G109" s="59" t="n"/>
+      <c r="G109" s="81" t="n"/>
       <c r="H109" s="59" t="n"/>
       <c r="I109" s="59" t="n"/>
+      <c r="J109" s="59" t="n"/>
     </row>
     <row r="110" ht="22" customHeight="1">
-      <c r="A110" s="93" t="inlineStr">
+      <c r="A110" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B110" s="93" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B110" s="76" t="inlineStr">
+      <c r="C110" s="76" t="inlineStr">
         <is>
           <t>W8</t>
         </is>
       </c>
-      <c r="C110" s="77" t="inlineStr">
+      <c r="D110" s="77" t="inlineStr">
         <is>
           <t>A·需求(50%)</t>
         </is>
       </c>
-      <c r="D110" s="78" t="inlineStr">
+      <c r="E110" s="78" t="inlineStr">
         <is>
           <t>• 验收 Sprint 3 交付（全量对账/连接器演示/报表）</t>
         </is>
       </c>
-      <c r="E110" s="79" t="inlineStr">
+      <c r="F110" s="79" t="inlineStr">
         <is>
           <t>S3 验收；UAT 脚本定稿</t>
         </is>
       </c>
-      <c r="F110" s="80" t="inlineStr"/>
-      <c r="G110" s="59" t="n"/>
+      <c r="G110" s="80" t="inlineStr"/>
       <c r="H110" s="59" t="n"/>
       <c r="I110" s="59" t="n"/>
+      <c r="J110" s="59" t="n"/>
     </row>
     <row r="111" ht="22" customHeight="1">
-      <c r="A111" s="81" t="n"/>
       <c r="B111" s="81" t="n"/>
-      <c r="C111" s="82" t="n"/>
-      <c r="D111" s="78" t="inlineStr">
+      <c r="C111" s="81" t="n"/>
+      <c r="D111" s="82" t="n"/>
+      <c r="E111" s="78" t="inlineStr">
         <is>
           <t>• UAT 场景脚本定稿（8 域场景）</t>
         </is>
       </c>
-      <c r="E111" s="81" t="n"/>
       <c r="F111" s="81" t="n"/>
-      <c r="G111" s="59" t="n"/>
+      <c r="G111" s="81" t="n"/>
       <c r="H111" s="59" t="n"/>
       <c r="I111" s="59" t="n"/>
+      <c r="J111" s="59" t="n"/>
     </row>
     <row r="112" ht="22" customHeight="1">
-      <c r="A112" s="93" t="inlineStr">
+      <c r="A112" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B112" s="93" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B112" s="76" t="inlineStr">
+      <c r="C112" s="76" t="inlineStr">
         <is>
           <t>W8</t>
         </is>
       </c>
-      <c r="C112" s="83" t="inlineStr">
+      <c r="D112" s="83" t="inlineStr">
         <is>
           <t>B·架构+开发</t>
         </is>
       </c>
-      <c r="D112" s="78" t="inlineStr">
+      <c r="E112" s="78" t="inlineStr">
         <is>
           <t>• CC 全量迁移收尾 + 对账复核</t>
         </is>
       </c>
-      <c r="E112" s="79" t="inlineStr">
+      <c r="F112" s="79" t="inlineStr">
         <is>
           <t>全量对账 100%；生产包就绪</t>
         </is>
       </c>
-      <c r="F112" s="80" t="inlineStr"/>
-      <c r="G112" s="59" t="n"/>
+      <c r="G112" s="80" t="inlineStr"/>
       <c r="H112" s="59" t="n"/>
       <c r="I112" s="59" t="n"/>
+      <c r="J112" s="59" t="n"/>
     </row>
     <row r="113" ht="22" customHeight="1">
-      <c r="A113" s="81" t="n"/>
       <c r="B113" s="81" t="n"/>
-      <c r="C113" s="84" t="n"/>
-      <c r="D113" s="78" t="inlineStr">
+      <c r="C113" s="81" t="n"/>
+      <c r="D113" s="84" t="n"/>
+      <c r="E113" s="78" t="inlineStr">
         <is>
           <t>• 生产发布准备：Helm values + UC 权限/掩码/生命周期/驻留 生产版脚本</t>
         </is>
       </c>
-      <c r="E113" s="81" t="n"/>
       <c r="F113" s="81" t="n"/>
-      <c r="G113" s="59" t="n"/>
+      <c r="G113" s="81" t="n"/>
       <c r="H113" s="59" t="n"/>
       <c r="I113" s="59" t="n"/>
+      <c r="J113" s="59" t="n"/>
     </row>
     <row r="114" ht="22" customHeight="1">
-      <c r="A114" s="93" t="inlineStr">
+      <c r="A114" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B114" s="93" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B114" s="76" t="inlineStr">
+      <c r="C114" s="76" t="inlineStr">
         <is>
           <t>W8</t>
         </is>
       </c>
-      <c r="C114" s="85" t="inlineStr">
+      <c r="D114" s="85" t="inlineStr">
         <is>
           <t>C·数据工程</t>
         </is>
       </c>
-      <c r="D114" s="78" t="inlineStr">
+      <c r="E114" s="78" t="inlineStr">
         <is>
           <t>• CC 全量迁移完成 + 全量对账报告</t>
         </is>
       </c>
-      <c r="E114" s="79" t="inlineStr">
+      <c r="F114" s="79" t="inlineStr">
         <is>
           <t>全量对账 100% 报告</t>
         </is>
       </c>
-      <c r="F114" s="80" t="inlineStr"/>
-      <c r="G114" s="59" t="n"/>
+      <c r="G114" s="80" t="inlineStr"/>
       <c r="H114" s="59" t="n"/>
       <c r="I114" s="59" t="n"/>
+      <c r="J114" s="59" t="n"/>
     </row>
     <row r="115" ht="22" customHeight="1">
-      <c r="A115" s="81" t="n"/>
       <c r="B115" s="81" t="n"/>
-      <c r="C115" s="86" t="n"/>
-      <c r="D115" s="78" t="inlineStr">
+      <c r="C115" s="81" t="n"/>
+      <c r="D115" s="86" t="n"/>
+      <c r="E115" s="78" t="inlineStr">
         <is>
           <t>• 生产 Jobs 准备（增量/Compaction/处置 生产版）</t>
         </is>
       </c>
-      <c r="E115" s="81" t="n"/>
       <c r="F115" s="81" t="n"/>
-      <c r="G115" s="59" t="n"/>
+      <c r="G115" s="81" t="n"/>
       <c r="H115" s="59" t="n"/>
       <c r="I115" s="59" t="n"/>
+      <c r="J115" s="59" t="n"/>
     </row>
     <row r="116" ht="22" customHeight="1">
-      <c r="A116" s="81" t="n"/>
       <c r="B116" s="81" t="n"/>
-      <c r="C116" s="86" t="n"/>
-      <c r="D116" s="78" t="inlineStr">
+      <c r="C116" s="81" t="n"/>
+      <c r="D116" s="86" t="n"/>
+      <c r="E116" s="78" t="inlineStr">
         <is>
           <t>• 增量链路稳定性加固（重试/告警）</t>
         </is>
       </c>
-      <c r="E116" s="81" t="n"/>
       <c r="F116" s="81" t="n"/>
-      <c r="G116" s="59" t="n"/>
+      <c r="G116" s="81" t="n"/>
       <c r="H116" s="59" t="n"/>
       <c r="I116" s="59" t="n"/>
+      <c r="J116" s="59" t="n"/>
     </row>
     <row r="117" ht="22" customHeight="1">
-      <c r="A117" s="93" t="inlineStr">
+      <c r="A117" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B117" s="93" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B117" s="76" t="inlineStr">
+      <c r="C117" s="76" t="inlineStr">
         <is>
           <t>W8</t>
         </is>
       </c>
-      <c r="C117" s="87" t="inlineStr">
+      <c r="D117" s="87" t="inlineStr">
         <is>
           <t>D·全栈+DevOps</t>
         </is>
       </c>
-      <c r="D117" s="78" t="inlineStr">
+      <c r="E117" s="78" t="inlineStr">
         <is>
           <t>• 全量回归测试支持 + Bug 修复</t>
         </is>
       </c>
-      <c r="E117" s="79" t="inlineStr">
+      <c r="F117" s="79" t="inlineStr">
         <is>
           <t>回归通过；监控就绪</t>
         </is>
       </c>
-      <c r="F117" s="80" t="inlineStr"/>
-      <c r="G117" s="59" t="n"/>
+      <c r="G117" s="80" t="inlineStr"/>
       <c r="H117" s="59" t="n"/>
       <c r="I117" s="59" t="n"/>
+      <c r="J117" s="59" t="n"/>
     </row>
     <row r="118" ht="22" customHeight="1">
-      <c r="A118" s="81" t="n"/>
       <c r="B118" s="81" t="n"/>
-      <c r="C118" s="88" t="n"/>
-      <c r="D118" s="78" t="inlineStr">
+      <c r="C118" s="81" t="n"/>
+      <c r="D118" s="88" t="n"/>
+      <c r="E118" s="78" t="inlineStr">
         <is>
           <t>• 生产监控接入（App Insights + 告警规则）</t>
         </is>
       </c>
-      <c r="E118" s="81" t="n"/>
       <c r="F118" s="81" t="n"/>
-      <c r="G118" s="59" t="n"/>
+      <c r="G118" s="81" t="n"/>
       <c r="H118" s="59" t="n"/>
       <c r="I118" s="59" t="n"/>
+      <c r="J118" s="59" t="n"/>
     </row>
     <row r="119" ht="22" customHeight="1">
-      <c r="A119" s="81" t="n"/>
       <c r="B119" s="81" t="n"/>
-      <c r="C119" s="88" t="n"/>
-      <c r="D119" s="78" t="inlineStr">
+      <c r="C119" s="81" t="n"/>
+      <c r="D119" s="88" t="n"/>
+      <c r="E119" s="78" t="inlineStr">
         <is>
           <t>• 安全回归：新增代码扫描全过 + CVE 清单处理</t>
         </is>
       </c>
-      <c r="E119" s="81" t="n"/>
       <c r="F119" s="81" t="n"/>
-      <c r="G119" s="59" t="n"/>
+      <c r="G119" s="81" t="n"/>
       <c r="H119" s="59" t="n"/>
       <c r="I119" s="59" t="n"/>
+      <c r="J119" s="59" t="n"/>
     </row>
     <row r="120" ht="22" customHeight="1">
-      <c r="A120" s="93" t="inlineStr">
+      <c r="A120" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B120" s="93" t="inlineStr">
         <is>
           <t>Sprint 3</t>
         </is>
       </c>
-      <c r="B120" s="76" t="inlineStr">
+      <c r="C120" s="76" t="inlineStr">
         <is>
           <t>W8</t>
         </is>
       </c>
-      <c r="C120" s="89" t="inlineStr">
+      <c r="D120" s="89" t="inlineStr">
         <is>
           <t>E·QA+SLC文档</t>
         </is>
       </c>
-      <c r="D120" s="78" t="inlineStr">
+      <c r="E120" s="78" t="inlineStr">
         <is>
           <t>• 全量回归测试（S1~S3 全功能）</t>
         </is>
       </c>
-      <c r="E120" s="79" t="inlineStr">
+      <c r="F120" s="79" t="inlineStr">
         <is>
           <t>回归全过；字典/运维初稿</t>
         </is>
       </c>
-      <c r="F120" s="80" t="inlineStr"/>
-      <c r="G120" s="59" t="n"/>
+      <c r="G120" s="80" t="inlineStr"/>
       <c r="H120" s="59" t="n"/>
       <c r="I120" s="59" t="n"/>
+      <c r="J120" s="59" t="n"/>
     </row>
     <row r="121" ht="22" customHeight="1">
-      <c r="A121" s="81" t="n"/>
       <c r="B121" s="81" t="n"/>
-      <c r="C121" s="90" t="n"/>
-      <c r="D121" s="78" t="inlineStr">
+      <c r="C121" s="81" t="n"/>
+      <c r="D121" s="90" t="n"/>
+      <c r="E121" s="78" t="inlineStr">
         <is>
           <t>• 性能测试（20GB P95&lt;5s）</t>
         </is>
       </c>
-      <c r="E121" s="81" t="n"/>
       <c r="F121" s="81" t="n"/>
-      <c r="G121" s="59" t="n"/>
+      <c r="G121" s="81" t="n"/>
       <c r="H121" s="59" t="n"/>
       <c r="I121" s="59" t="n"/>
+      <c r="J121" s="59" t="n"/>
     </row>
     <row r="122" ht="22" customHeight="1">
-      <c r="A122" s="81" t="n"/>
       <c r="B122" s="81" t="n"/>
-      <c r="C122" s="90" t="n"/>
-      <c r="D122" s="78" t="inlineStr">
+      <c r="C122" s="81" t="n"/>
+      <c r="D122" s="90" t="n"/>
+      <c r="E122" s="78" t="inlineStr">
         <is>
           <t>• 数据字典初稿 + 运维手册初稿</t>
         </is>
       </c>
-      <c r="E122" s="81" t="n"/>
       <c r="F122" s="81" t="n"/>
-      <c r="G122" s="59" t="n"/>
+      <c r="G122" s="81" t="n"/>
       <c r="H122" s="59" t="n"/>
       <c r="I122" s="59" t="n"/>
+      <c r="J122" s="59" t="n"/>
     </row>
     <row r="123" ht="22" customHeight="1">
-      <c r="A123" s="81" t="n"/>
       <c r="B123" s="81" t="n"/>
-      <c r="C123" s="90" t="n"/>
-      <c r="D123" s="78" t="inlineStr">
+      <c r="C123" s="81" t="n"/>
+      <c r="D123" s="90" t="n"/>
+      <c r="E123" s="78" t="inlineStr">
         <is>
           <t>• Sprint 3 测试报告</t>
         </is>
       </c>
-      <c r="E123" s="81" t="n"/>
       <c r="F123" s="81" t="n"/>
-      <c r="G123" s="59" t="n"/>
+      <c r="G123" s="81" t="n"/>
       <c r="H123" s="59" t="n"/>
       <c r="I123" s="59" t="n"/>
+      <c r="J123" s="59" t="n"/>
     </row>
     <row r="124" ht="22" customHeight="1">
-      <c r="A124" s="94" t="inlineStr">
+      <c r="A124" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B124" s="94" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B124" s="76" t="inlineStr">
+      <c r="C124" s="76" t="inlineStr">
         <is>
           <t>W9</t>
         </is>
       </c>
-      <c r="C124" s="77" t="inlineStr">
+      <c r="D124" s="77" t="inlineStr">
         <is>
           <t>A·需求(50%)</t>
         </is>
       </c>
-      <c r="D124" s="78" t="inlineStr">
-        <is>
-          <t>• UAT 组织协调（业务方排期 + 环境准备）</t>
-        </is>
-      </c>
-      <c r="E124" s="79" t="inlineStr">
-        <is>
-          <t>UAT 排期确认；冻结声明</t>
-        </is>
-      </c>
-      <c r="F124" s="80" t="inlineStr">
-        <is>
-          <t>业务方排期</t>
-        </is>
-      </c>
-      <c r="G124" s="59" t="n"/>
+      <c r="E124" s="78" t="inlineStr">
+        <is>
+          <t>• 功能验收收口（S1~S4 用户故事全覆盖核对）</t>
+        </is>
+      </c>
+      <c r="F124" s="119" t="inlineStr">
+        <is>
+          <t>功能验收清单 100%</t>
+        </is>
+      </c>
+      <c r="G124" s="80" t="inlineStr"/>
       <c r="H124" s="59" t="n"/>
       <c r="I124" s="59" t="n"/>
+      <c r="J124" s="59" t="n"/>
     </row>
     <row r="125" ht="22" customHeight="1">
-      <c r="A125" s="81" t="n"/>
-      <c r="B125" s="81" t="n"/>
-      <c r="C125" s="82" t="n"/>
-      <c r="D125" s="78" t="inlineStr">
-        <is>
-          <t>• 需求冻结（Scope Freeze）宣布</t>
-        </is>
-      </c>
-      <c r="E125" s="81" t="n"/>
-      <c r="F125" s="81" t="n"/>
-      <c r="G125" s="59" t="n"/>
+      <c r="B125" s="120" t="n"/>
+      <c r="C125" s="120" t="n"/>
+      <c r="D125" s="121" t="n"/>
+      <c r="E125" s="78" t="inlineStr">
+        <is>
+          <t>• 生产迁移范围最终确认（含增量基线）</t>
+        </is>
+      </c>
+      <c r="F125" s="120" t="n"/>
+      <c r="G125" s="120" t="n"/>
       <c r="H125" s="59" t="n"/>
       <c r="I125" s="59" t="n"/>
-    </row>
-    <row r="126" ht="22" customHeight="1">
-      <c r="A126" s="94" t="inlineStr">
+      <c r="J125" s="59" t="n"/>
+    </row>
+    <row r="126" ht="30" customHeight="1">
+      <c r="A126" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B126" s="94" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B126" s="76" t="inlineStr">
+      <c r="C126" s="76" t="inlineStr">
         <is>
           <t>W9</t>
         </is>
       </c>
-      <c r="C126" s="83" t="inlineStr">
+      <c r="D126" s="83" t="inlineStr">
         <is>
           <t>B·架构+开发</t>
         </is>
       </c>
-      <c r="D126" s="78" t="inlineStr">
-        <is>
-          <t>• 生产发布执行：Helm + UC 权限/掩码/生命周期/驻留核查生产版</t>
-        </is>
-      </c>
-      <c r="E126" s="79" t="inlineStr">
-        <is>
-          <t>生产环境 8 域就绪；安全材料</t>
-        </is>
-      </c>
-      <c r="F126" s="80" t="inlineStr">
-        <is>
-          <t>生产环境</t>
-        </is>
-      </c>
-      <c r="G126" s="59" t="n"/>
+      <c r="E126" s="78" t="inlineStr">
+        <is>
+          <t>• 🤖 生产发布包：Helm 生产 values + UC 权限/掩码/生命周期/驻留 生产脚本（一键发布就绪）</t>
+        </is>
+      </c>
+      <c r="F126" s="119" t="inlineStr">
+        <is>
+          <t>发布包就绪；回退演练通过</t>
+        </is>
+      </c>
+      <c r="G126" s="80" t="inlineStr"/>
       <c r="H126" s="59" t="n"/>
       <c r="I126" s="59" t="n"/>
+      <c r="J126" s="59" t="n"/>
     </row>
     <row r="127" ht="22" customHeight="1">
-      <c r="A127" s="81" t="n"/>
-      <c r="B127" s="81" t="n"/>
-      <c r="C127" s="84" t="n"/>
-      <c r="D127" s="78" t="inlineStr">
-        <is>
-          <t>• 安全评审材料（加密/脱敏/驻留/权限技术说明）</t>
-        </is>
-      </c>
-      <c r="E127" s="81" t="n"/>
-      <c r="F127" s="81" t="n"/>
-      <c r="G127" s="59" t="n"/>
+      <c r="B127" s="120" t="n"/>
+      <c r="C127" s="120" t="n"/>
+      <c r="D127" s="122" t="n"/>
+      <c r="E127" s="78" t="inlineStr">
+        <is>
+          <t>• 回退预案制定与演练（发布回滚 + UC 配置回滚）</t>
+        </is>
+      </c>
+      <c r="F127" s="120" t="n"/>
+      <c r="G127" s="120" t="n"/>
       <c r="H127" s="59" t="n"/>
       <c r="I127" s="59" t="n"/>
+      <c r="J127" s="59" t="n"/>
     </row>
     <row r="128" ht="22" customHeight="1">
-      <c r="A128" s="94" t="inlineStr">
+      <c r="A128" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B128" s="94" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B128" s="76" t="inlineStr">
+      <c r="C128" s="76" t="inlineStr">
         <is>
           <t>W9</t>
         </is>
       </c>
-      <c r="C128" s="85" t="inlineStr">
+      <c r="D128" s="85" t="inlineStr">
         <is>
           <t>C·数据工程</t>
         </is>
       </c>
-      <c r="D128" s="78" t="inlineStr">
-        <is>
-          <t>• CC 生产全量迁移执行（分批 + 对账）</t>
-        </is>
-      </c>
-      <c r="E128" s="79" t="inlineStr">
-        <is>
-          <t>生产全量入湖；对账通过</t>
-        </is>
-      </c>
-      <c r="F128" s="80" t="inlineStr">
-        <is>
-          <t>生产资源就绪</t>
-        </is>
-      </c>
-      <c r="G128" s="59" t="n"/>
+      <c r="E128" s="78" t="inlineStr">
+        <is>
+          <t>• 【01】CC 全量迁移预跑（Staging 全量或大样本批次，验证时长与失败率）</t>
+        </is>
+      </c>
+      <c r="F128" s="119" t="inlineStr">
+        <is>
+          <t>预跑完成；Runbook 定稿</t>
+        </is>
+      </c>
+      <c r="G128" s="80" t="inlineStr">
+        <is>
+          <t>生产窗口审批</t>
+        </is>
+      </c>
       <c r="H128" s="59" t="n"/>
       <c r="I128" s="59" t="n"/>
+      <c r="J128" s="59" t="n"/>
     </row>
     <row r="129" ht="22" customHeight="1">
-      <c r="A129" s="81" t="n"/>
-      <c r="B129" s="81" t="n"/>
-      <c r="C129" s="86" t="n"/>
-      <c r="D129" s="78" t="inlineStr">
-        <is>
-          <t>• 生产 Jobs 发布（增量/Compaction/处置）</t>
-        </is>
-      </c>
-      <c r="E129" s="81" t="n"/>
-      <c r="F129" s="81" t="n"/>
-      <c r="G129" s="59" t="n"/>
+      <c r="B129" s="120" t="n"/>
+      <c r="C129" s="120" t="n"/>
+      <c r="D129" s="123" t="n"/>
+      <c r="E129" s="78" t="inlineStr">
+        <is>
+          <t>• 生产迁移窗口预约（W10 晚或 W11 周末）+ 迁移 Runbook</t>
+        </is>
+      </c>
+      <c r="F129" s="120" t="n"/>
+      <c r="G129" s="120" t="n"/>
       <c r="H129" s="59" t="n"/>
       <c r="I129" s="59" t="n"/>
+      <c r="J129" s="59" t="n"/>
     </row>
     <row r="130" ht="22" customHeight="1">
-      <c r="A130" s="81" t="n"/>
-      <c r="B130" s="81" t="n"/>
-      <c r="C130" s="86" t="n"/>
-      <c r="D130" s="78" t="inlineStr">
-        <is>
-          <t>• 迁移问题处理</t>
-        </is>
-      </c>
-      <c r="E130" s="81" t="n"/>
-      <c r="F130" s="81" t="n"/>
-      <c r="G130" s="59" t="n"/>
+      <c r="B130" s="120" t="n"/>
+      <c r="C130" s="120" t="n"/>
+      <c r="D130" s="123" t="n"/>
+      <c r="E130" s="78" t="inlineStr">
+        <is>
+          <t>• 增量链路稳定性加固（重试/告警/幂等）</t>
+        </is>
+      </c>
+      <c r="F130" s="120" t="n"/>
+      <c r="G130" s="120" t="n"/>
       <c r="H130" s="59" t="n"/>
       <c r="I130" s="59" t="n"/>
+      <c r="J130" s="59" t="n"/>
     </row>
     <row r="131" ht="22" customHeight="1">
-      <c r="A131" s="94" t="inlineStr">
+      <c r="A131" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B131" s="94" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B131" s="76" t="inlineStr">
+      <c r="C131" s="76" t="inlineStr">
         <is>
           <t>W9</t>
         </is>
       </c>
-      <c r="C131" s="87" t="inlineStr">
+      <c r="D131" s="87" t="inlineStr">
         <is>
           <t>D·全栈+DevOps</t>
         </is>
       </c>
-      <c r="D131" s="78" t="inlineStr">
-        <is>
-          <t>• 生产部署验证（8 域功能全通）</t>
-        </is>
-      </c>
-      <c r="E131" s="79" t="inlineStr">
-        <is>
-          <t>生产验证通过；安全终检过</t>
-        </is>
-      </c>
-      <c r="F131" s="80" t="inlineStr"/>
-      <c r="G131" s="59" t="n"/>
+      <c r="E131" s="78" t="inlineStr">
+        <is>
+          <t>• 安全终检：四道门禁生产版全过（SAST/依赖/密钥/镜像）+ 渗透测试配合</t>
+        </is>
+      </c>
+      <c r="F131" s="119" t="inlineStr">
+        <is>
+          <t>安全终检通过；监控就绪</t>
+        </is>
+      </c>
+      <c r="G131" s="80" t="inlineStr">
+        <is>
+          <t>渗透测试排期</t>
+        </is>
+      </c>
       <c r="H131" s="59" t="n"/>
       <c r="I131" s="59" t="n"/>
+      <c r="J131" s="59" t="n"/>
     </row>
     <row r="132" ht="22" customHeight="1">
-      <c r="A132" s="81" t="n"/>
-      <c r="B132" s="81" t="n"/>
-      <c r="C132" s="88" t="n"/>
-      <c r="D132" s="78" t="inlineStr">
-        <is>
-          <t>• 安全四门禁生产终检（SAST/依赖/密钥/镜像全过 + 渗透配合）</t>
-        </is>
-      </c>
-      <c r="E132" s="81" t="n"/>
-      <c r="F132" s="81" t="n"/>
-      <c r="G132" s="59" t="n"/>
+      <c r="B132" s="120" t="n"/>
+      <c r="C132" s="120" t="n"/>
+      <c r="D132" s="124" t="n"/>
+      <c r="E132" s="78" t="inlineStr">
+        <is>
+          <t>• 生产监控告警就绪（App Insights + 告警规则 + Dashboard）</t>
+        </is>
+      </c>
+      <c r="F132" s="120" t="n"/>
+      <c r="G132" s="120" t="n"/>
       <c r="H132" s="59" t="n"/>
       <c r="I132" s="59" t="n"/>
+      <c r="J132" s="59" t="n"/>
     </row>
     <row r="133" ht="22" customHeight="1">
-      <c r="A133" s="81" t="n"/>
-      <c r="B133" s="81" t="n"/>
-      <c r="C133" s="88" t="n"/>
-      <c r="D133" s="78" t="inlineStr">
-        <is>
-          <t>• 监控 Dashboard 完善</t>
-        </is>
-      </c>
-      <c r="E133" s="81" t="n"/>
-      <c r="F133" s="81" t="n"/>
-      <c r="G133" s="59" t="n"/>
+      <c r="B133" s="120" t="n"/>
+      <c r="C133" s="120" t="n"/>
+      <c r="D133" s="124" t="n"/>
+      <c r="E133" s="78" t="inlineStr">
+        <is>
+          <t>• 功能打磨：性能优化 + 遗留 Bug 清零</t>
+        </is>
+      </c>
+      <c r="F133" s="120" t="n"/>
+      <c r="G133" s="120" t="n"/>
       <c r="H133" s="59" t="n"/>
       <c r="I133" s="59" t="n"/>
+      <c r="J133" s="59" t="n"/>
     </row>
     <row r="134" ht="22" customHeight="1">
-      <c r="A134" s="94" t="inlineStr">
+      <c r="A134" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B134" s="94" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B134" s="76" t="inlineStr">
+      <c r="C134" s="76" t="inlineStr">
         <is>
           <t>W9</t>
         </is>
       </c>
-      <c r="C134" s="89" t="inlineStr">
+      <c r="D134" s="89" t="inlineStr">
         <is>
           <t>E·QA+SLC文档</t>
         </is>
       </c>
-      <c r="D134" s="78" t="inlineStr">
-        <is>
-          <t>• 文档冲刺：用户手册 80% + 运维手册 80% + 数据字典 80% + 架构图更新</t>
-        </is>
-      </c>
-      <c r="E134" s="79" t="inlineStr">
-        <is>
-          <t>6 套文档 80%；审批材料初稿</t>
-        </is>
-      </c>
-      <c r="F134" s="80" t="inlineStr"/>
-      <c r="G134" s="59" t="n"/>
+      <c r="E134" s="78" t="inlineStr">
+        <is>
+          <t>• 文档 80%：用户手册/运维手册/数据字典/架构图更新到实际部署</t>
+        </is>
+      </c>
+      <c r="F134" s="119" t="inlineStr">
+        <is>
+          <t>文档 80%；材料初稿；UAT 脚本 v2</t>
+        </is>
+      </c>
+      <c r="G134" s="80" t="inlineStr"/>
       <c r="H134" s="59" t="n"/>
       <c r="I134" s="59" t="n"/>
+      <c r="J134" s="59" t="n"/>
     </row>
     <row r="135" ht="22" customHeight="1">
-      <c r="A135" s="81" t="n"/>
-      <c r="B135" s="81" t="n"/>
-      <c r="C135" s="90" t="n"/>
-      <c r="D135" s="78" t="inlineStr">
-        <is>
-          <t>• 审批材料包初稿（技术方案/安全评估/合规对照）</t>
-        </is>
-      </c>
-      <c r="E135" s="81" t="n"/>
-      <c r="F135" s="81" t="n"/>
-      <c r="G135" s="59" t="n"/>
+      <c r="B135" s="120" t="n"/>
+      <c r="C135" s="120" t="n"/>
+      <c r="D135" s="125" t="n"/>
+      <c r="E135" s="78" t="inlineStr">
+        <is>
+          <t>• 🤖 审批材料起稿（技术方案/安全评估/合规对照）</t>
+        </is>
+      </c>
+      <c r="F135" s="120" t="n"/>
+      <c r="G135" s="120" t="n"/>
       <c r="H135" s="59" t="n"/>
       <c r="I135" s="59" t="n"/>
+      <c r="J135" s="59" t="n"/>
     </row>
     <row r="136" ht="22" customHeight="1">
-      <c r="A136" s="94" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="B136" s="76" t="inlineStr">
-        <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="C136" s="77" t="inlineStr">
-        <is>
-          <t>A·需求(50%)</t>
-        </is>
-      </c>
-      <c r="D136" s="78" t="inlineStr">
-        <is>
-          <t>• UAT 执行主持（8 域场景走查 + 记录）</t>
-        </is>
-      </c>
-      <c r="E136" s="79" t="inlineStr">
-        <is>
-          <t>UAT 报告（含签字）</t>
-        </is>
-      </c>
-      <c r="F136" s="80" t="inlineStr">
-        <is>
-          <t>业务方参与</t>
-        </is>
-      </c>
-      <c r="G136" s="59" t="n"/>
+      <c r="B136" s="120" t="n"/>
+      <c r="C136" s="120" t="n"/>
+      <c r="D136" s="125" t="n"/>
+      <c r="E136" s="78" t="inlineStr">
+        <is>
+          <t>• UAT 脚本 v2（8 域场景细化到操作步骤）</t>
+        </is>
+      </c>
+      <c r="F136" s="120" t="n"/>
+      <c r="G136" s="120" t="n"/>
       <c r="H136" s="59" t="n"/>
       <c r="I136" s="59" t="n"/>
+      <c r="J136" s="59" t="n"/>
     </row>
     <row r="137" ht="22" customHeight="1">
-      <c r="A137" s="81" t="n"/>
-      <c r="B137" s="81" t="n"/>
-      <c r="C137" s="82" t="n"/>
-      <c r="D137" s="78" t="inlineStr">
-        <is>
-          <t>• UAT 反馈分类（Bug/变更/澄清）+ 裁决</t>
-        </is>
-      </c>
-      <c r="E137" s="81" t="n"/>
-      <c r="F137" s="81" t="n"/>
-      <c r="G137" s="59" t="n"/>
+      <c r="A137" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B137" s="94" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C137" s="76" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="D137" s="77" t="inlineStr">
+        <is>
+          <t>A·需求(50%)</t>
+        </is>
+      </c>
+      <c r="E137" s="78" t="inlineStr">
+        <is>
+          <t>• UAT 预演主持（Staging 8 域走查，业务方提前介入）</t>
+        </is>
+      </c>
+      <c r="F137" s="119" t="inlineStr">
+        <is>
+          <t>预演完成；反馈清单</t>
+        </is>
+      </c>
+      <c r="G137" s="80" t="inlineStr">
+        <is>
+          <t>业务方预演排期</t>
+        </is>
+      </c>
       <c r="H137" s="59" t="n"/>
       <c r="I137" s="59" t="n"/>
+      <c r="J137" s="59" t="n"/>
     </row>
     <row r="138" ht="22" customHeight="1">
-      <c r="A138" s="94" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="B138" s="76" t="inlineStr">
-        <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="C138" s="83" t="inlineStr">
-        <is>
-          <t>B·架构+开发</t>
-        </is>
-      </c>
-      <c r="D138" s="78" t="inlineStr">
-        <is>
-          <t>• UAT 支撑：权限/处置/驻留问题修复</t>
-        </is>
-      </c>
-      <c r="E138" s="79" t="inlineStr">
-        <is>
-          <t>UAT 问题关闭；审批提交</t>
-        </is>
-      </c>
-      <c r="F138" s="80" t="inlineStr">
-        <is>
-          <t>审批方反馈</t>
-        </is>
-      </c>
-      <c r="G138" s="59" t="n"/>
+      <c r="B138" s="120" t="n"/>
+      <c r="C138" s="120" t="n"/>
+      <c r="D138" s="121" t="n"/>
+      <c r="E138" s="78" t="inlineStr">
+        <is>
+          <t>• UAT 反馈预分类（可修/可延/争议项裁决）</t>
+        </is>
+      </c>
+      <c r="F138" s="120" t="n"/>
+      <c r="G138" s="120" t="n"/>
       <c r="H138" s="59" t="n"/>
       <c r="I138" s="59" t="n"/>
+      <c r="J138" s="59" t="n"/>
     </row>
     <row r="139" ht="22" customHeight="1">
-      <c r="A139" s="81" t="n"/>
-      <c r="B139" s="81" t="n"/>
-      <c r="C139" s="84" t="n"/>
-      <c r="D139" s="78" t="inlineStr">
-        <is>
-          <t>• 审批文档技术部分定稿</t>
-        </is>
-      </c>
-      <c r="E139" s="81" t="n"/>
-      <c r="F139" s="81" t="n"/>
-      <c r="G139" s="59" t="n"/>
+      <c r="A139" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B139" s="94" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C139" s="76" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="D139" s="83" t="inlineStr">
+        <is>
+          <t>B·架构+开发</t>
+        </is>
+      </c>
+      <c r="E139" s="78" t="inlineStr">
+        <is>
+          <t>• 预演问题修复（权限/处置/驻留相关）</t>
+        </is>
+      </c>
+      <c r="F139" s="119" t="inlineStr">
+        <is>
+          <t>预演问题关闭；发布包冻结</t>
+        </is>
+      </c>
+      <c r="G139" s="80" t="inlineStr"/>
       <c r="H139" s="59" t="n"/>
       <c r="I139" s="59" t="n"/>
+      <c r="J139" s="59" t="n"/>
     </row>
     <row r="140" ht="22" customHeight="1">
-      <c r="A140" s="81" t="n"/>
-      <c r="B140" s="81" t="n"/>
-      <c r="C140" s="84" t="n"/>
-      <c r="D140" s="78" t="inlineStr">
-        <is>
-          <t>• 上线技术准备（回退方案 + 应急预案）</t>
-        </is>
-      </c>
-      <c r="E140" s="81" t="n"/>
-      <c r="F140" s="81" t="n"/>
-      <c r="G140" s="59" t="n"/>
+      <c r="B140" s="120" t="n"/>
+      <c r="C140" s="120" t="n"/>
+      <c r="D140" s="122" t="n"/>
+      <c r="E140" s="78" t="inlineStr">
+        <is>
+          <t>• 发布包冻结（W10 末起只修 P0/P1，不再加功能）</t>
+        </is>
+      </c>
+      <c r="F140" s="120" t="n"/>
+      <c r="G140" s="120" t="n"/>
       <c r="H140" s="59" t="n"/>
       <c r="I140" s="59" t="n"/>
+      <c r="J140" s="59" t="n"/>
     </row>
     <row r="141" ht="22" customHeight="1">
-      <c r="A141" s="94" t="inlineStr">
+      <c r="A141" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B141" s="94" t="inlineStr">
         <is>
           <t>Sprint 4</t>
         </is>
       </c>
-      <c r="B141" s="76" t="inlineStr">
+      <c r="C141" s="76" t="inlineStr">
         <is>
           <t>W10</t>
         </is>
       </c>
-      <c r="C141" s="85" t="inlineStr">
+      <c r="D141" s="85" t="inlineStr">
         <is>
           <t>C·数据工程</t>
         </is>
       </c>
-      <c r="D141" s="78" t="inlineStr">
-        <is>
-          <t>• UAT 数据问题排查修复</t>
-        </is>
-      </c>
-      <c r="E141" s="79" t="inlineStr">
-        <is>
-          <t>生产 Jobs 首跑成功</t>
-        </is>
-      </c>
-      <c r="F141" s="80" t="inlineStr"/>
-      <c r="G141" s="59" t="n"/>
+      <c r="E141" s="78" t="inlineStr">
+        <is>
+          <t>• 预跑数据修正 + 生产迁移最终方案（分批清单/时间表）</t>
+        </is>
+      </c>
+      <c r="F141" s="119" t="inlineStr">
+        <is>
+          <t>迁移方案定稿</t>
+        </is>
+      </c>
+      <c r="G141" s="80" t="inlineStr"/>
       <c r="H141" s="59" t="n"/>
       <c r="I141" s="59" t="n"/>
+      <c r="J141" s="59" t="n"/>
     </row>
     <row r="142" ht="22" customHeight="1">
-      <c r="A142" s="81" t="n"/>
-      <c r="B142" s="81" t="n"/>
-      <c r="C142" s="86" t="n"/>
-      <c r="D142" s="78" t="inlineStr">
-        <is>
-          <t>• 生产增量/Compaction/处置 首次运行验证</t>
-        </is>
-      </c>
-      <c r="E142" s="81" t="n"/>
-      <c r="F142" s="81" t="n"/>
-      <c r="G142" s="59" t="n"/>
+      <c r="B142" s="120" t="n"/>
+      <c r="C142" s="120" t="n"/>
+      <c r="D142" s="123" t="n"/>
+      <c r="E142" s="78" t="inlineStr">
+        <is>
+          <t>• 生产 Jobs 就绪（增量/Compaction/处置 生产版待发）</t>
+        </is>
+      </c>
+      <c r="F142" s="120" t="n"/>
+      <c r="G142" s="120" t="n"/>
       <c r="H142" s="59" t="n"/>
       <c r="I142" s="59" t="n"/>
+      <c r="J142" s="59" t="n"/>
     </row>
     <row r="143" ht="22" customHeight="1">
-      <c r="A143" s="81" t="n"/>
-      <c r="B143" s="81" t="n"/>
-      <c r="C143" s="86" t="n"/>
-      <c r="D143" s="78" t="inlineStr">
-        <is>
-          <t>• CC 增量链路稳定性确认</t>
-        </is>
-      </c>
-      <c r="E143" s="81" t="n"/>
-      <c r="F143" s="81" t="n"/>
-      <c r="G143" s="59" t="n"/>
+      <c r="A143" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B143" s="94" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C143" s="76" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="D143" s="87" t="inlineStr">
+        <is>
+          <t>D·全栈+DevOps</t>
+        </is>
+      </c>
+      <c r="E143" s="78" t="inlineStr">
+        <is>
+          <t>• UAT 预演技术支撑 + 环境问题修复</t>
+        </is>
+      </c>
+      <c r="F143" s="119" t="inlineStr">
+        <is>
+          <t>Checklist v1</t>
+        </is>
+      </c>
+      <c r="G143" s="80" t="inlineStr"/>
       <c r="H143" s="59" t="n"/>
       <c r="I143" s="59" t="n"/>
+      <c r="J143" s="59" t="n"/>
     </row>
     <row r="144" ht="22" customHeight="1">
-      <c r="A144" s="94" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="B144" s="76" t="inlineStr">
-        <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="C144" s="87" t="inlineStr">
-        <is>
-          <t>D·全栈+DevOps</t>
-        </is>
-      </c>
-      <c r="D144" s="78" t="inlineStr">
-        <is>
-          <t>• UAT Bug 修复（前后端）</t>
-        </is>
-      </c>
-      <c r="E144" s="79" t="inlineStr">
-        <is>
-          <t>安全整改复测通过</t>
-        </is>
-      </c>
-      <c r="F144" s="80" t="inlineStr"/>
-      <c r="G144" s="59" t="n"/>
+      <c r="B144" s="120" t="n"/>
+      <c r="C144" s="120" t="n"/>
+      <c r="D144" s="124" t="n"/>
+      <c r="E144" s="78" t="inlineStr">
+        <is>
+          <t>• 上线 Checklist 编写（部署顺序/验证点/回退点）</t>
+        </is>
+      </c>
+      <c r="F144" s="120" t="n"/>
+      <c r="G144" s="120" t="n"/>
       <c r="H144" s="59" t="n"/>
       <c r="I144" s="59" t="n"/>
+      <c r="J144" s="59" t="n"/>
     </row>
     <row r="145" ht="22" customHeight="1">
-      <c r="A145" s="81" t="n"/>
-      <c r="B145" s="81" t="n"/>
-      <c r="C145" s="88" t="n"/>
-      <c r="D145" s="78" t="inlineStr">
-        <is>
-          <t>• 安全整改：渗透/评审问题修复 + 复测</t>
-        </is>
-      </c>
-      <c r="E145" s="81" t="n"/>
-      <c r="F145" s="81" t="n"/>
-      <c r="G145" s="59" t="n"/>
+      <c r="A145" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B145" s="94" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="C145" s="76" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="D145" s="89" t="inlineStr">
+        <is>
+          <t>E·QA+SLC文档</t>
+        </is>
+      </c>
+      <c r="E145" s="78" t="inlineStr">
+        <is>
+          <t>• 文档终审推进（7 套进入终稿）</t>
+        </is>
+      </c>
+      <c r="F145" s="119" t="inlineStr">
+        <is>
+          <t>★ 就绪检查 100% 通过（W11 上线前置）</t>
+        </is>
+      </c>
+      <c r="G145" s="80" t="inlineStr">
+        <is>
+          <t>各角色材料齐备</t>
+        </is>
+      </c>
       <c r="H145" s="59" t="n"/>
       <c r="I145" s="59" t="n"/>
+      <c r="J145" s="59" t="n"/>
     </row>
     <row r="146" ht="22" customHeight="1">
-      <c r="A146" s="81" t="n"/>
-      <c r="B146" s="81" t="n"/>
-      <c r="C146" s="88" t="n"/>
-      <c r="D146" s="78" t="inlineStr">
-        <is>
-          <t>• 文档截图与生产对齐</t>
-        </is>
-      </c>
-      <c r="E146" s="81" t="n"/>
-      <c r="F146" s="81" t="n"/>
-      <c r="G146" s="59" t="n"/>
+      <c r="B146" s="120" t="n"/>
+      <c r="C146" s="120" t="n"/>
+      <c r="D146" s="125" t="n"/>
+      <c r="E146" s="78" t="inlineStr">
+        <is>
+          <t>• 上线就绪检查组织（W10 末：发布包/材料/预演/回退预案 逐项核对）</t>
+        </is>
+      </c>
+      <c r="F146" s="120" t="n"/>
+      <c r="G146" s="120" t="n"/>
       <c r="H146" s="59" t="n"/>
       <c r="I146" s="59" t="n"/>
+      <c r="J146" s="59" t="n"/>
     </row>
     <row r="147" ht="22" customHeight="1">
-      <c r="A147" s="94" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="B147" s="76" t="inlineStr">
-        <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="C147" s="89" t="inlineStr">
-        <is>
-          <t>E·QA+SLC文档</t>
-        </is>
-      </c>
-      <c r="D147" s="78" t="inlineStr">
-        <is>
-          <t>• UAT 执行协调 + 结果记录</t>
-        </is>
-      </c>
-      <c r="E147" s="79" t="inlineStr">
-        <is>
-          <t>7 套文档终版；Checklist 通过</t>
-        </is>
-      </c>
-      <c r="F147" s="80" t="inlineStr"/>
-      <c r="G147" s="59" t="n"/>
+      <c r="A147" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B147" s="95" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C147" s="76" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="D147" s="77" t="inlineStr">
+        <is>
+          <t>A·需求(50%)</t>
+        </is>
+      </c>
+      <c r="E147" s="78" t="inlineStr">
+        <is>
+          <t>• Go/No-Go 决策参与（需求满足度视角）</t>
+        </is>
+      </c>
+      <c r="F147" s="119" t="inlineStr">
+        <is>
+          <t>★ UAT 签字</t>
+        </is>
+      </c>
+      <c r="G147" s="80" t="inlineStr">
+        <is>
+          <t>UAT 业务方时间</t>
+        </is>
+      </c>
       <c r="H147" s="59" t="n"/>
       <c r="I147" s="59" t="n"/>
+      <c r="J147" s="59" t="n"/>
     </row>
     <row r="148" ht="22" customHeight="1">
-      <c r="A148" s="81" t="n"/>
-      <c r="B148" s="81" t="n"/>
-      <c r="C148" s="90" t="n"/>
-      <c r="D148" s="78" t="inlineStr">
-        <is>
-          <t>• 文档终审（7 套 + 审批包）</t>
-        </is>
-      </c>
-      <c r="E148" s="81" t="n"/>
-      <c r="F148" s="81" t="n"/>
-      <c r="G148" s="59" t="n"/>
+      <c r="B148" s="120" t="n"/>
+      <c r="C148" s="120" t="n"/>
+      <c r="D148" s="121" t="n"/>
+      <c r="E148" s="78" t="inlineStr">
+        <is>
+          <t>• UAT 正式执行主持（8 域场景 + 记录 + 签字）</t>
+        </is>
+      </c>
+      <c r="F148" s="120" t="n"/>
+      <c r="G148" s="120" t="n"/>
       <c r="H148" s="59" t="n"/>
       <c r="I148" s="59" t="n"/>
+      <c r="J148" s="59" t="n"/>
     </row>
     <row r="149" ht="22" customHeight="1">
-      <c r="A149" s="81" t="n"/>
-      <c r="B149" s="81" t="n"/>
-      <c r="C149" s="90" t="n"/>
-      <c r="D149" s="78" t="inlineStr">
-        <is>
-          <t>• 上线 Checklist 评审</t>
-        </is>
-      </c>
-      <c r="E149" s="81" t="n"/>
-      <c r="F149" s="81" t="n"/>
-      <c r="G149" s="59" t="n"/>
+      <c r="B149" s="120" t="n"/>
+      <c r="C149" s="120" t="n"/>
+      <c r="D149" s="121" t="n"/>
+      <c r="E149" s="78" t="inlineStr">
+        <is>
+          <t>• 上线后用户反馈分诊</t>
+        </is>
+      </c>
+      <c r="F149" s="120" t="n"/>
+      <c r="G149" s="120" t="n"/>
       <c r="H149" s="59" t="n"/>
       <c r="I149" s="59" t="n"/>
+      <c r="J149" s="59" t="n"/>
     </row>
     <row r="150" ht="22" customHeight="1">
-      <c r="A150" s="95" t="inlineStr">
+      <c r="A150" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B150" s="95" t="inlineStr">
         <is>
           <t>Sprint 5</t>
         </is>
       </c>
-      <c r="B150" s="76" t="inlineStr">
+      <c r="C150" s="76" t="inlineStr">
         <is>
           <t>W11</t>
         </is>
       </c>
-      <c r="C150" s="77" t="inlineStr">
-        <is>
-          <t>A·需求(50%)</t>
-        </is>
-      </c>
-      <c r="D150" s="78" t="inlineStr">
-        <is>
-          <t>• Go/No-Go 决策参与（需求满足度视角）</t>
-        </is>
-      </c>
-      <c r="E150" s="79" t="inlineStr">
-        <is>
-          <t>Go 决策；反馈清单</t>
-        </is>
-      </c>
-      <c r="F150" s="80" t="inlineStr"/>
-      <c r="G150" s="59" t="n"/>
+      <c r="D150" s="83" t="inlineStr">
+        <is>
+          <t>B·架构+开发</t>
+        </is>
+      </c>
+      <c r="E150" s="78" t="inlineStr">
+        <is>
+          <t>• Go/No-Go 技术评估（权限/存储/性能）</t>
+        </is>
+      </c>
+      <c r="F150" s="119" t="inlineStr">
+        <is>
+          <t>★ Go-Live</t>
+        </is>
+      </c>
+      <c r="G150" s="80" t="inlineStr"/>
       <c r="H150" s="59" t="n"/>
       <c r="I150" s="59" t="n"/>
+      <c r="J150" s="59" t="n"/>
     </row>
     <row r="151" ht="22" customHeight="1">
-      <c r="A151" s="81" t="n"/>
-      <c r="B151" s="81" t="n"/>
-      <c r="C151" s="82" t="n"/>
-      <c r="D151" s="78" t="inlineStr">
-        <is>
-          <t>• 上线后用户反馈收集与分诊（Bug/优化建议）</t>
-        </is>
-      </c>
-      <c r="E151" s="81" t="n"/>
-      <c r="F151" s="81" t="n"/>
-      <c r="G151" s="59" t="n"/>
+      <c r="B151" s="120" t="n"/>
+      <c r="C151" s="120" t="n"/>
+      <c r="D151" s="122" t="n"/>
+      <c r="E151" s="78" t="inlineStr">
+        <is>
+          <t>• 生产发布执行（就绪包一键发布 + Environments 审批）</t>
+        </is>
+      </c>
+      <c r="F151" s="120" t="n"/>
+      <c r="G151" s="120" t="n"/>
       <c r="H151" s="59" t="n"/>
       <c r="I151" s="59" t="n"/>
+      <c r="J151" s="59" t="n"/>
     </row>
     <row r="152" ht="22" customHeight="1">
-      <c r="A152" s="95" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B152" s="76" t="inlineStr">
-        <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="C152" s="83" t="inlineStr">
-        <is>
-          <t>B·架构+开发</t>
-        </is>
-      </c>
-      <c r="D152" s="78" t="inlineStr">
-        <is>
-          <t>• Go/No-Go 技术评估（权限/存储/性能三维度）</t>
-        </is>
-      </c>
-      <c r="E152" s="79" t="inlineStr">
-        <is>
-          <t>上线成功</t>
-        </is>
-      </c>
-      <c r="F152" s="80" t="inlineStr"/>
-      <c r="G152" s="59" t="n"/>
+      <c r="B152" s="120" t="n"/>
+      <c r="C152" s="120" t="n"/>
+      <c r="D152" s="122" t="n"/>
+      <c r="E152" s="78" t="inlineStr">
+        <is>
+          <t>• 48h 值守（权限/存储）</t>
+        </is>
+      </c>
+      <c r="F152" s="120" t="n"/>
+      <c r="G152" s="120" t="n"/>
       <c r="H152" s="59" t="n"/>
       <c r="I152" s="59" t="n"/>
+      <c r="J152" s="59" t="n"/>
     </row>
     <row r="153" ht="22" customHeight="1">
-      <c r="A153" s="81" t="n"/>
-      <c r="B153" s="81" t="n"/>
-      <c r="C153" s="84" t="n"/>
-      <c r="D153" s="78" t="inlineStr">
-        <is>
-          <t>• 上线执行：发布编排 + 验证点 + 回退预案</t>
-        </is>
-      </c>
-      <c r="E153" s="81" t="n"/>
-      <c r="F153" s="81" t="n"/>
-      <c r="G153" s="59" t="n"/>
+      <c r="A153" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B153" s="95" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C153" s="76" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="D153" s="85" t="inlineStr">
+        <is>
+          <t>C·数据工程</t>
+        </is>
+      </c>
+      <c r="E153" s="78" t="inlineStr">
+        <is>
+          <t>• CC 生产全量迁移收尾（预跑后增量补齐 + 对账）</t>
+        </is>
+      </c>
+      <c r="F153" s="119" t="inlineStr">
+        <is>
+          <t>生产全量对账通过</t>
+        </is>
+      </c>
+      <c r="G153" s="80" t="inlineStr"/>
       <c r="H153" s="59" t="n"/>
       <c r="I153" s="59" t="n"/>
+      <c r="J153" s="59" t="n"/>
     </row>
     <row r="154" ht="22" customHeight="1">
-      <c r="A154" s="81" t="n"/>
-      <c r="B154" s="81" t="n"/>
-      <c r="C154" s="84" t="n"/>
-      <c r="D154" s="78" t="inlineStr">
-        <is>
-          <t>• 48h 值守（权限异常/存储倾斜）</t>
-        </is>
-      </c>
-      <c r="E154" s="81" t="n"/>
-      <c r="F154" s="81" t="n"/>
-      <c r="G154" s="59" t="n"/>
+      <c r="B154" s="120" t="n"/>
+      <c r="C154" s="120" t="n"/>
+      <c r="D154" s="123" t="n"/>
+      <c r="E154" s="78" t="inlineStr">
+        <is>
+          <t>• 生产 Jobs 启动（增量/Compaction/处置）</t>
+        </is>
+      </c>
+      <c r="F154" s="120" t="n"/>
+      <c r="G154" s="120" t="n"/>
       <c r="H154" s="59" t="n"/>
       <c r="I154" s="59" t="n"/>
+      <c r="J154" s="59" t="n"/>
     </row>
     <row r="155" ht="22" customHeight="1">
-      <c r="A155" s="95" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B155" s="76" t="inlineStr">
-        <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="C155" s="85" t="inlineStr">
-        <is>
-          <t>C·数据工程</t>
-        </is>
-      </c>
-      <c r="D155" s="78" t="inlineStr">
-        <is>
-          <t>• 生产运行监控（增量/Compaction/处置 Jobs）</t>
-        </is>
-      </c>
-      <c r="E155" s="79" t="inlineStr">
-        <is>
-          <t>生产 Jobs 正常</t>
-        </is>
-      </c>
-      <c r="F155" s="80" t="inlineStr"/>
-      <c r="G155" s="59" t="n"/>
+      <c r="B155" s="120" t="n"/>
+      <c r="C155" s="120" t="n"/>
+      <c r="D155" s="123" t="n"/>
+      <c r="E155" s="78" t="inlineStr">
+        <is>
+          <t>• 48h 值守（数据链路）</t>
+        </is>
+      </c>
+      <c r="F155" s="120" t="n"/>
+      <c r="G155" s="120" t="n"/>
       <c r="H155" s="59" t="n"/>
       <c r="I155" s="59" t="n"/>
+      <c r="J155" s="59" t="n"/>
     </row>
     <row r="156" ht="22" customHeight="1">
-      <c r="A156" s="81" t="n"/>
-      <c r="B156" s="81" t="n"/>
-      <c r="C156" s="86" t="n"/>
-      <c r="D156" s="78" t="inlineStr">
-        <is>
-          <t>• 异常处理（首周重点）</t>
-        </is>
-      </c>
-      <c r="E156" s="81" t="n"/>
-      <c r="F156" s="81" t="n"/>
-      <c r="G156" s="59" t="n"/>
+      <c r="A156" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B156" s="95" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C156" s="76" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="D156" s="87" t="inlineStr">
+        <is>
+          <t>D·全栈+DevOps</t>
+        </is>
+      </c>
+      <c r="E156" s="78" t="inlineStr">
+        <is>
+          <t>• 生产部署验证（8 域功能全通）</t>
+        </is>
+      </c>
+      <c r="F156" s="119" t="inlineStr">
+        <is>
+          <t>验证通过</t>
+        </is>
+      </c>
+      <c r="G156" s="80" t="inlineStr"/>
       <c r="H156" s="59" t="n"/>
       <c r="I156" s="59" t="n"/>
+      <c r="J156" s="59" t="n"/>
     </row>
     <row r="157" ht="22" customHeight="1">
-      <c r="A157" s="81" t="n"/>
-      <c r="B157" s="81" t="n"/>
-      <c r="C157" s="86" t="n"/>
-      <c r="D157" s="78" t="inlineStr">
-        <is>
-          <t>• 48h 值守（数据链路）</t>
-        </is>
-      </c>
-      <c r="E157" s="81" t="n"/>
-      <c r="F157" s="81" t="n"/>
-      <c r="G157" s="59" t="n"/>
+      <c r="B157" s="120" t="n"/>
+      <c r="C157" s="120" t="n"/>
+      <c r="D157" s="124" t="n"/>
+      <c r="E157" s="78" t="inlineStr">
+        <is>
+          <t>• P1 问题当日清 + 热修发布</t>
+        </is>
+      </c>
+      <c r="F157" s="120" t="n"/>
+      <c r="G157" s="120" t="n"/>
       <c r="H157" s="59" t="n"/>
       <c r="I157" s="59" t="n"/>
+      <c r="J157" s="59" t="n"/>
     </row>
     <row r="158" ht="22" customHeight="1">
-      <c r="A158" s="95" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B158" s="76" t="inlineStr">
-        <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="C158" s="87" t="inlineStr">
-        <is>
-          <t>D·全栈+DevOps</t>
-        </is>
-      </c>
-      <c r="D158" s="78" t="inlineStr">
-        <is>
-          <t>• 生产运行监控（查询/前端/SSO）</t>
-        </is>
-      </c>
-      <c r="E158" s="79" t="inlineStr">
-        <is>
-          <t>查询正常；用户可用</t>
-        </is>
-      </c>
-      <c r="F158" s="80" t="inlineStr"/>
-      <c r="G158" s="59" t="n"/>
+      <c r="B158" s="120" t="n"/>
+      <c r="C158" s="120" t="n"/>
+      <c r="D158" s="124" t="n"/>
+      <c r="E158" s="78" t="inlineStr">
+        <is>
+          <t>• 48h 值守（应用/前端/SSO）</t>
+        </is>
+      </c>
+      <c r="F158" s="120" t="n"/>
+      <c r="G158" s="120" t="n"/>
       <c r="H158" s="59" t="n"/>
       <c r="I158" s="59" t="n"/>
+      <c r="J158" s="59" t="n"/>
     </row>
     <row r="159" ht="22" customHeight="1">
-      <c r="A159" s="81" t="n"/>
-      <c r="B159" s="81" t="n"/>
-      <c r="C159" s="88" t="n"/>
-      <c r="D159" s="78" t="inlineStr">
-        <is>
-          <t>• 用户反馈快速响应与热修</t>
-        </is>
-      </c>
-      <c r="E159" s="81" t="n"/>
-      <c r="F159" s="81" t="n"/>
-      <c r="G159" s="59" t="n"/>
+      <c r="A159" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B159" s="95" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C159" s="76" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="D159" s="89" t="inlineStr">
+        <is>
+          <t>E·QA+SLC文档</t>
+        </is>
+      </c>
+      <c r="E159" s="78" t="inlineStr">
+        <is>
+          <t>• 上线执行记录（Checklist 逐项勾选）</t>
+        </is>
+      </c>
+      <c r="F159" s="119" t="inlineStr">
+        <is>
+          <t>★ 审批受理；上线报告</t>
+        </is>
+      </c>
+      <c r="G159" s="80" t="inlineStr">
+        <is>
+          <t>审批方受理</t>
+        </is>
+      </c>
       <c r="H159" s="59" t="n"/>
       <c r="I159" s="59" t="n"/>
+      <c r="J159" s="59" t="n"/>
     </row>
     <row r="160" ht="22" customHeight="1">
-      <c r="A160" s="81" t="n"/>
-      <c r="B160" s="81" t="n"/>
-      <c r="C160" s="88" t="n"/>
-      <c r="D160" s="78" t="inlineStr">
-        <is>
-          <t>• 48h 值守（应用侧）</t>
-        </is>
-      </c>
-      <c r="E160" s="81" t="n"/>
-      <c r="F160" s="81" t="n"/>
-      <c r="G160" s="59" t="n"/>
+      <c r="B160" s="120" t="n"/>
+      <c r="C160" s="120" t="n"/>
+      <c r="D160" s="125" t="n"/>
+      <c r="E160" s="78" t="inlineStr">
+        <is>
+          <t>• 审批材料提交（受理）</t>
+        </is>
+      </c>
+      <c r="F160" s="120" t="n"/>
+      <c r="G160" s="120" t="n"/>
       <c r="H160" s="59" t="n"/>
       <c r="I160" s="59" t="n"/>
+      <c r="J160" s="59" t="n"/>
     </row>
     <row r="161" ht="22" customHeight="1">
-      <c r="A161" s="95" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B161" s="76" t="inlineStr">
-        <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="C161" s="89" t="inlineStr">
-        <is>
-          <t>E·QA+SLC文档</t>
-        </is>
-      </c>
-      <c r="D161" s="78" t="inlineStr">
-        <is>
-          <t>• 上线执行记录（部署顺序/验证点/回退点）</t>
-        </is>
-      </c>
-      <c r="E161" s="79" t="inlineStr">
-        <is>
-          <t>上线报告</t>
-        </is>
-      </c>
-      <c r="F161" s="80" t="inlineStr"/>
-      <c r="G161" s="59" t="n"/>
+      <c r="B161" s="120" t="n"/>
+      <c r="C161" s="120" t="n"/>
+      <c r="D161" s="125" t="n"/>
+      <c r="E161" s="78" t="inlineStr">
+        <is>
+          <t>• 48h 值守 + 告警验证</t>
+        </is>
+      </c>
+      <c r="F161" s="120" t="n"/>
+      <c r="G161" s="120" t="n"/>
       <c r="H161" s="59" t="n"/>
       <c r="I161" s="59" t="n"/>
+      <c r="J161" s="59" t="n"/>
     </row>
     <row r="162" ht="22" customHeight="1">
-      <c r="A162" s="81" t="n"/>
-      <c r="B162" s="81" t="n"/>
-      <c r="C162" s="90" t="n"/>
-      <c r="D162" s="78" t="inlineStr">
-        <is>
-          <t>• 48h 值守 + 告警验证</t>
-        </is>
-      </c>
-      <c r="E162" s="81" t="n"/>
-      <c r="F162" s="81" t="n"/>
-      <c r="G162" s="59" t="n"/>
+      <c r="B162" s="120" t="n"/>
+      <c r="C162" s="120" t="n"/>
+      <c r="D162" s="125" t="n"/>
+      <c r="E162" s="78" t="inlineStr">
+        <is>
+          <t>• 上线验证报告</t>
+        </is>
+      </c>
+      <c r="F162" s="120" t="n"/>
+      <c r="G162" s="120" t="n"/>
       <c r="H162" s="59" t="n"/>
       <c r="I162" s="59" t="n"/>
+      <c r="J162" s="59" t="n"/>
     </row>
     <row r="163" ht="22" customHeight="1">
-      <c r="A163" s="81" t="n"/>
-      <c r="B163" s="81" t="n"/>
-      <c r="C163" s="90" t="n"/>
-      <c r="D163" s="78" t="inlineStr">
-        <is>
-          <t>• 上线验证报告</t>
-        </is>
-      </c>
-      <c r="E163" s="81" t="n"/>
-      <c r="F163" s="81" t="n"/>
-      <c r="G163" s="59" t="n"/>
+      <c r="A163" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B163" s="95" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C163" s="76" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="D163" s="77" t="inlineStr">
+        <is>
+          <t>A·需求(50%)</t>
+        </is>
+      </c>
+      <c r="E163" s="78" t="inlineStr">
+        <is>
+          <t>• 上线一周稳定性观察（需求满足度回顾）</t>
+        </is>
+      </c>
+      <c r="F163" s="119" t="inlineStr">
+        <is>
+          <t>稳定性确认；遗留清单</t>
+        </is>
+      </c>
+      <c r="G163" s="80" t="inlineStr"/>
       <c r="H163" s="59" t="n"/>
       <c r="I163" s="59" t="n"/>
+      <c r="J163" s="59" t="n"/>
     </row>
     <row r="164" ht="22" customHeight="1">
-      <c r="A164" s="95" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B164" s="76" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="C164" s="77" t="inlineStr">
-        <is>
-          <t>A·需求(50%)</t>
-        </is>
-      </c>
-      <c r="D164" s="78" t="inlineStr">
-        <is>
-          <t>• 上线一周稳定性观察（需求满足度回顾）</t>
-        </is>
-      </c>
-      <c r="E164" s="79" t="inlineStr">
-        <is>
-          <t>稳定性确认；遗留清单</t>
-        </is>
-      </c>
-      <c r="F164" s="80" t="inlineStr"/>
-      <c r="G164" s="59" t="n"/>
+      <c r="B164" s="120" t="n"/>
+      <c r="C164" s="120" t="n"/>
+      <c r="D164" s="121" t="n"/>
+      <c r="E164" s="78" t="inlineStr">
+        <is>
+          <t>• 遗留问题清单确认</t>
+        </is>
+      </c>
+      <c r="F164" s="120" t="n"/>
+      <c r="G164" s="120" t="n"/>
       <c r="H164" s="59" t="n"/>
       <c r="I164" s="59" t="n"/>
+      <c r="J164" s="59" t="n"/>
     </row>
     <row r="165" ht="22" customHeight="1">
-      <c r="A165" s="81" t="n"/>
-      <c r="B165" s="81" t="n"/>
-      <c r="C165" s="82" t="n"/>
-      <c r="D165" s="78" t="inlineStr">
-        <is>
-          <t>• 遗留问题清单确认（Bug/优化项交接）</t>
-        </is>
-      </c>
-      <c r="E165" s="81" t="n"/>
-      <c r="F165" s="81" t="n"/>
-      <c r="G165" s="59" t="n"/>
+      <c r="B165" s="120" t="n"/>
+      <c r="C165" s="120" t="n"/>
+      <c r="D165" s="121" t="n"/>
+      <c r="E165" s="78" t="inlineStr">
+        <is>
+          <t>• 项目结束确认</t>
+        </is>
+      </c>
+      <c r="F165" s="120" t="n"/>
+      <c r="G165" s="120" t="n"/>
       <c r="H165" s="59" t="n"/>
       <c r="I165" s="59" t="n"/>
+      <c r="J165" s="59" t="n"/>
     </row>
     <row r="166" ht="22" customHeight="1">
-      <c r="A166" s="81" t="n"/>
-      <c r="B166" s="81" t="n"/>
-      <c r="C166" s="82" t="n"/>
-      <c r="D166" s="78" t="inlineStr">
-        <is>
-          <t>• 项目结束确认</t>
-        </is>
-      </c>
-      <c r="E166" s="81" t="n"/>
-      <c r="F166" s="81" t="n"/>
-      <c r="G166" s="59" t="n"/>
+      <c r="A166" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B166" s="95" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C166" s="76" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="D166" s="83" t="inlineStr">
+        <is>
+          <t>B·架构+开发</t>
+        </is>
+      </c>
+      <c r="E166" s="78" t="inlineStr">
+        <is>
+          <t>• 遗留问题修复（技术债清零）</t>
+        </is>
+      </c>
+      <c r="F166" s="119" t="inlineStr">
+        <is>
+          <t>交付物归档</t>
+        </is>
+      </c>
+      <c r="G166" s="80" t="inlineStr"/>
       <c r="H166" s="59" t="n"/>
       <c r="I166" s="59" t="n"/>
+      <c r="J166" s="59" t="n"/>
     </row>
     <row r="167" ht="22" customHeight="1">
-      <c r="A167" s="95" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B167" s="76" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="C167" s="83" t="inlineStr">
-        <is>
-          <t>B·架构+开发</t>
-        </is>
-      </c>
-      <c r="D167" s="78" t="inlineStr">
-        <is>
-          <t>• 遗留问题修复（技术债清零）</t>
-        </is>
-      </c>
-      <c r="E167" s="79" t="inlineStr">
-        <is>
-          <t>技术债清零；交付物归档</t>
-        </is>
-      </c>
-      <c r="F167" s="80" t="inlineStr"/>
-      <c r="G167" s="59" t="n"/>
+      <c r="B167" s="120" t="n"/>
+      <c r="C167" s="120" t="n"/>
+      <c r="D167" s="122" t="n"/>
+      <c r="E167" s="78" t="inlineStr">
+        <is>
+          <t>• 交付物归档：架构文档/ADR/部署脚本 + 版本 tag</t>
+        </is>
+      </c>
+      <c r="F167" s="120" t="n"/>
+      <c r="G167" s="120" t="n"/>
       <c r="H167" s="59" t="n"/>
       <c r="I167" s="59" t="n"/>
+      <c r="J167" s="59" t="n"/>
     </row>
     <row r="168" ht="22" customHeight="1">
-      <c r="A168" s="81" t="n"/>
-      <c r="B168" s="81" t="n"/>
-      <c r="C168" s="84" t="n"/>
-      <c r="D168" s="78" t="inlineStr">
-        <is>
-          <t>• 交付物归档：架构文档/ADR/部署脚本 + 版本 tag</t>
-        </is>
-      </c>
-      <c r="E168" s="81" t="n"/>
-      <c r="F168" s="81" t="n"/>
-      <c r="G168" s="59" t="n"/>
+      <c r="A168" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B168" s="95" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C168" s="76" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="D168" s="85" t="inlineStr">
+        <is>
+          <t>C·数据工程</t>
+        </is>
+      </c>
+      <c r="E168" s="78" t="inlineStr">
+        <is>
+          <t>• 增量/处置链路稳定运行确认（一周无失败）</t>
+        </is>
+      </c>
+      <c r="F168" s="119" t="inlineStr">
+        <is>
+          <t>交付物归档</t>
+        </is>
+      </c>
+      <c r="G168" s="80" t="inlineStr"/>
       <c r="H168" s="59" t="n"/>
       <c r="I168" s="59" t="n"/>
+      <c r="J168" s="59" t="n"/>
     </row>
     <row r="169" ht="22" customHeight="1">
-      <c r="A169" s="95" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B169" s="76" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="C169" s="85" t="inlineStr">
-        <is>
-          <t>C·数据工程</t>
-        </is>
-      </c>
-      <c r="D169" s="78" t="inlineStr">
-        <is>
-          <t>• 增量链路稳定运行确认（一周无失败）</t>
-        </is>
-      </c>
-      <c r="E169" s="79" t="inlineStr">
-        <is>
-          <t>增量稳定；交付物归档</t>
-        </is>
-      </c>
-      <c r="F169" s="80" t="inlineStr"/>
-      <c r="G169" s="59" t="n"/>
+      <c r="B169" s="120" t="n"/>
+      <c r="C169" s="120" t="n"/>
+      <c r="D169" s="123" t="n"/>
+      <c r="E169" s="78" t="inlineStr">
+        <is>
+          <t>• 交付物归档：四层 SQL/Jobs/对账工具</t>
+        </is>
+      </c>
+      <c r="F169" s="120" t="n"/>
+      <c r="G169" s="120" t="n"/>
       <c r="H169" s="59" t="n"/>
       <c r="I169" s="59" t="n"/>
+      <c r="J169" s="59" t="n"/>
     </row>
     <row r="170" ht="22" customHeight="1">
-      <c r="A170" s="81" t="n"/>
-      <c r="B170" s="81" t="n"/>
-      <c r="C170" s="86" t="n"/>
-      <c r="D170" s="78" t="inlineStr">
-        <is>
-          <t>• 交付物归档：四层 SQL/Jobs 脚本/对账工具</t>
-        </is>
-      </c>
-      <c r="E170" s="81" t="n"/>
-      <c r="F170" s="81" t="n"/>
-      <c r="G170" s="59" t="n"/>
+      <c r="A170" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B170" s="95" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C170" s="76" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="D170" s="87" t="inlineStr">
+        <is>
+          <t>D·全栈+DevOps</t>
+        </is>
+      </c>
+      <c r="E170" s="78" t="inlineStr">
+        <is>
+          <t>• 遗留 Bug 修复 + 代码库整理（README/版本 tag）</t>
+        </is>
+      </c>
+      <c r="F170" s="119" t="inlineStr">
+        <is>
+          <t>交付物归档</t>
+        </is>
+      </c>
+      <c r="G170" s="80" t="inlineStr"/>
       <c r="H170" s="59" t="n"/>
       <c r="I170" s="59" t="n"/>
+      <c r="J170" s="59" t="n"/>
     </row>
     <row r="171" ht="22" customHeight="1">
-      <c r="A171" s="95" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B171" s="76" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="C171" s="87" t="inlineStr">
-        <is>
-          <t>D·全栈+DevOps</t>
-        </is>
-      </c>
-      <c r="D171" s="78" t="inlineStr">
-        <is>
-          <t>• 遗留 Bug 修复 + 代码库整理（README/版本 tag）</t>
-        </is>
-      </c>
-      <c r="E171" s="79" t="inlineStr">
-        <is>
-          <t>代码归档；版本 tag</t>
-        </is>
-      </c>
-      <c r="F171" s="80" t="inlineStr"/>
-      <c r="G171" s="59" t="n"/>
+      <c r="B171" s="120" t="n"/>
+      <c r="C171" s="120" t="n"/>
+      <c r="D171" s="124" t="n"/>
+      <c r="E171" s="78" t="inlineStr">
+        <is>
+          <t>• 交付物归档：前后端代码/CI-CD/Helm</t>
+        </is>
+      </c>
+      <c r="F171" s="120" t="n"/>
+      <c r="G171" s="120" t="n"/>
       <c r="H171" s="59" t="n"/>
       <c r="I171" s="59" t="n"/>
+      <c r="J171" s="59" t="n"/>
     </row>
     <row r="172" ht="22" customHeight="1">
-      <c r="A172" s="81" t="n"/>
-      <c r="B172" s="81" t="n"/>
-      <c r="C172" s="88" t="n"/>
-      <c r="D172" s="78" t="inlineStr">
-        <is>
-          <t>• 交付物归档：前后端代码/CI-CD/Helm</t>
-        </is>
-      </c>
-      <c r="E172" s="81" t="n"/>
-      <c r="F172" s="81" t="n"/>
-      <c r="G172" s="59" t="n"/>
+      <c r="A172" s="118" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B172" s="95" t="inlineStr">
+        <is>
+          <t>Sprint 5</t>
+        </is>
+      </c>
+      <c r="C172" s="76" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="D172" s="89" t="inlineStr">
+        <is>
+          <t>E·QA+SLC文档</t>
+        </is>
+      </c>
+      <c r="E172" s="78" t="inlineStr">
+        <is>
+          <t>• 文档终版归档（7 套 + 审批包 + Checklist）</t>
+        </is>
+      </c>
+      <c r="F172" s="119" t="inlineStr">
+        <is>
+          <t>★ Release 2 交付完成</t>
+        </is>
+      </c>
+      <c r="G172" s="80" t="inlineStr"/>
       <c r="H172" s="59" t="n"/>
       <c r="I172" s="59" t="n"/>
+      <c r="J172" s="59" t="n"/>
     </row>
     <row r="173" ht="22" customHeight="1">
-      <c r="A173" s="95" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B173" s="76" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="C173" s="89" t="inlineStr">
-        <is>
-          <t>E·QA+SLC文档</t>
-        </is>
-      </c>
-      <c r="D173" s="78" t="inlineStr">
-        <is>
-          <t>• 交付物最终归档（7 套文档 + 培训视频 + Checklist）</t>
-        </is>
-      </c>
-      <c r="E173" s="79" t="inlineStr">
-        <is>
-          <t>全部归档；稳定性报告</t>
-        </is>
-      </c>
-      <c r="F173" s="80" t="inlineStr"/>
-      <c r="G173" s="59" t="n"/>
+      <c r="B173" s="120" t="n"/>
+      <c r="C173" s="120" t="n"/>
+      <c r="D173" s="125" t="n"/>
+      <c r="E173" s="78" t="inlineStr">
+        <is>
+          <t>• 上线一周稳定性报告</t>
+        </is>
+      </c>
+      <c r="F173" s="120" t="n"/>
+      <c r="G173" s="120" t="n"/>
       <c r="H173" s="59" t="n"/>
       <c r="I173" s="59" t="n"/>
+      <c r="J173" s="59" t="n"/>
     </row>
     <row r="174" ht="22" customHeight="1">
-      <c r="A174" s="81" t="n"/>
-      <c r="B174" s="81" t="n"/>
-      <c r="C174" s="90" t="n"/>
-      <c r="D174" s="78" t="inlineStr">
-        <is>
-          <t>• 上线一周稳定性报告</t>
-        </is>
-      </c>
-      <c r="E174" s="81" t="n"/>
-      <c r="F174" s="81" t="n"/>
-      <c r="G174" s="59" t="n"/>
+      <c r="B174" s="120" t="n"/>
+      <c r="C174" s="120" t="n"/>
+      <c r="D174" s="125" t="n"/>
+      <c r="E174" s="78" t="inlineStr">
+        <is>
+          <t>• 项目结束</t>
+        </is>
+      </c>
+      <c r="F174" s="120" t="n"/>
+      <c r="G174" s="120" t="n"/>
       <c r="H174" s="59" t="n"/>
       <c r="I174" s="59" t="n"/>
-    </row>
-    <row r="175" ht="22" customHeight="1"/>
-    <row r="176" ht="22" customHeight="1"/>
-    <row r="177" ht="22" customHeight="1"/>
-    <row r="178" ht="22" customHeight="1"/>
-    <row r="179" ht="22" customHeight="1"/>
-    <row r="180" ht="22" customHeight="1"/>
-    <row r="181" ht="22" customHeight="1"/>
-    <row r="182" ht="22" customHeight="1"/>
-    <row r="183" ht="22" customHeight="1"/>
-    <row r="184" ht="22" customHeight="1"/>
-    <row r="185" ht="22" customHeight="1"/>
-    <row r="186" ht="22" customHeight="1"/>
-    <row r="187" ht="22" customHeight="1"/>
-    <row r="188" ht="22" customHeight="1"/>
-    <row r="189" ht="22" customHeight="1"/>
-    <row r="190" ht="22" customHeight="1"/>
-    <row r="191" ht="22" customHeight="1"/>
-    <row r="192" ht="22" customHeight="1"/>
-    <row r="193" ht="22" customHeight="1"/>
-    <row r="194" ht="22" customHeight="1"/>
-    <row r="195" ht="22" customHeight="1"/>
-    <row r="196" ht="22" customHeight="1"/>
-    <row r="197" ht="22" customHeight="1"/>
-    <row r="198" ht="22" customHeight="1"/>
-    <row r="199" ht="22" customHeight="1"/>
-    <row r="200" ht="22" customHeight="1"/>
-    <row r="201" ht="22" customHeight="1"/>
-    <row r="202" ht="22" customHeight="1"/>
-    <row r="203" ht="22" customHeight="1"/>
-    <row r="204" ht="22" customHeight="1"/>
-    <row r="205" ht="22" customHeight="1"/>
-    <row r="206" ht="22" customHeight="1"/>
+      <c r="J174" s="59" t="n"/>
+    </row>
+    <row r="175" ht="22" customHeight="1">
+      <c r="B175" s="59" t="n"/>
+      <c r="C175" s="59" t="n"/>
+      <c r="D175" s="59" t="n"/>
+      <c r="E175" s="59" t="n"/>
+      <c r="F175" s="59" t="n"/>
+      <c r="G175" s="59" t="n"/>
+      <c r="H175" s="59" t="n"/>
+      <c r="I175" s="59" t="n"/>
+      <c r="J175" s="59" t="n"/>
+    </row>
+    <row r="176" ht="22" customHeight="1">
+      <c r="B176" s="59" t="n"/>
+      <c r="C176" s="59" t="n"/>
+      <c r="D176" s="59" t="n"/>
+      <c r="E176" s="59" t="n"/>
+      <c r="F176" s="59" t="n"/>
+      <c r="G176" s="59" t="n"/>
+      <c r="H176" s="59" t="n"/>
+      <c r="I176" s="59" t="n"/>
+      <c r="J176" s="59" t="n"/>
+    </row>
+    <row r="177" ht="22" customHeight="1">
+      <c r="B177" s="59" t="n"/>
+      <c r="C177" s="59" t="n"/>
+      <c r="D177" s="59" t="n"/>
+      <c r="E177" s="59" t="n"/>
+      <c r="F177" s="59" t="n"/>
+      <c r="G177" s="59" t="n"/>
+      <c r="H177" s="59" t="n"/>
+      <c r="I177" s="59" t="n"/>
+      <c r="J177" s="59" t="n"/>
+    </row>
+    <row r="178" ht="22" customHeight="1">
+      <c r="B178" s="59" t="n"/>
+      <c r="C178" s="59" t="n"/>
+      <c r="D178" s="59" t="n"/>
+      <c r="E178" s="59" t="n"/>
+      <c r="F178" s="59" t="n"/>
+      <c r="G178" s="59" t="n"/>
+      <c r="H178" s="59" t="n"/>
+      <c r="I178" s="59" t="n"/>
+      <c r="J178" s="59" t="n"/>
+    </row>
+    <row r="179" ht="22" customHeight="1">
+      <c r="B179" s="59" t="n"/>
+      <c r="C179" s="59" t="n"/>
+      <c r="D179" s="59" t="n"/>
+      <c r="E179" s="59" t="n"/>
+      <c r="F179" s="59" t="n"/>
+      <c r="G179" s="59" t="n"/>
+      <c r="H179" s="59" t="n"/>
+      <c r="I179" s="59" t="n"/>
+      <c r="J179" s="59" t="n"/>
+    </row>
+    <row r="180" ht="22" customHeight="1">
+      <c r="B180" s="59" t="n"/>
+      <c r="C180" s="59" t="n"/>
+      <c r="D180" s="59" t="n"/>
+      <c r="E180" s="59" t="n"/>
+      <c r="F180" s="59" t="n"/>
+      <c r="G180" s="59" t="n"/>
+      <c r="H180" s="59" t="n"/>
+      <c r="I180" s="59" t="n"/>
+      <c r="J180" s="59" t="n"/>
+    </row>
+    <row r="181" ht="22" customHeight="1">
+      <c r="B181" s="59" t="n"/>
+      <c r="C181" s="59" t="n"/>
+      <c r="D181" s="59" t="n"/>
+      <c r="E181" s="59" t="n"/>
+      <c r="F181" s="59" t="n"/>
+      <c r="G181" s="59" t="n"/>
+      <c r="H181" s="59" t="n"/>
+      <c r="I181" s="59" t="n"/>
+      <c r="J181" s="59" t="n"/>
+    </row>
+    <row r="182" ht="22" customHeight="1">
+      <c r="B182" s="59" t="n"/>
+      <c r="C182" s="59" t="n"/>
+      <c r="D182" s="59" t="n"/>
+      <c r="E182" s="59" t="n"/>
+      <c r="F182" s="59" t="n"/>
+      <c r="G182" s="59" t="n"/>
+      <c r="H182" s="59" t="n"/>
+      <c r="I182" s="59" t="n"/>
+      <c r="J182" s="59" t="n"/>
+    </row>
+    <row r="183" ht="22" customHeight="1">
+      <c r="B183" s="59" t="n"/>
+      <c r="C183" s="59" t="n"/>
+      <c r="D183" s="59" t="n"/>
+      <c r="E183" s="59" t="n"/>
+      <c r="F183" s="59" t="n"/>
+      <c r="G183" s="59" t="n"/>
+      <c r="H183" s="59" t="n"/>
+      <c r="I183" s="59" t="n"/>
+      <c r="J183" s="59" t="n"/>
+    </row>
+    <row r="184" ht="22" customHeight="1">
+      <c r="B184" s="59" t="n"/>
+      <c r="C184" s="59" t="n"/>
+      <c r="D184" s="59" t="n"/>
+      <c r="E184" s="59" t="n"/>
+      <c r="F184" s="59" t="n"/>
+      <c r="G184" s="59" t="n"/>
+      <c r="H184" s="59" t="n"/>
+      <c r="I184" s="59" t="n"/>
+      <c r="J184" s="59" t="n"/>
+    </row>
+    <row r="185" ht="22" customHeight="1">
+      <c r="B185" s="59" t="n"/>
+      <c r="C185" s="59" t="n"/>
+      <c r="D185" s="59" t="n"/>
+      <c r="E185" s="59" t="n"/>
+      <c r="F185" s="59" t="n"/>
+      <c r="G185" s="59" t="n"/>
+      <c r="H185" s="59" t="n"/>
+      <c r="I185" s="59" t="n"/>
+      <c r="J185" s="59" t="n"/>
+    </row>
+    <row r="186" ht="22" customHeight="1">
+      <c r="B186" s="59" t="n"/>
+      <c r="C186" s="59" t="n"/>
+      <c r="D186" s="59" t="n"/>
+      <c r="E186" s="59" t="n"/>
+      <c r="F186" s="59" t="n"/>
+      <c r="G186" s="59" t="n"/>
+      <c r="H186" s="59" t="n"/>
+      <c r="I186" s="59" t="n"/>
+      <c r="J186" s="59" t="n"/>
+    </row>
+    <row r="187" ht="22" customHeight="1">
+      <c r="B187" s="59" t="n"/>
+      <c r="C187" s="59" t="n"/>
+      <c r="D187" s="59" t="n"/>
+      <c r="E187" s="59" t="n"/>
+      <c r="F187" s="59" t="n"/>
+      <c r="G187" s="59" t="n"/>
+      <c r="H187" s="59" t="n"/>
+      <c r="I187" s="59" t="n"/>
+      <c r="J187" s="59" t="n"/>
+    </row>
+    <row r="188" ht="22" customHeight="1">
+      <c r="B188" s="59" t="n"/>
+      <c r="C188" s="59" t="n"/>
+      <c r="D188" s="59" t="n"/>
+      <c r="E188" s="59" t="n"/>
+      <c r="F188" s="59" t="n"/>
+      <c r="G188" s="59" t="n"/>
+      <c r="H188" s="59" t="n"/>
+      <c r="I188" s="59" t="n"/>
+      <c r="J188" s="59" t="n"/>
+    </row>
+    <row r="189" ht="22" customHeight="1">
+      <c r="B189" s="59" t="n"/>
+      <c r="C189" s="59" t="n"/>
+      <c r="D189" s="59" t="n"/>
+      <c r="E189" s="59" t="n"/>
+      <c r="F189" s="59" t="n"/>
+      <c r="G189" s="59" t="n"/>
+      <c r="H189" s="59" t="n"/>
+      <c r="I189" s="59" t="n"/>
+      <c r="J189" s="59" t="n"/>
+    </row>
+    <row r="190" ht="22" customHeight="1">
+      <c r="B190" s="59" t="n"/>
+      <c r="C190" s="59" t="n"/>
+      <c r="D190" s="59" t="n"/>
+      <c r="E190" s="59" t="n"/>
+      <c r="F190" s="59" t="n"/>
+      <c r="G190" s="59" t="n"/>
+      <c r="H190" s="59" t="n"/>
+      <c r="I190" s="59" t="n"/>
+      <c r="J190" s="59" t="n"/>
+    </row>
+    <row r="191" ht="22" customHeight="1">
+      <c r="B191" s="59" t="n"/>
+      <c r="C191" s="59" t="n"/>
+      <c r="D191" s="59" t="n"/>
+      <c r="E191" s="59" t="n"/>
+      <c r="F191" s="59" t="n"/>
+      <c r="G191" s="59" t="n"/>
+      <c r="H191" s="59" t="n"/>
+      <c r="I191" s="59" t="n"/>
+      <c r="J191" s="59" t="n"/>
+    </row>
+    <row r="192" ht="22" customHeight="1">
+      <c r="B192" s="59" t="n"/>
+      <c r="C192" s="59" t="n"/>
+      <c r="D192" s="59" t="n"/>
+      <c r="E192" s="59" t="n"/>
+      <c r="F192" s="59" t="n"/>
+      <c r="G192" s="59" t="n"/>
+      <c r="H192" s="59" t="n"/>
+      <c r="I192" s="59" t="n"/>
+      <c r="J192" s="59" t="n"/>
+    </row>
+    <row r="193" ht="22" customHeight="1">
+      <c r="B193" s="59" t="n"/>
+      <c r="C193" s="59" t="n"/>
+      <c r="D193" s="59" t="n"/>
+      <c r="E193" s="59" t="n"/>
+      <c r="F193" s="59" t="n"/>
+      <c r="G193" s="59" t="n"/>
+      <c r="H193" s="59" t="n"/>
+      <c r="I193" s="59" t="n"/>
+      <c r="J193" s="59" t="n"/>
+    </row>
+    <row r="194" ht="22" customHeight="1">
+      <c r="B194" s="59" t="n"/>
+      <c r="C194" s="59" t="n"/>
+      <c r="D194" s="59" t="n"/>
+      <c r="E194" s="59" t="n"/>
+      <c r="F194" s="59" t="n"/>
+      <c r="G194" s="59" t="n"/>
+      <c r="H194" s="59" t="n"/>
+      <c r="I194" s="59" t="n"/>
+      <c r="J194" s="59" t="n"/>
+    </row>
+    <row r="195" ht="22" customHeight="1">
+      <c r="B195" s="59" t="n"/>
+      <c r="C195" s="59" t="n"/>
+      <c r="D195" s="59" t="n"/>
+      <c r="E195" s="59" t="n"/>
+      <c r="F195" s="59" t="n"/>
+      <c r="G195" s="59" t="n"/>
+      <c r="H195" s="59" t="n"/>
+      <c r="I195" s="59" t="n"/>
+      <c r="J195" s="59" t="n"/>
+    </row>
+    <row r="196" ht="22" customHeight="1">
+      <c r="B196" s="59" t="n"/>
+      <c r="C196" s="59" t="n"/>
+      <c r="D196" s="59" t="n"/>
+      <c r="E196" s="59" t="n"/>
+      <c r="F196" s="59" t="n"/>
+      <c r="G196" s="59" t="n"/>
+      <c r="H196" s="59" t="n"/>
+      <c r="I196" s="59" t="n"/>
+      <c r="J196" s="59" t="n"/>
+    </row>
+    <row r="197" ht="22" customHeight="1">
+      <c r="B197" s="59" t="n"/>
+      <c r="C197" s="59" t="n"/>
+      <c r="D197" s="59" t="n"/>
+      <c r="E197" s="59" t="n"/>
+      <c r="F197" s="59" t="n"/>
+      <c r="G197" s="59" t="n"/>
+      <c r="H197" s="59" t="n"/>
+      <c r="I197" s="59" t="n"/>
+      <c r="J197" s="59" t="n"/>
+    </row>
+    <row r="198" ht="22" customHeight="1">
+      <c r="B198" s="59" t="n"/>
+      <c r="C198" s="59" t="n"/>
+      <c r="D198" s="59" t="n"/>
+      <c r="E198" s="59" t="n"/>
+      <c r="F198" s="59" t="n"/>
+      <c r="G198" s="59" t="n"/>
+      <c r="H198" s="59" t="n"/>
+      <c r="I198" s="59" t="n"/>
+      <c r="J198" s="59" t="n"/>
+    </row>
+    <row r="199" ht="22" customHeight="1">
+      <c r="B199" s="59" t="n"/>
+      <c r="C199" s="59" t="n"/>
+      <c r="D199" s="59" t="n"/>
+      <c r="E199" s="59" t="n"/>
+      <c r="F199" s="59" t="n"/>
+      <c r="G199" s="59" t="n"/>
+      <c r="H199" s="59" t="n"/>
+      <c r="I199" s="59" t="n"/>
+      <c r="J199" s="59" t="n"/>
+    </row>
+    <row r="200" ht="22" customHeight="1">
+      <c r="B200" s="59" t="n"/>
+      <c r="C200" s="59" t="n"/>
+      <c r="D200" s="59" t="n"/>
+      <c r="E200" s="59" t="n"/>
+      <c r="F200" s="59" t="n"/>
+      <c r="G200" s="59" t="n"/>
+      <c r="H200" s="59" t="n"/>
+      <c r="I200" s="59" t="n"/>
+      <c r="J200" s="59" t="n"/>
+    </row>
+    <row r="201" ht="22" customHeight="1">
+      <c r="B201" s="59" t="n"/>
+      <c r="C201" s="59" t="n"/>
+      <c r="D201" s="59" t="n"/>
+      <c r="E201" s="59" t="n"/>
+      <c r="F201" s="59" t="n"/>
+      <c r="G201" s="59" t="n"/>
+      <c r="H201" s="59" t="n"/>
+      <c r="I201" s="59" t="n"/>
+      <c r="J201" s="59" t="n"/>
+    </row>
+    <row r="202" ht="22" customHeight="1">
+      <c r="B202" s="59" t="n"/>
+      <c r="C202" s="59" t="n"/>
+      <c r="D202" s="59" t="n"/>
+      <c r="E202" s="59" t="n"/>
+      <c r="F202" s="59" t="n"/>
+      <c r="G202" s="59" t="n"/>
+      <c r="H202" s="59" t="n"/>
+      <c r="I202" s="59" t="n"/>
+      <c r="J202" s="59" t="n"/>
+    </row>
+    <row r="203" ht="22" customHeight="1">
+      <c r="B203" s="59" t="n"/>
+      <c r="C203" s="59" t="n"/>
+      <c r="D203" s="59" t="n"/>
+      <c r="E203" s="59" t="n"/>
+      <c r="F203" s="59" t="n"/>
+      <c r="G203" s="59" t="n"/>
+      <c r="H203" s="59" t="n"/>
+      <c r="I203" s="59" t="n"/>
+      <c r="J203" s="59" t="n"/>
+    </row>
+    <row r="204" ht="22" customHeight="1">
+      <c r="B204" s="59" t="n"/>
+      <c r="C204" s="59" t="n"/>
+      <c r="D204" s="59" t="n"/>
+      <c r="E204" s="59" t="n"/>
+      <c r="F204" s="59" t="n"/>
+      <c r="G204" s="59" t="n"/>
+      <c r="H204" s="59" t="n"/>
+      <c r="I204" s="59" t="n"/>
+      <c r="J204" s="59" t="n"/>
+    </row>
+    <row r="205" ht="22" customHeight="1">
+      <c r="B205" s="59" t="n"/>
+      <c r="C205" s="59" t="n"/>
+      <c r="D205" s="59" t="n"/>
+      <c r="E205" s="59" t="n"/>
+      <c r="F205" s="59" t="n"/>
+      <c r="G205" s="59" t="n"/>
+      <c r="H205" s="59" t="n"/>
+      <c r="I205" s="59" t="n"/>
+      <c r="J205" s="59" t="n"/>
+    </row>
+    <row r="206" ht="22" customHeight="1">
+      <c r="B206" s="59" t="n"/>
+      <c r="C206" s="59" t="n"/>
+      <c r="D206" s="59" t="n"/>
+      <c r="E206" s="59" t="n"/>
+      <c r="F206" s="59" t="n"/>
+      <c r="G206" s="59" t="n"/>
+      <c r="H206" s="59" t="n"/>
+      <c r="I206" s="59" t="n"/>
+      <c r="J206" s="59" t="n"/>
+    </row>
+    <row r="207">
+      <c r="B207" s="59" t="n"/>
+      <c r="C207" s="59" t="n"/>
+      <c r="D207" s="59" t="n"/>
+      <c r="E207" s="59" t="n"/>
+      <c r="F207" s="59" t="n"/>
+      <c r="G207" s="59" t="n"/>
+      <c r="H207" s="59" t="n"/>
+      <c r="I207" s="59" t="n"/>
+      <c r="J207" s="59" t="n"/>
+    </row>
+    <row r="208">
+      <c r="B208" s="59" t="n"/>
+      <c r="C208" s="59" t="n"/>
+      <c r="D208" s="59" t="n"/>
+      <c r="E208" s="59" t="n"/>
+      <c r="F208" s="59" t="n"/>
+      <c r="G208" s="59" t="n"/>
+      <c r="H208" s="59" t="n"/>
+      <c r="I208" s="59" t="n"/>
+      <c r="J208" s="59" t="n"/>
+    </row>
+    <row r="209">
+      <c r="B209" s="59" t="n"/>
+      <c r="C209" s="59" t="n"/>
+      <c r="D209" s="59" t="n"/>
+      <c r="E209" s="59" t="n"/>
+      <c r="F209" s="59" t="n"/>
+      <c r="G209" s="59" t="n"/>
+      <c r="H209" s="59" t="n"/>
+      <c r="I209" s="59" t="n"/>
+      <c r="J209" s="59" t="n"/>
+    </row>
+    <row r="210">
+      <c r="B210" s="59" t="n"/>
+      <c r="C210" s="59" t="n"/>
+      <c r="D210" s="59" t="n"/>
+      <c r="E210" s="59" t="n"/>
+      <c r="F210" s="59" t="n"/>
+      <c r="G210" s="59" t="n"/>
+      <c r="H210" s="59" t="n"/>
+      <c r="I210" s="59" t="n"/>
+      <c r="J210" s="59" t="n"/>
+    </row>
+    <row r="211">
+      <c r="B211" s="59" t="n"/>
+      <c r="C211" s="59" t="n"/>
+      <c r="D211" s="59" t="n"/>
+      <c r="E211" s="59" t="n"/>
+      <c r="F211" s="59" t="n"/>
+      <c r="G211" s="59" t="n"/>
+      <c r="H211" s="59" t="n"/>
+      <c r="I211" s="59" t="n"/>
+      <c r="J211" s="59" t="n"/>
+    </row>
+    <row r="212">
+      <c r="B212" s="59" t="n"/>
+      <c r="C212" s="59" t="n"/>
+      <c r="D212" s="59" t="n"/>
+      <c r="E212" s="59" t="n"/>
+      <c r="F212" s="59" t="n"/>
+      <c r="G212" s="59" t="n"/>
+      <c r="H212" s="59" t="n"/>
+      <c r="I212" s="59" t="n"/>
+      <c r="J212" s="59" t="n"/>
+    </row>
+    <row r="213">
+      <c r="B213" s="59" t="n"/>
+      <c r="C213" s="59" t="n"/>
+      <c r="D213" s="59" t="n"/>
+      <c r="E213" s="59" t="n"/>
+      <c r="F213" s="59" t="n"/>
+      <c r="G213" s="59" t="n"/>
+      <c r="H213" s="59" t="n"/>
+      <c r="I213" s="59" t="n"/>
+      <c r="J213" s="59" t="n"/>
+    </row>
+    <row r="214">
+      <c r="B214" s="59" t="n"/>
+      <c r="C214" s="59" t="n"/>
+      <c r="D214" s="59" t="n"/>
+      <c r="E214" s="59" t="n"/>
+      <c r="F214" s="59" t="n"/>
+      <c r="G214" s="59" t="n"/>
+      <c r="H214" s="59" t="n"/>
+      <c r="I214" s="59" t="n"/>
+      <c r="J214" s="59" t="n"/>
+    </row>
+    <row r="215">
+      <c r="B215" s="59" t="n"/>
+      <c r="C215" s="59" t="n"/>
+      <c r="D215" s="59" t="n"/>
+      <c r="E215" s="59" t="n"/>
+      <c r="F215" s="59" t="n"/>
+      <c r="G215" s="59" t="n"/>
+      <c r="H215" s="59" t="n"/>
+      <c r="I215" s="59" t="n"/>
+      <c r="J215" s="59" t="n"/>
+    </row>
+    <row r="216">
+      <c r="B216" s="59" t="n"/>
+      <c r="C216" s="59" t="n"/>
+      <c r="D216" s="59" t="n"/>
+      <c r="E216" s="59" t="n"/>
+      <c r="F216" s="59" t="n"/>
+      <c r="G216" s="59" t="n"/>
+      <c r="H216" s="59" t="n"/>
+      <c r="I216" s="59" t="n"/>
+      <c r="J216" s="59" t="n"/>
+    </row>
+    <row r="217">
+      <c r="B217" s="59" t="n"/>
+      <c r="C217" s="59" t="n"/>
+      <c r="D217" s="59" t="n"/>
+      <c r="E217" s="59" t="n"/>
+      <c r="F217" s="59" t="n"/>
+      <c r="G217" s="59" t="n"/>
+      <c r="H217" s="59" t="n"/>
+      <c r="I217" s="59" t="n"/>
+      <c r="J217" s="59" t="n"/>
+    </row>
+    <row r="218">
+      <c r="B218" s="59" t="n"/>
+      <c r="C218" s="59" t="n"/>
+      <c r="D218" s="59" t="n"/>
+      <c r="E218" s="59" t="n"/>
+      <c r="F218" s="59" t="n"/>
+      <c r="G218" s="59" t="n"/>
+      <c r="H218" s="59" t="n"/>
+      <c r="I218" s="59" t="n"/>
+      <c r="J218" s="59" t="n"/>
+    </row>
+    <row r="219">
+      <c r="B219" s="59" t="n"/>
+      <c r="C219" s="59" t="n"/>
+      <c r="D219" s="59" t="n"/>
+      <c r="E219" s="59" t="n"/>
+      <c r="F219" s="59" t="n"/>
+      <c r="G219" s="59" t="n"/>
+      <c r="H219" s="59" t="n"/>
+      <c r="I219" s="59" t="n"/>
+      <c r="J219" s="59" t="n"/>
+    </row>
+    <row r="220">
+      <c r="B220" s="59" t="n"/>
+      <c r="C220" s="59" t="n"/>
+      <c r="D220" s="59" t="n"/>
+      <c r="E220" s="59" t="n"/>
+      <c r="F220" s="59" t="n"/>
+      <c r="G220" s="59" t="n"/>
+      <c r="H220" s="59" t="n"/>
+      <c r="I220" s="59" t="n"/>
+      <c r="J220" s="59" t="n"/>
+    </row>
+    <row r="221">
+      <c r="B221" s="59" t="n"/>
+      <c r="C221" s="59" t="n"/>
+      <c r="D221" s="59" t="n"/>
+      <c r="E221" s="59" t="n"/>
+      <c r="F221" s="59" t="n"/>
+      <c r="G221" s="59" t="n"/>
+      <c r="H221" s="59" t="n"/>
+      <c r="I221" s="59" t="n"/>
+      <c r="J221" s="59" t="n"/>
+    </row>
+    <row r="222">
+      <c r="B222" s="59" t="n"/>
+      <c r="C222" s="59" t="n"/>
+      <c r="D222" s="59" t="n"/>
+      <c r="E222" s="59" t="n"/>
+      <c r="F222" s="59" t="n"/>
+      <c r="G222" s="59" t="n"/>
+      <c r="H222" s="59" t="n"/>
+      <c r="I222" s="59" t="n"/>
+      <c r="J222" s="59" t="n"/>
+    </row>
+    <row r="223">
+      <c r="B223" s="59" t="n"/>
+      <c r="C223" s="59" t="n"/>
+      <c r="D223" s="59" t="n"/>
+      <c r="E223" s="59" t="n"/>
+      <c r="F223" s="59" t="n"/>
+      <c r="G223" s="59" t="n"/>
+      <c r="H223" s="59" t="n"/>
+      <c r="I223" s="59" t="n"/>
+      <c r="J223" s="59" t="n"/>
+    </row>
+    <row r="224">
+      <c r="B224" s="59" t="n"/>
+      <c r="C224" s="59" t="n"/>
+      <c r="D224" s="59" t="n"/>
+      <c r="E224" s="59" t="n"/>
+      <c r="F224" s="59" t="n"/>
+      <c r="G224" s="59" t="n"/>
+      <c r="H224" s="59" t="n"/>
+      <c r="I224" s="59" t="n"/>
+      <c r="J224" s="59" t="n"/>
+    </row>
+    <row r="225">
+      <c r="B225" s="59" t="n"/>
+      <c r="C225" s="59" t="n"/>
+      <c r="D225" s="59" t="n"/>
+      <c r="E225" s="59" t="n"/>
+      <c r="F225" s="59" t="n"/>
+      <c r="G225" s="59" t="n"/>
+      <c r="H225" s="59" t="n"/>
+      <c r="I225" s="59" t="n"/>
+      <c r="J225" s="59" t="n"/>
+    </row>
+    <row r="226">
+      <c r="B226" s="59" t="n"/>
+      <c r="C226" s="59" t="n"/>
+      <c r="D226" s="59" t="n"/>
+      <c r="E226" s="59" t="n"/>
+      <c r="F226" s="59" t="n"/>
+      <c r="G226" s="59" t="n"/>
+      <c r="H226" s="59" t="n"/>
+      <c r="I226" s="59" t="n"/>
+      <c r="J226" s="59" t="n"/>
+    </row>
+    <row r="227">
+      <c r="B227" s="59" t="n"/>
+      <c r="C227" s="59" t="n"/>
+      <c r="D227" s="59" t="n"/>
+      <c r="E227" s="59" t="n"/>
+      <c r="F227" s="59" t="n"/>
+      <c r="G227" s="59" t="n"/>
+      <c r="H227" s="59" t="n"/>
+      <c r="I227" s="59" t="n"/>
+      <c r="J227" s="59" t="n"/>
+    </row>
+    <row r="228">
+      <c r="B228" s="59" t="n"/>
+      <c r="C228" s="59" t="n"/>
+      <c r="D228" s="59" t="n"/>
+      <c r="E228" s="59" t="n"/>
+      <c r="F228" s="59" t="n"/>
+      <c r="G228" s="59" t="n"/>
+      <c r="H228" s="59" t="n"/>
+      <c r="I228" s="59" t="n"/>
+      <c r="J228" s="59" t="n"/>
+    </row>
+    <row r="229">
+      <c r="B229" s="59" t="n"/>
+      <c r="C229" s="59" t="n"/>
+      <c r="D229" s="59" t="n"/>
+      <c r="E229" s="59" t="n"/>
+      <c r="F229" s="59" t="n"/>
+      <c r="G229" s="59" t="n"/>
+      <c r="H229" s="59" t="n"/>
+      <c r="I229" s="59" t="n"/>
+      <c r="J229" s="59" t="n"/>
+    </row>
+    <row r="230">
+      <c r="B230" s="59" t="n"/>
+      <c r="C230" s="59" t="n"/>
+      <c r="D230" s="59" t="n"/>
+      <c r="E230" s="59" t="n"/>
+      <c r="F230" s="59" t="n"/>
+      <c r="G230" s="59" t="n"/>
+      <c r="H230" s="59" t="n"/>
+      <c r="I230" s="59" t="n"/>
+      <c r="J230" s="59" t="n"/>
+    </row>
+    <row r="231">
+      <c r="B231" s="59" t="n"/>
+      <c r="C231" s="59" t="n"/>
+      <c r="D231" s="59" t="n"/>
+      <c r="E231" s="59" t="n"/>
+      <c r="F231" s="59" t="n"/>
+      <c r="G231" s="59" t="n"/>
+      <c r="H231" s="59" t="n"/>
+      <c r="I231" s="59" t="n"/>
+      <c r="J231" s="59" t="n"/>
+    </row>
+    <row r="232">
+      <c r="B232" s="59" t="n"/>
+      <c r="C232" s="59" t="n"/>
+      <c r="D232" s="59" t="n"/>
+      <c r="E232" s="59" t="n"/>
+      <c r="F232" s="59" t="n"/>
+      <c r="G232" s="59" t="n"/>
+      <c r="H232" s="59" t="n"/>
+      <c r="I232" s="59" t="n"/>
+      <c r="J232" s="59" t="n"/>
+    </row>
+    <row r="233">
+      <c r="B233" s="59" t="n"/>
+      <c r="C233" s="59" t="n"/>
+      <c r="D233" s="59" t="n"/>
+      <c r="E233" s="59" t="n"/>
+      <c r="F233" s="59" t="n"/>
+      <c r="G233" s="59" t="n"/>
+      <c r="H233" s="59" t="n"/>
+      <c r="I233" s="59" t="n"/>
+      <c r="J233" s="59" t="n"/>
+    </row>
+    <row r="234">
+      <c r="B234" s="59" t="n"/>
+      <c r="C234" s="59" t="n"/>
+      <c r="D234" s="59" t="n"/>
+      <c r="E234" s="59" t="n"/>
+      <c r="F234" s="59" t="n"/>
+      <c r="G234" s="59" t="n"/>
+      <c r="H234" s="59" t="n"/>
+      <c r="I234" s="59" t="n"/>
+      <c r="J234" s="59" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report/项目执行计划.xlsx
+++ b/report/项目执行计划.xlsx
@@ -7313,7 +7313,7 @@
     <row r="163" ht="22" customHeight="1">
       <c r="A163" s="118" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B163" s="95" t="inlineStr">
@@ -7379,7 +7379,7 @@
     <row r="166" ht="22" customHeight="1">
       <c r="A166" s="118" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B166" s="95" t="inlineStr">
@@ -7430,7 +7430,7 @@
     <row r="168" ht="22" customHeight="1">
       <c r="A168" s="118" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B168" s="95" t="inlineStr">
@@ -7481,7 +7481,7 @@
     <row r="170" ht="22" customHeight="1">
       <c r="A170" s="118" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B170" s="95" t="inlineStr">
@@ -7532,7 +7532,7 @@
     <row r="172" ht="22" customHeight="1">
       <c r="A172" s="118" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B172" s="95" t="inlineStr">
